--- a/design-detail/DD_Staff_v1.0.xlsx
+++ b/design-detail/DD_Staff_v1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Document\Detail-design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\design-detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728A4DF6-2E26-42CA-BFDB-5A04330B25B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD1B36A-68EA-4B7E-8CB6-D354639FEC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="His" sheetId="32" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="110">
   <si>
     <t>Label</t>
   </si>
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>where ST.FIRST_NAME = %s order by ST.CREATED_DATE desc limit 1</t>
+  </si>
+  <si>
+    <t>Update</t>
   </si>
 </sst>
 </file>
@@ -1789,7 +1792,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1958,6 +1961,129 @@
     <xf numFmtId="14" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="133" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1979,6 +2105,66 @@
     <xf numFmtId="49" fontId="47" fillId="0" borderId="42" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="38" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2021,27 +2207,6 @@
     <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2057,9 +2222,6 @@
     <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -2075,18 +2237,6 @@
     <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="14" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2096,30 +2246,6 @@
     <xf numFmtId="14" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -2147,32 +2273,23 @@
     <xf numFmtId="14" fontId="47" fillId="0" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="133" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2180,66 +2297,6 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="133" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2258,71 +2315,14 @@
     <xf numFmtId="0" fontId="51" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="133" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="47" fillId="37" borderId="16" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="144">
@@ -3021,12 +3021,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="48" t="s">
@@ -3060,7 +3060,9 @@
       <c r="B5" s="53"/>
       <c r="C5" s="55"/>
       <c r="D5" s="54"/>
-      <c r="E5" s="41"/>
+      <c r="E5" s="41" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="41"/>
@@ -3201,248 +3203,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="5" customFormat="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="87"/>
-      <c r="AE1" s="87"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="87"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="99" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="141"/>
+      <c r="AE1" s="141"/>
+      <c r="AF1" s="141"/>
+      <c r="AG1" s="141"/>
+      <c r="AH1" s="142"/>
+      <c r="AI1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="AJ1" s="100"/>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AJ1" s="149"/>
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="99" t="s">
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="AT1" s="100"/>
-      <c r="AU1" s="100"/>
-      <c r="AV1" s="100"/>
-      <c r="AW1" s="101"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="149"/>
+      <c r="AU1" s="149"/>
+      <c r="AV1" s="149"/>
+      <c r="AW1" s="150"/>
+      <c r="AX1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="75"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="73" t="s">
+      <c r="AY1" s="136"/>
+      <c r="AZ1" s="136"/>
+      <c r="BA1" s="136"/>
+      <c r="BB1" s="137"/>
+      <c r="BC1" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="BD1" s="74"/>
-      <c r="BE1" s="74"/>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="69" t="s">
+      <c r="BD1" s="135"/>
+      <c r="BE1" s="135"/>
+      <c r="BF1" s="136"/>
+      <c r="BG1" s="137"/>
+      <c r="BH1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="BI1" s="70"/>
-      <c r="BJ1" s="71"/>
-      <c r="BK1" s="71"/>
-      <c r="BL1" s="72"/>
+      <c r="BI1" s="131"/>
+      <c r="BJ1" s="132"/>
+      <c r="BK1" s="132"/>
+      <c r="BL1" s="133"/>
       <c r="BM1" s="2"/>
     </row>
     <row r="2" spans="1:65" s="5" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="89" t="s">
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="95" t="s">
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="105" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="105" t="s">
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="105" t="s">
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="96"/>
-      <c r="AI2" s="77">
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="105"/>
+      <c r="AA2" s="105"/>
+      <c r="AB2" s="105"/>
+      <c r="AC2" s="105"/>
+      <c r="AD2" s="105"/>
+      <c r="AE2" s="105"/>
+      <c r="AF2" s="105"/>
+      <c r="AG2" s="105"/>
+      <c r="AH2" s="106"/>
+      <c r="AI2" s="110">
         <v>45701</v>
       </c>
-      <c r="AJ2" s="78"/>
-      <c r="AK2" s="78"/>
-      <c r="AL2" s="78"/>
-      <c r="AM2" s="79"/>
-      <c r="AN2" s="89" t="s">
+      <c r="AJ2" s="111"/>
+      <c r="AK2" s="111"/>
+      <c r="AL2" s="111"/>
+      <c r="AM2" s="112"/>
+      <c r="AN2" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="AO2" s="107"/>
-      <c r="AP2" s="107"/>
-      <c r="AQ2" s="107"/>
-      <c r="AR2" s="107"/>
-      <c r="AS2" s="77">
+      <c r="AO2" s="117"/>
+      <c r="AP2" s="117"/>
+      <c r="AQ2" s="117"/>
+      <c r="AR2" s="117"/>
+      <c r="AS2" s="110">
         <v>45707</v>
       </c>
-      <c r="AT2" s="78"/>
-      <c r="AU2" s="78"/>
-      <c r="AV2" s="78"/>
-      <c r="AW2" s="79"/>
-      <c r="AX2" s="83" t="s">
+      <c r="AT2" s="111"/>
+      <c r="AU2" s="111"/>
+      <c r="AV2" s="111"/>
+      <c r="AW2" s="112"/>
+      <c r="AX2" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="AY2" s="83"/>
-      <c r="AZ2" s="83"/>
-      <c r="BA2" s="83"/>
-      <c r="BB2" s="83"/>
-      <c r="BC2" s="77">
+      <c r="AY2" s="120"/>
+      <c r="AZ2" s="120"/>
+      <c r="BA2" s="120"/>
+      <c r="BB2" s="120"/>
+      <c r="BC2" s="110">
         <v>45701</v>
       </c>
-      <c r="BD2" s="78"/>
-      <c r="BE2" s="78"/>
-      <c r="BF2" s="78"/>
-      <c r="BG2" s="79"/>
-      <c r="BH2" s="83" t="s">
+      <c r="BD2" s="111"/>
+      <c r="BE2" s="111"/>
+      <c r="BF2" s="111"/>
+      <c r="BG2" s="112"/>
+      <c r="BH2" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="BI2" s="83"/>
-      <c r="BJ2" s="83"/>
-      <c r="BK2" s="83"/>
-      <c r="BL2" s="83"/>
+      <c r="BI2" s="120"/>
+      <c r="BJ2" s="120"/>
+      <c r="BK2" s="120"/>
+      <c r="BL2" s="120"/>
       <c r="BM2" s="2"/>
     </row>
     <row r="3" spans="1:65" s="5" customFormat="1" ht="10.5" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="97"/>
-      <c r="Y3" s="97"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="97"/>
-      <c r="AC3" s="97"/>
-      <c r="AD3" s="97"/>
-      <c r="AE3" s="97"/>
-      <c r="AF3" s="97"/>
-      <c r="AG3" s="97"/>
-      <c r="AH3" s="98"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="108"/>
-      <c r="AO3" s="109"/>
-      <c r="AP3" s="109"/>
-      <c r="AQ3" s="109"/>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="81"/>
-      <c r="AU3" s="81"/>
-      <c r="AV3" s="81"/>
-      <c r="AW3" s="82"/>
-      <c r="AX3" s="83"/>
-      <c r="AY3" s="83"/>
-      <c r="AZ3" s="83"/>
-      <c r="BA3" s="83"/>
-      <c r="BB3" s="83"/>
-      <c r="BC3" s="80"/>
-      <c r="BD3" s="81"/>
-      <c r="BE3" s="81"/>
-      <c r="BF3" s="81"/>
-      <c r="BG3" s="82"/>
-      <c r="BH3" s="83"/>
-      <c r="BI3" s="83"/>
-      <c r="BJ3" s="83"/>
-      <c r="BK3" s="83"/>
-      <c r="BL3" s="83"/>
+      <c r="A3" s="145"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="107"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
+      <c r="AA3" s="108"/>
+      <c r="AB3" s="108"/>
+      <c r="AC3" s="108"/>
+      <c r="AD3" s="108"/>
+      <c r="AE3" s="108"/>
+      <c r="AF3" s="108"/>
+      <c r="AG3" s="108"/>
+      <c r="AH3" s="109"/>
+      <c r="AI3" s="113"/>
+      <c r="AJ3" s="114"/>
+      <c r="AK3" s="114"/>
+      <c r="AL3" s="114"/>
+      <c r="AM3" s="115"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="113"/>
+      <c r="AT3" s="114"/>
+      <c r="AU3" s="114"/>
+      <c r="AV3" s="114"/>
+      <c r="AW3" s="115"/>
+      <c r="AX3" s="120"/>
+      <c r="AY3" s="120"/>
+      <c r="AZ3" s="120"/>
+      <c r="BA3" s="120"/>
+      <c r="BB3" s="120"/>
+      <c r="BC3" s="113"/>
+      <c r="BD3" s="114"/>
+      <c r="BE3" s="114"/>
+      <c r="BF3" s="114"/>
+      <c r="BG3" s="115"/>
+      <c r="BH3" s="120"/>
+      <c r="BI3" s="120"/>
+      <c r="BJ3" s="120"/>
+      <c r="BK3" s="120"/>
+      <c r="BL3" s="120"/>
       <c r="BM3" s="2"/>
     </row>
     <row r="4" spans="1:65" s="5" customFormat="1" ht="9.75" customHeight="1">
@@ -3699,23 +3701,23 @@
         <v>24</v>
       </c>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="102" t="s">
+      <c r="AO10" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="AP10" s="103"/>
-      <c r="AQ10" s="103"/>
-      <c r="AR10" s="103"/>
-      <c r="AS10" s="103"/>
-      <c r="AT10" s="103"/>
-      <c r="AU10" s="103"/>
-      <c r="AV10" s="103"/>
-      <c r="AW10" s="103"/>
-      <c r="AX10" s="103"/>
-      <c r="AY10" s="103"/>
-      <c r="AZ10" s="103"/>
-      <c r="BA10" s="103"/>
-      <c r="BB10" s="103"/>
-      <c r="BC10" s="104"/>
+      <c r="AP10" s="122"/>
+      <c r="AQ10" s="122"/>
+      <c r="AR10" s="122"/>
+      <c r="AS10" s="122"/>
+      <c r="AT10" s="122"/>
+      <c r="AU10" s="122"/>
+      <c r="AV10" s="122"/>
+      <c r="AW10" s="122"/>
+      <c r="AX10" s="122"/>
+      <c r="AY10" s="122"/>
+      <c r="AZ10" s="122"/>
+      <c r="BA10" s="122"/>
+      <c r="BB10" s="122"/>
+      <c r="BC10" s="123"/>
       <c r="BD10" s="21" t="s">
         <v>5</v>
       </c>
@@ -3725,31 +3727,31 @@
     </row>
     <row r="11" spans="1:65" ht="15" customHeight="1">
       <c r="A11" s="13"/>
-      <c r="AM11" s="59" t="s">
+      <c r="AM11" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="AN11" s="60"/>
-      <c r="AO11" s="63" t="s">
+      <c r="AN11" s="101"/>
+      <c r="AO11" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="AP11" s="64"/>
-      <c r="AQ11" s="64"/>
-      <c r="AR11" s="64"/>
-      <c r="AS11" s="64"/>
-      <c r="AT11" s="64"/>
-      <c r="AU11" s="64"/>
-      <c r="AV11" s="64"/>
-      <c r="AW11" s="64"/>
-      <c r="AX11" s="64"/>
-      <c r="AY11" s="64"/>
-      <c r="AZ11" s="64"/>
-      <c r="BA11" s="64"/>
-      <c r="BB11" s="64"/>
-      <c r="BC11" s="65"/>
-      <c r="BD11" s="61" t="s">
+      <c r="AP11" s="125"/>
+      <c r="AQ11" s="125"/>
+      <c r="AR11" s="125"/>
+      <c r="AS11" s="125"/>
+      <c r="AT11" s="125"/>
+      <c r="AU11" s="125"/>
+      <c r="AV11" s="125"/>
+      <c r="AW11" s="125"/>
+      <c r="AX11" s="125"/>
+      <c r="AY11" s="125"/>
+      <c r="AZ11" s="125"/>
+      <c r="BA11" s="125"/>
+      <c r="BB11" s="125"/>
+      <c r="BC11" s="126"/>
+      <c r="BD11" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="BE11" s="62"/>
+      <c r="BE11" s="103"/>
       <c r="BF11" s="13"/>
       <c r="BL11" s="3"/>
     </row>
@@ -3758,61 +3760,61 @@
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM12" s="59" t="s">
+      <c r="AM12" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="AN12" s="60"/>
-      <c r="AO12" s="66" t="s">
+      <c r="AN12" s="101"/>
+      <c r="AO12" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="AP12" s="67"/>
-      <c r="AQ12" s="67"/>
-      <c r="AR12" s="67"/>
-      <c r="AS12" s="67"/>
-      <c r="AT12" s="67"/>
-      <c r="AU12" s="67"/>
-      <c r="AV12" s="67"/>
-      <c r="AW12" s="67"/>
-      <c r="AX12" s="67"/>
-      <c r="AY12" s="67"/>
-      <c r="AZ12" s="67"/>
-      <c r="BA12" s="67"/>
-      <c r="BB12" s="67"/>
-      <c r="BC12" s="68"/>
-      <c r="BD12" s="61" t="s">
+      <c r="AP12" s="128"/>
+      <c r="AQ12" s="128"/>
+      <c r="AR12" s="128"/>
+      <c r="AS12" s="128"/>
+      <c r="AT12" s="128"/>
+      <c r="AU12" s="128"/>
+      <c r="AV12" s="128"/>
+      <c r="AW12" s="128"/>
+      <c r="AX12" s="128"/>
+      <c r="AY12" s="128"/>
+      <c r="AZ12" s="128"/>
+      <c r="BA12" s="128"/>
+      <c r="BB12" s="128"/>
+      <c r="BC12" s="129"/>
+      <c r="BD12" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="BE12" s="62"/>
+      <c r="BE12" s="103"/>
       <c r="BF12" s="13"/>
       <c r="BL12" s="3"/>
     </row>
     <row r="13" spans="1:65" ht="15" customHeight="1">
       <c r="A13" s="13"/>
-      <c r="AM13" s="59" t="s">
+      <c r="AM13" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="AN13" s="60"/>
-      <c r="AO13" s="66" t="s">
+      <c r="AN13" s="101"/>
+      <c r="AO13" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="AP13" s="67"/>
-      <c r="AQ13" s="67"/>
-      <c r="AR13" s="67"/>
-      <c r="AS13" s="67"/>
-      <c r="AT13" s="67"/>
-      <c r="AU13" s="67"/>
-      <c r="AV13" s="67"/>
-      <c r="AW13" s="67"/>
-      <c r="AX13" s="67"/>
-      <c r="AY13" s="67"/>
-      <c r="AZ13" s="67"/>
-      <c r="BA13" s="67"/>
-      <c r="BB13" s="67"/>
-      <c r="BC13" s="68"/>
-      <c r="BD13" s="61" t="s">
+      <c r="AP13" s="128"/>
+      <c r="AQ13" s="128"/>
+      <c r="AR13" s="128"/>
+      <c r="AS13" s="128"/>
+      <c r="AT13" s="128"/>
+      <c r="AU13" s="128"/>
+      <c r="AV13" s="128"/>
+      <c r="AW13" s="128"/>
+      <c r="AX13" s="128"/>
+      <c r="AY13" s="128"/>
+      <c r="AZ13" s="128"/>
+      <c r="BA13" s="128"/>
+      <c r="BB13" s="128"/>
+      <c r="BC13" s="129"/>
+      <c r="BD13" s="102" t="s">
         <v>42</v>
       </c>
-      <c r="BE13" s="62"/>
+      <c r="BE13" s="103"/>
       <c r="BF13" s="13"/>
       <c r="BL13" s="3"/>
     </row>
@@ -3820,21 +3822,21 @@
       <c r="A14" s="13"/>
       <c r="AM14" s="27"/>
       <c r="AN14" s="28"/>
-      <c r="AO14" s="63"/>
-      <c r="AP14" s="64"/>
-      <c r="AQ14" s="64"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="64"/>
-      <c r="AT14" s="64"/>
-      <c r="AU14" s="64"/>
-      <c r="AV14" s="64"/>
-      <c r="AW14" s="64"/>
-      <c r="AX14" s="64"/>
-      <c r="AY14" s="64"/>
-      <c r="AZ14" s="64"/>
-      <c r="BA14" s="64"/>
-      <c r="BB14" s="64"/>
-      <c r="BC14" s="65"/>
+      <c r="AO14" s="124"/>
+      <c r="AP14" s="125"/>
+      <c r="AQ14" s="125"/>
+      <c r="AR14" s="125"/>
+      <c r="AS14" s="125"/>
+      <c r="AT14" s="125"/>
+      <c r="AU14" s="125"/>
+      <c r="AV14" s="125"/>
+      <c r="AW14" s="125"/>
+      <c r="AX14" s="125"/>
+      <c r="AY14" s="125"/>
+      <c r="AZ14" s="125"/>
+      <c r="BA14" s="125"/>
+      <c r="BB14" s="125"/>
+      <c r="BC14" s="126"/>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="13"/>
@@ -3844,21 +3846,21 @@
       <c r="A15" s="13"/>
       <c r="AM15" s="27"/>
       <c r="AN15" s="28"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="64"/>
-      <c r="AQ15" s="64"/>
-      <c r="AR15" s="64"/>
-      <c r="AS15" s="64"/>
-      <c r="AT15" s="64"/>
-      <c r="AU15" s="64"/>
-      <c r="AV15" s="64"/>
-      <c r="AW15" s="64"/>
-      <c r="AX15" s="64"/>
-      <c r="AY15" s="64"/>
-      <c r="AZ15" s="64"/>
-      <c r="BA15" s="64"/>
-      <c r="BB15" s="64"/>
-      <c r="BC15" s="65"/>
+      <c r="AO15" s="124"/>
+      <c r="AP15" s="125"/>
+      <c r="AQ15" s="125"/>
+      <c r="AR15" s="125"/>
+      <c r="AS15" s="125"/>
+      <c r="AT15" s="125"/>
+      <c r="AU15" s="125"/>
+      <c r="AV15" s="125"/>
+      <c r="AW15" s="125"/>
+      <c r="AX15" s="125"/>
+      <c r="AY15" s="125"/>
+      <c r="AZ15" s="125"/>
+      <c r="BA15" s="125"/>
+      <c r="BB15" s="125"/>
+      <c r="BC15" s="126"/>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="13"/>
@@ -3868,21 +3870,21 @@
       <c r="A16" s="13"/>
       <c r="AM16" s="27"/>
       <c r="AN16" s="28"/>
-      <c r="AO16" s="63"/>
-      <c r="AP16" s="64"/>
-      <c r="AQ16" s="64"/>
-      <c r="AR16" s="64"/>
-      <c r="AS16" s="64"/>
-      <c r="AT16" s="64"/>
-      <c r="AU16" s="64"/>
-      <c r="AV16" s="64"/>
-      <c r="AW16" s="64"/>
-      <c r="AX16" s="64"/>
-      <c r="AY16" s="64"/>
-      <c r="AZ16" s="64"/>
-      <c r="BA16" s="64"/>
-      <c r="BB16" s="64"/>
-      <c r="BC16" s="65"/>
+      <c r="AO16" s="124"/>
+      <c r="AP16" s="125"/>
+      <c r="AQ16" s="125"/>
+      <c r="AR16" s="125"/>
+      <c r="AS16" s="125"/>
+      <c r="AT16" s="125"/>
+      <c r="AU16" s="125"/>
+      <c r="AV16" s="125"/>
+      <c r="AW16" s="125"/>
+      <c r="AX16" s="125"/>
+      <c r="AY16" s="125"/>
+      <c r="AZ16" s="125"/>
+      <c r="BA16" s="125"/>
+      <c r="BB16" s="125"/>
+      <c r="BC16" s="126"/>
       <c r="BD16" s="31"/>
       <c r="BE16" s="32"/>
       <c r="BF16" s="13"/>
@@ -3892,21 +3894,21 @@
       <c r="A17" s="13"/>
       <c r="AM17" s="27"/>
       <c r="AN17" s="28"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="64"/>
-      <c r="AQ17" s="64"/>
-      <c r="AR17" s="64"/>
-      <c r="AS17" s="64"/>
-      <c r="AT17" s="64"/>
-      <c r="AU17" s="64"/>
-      <c r="AV17" s="64"/>
-      <c r="AW17" s="64"/>
-      <c r="AX17" s="64"/>
-      <c r="AY17" s="64"/>
-      <c r="AZ17" s="64"/>
-      <c r="BA17" s="64"/>
-      <c r="BB17" s="64"/>
-      <c r="BC17" s="65"/>
+      <c r="AO17" s="124"/>
+      <c r="AP17" s="125"/>
+      <c r="AQ17" s="125"/>
+      <c r="AR17" s="125"/>
+      <c r="AS17" s="125"/>
+      <c r="AT17" s="125"/>
+      <c r="AU17" s="125"/>
+      <c r="AV17" s="125"/>
+      <c r="AW17" s="125"/>
+      <c r="AX17" s="125"/>
+      <c r="AY17" s="125"/>
+      <c r="AZ17" s="125"/>
+      <c r="BA17" s="125"/>
+      <c r="BB17" s="125"/>
+      <c r="BC17" s="126"/>
       <c r="BD17" s="31"/>
       <c r="BE17" s="32"/>
       <c r="BF17" s="13"/>
@@ -3916,21 +3918,21 @@
       <c r="A18" s="13"/>
       <c r="AM18" s="27"/>
       <c r="AN18" s="28"/>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="64"/>
-      <c r="AQ18" s="64"/>
-      <c r="AR18" s="64"/>
-      <c r="AS18" s="64"/>
-      <c r="AT18" s="64"/>
-      <c r="AU18" s="64"/>
-      <c r="AV18" s="64"/>
-      <c r="AW18" s="64"/>
-      <c r="AX18" s="64"/>
-      <c r="AY18" s="64"/>
-      <c r="AZ18" s="64"/>
-      <c r="BA18" s="64"/>
-      <c r="BB18" s="64"/>
-      <c r="BC18" s="65"/>
+      <c r="AO18" s="124"/>
+      <c r="AP18" s="125"/>
+      <c r="AQ18" s="125"/>
+      <c r="AR18" s="125"/>
+      <c r="AS18" s="125"/>
+      <c r="AT18" s="125"/>
+      <c r="AU18" s="125"/>
+      <c r="AV18" s="125"/>
+      <c r="AW18" s="125"/>
+      <c r="AX18" s="125"/>
+      <c r="AY18" s="125"/>
+      <c r="AZ18" s="125"/>
+      <c r="BA18" s="125"/>
+      <c r="BB18" s="125"/>
+      <c r="BC18" s="126"/>
       <c r="BD18" s="34"/>
       <c r="BE18" s="35"/>
       <c r="BF18" s="13"/>
@@ -4122,22 +4124,11 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="AM11:AN11"/>
-    <mergeCell ref="BD11:BE11"/>
-    <mergeCell ref="AM12:AN12"/>
-    <mergeCell ref="BD12:BE12"/>
-    <mergeCell ref="AM13:AN13"/>
-    <mergeCell ref="BD13:BE13"/>
-    <mergeCell ref="P2:T3"/>
-    <mergeCell ref="U2:AH3"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="AS2:AW3"/>
-    <mergeCell ref="AX2:BB3"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO11:BC11"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="AO14:BC14"/>
+    <mergeCell ref="AO18:BC18"/>
+    <mergeCell ref="AO15:BC15"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="AO17:BC17"/>
     <mergeCell ref="BH1:BL1"/>
     <mergeCell ref="BC1:BG1"/>
     <mergeCell ref="BC2:BG3"/>
@@ -4154,11 +4145,22 @@
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="AO14:BC14"/>
-    <mergeCell ref="AO18:BC18"/>
-    <mergeCell ref="AO15:BC15"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="AX2:BB3"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO11:BC11"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="AO13:BC13"/>
+    <mergeCell ref="P2:T3"/>
+    <mergeCell ref="U2:AH3"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="AS2:AW3"/>
+    <mergeCell ref="AM11:AN11"/>
+    <mergeCell ref="BD11:BE11"/>
+    <mergeCell ref="AM12:AN12"/>
+    <mergeCell ref="BD12:BE12"/>
+    <mergeCell ref="AM13:AN13"/>
+    <mergeCell ref="BD13:BE13"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4191,182 +4193,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="136"/>
+      <c r="AU1" s="136"/>
+      <c r="AV1" s="136"/>
+      <c r="AW1" s="137"/>
+      <c r="AX1" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="136"/>
+      <c r="BB1" s="137"/>
+      <c r="BC1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="131"/>
+      <c r="BE1" s="132"/>
+      <c r="BF1" s="132"/>
+      <c r="BG1" s="133"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="151" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="151" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="154" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="156" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="156" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="157">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="158"/>
+      <c r="AG2" s="158"/>
+      <c r="AH2" s="158"/>
+      <c r="AI2" s="159"/>
+      <c r="AJ2" s="151" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="152"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="157">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="158"/>
+      <c r="AP2" s="158"/>
+      <c r="AQ2" s="158"/>
+      <c r="AR2" s="159"/>
+      <c r="AS2" s="120" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="120"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
+      <c r="AW2" s="120"/>
+      <c r="AX2" s="157">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="158"/>
+      <c r="AZ2" s="158"/>
+      <c r="BA2" s="158"/>
+      <c r="BB2" s="159"/>
+      <c r="BC2" s="151" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="153"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -4623,28 +4625,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="BC2:BG2"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BG1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="BC2:BG2"/>
-    <mergeCell ref="AJ1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -4676,182 +4678,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="136"/>
+      <c r="AU1" s="136"/>
+      <c r="AV1" s="136"/>
+      <c r="AW1" s="137"/>
+      <c r="AX1" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="136"/>
+      <c r="BB1" s="137"/>
+      <c r="BC1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="131"/>
+      <c r="BE1" s="132"/>
+      <c r="BF1" s="132"/>
+      <c r="BG1" s="133"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="151" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="151" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="154" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="156" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="156" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="157">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="158"/>
+      <c r="AG2" s="158"/>
+      <c r="AH2" s="158"/>
+      <c r="AI2" s="159"/>
+      <c r="AJ2" s="151" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="152"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="157">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="158"/>
+      <c r="AP2" s="158"/>
+      <c r="AQ2" s="158"/>
+      <c r="AR2" s="159"/>
+      <c r="AS2" s="120" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="120"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
+      <c r="AW2" s="120"/>
+      <c r="AX2" s="157">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="158"/>
+      <c r="AZ2" s="158"/>
+      <c r="BA2" s="158"/>
+      <c r="BB2" s="159"/>
+      <c r="BC2" s="151" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="153"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5048,28 +5050,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="BC2:BG2"/>
     <mergeCell ref="AJ1:AM1"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
     <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5102,182 +5104,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="136"/>
+      <c r="AU1" s="136"/>
+      <c r="AV1" s="136"/>
+      <c r="AW1" s="137"/>
+      <c r="AX1" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="136"/>
+      <c r="BB1" s="137"/>
+      <c r="BC1" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="131"/>
+      <c r="BE1" s="132"/>
+      <c r="BF1" s="132"/>
+      <c r="BG1" s="133"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="151" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="151" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="154" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="156" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="156" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="157">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="158"/>
+      <c r="AG2" s="158"/>
+      <c r="AH2" s="158"/>
+      <c r="AI2" s="159"/>
+      <c r="AJ2" s="151" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="152"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="157">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="158"/>
+      <c r="AP2" s="158"/>
+      <c r="AQ2" s="158"/>
+      <c r="AR2" s="159"/>
+      <c r="AS2" s="120" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="120"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
+      <c r="AW2" s="120"/>
+      <c r="AX2" s="157">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="158"/>
+      <c r="AZ2" s="158"/>
+      <c r="BA2" s="158"/>
+      <c r="BB2" s="159"/>
+      <c r="BC2" s="151" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="153"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5474,28 +5476,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="BC2:BG2"/>
     <mergeCell ref="AJ1:AM1"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
     <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5532,80 +5534,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="139" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="142"/>
+      <c r="U1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="141"/>
+      <c r="AC1" s="141"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="150"/>
+      <c r="AJ1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="149"/>
+      <c r="AL1" s="149"/>
+      <c r="AM1" s="150"/>
+      <c r="AN1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="149"/>
+      <c r="AP1" s="149"/>
+      <c r="AQ1" s="149"/>
+      <c r="AR1" s="150"/>
+      <c r="AS1" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="136"/>
+      <c r="AU1" s="136"/>
+      <c r="AV1" s="136"/>
+      <c r="AW1" s="137"/>
+      <c r="AX1" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="135"/>
+      <c r="BA1" s="136"/>
+      <c r="BB1" s="137"/>
       <c r="BC1" s="174" t="s">
         <v>21</v>
       </c>
@@ -5628,90 +5630,90 @@
       <c r="BT1" s="175"/>
     </row>
     <row r="2" spans="1:72" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="151" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="151" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="153"/>
+      <c r="K2" s="154" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="156" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="154"/>
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="156" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="154"/>
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="157">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="158"/>
+      <c r="AG2" s="158"/>
+      <c r="AH2" s="158"/>
+      <c r="AI2" s="159"/>
+      <c r="AJ2" s="151" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="152"/>
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="157">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="158"/>
+      <c r="AP2" s="158"/>
+      <c r="AQ2" s="158"/>
+      <c r="AR2" s="159"/>
+      <c r="AS2" s="120" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="120"/>
+      <c r="AU2" s="120"/>
+      <c r="AV2" s="120"/>
+      <c r="AW2" s="120"/>
+      <c r="AX2" s="157">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
+      <c r="AY2" s="158"/>
+      <c r="AZ2" s="158"/>
+      <c r="BA2" s="158"/>
+      <c r="BB2" s="159"/>
       <c r="BC2" s="176" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
@@ -5934,2854 +5936,2836 @@
       <c r="BS5" s="49"/>
       <c r="BT5" s="50"/>
     </row>
-    <row r="7" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="C7" s="121" t="s">
+    <row r="7" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A7" s="56"/>
+      <c r="C7" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123" t="s">
+      <c r="D7" s="59"/>
+      <c r="E7" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="124"/>
-      <c r="Z7" s="124"/>
-      <c r="AA7" s="124"/>
-      <c r="AB7" s="124"/>
-      <c r="AC7" s="124"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="124"/>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="125" t="s">
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="61"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="61"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="61"/>
+      <c r="Y7" s="61"/>
+      <c r="Z7" s="61"/>
+      <c r="AA7" s="61"/>
+      <c r="AB7" s="61"/>
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="124"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="124"/>
-      <c r="AP7" s="124"/>
-      <c r="AQ7" s="124"/>
-      <c r="AR7" s="124"/>
-      <c r="AS7" s="124"/>
-      <c r="AT7" s="124"/>
-      <c r="AU7" s="124"/>
-      <c r="AV7" s="124"/>
-      <c r="AW7" s="124"/>
-      <c r="AX7" s="124"/>
-      <c r="AY7" s="124"/>
-      <c r="AZ7" s="124"/>
-      <c r="BA7" s="124"/>
-      <c r="BB7" s="125" t="s">
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="61"/>
+      <c r="AM7" s="61"/>
+      <c r="AN7" s="61"/>
+      <c r="AO7" s="61"/>
+      <c r="AP7" s="61"/>
+      <c r="AQ7" s="61"/>
+      <c r="AR7" s="61"/>
+      <c r="AS7" s="61"/>
+      <c r="AT7" s="61"/>
+      <c r="AU7" s="61"/>
+      <c r="AV7" s="61"/>
+      <c r="AW7" s="61"/>
+      <c r="AX7" s="61"/>
+      <c r="AY7" s="61"/>
+      <c r="AZ7" s="61"/>
+      <c r="BA7" s="61"/>
+      <c r="BB7" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="BC7" s="124"/>
-      <c r="BD7" s="124"/>
-      <c r="BE7" s="124"/>
-      <c r="BF7" s="124"/>
-      <c r="BG7" s="124"/>
-      <c r="BH7" s="124"/>
-      <c r="BI7" s="124"/>
-      <c r="BJ7" s="124"/>
-      <c r="BK7" s="124"/>
-      <c r="BL7" s="124"/>
-      <c r="BM7" s="124"/>
-      <c r="BN7" s="124"/>
-      <c r="BO7" s="124"/>
-      <c r="BP7" s="124"/>
-      <c r="BQ7" s="124"/>
-      <c r="BR7" s="126"/>
-      <c r="BT7" s="127"/>
-    </row>
-    <row r="8" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="C8" s="128">
+      <c r="BC7" s="61"/>
+      <c r="BD7" s="61"/>
+      <c r="BE7" s="61"/>
+      <c r="BF7" s="61"/>
+      <c r="BG7" s="61"/>
+      <c r="BH7" s="61"/>
+      <c r="BI7" s="61"/>
+      <c r="BJ7" s="61"/>
+      <c r="BK7" s="61"/>
+      <c r="BL7" s="61"/>
+      <c r="BM7" s="61"/>
+      <c r="BN7" s="61"/>
+      <c r="BO7" s="61"/>
+      <c r="BP7" s="61"/>
+      <c r="BQ7" s="61"/>
+      <c r="BR7" s="63"/>
+      <c r="BT7" s="64"/>
+    </row>
+    <row r="8" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="C8" s="166">
         <v>1</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="130" t="s">
+      <c r="D8" s="167"/>
+      <c r="E8" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131"/>
-      <c r="K8" s="131"/>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="131"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131"/>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="131"/>
-      <c r="AB8" s="131"/>
-      <c r="AC8" s="131"/>
-      <c r="AD8" s="131"/>
-      <c r="AE8" s="131"/>
-      <c r="AF8" s="131"/>
-      <c r="AG8" s="131"/>
-      <c r="AH8" s="131"/>
-      <c r="AI8" s="131"/>
-      <c r="AJ8" s="132" t="s">
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="66"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AK8" s="131"/>
-      <c r="AL8" s="131"/>
-      <c r="AM8" s="131"/>
-      <c r="AN8" s="131"/>
-      <c r="AO8" s="131"/>
-      <c r="AP8" s="131"/>
-      <c r="AQ8" s="131"/>
-      <c r="AR8" s="131"/>
-      <c r="AS8" s="131"/>
-      <c r="AT8" s="131"/>
-      <c r="AU8" s="131"/>
-      <c r="AV8" s="131"/>
-      <c r="AW8" s="131"/>
-      <c r="AX8" s="131"/>
-      <c r="AY8" s="131"/>
-      <c r="AZ8" s="131"/>
-      <c r="BA8" s="131"/>
-      <c r="BB8" s="132" t="s">
+      <c r="AK8" s="66"/>
+      <c r="AL8" s="66"/>
+      <c r="AM8" s="66"/>
+      <c r="AN8" s="66"/>
+      <c r="AO8" s="66"/>
+      <c r="AP8" s="66"/>
+      <c r="AQ8" s="66"/>
+      <c r="AR8" s="66"/>
+      <c r="AS8" s="66"/>
+      <c r="AT8" s="66"/>
+      <c r="AU8" s="66"/>
+      <c r="AV8" s="66"/>
+      <c r="AW8" s="66"/>
+      <c r="AX8" s="66"/>
+      <c r="AY8" s="66"/>
+      <c r="AZ8" s="66"/>
+      <c r="BA8" s="66"/>
+      <c r="BB8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="BC8" s="131"/>
-      <c r="BD8" s="131"/>
-      <c r="BE8" s="131"/>
-      <c r="BF8" s="131"/>
-      <c r="BG8" s="131"/>
-      <c r="BH8" s="131"/>
-      <c r="BI8" s="131"/>
-      <c r="BJ8" s="131"/>
-      <c r="BK8" s="131"/>
-      <c r="BL8" s="131"/>
-      <c r="BM8" s="131"/>
-      <c r="BN8" s="131"/>
-      <c r="BO8" s="131"/>
-      <c r="BP8" s="131"/>
-      <c r="BQ8" s="131"/>
-      <c r="BR8" s="133"/>
-      <c r="BT8" s="127"/>
-    </row>
-    <row r="9" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135" t="s">
+      <c r="BC8" s="66"/>
+      <c r="BD8" s="66"/>
+      <c r="BE8" s="66"/>
+      <c r="BF8" s="66"/>
+      <c r="BG8" s="66"/>
+      <c r="BH8" s="66"/>
+      <c r="BI8" s="66"/>
+      <c r="BJ8" s="66"/>
+      <c r="BK8" s="66"/>
+      <c r="BL8" s="66"/>
+      <c r="BM8" s="66"/>
+      <c r="BN8" s="66"/>
+      <c r="BO8" s="66"/>
+      <c r="BP8" s="66"/>
+      <c r="BQ8" s="66"/>
+      <c r="BR8" s="68"/>
+      <c r="BT8" s="64"/>
+    </row>
+    <row r="9" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="131" t="s">
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="131"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131"/>
-      <c r="U9" s="131"/>
-      <c r="V9" s="131"/>
-      <c r="W9" s="131"/>
-      <c r="X9" s="131"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="131"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="131"/>
-      <c r="AC9" s="131"/>
-      <c r="AD9" s="131"/>
-      <c r="AE9" s="131"/>
-      <c r="AF9" s="131"/>
-      <c r="AG9" s="131"/>
-      <c r="AH9" s="131"/>
-      <c r="AI9" s="131"/>
-      <c r="AJ9" s="131"/>
-      <c r="AK9" s="131"/>
-      <c r="AL9" s="131"/>
-      <c r="AM9" s="131"/>
-      <c r="AN9" s="131"/>
-      <c r="AO9" s="131"/>
-      <c r="AP9" s="131"/>
-      <c r="AQ9" s="131"/>
-      <c r="AR9" s="131"/>
-      <c r="AS9" s="131"/>
-      <c r="AT9" s="131"/>
-      <c r="AU9" s="131"/>
-      <c r="AV9" s="131"/>
-      <c r="AW9" s="131"/>
-      <c r="AX9" s="131"/>
-      <c r="AY9" s="131"/>
-      <c r="AZ9" s="131"/>
-      <c r="BA9" s="131"/>
-      <c r="BB9" s="131"/>
-      <c r="BC9" s="131"/>
-      <c r="BD9" s="131"/>
-      <c r="BE9" s="131"/>
-      <c r="BF9" s="131"/>
-      <c r="BG9" s="131"/>
-      <c r="BH9" s="131"/>
-      <c r="BI9" s="131"/>
-      <c r="BJ9" s="131"/>
-      <c r="BK9" s="131"/>
-      <c r="BL9" s="131"/>
-      <c r="BM9" s="131"/>
-      <c r="BN9" s="131"/>
-      <c r="BO9" s="131"/>
-      <c r="BP9" s="131"/>
-      <c r="BQ9" s="131"/>
-      <c r="BR9" s="133"/>
-    </row>
-    <row r="10" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="135" t="s">
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="66"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
+      <c r="AC9" s="66"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="66"/>
+      <c r="AG9" s="66"/>
+      <c r="AH9" s="66"/>
+      <c r="AI9" s="66"/>
+      <c r="AJ9" s="66"/>
+      <c r="AK9" s="66"/>
+      <c r="AL9" s="66"/>
+      <c r="AM9" s="66"/>
+      <c r="AN9" s="66"/>
+      <c r="AO9" s="66"/>
+      <c r="AP9" s="66"/>
+      <c r="AQ9" s="66"/>
+      <c r="AR9" s="66"/>
+      <c r="AS9" s="66"/>
+      <c r="AT9" s="66"/>
+      <c r="AU9" s="66"/>
+      <c r="AV9" s="66"/>
+      <c r="AW9" s="66"/>
+      <c r="AX9" s="66"/>
+      <c r="AY9" s="66"/>
+      <c r="AZ9" s="66"/>
+      <c r="BA9" s="66"/>
+      <c r="BB9" s="66"/>
+      <c r="BC9" s="66"/>
+      <c r="BD9" s="66"/>
+      <c r="BE9" s="66"/>
+      <c r="BF9" s="66"/>
+      <c r="BG9" s="66"/>
+      <c r="BH9" s="66"/>
+      <c r="BI9" s="66"/>
+      <c r="BJ9" s="66"/>
+      <c r="BK9" s="66"/>
+      <c r="BL9" s="66"/>
+      <c r="BM9" s="66"/>
+      <c r="BN9" s="66"/>
+      <c r="BO9" s="66"/>
+      <c r="BP9" s="66"/>
+      <c r="BQ9" s="66"/>
+      <c r="BR9" s="68"/>
+    </row>
+    <row r="10" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="131" t="s">
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="131"/>
-      <c r="W10" s="131"/>
-      <c r="X10" s="131"/>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="131"/>
-      <c r="AB10" s="131"/>
-      <c r="AC10" s="131"/>
-      <c r="AD10" s="131"/>
-      <c r="AE10" s="131"/>
-      <c r="AF10" s="131"/>
-      <c r="AG10" s="131"/>
-      <c r="AH10" s="131"/>
-      <c r="AI10" s="131"/>
-      <c r="AJ10" s="131"/>
-      <c r="AK10" s="131"/>
-      <c r="AL10" s="131"/>
-      <c r="AM10" s="131"/>
-      <c r="AN10" s="131"/>
-      <c r="AO10" s="131"/>
-      <c r="AP10" s="131"/>
-      <c r="AQ10" s="131"/>
-      <c r="AR10" s="131"/>
-      <c r="AS10" s="131"/>
-      <c r="AT10" s="131"/>
-      <c r="AU10" s="131"/>
-      <c r="AV10" s="131"/>
-      <c r="AW10" s="131"/>
-      <c r="AX10" s="131"/>
-      <c r="AY10" s="131"/>
-      <c r="AZ10" s="131"/>
-      <c r="BA10" s="131"/>
-      <c r="BB10" s="131"/>
-      <c r="BC10" s="131"/>
-      <c r="BD10" s="131"/>
-      <c r="BE10" s="131"/>
-      <c r="BF10" s="131"/>
-      <c r="BG10" s="131"/>
-      <c r="BH10" s="131"/>
-      <c r="BI10" s="131"/>
-      <c r="BJ10" s="131"/>
-      <c r="BK10" s="131"/>
-      <c r="BL10" s="131"/>
-      <c r="BM10" s="131"/>
-      <c r="BN10" s="131"/>
-      <c r="BO10" s="131"/>
-      <c r="BP10" s="131"/>
-      <c r="BQ10" s="131"/>
-      <c r="BR10" s="133"/>
-    </row>
-    <row r="11" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="139"/>
-      <c r="BR11" s="140"/>
-      <c r="BT11" s="127"/>
-    </row>
-    <row r="12" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A12" s="119"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="120" t="s">
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="66"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="66"/>
+      <c r="AI10" s="66"/>
+      <c r="AJ10" s="66"/>
+      <c r="AK10" s="66"/>
+      <c r="AL10" s="66"/>
+      <c r="AM10" s="66"/>
+      <c r="AN10" s="66"/>
+      <c r="AO10" s="66"/>
+      <c r="AP10" s="66"/>
+      <c r="AQ10" s="66"/>
+      <c r="AR10" s="66"/>
+      <c r="AS10" s="66"/>
+      <c r="AT10" s="66"/>
+      <c r="AU10" s="66"/>
+      <c r="AV10" s="66"/>
+      <c r="AW10" s="66"/>
+      <c r="AX10" s="66"/>
+      <c r="AY10" s="66"/>
+      <c r="AZ10" s="66"/>
+      <c r="BA10" s="66"/>
+      <c r="BB10" s="66"/>
+      <c r="BC10" s="66"/>
+      <c r="BD10" s="66"/>
+      <c r="BE10" s="66"/>
+      <c r="BF10" s="66"/>
+      <c r="BG10" s="66"/>
+      <c r="BH10" s="66"/>
+      <c r="BI10" s="66"/>
+      <c r="BJ10" s="66"/>
+      <c r="BK10" s="66"/>
+      <c r="BL10" s="66"/>
+      <c r="BM10" s="66"/>
+      <c r="BN10" s="66"/>
+      <c r="BO10" s="66"/>
+      <c r="BP10" s="66"/>
+      <c r="BQ10" s="66"/>
+      <c r="BR10" s="68"/>
+    </row>
+    <row r="11" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="BR11" s="75"/>
+      <c r="BT11" s="64"/>
+    </row>
+    <row r="12" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="BR12" s="127"/>
-      <c r="BT12" s="127"/>
-    </row>
-    <row r="13" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A13" s="119"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="138"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="120" t="s">
+      <c r="BR12" s="64"/>
+      <c r="BT12" s="64"/>
+    </row>
+    <row r="13" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="73"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="BR13" s="127"/>
-      <c r="BT13" s="127"/>
-    </row>
-    <row r="14" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A14" s="119"/>
-      <c r="C14" s="138"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="143" t="s">
+      <c r="BR13" s="64"/>
+      <c r="BT13" s="64"/>
+    </row>
+    <row r="14" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A14" s="56"/>
+      <c r="C14" s="73"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="144"/>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="144"/>
-      <c r="AH14" s="144"/>
-      <c r="AI14" s="144"/>
-      <c r="AJ14" s="144"/>
-      <c r="AK14" s="144"/>
-      <c r="AL14" s="144"/>
-      <c r="AM14" s="144"/>
-      <c r="AN14" s="144"/>
-      <c r="AO14" s="144"/>
-      <c r="AP14" s="144"/>
-      <c r="AQ14" s="144"/>
-      <c r="AR14" s="144"/>
-      <c r="AS14" s="144"/>
-      <c r="AT14" s="144"/>
-      <c r="AU14" s="144"/>
-      <c r="AV14" s="144"/>
-      <c r="AW14" s="144"/>
-      <c r="AX14" s="144"/>
-      <c r="AY14" s="144"/>
-      <c r="AZ14" s="144"/>
-      <c r="BA14" s="144"/>
-      <c r="BB14" s="144"/>
-      <c r="BC14" s="144"/>
-      <c r="BD14" s="144"/>
-      <c r="BE14" s="144"/>
-      <c r="BF14" s="144"/>
-      <c r="BG14" s="144"/>
-      <c r="BH14" s="144"/>
-      <c r="BI14" s="144"/>
-      <c r="BJ14" s="144"/>
-      <c r="BK14" s="144"/>
-      <c r="BL14" s="145"/>
-      <c r="BR14" s="127"/>
-      <c r="BT14" s="127"/>
-    </row>
-    <row r="15" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A15" s="119"/>
-      <c r="C15" s="138"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="146" t="s">
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="79"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="79"/>
+      <c r="V14" s="79"/>
+      <c r="W14" s="79"/>
+      <c r="X14" s="79"/>
+      <c r="Y14" s="79"/>
+      <c r="Z14" s="79"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="79"/>
+      <c r="AC14" s="79"/>
+      <c r="AD14" s="79"/>
+      <c r="AE14" s="79"/>
+      <c r="AF14" s="79"/>
+      <c r="AG14" s="79"/>
+      <c r="AH14" s="79"/>
+      <c r="AI14" s="79"/>
+      <c r="AJ14" s="79"/>
+      <c r="AK14" s="79"/>
+      <c r="AL14" s="79"/>
+      <c r="AM14" s="79"/>
+      <c r="AN14" s="79"/>
+      <c r="AO14" s="79"/>
+      <c r="AP14" s="79"/>
+      <c r="AQ14" s="79"/>
+      <c r="AR14" s="79"/>
+      <c r="AS14" s="79"/>
+      <c r="AT14" s="79"/>
+      <c r="AU14" s="79"/>
+      <c r="AV14" s="79"/>
+      <c r="AW14" s="79"/>
+      <c r="AX14" s="79"/>
+      <c r="AY14" s="79"/>
+      <c r="AZ14" s="79"/>
+      <c r="BA14" s="79"/>
+      <c r="BB14" s="79"/>
+      <c r="BC14" s="79"/>
+      <c r="BD14" s="79"/>
+      <c r="BE14" s="79"/>
+      <c r="BF14" s="79"/>
+      <c r="BG14" s="79"/>
+      <c r="BH14" s="79"/>
+      <c r="BI14" s="79"/>
+      <c r="BJ14" s="79"/>
+      <c r="BK14" s="79"/>
+      <c r="BL14" s="80"/>
+      <c r="BR14" s="64"/>
+      <c r="BT14" s="64"/>
+    </row>
+    <row r="15" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A15" s="56"/>
+      <c r="C15" s="73"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="148"/>
-      <c r="L15" s="132" t="s">
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="M15" s="131"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="131"/>
-      <c r="T15" s="131"/>
-      <c r="U15" s="131"/>
-      <c r="V15" s="131"/>
-      <c r="W15" s="131"/>
-      <c r="X15" s="131"/>
-      <c r="Y15" s="131"/>
-      <c r="Z15" s="131"/>
-      <c r="AA15" s="131"/>
-      <c r="AB15" s="131"/>
-      <c r="AC15" s="131"/>
-      <c r="AD15" s="131"/>
-      <c r="AE15" s="131"/>
-      <c r="AF15" s="131"/>
-      <c r="AG15" s="131"/>
-      <c r="AH15" s="131"/>
-      <c r="AI15" s="131"/>
-      <c r="AJ15" s="131"/>
-      <c r="AK15" s="131"/>
-      <c r="AL15" s="131"/>
-      <c r="AM15" s="131"/>
-      <c r="AN15" s="131"/>
-      <c r="AO15" s="131"/>
-      <c r="AP15" s="131"/>
-      <c r="AQ15" s="131"/>
-      <c r="AR15" s="131"/>
-      <c r="AS15" s="131"/>
-      <c r="AT15" s="131"/>
-      <c r="AU15" s="131"/>
-      <c r="AV15" s="131"/>
-      <c r="AW15" s="131"/>
-      <c r="AX15" s="131"/>
-      <c r="AY15" s="131"/>
-      <c r="AZ15" s="131"/>
-      <c r="BA15" s="131"/>
-      <c r="BB15" s="131"/>
-      <c r="BC15" s="131"/>
-      <c r="BD15" s="131"/>
-      <c r="BE15" s="131"/>
-      <c r="BF15" s="131"/>
-      <c r="BG15" s="131"/>
-      <c r="BH15" s="131"/>
-      <c r="BI15" s="131"/>
-      <c r="BJ15" s="131"/>
-      <c r="BK15" s="131"/>
-      <c r="BL15" s="133"/>
-      <c r="BR15" s="149"/>
-      <c r="BT15" s="127"/>
-    </row>
-    <row r="16" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A16" s="119"/>
-      <c r="C16" s="138"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="150" t="s">
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="66"/>
+      <c r="AC15" s="66"/>
+      <c r="AD15" s="66"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="66"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="66"/>
+      <c r="AK15" s="66"/>
+      <c r="AL15" s="66"/>
+      <c r="AM15" s="66"/>
+      <c r="AN15" s="66"/>
+      <c r="AO15" s="66"/>
+      <c r="AP15" s="66"/>
+      <c r="AQ15" s="66"/>
+      <c r="AR15" s="66"/>
+      <c r="AS15" s="66"/>
+      <c r="AT15" s="66"/>
+      <c r="AU15" s="66"/>
+      <c r="AV15" s="66"/>
+      <c r="AW15" s="66"/>
+      <c r="AX15" s="66"/>
+      <c r="AY15" s="66"/>
+      <c r="AZ15" s="66"/>
+      <c r="BA15" s="66"/>
+      <c r="BB15" s="66"/>
+      <c r="BC15" s="66"/>
+      <c r="BD15" s="66"/>
+      <c r="BE15" s="66"/>
+      <c r="BF15" s="66"/>
+      <c r="BG15" s="66"/>
+      <c r="BH15" s="66"/>
+      <c r="BI15" s="66"/>
+      <c r="BJ15" s="66"/>
+      <c r="BK15" s="66"/>
+      <c r="BL15" s="68"/>
+      <c r="BR15" s="84"/>
+      <c r="BT15" s="64"/>
+    </row>
+    <row r="16" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A16" s="56"/>
+      <c r="C16" s="73"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="152"/>
-      <c r="L16" s="132" t="s">
+      <c r="G16" s="169"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="169"/>
+      <c r="J16" s="169"/>
+      <c r="K16" s="170"/>
+      <c r="L16" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="131"/>
-      <c r="S16" s="131"/>
-      <c r="T16" s="131"/>
-      <c r="U16" s="131"/>
-      <c r="V16" s="131"/>
-      <c r="W16" s="131"/>
-      <c r="X16" s="131"/>
-      <c r="Y16" s="131"/>
-      <c r="Z16" s="131"/>
-      <c r="AA16" s="131"/>
-      <c r="AB16" s="131"/>
-      <c r="AC16" s="131"/>
-      <c r="AD16" s="131"/>
-      <c r="AE16" s="131"/>
-      <c r="AF16" s="131"/>
-      <c r="AG16" s="131"/>
-      <c r="AH16" s="131"/>
-      <c r="AI16" s="131"/>
-      <c r="AJ16" s="131"/>
-      <c r="AK16" s="132" t="s">
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="66"/>
+      <c r="X16" s="66"/>
+      <c r="Y16" s="66"/>
+      <c r="Z16" s="66"/>
+      <c r="AA16" s="66"/>
+      <c r="AB16" s="66"/>
+      <c r="AC16" s="66"/>
+      <c r="AD16" s="66"/>
+      <c r="AE16" s="66"/>
+      <c r="AF16" s="66"/>
+      <c r="AG16" s="66"/>
+      <c r="AH16" s="66"/>
+      <c r="AI16" s="66"/>
+      <c r="AJ16" s="66"/>
+      <c r="AK16" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AL16" s="131"/>
-      <c r="AM16" s="131"/>
-      <c r="AN16" s="131"/>
-      <c r="AO16" s="131"/>
-      <c r="AP16" s="131"/>
-      <c r="AQ16" s="131"/>
-      <c r="AR16" s="131"/>
-      <c r="AS16" s="131"/>
-      <c r="AT16" s="131"/>
-      <c r="AU16" s="131"/>
-      <c r="AV16" s="131"/>
-      <c r="AW16" s="131"/>
-      <c r="AX16" s="131"/>
-      <c r="AY16" s="131"/>
-      <c r="AZ16" s="131"/>
-      <c r="BA16" s="131"/>
-      <c r="BB16" s="131"/>
-      <c r="BC16" s="131"/>
-      <c r="BD16" s="131"/>
-      <c r="BE16" s="131"/>
-      <c r="BF16" s="131"/>
-      <c r="BG16" s="131"/>
-      <c r="BH16" s="131"/>
-      <c r="BI16" s="131"/>
-      <c r="BJ16" s="131"/>
-      <c r="BK16" s="131"/>
-      <c r="BL16" s="133"/>
-      <c r="BR16" s="127"/>
-      <c r="BT16" s="127"/>
-    </row>
-    <row r="17" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="119"/>
-      <c r="C17" s="138"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="154"/>
-      <c r="K17" s="155"/>
-      <c r="L17" s="132" t="s">
+      <c r="AL16" s="66"/>
+      <c r="AM16" s="66"/>
+      <c r="AN16" s="66"/>
+      <c r="AO16" s="66"/>
+      <c r="AP16" s="66"/>
+      <c r="AQ16" s="66"/>
+      <c r="AR16" s="66"/>
+      <c r="AS16" s="66"/>
+      <c r="AT16" s="66"/>
+      <c r="AU16" s="66"/>
+      <c r="AV16" s="66"/>
+      <c r="AW16" s="66"/>
+      <c r="AX16" s="66"/>
+      <c r="AY16" s="66"/>
+      <c r="AZ16" s="66"/>
+      <c r="BA16" s="66"/>
+      <c r="BB16" s="66"/>
+      <c r="BC16" s="66"/>
+      <c r="BD16" s="66"/>
+      <c r="BE16" s="66"/>
+      <c r="BF16" s="66"/>
+      <c r="BG16" s="66"/>
+      <c r="BH16" s="66"/>
+      <c r="BI16" s="66"/>
+      <c r="BJ16" s="66"/>
+      <c r="BK16" s="66"/>
+      <c r="BL16" s="68"/>
+      <c r="BR16" s="64"/>
+      <c r="BT16" s="64"/>
+    </row>
+    <row r="17" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A17" s="56"/>
+      <c r="C17" s="73"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="172"/>
+      <c r="H17" s="172"/>
+      <c r="I17" s="172"/>
+      <c r="J17" s="172"/>
+      <c r="K17" s="173"/>
+      <c r="L17" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="M17" s="131"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="131"/>
-      <c r="S17" s="131"/>
-      <c r="T17" s="131"/>
-      <c r="U17" s="131"/>
-      <c r="V17" s="131"/>
-      <c r="W17" s="131"/>
-      <c r="X17" s="131"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="131"/>
-      <c r="AA17" s="131"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="131"/>
-      <c r="AD17" s="131"/>
-      <c r="AE17" s="131"/>
-      <c r="AF17" s="131"/>
-      <c r="AG17" s="131"/>
-      <c r="AH17" s="131"/>
-      <c r="AI17" s="131"/>
-      <c r="AJ17" s="131"/>
-      <c r="AK17" s="132" t="s">
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="66"/>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="66"/>
+      <c r="AC17" s="66"/>
+      <c r="AD17" s="66"/>
+      <c r="AE17" s="66"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="66"/>
+      <c r="AH17" s="66"/>
+      <c r="AI17" s="66"/>
+      <c r="AJ17" s="66"/>
+      <c r="AK17" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AL17" s="131"/>
-      <c r="AM17" s="131"/>
-      <c r="AN17" s="131"/>
-      <c r="AO17" s="131"/>
-      <c r="AP17" s="131"/>
-      <c r="AQ17" s="131"/>
-      <c r="AR17" s="131"/>
-      <c r="AS17" s="131"/>
-      <c r="AT17" s="131"/>
-      <c r="AU17" s="131"/>
-      <c r="AV17" s="131"/>
-      <c r="AW17" s="131"/>
-      <c r="AX17" s="131"/>
-      <c r="AY17" s="131"/>
-      <c r="AZ17" s="131"/>
-      <c r="BA17" s="131"/>
-      <c r="BB17" s="131"/>
-      <c r="BC17" s="131"/>
-      <c r="BD17" s="131"/>
-      <c r="BE17" s="131"/>
-      <c r="BF17" s="131"/>
-      <c r="BG17" s="131"/>
-      <c r="BH17" s="131"/>
-      <c r="BI17" s="131"/>
-      <c r="BJ17" s="131"/>
-      <c r="BK17" s="131"/>
-      <c r="BL17" s="133"/>
-      <c r="BR17" s="127"/>
-      <c r="BT17" s="127"/>
-    </row>
-    <row r="18" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="C18" s="138"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="146" t="s">
+      <c r="AL17" s="66"/>
+      <c r="AM17" s="66"/>
+      <c r="AN17" s="66"/>
+      <c r="AO17" s="66"/>
+      <c r="AP17" s="66"/>
+      <c r="AQ17" s="66"/>
+      <c r="AR17" s="66"/>
+      <c r="AS17" s="66"/>
+      <c r="AT17" s="66"/>
+      <c r="AU17" s="66"/>
+      <c r="AV17" s="66"/>
+      <c r="AW17" s="66"/>
+      <c r="AX17" s="66"/>
+      <c r="AY17" s="66"/>
+      <c r="AZ17" s="66"/>
+      <c r="BA17" s="66"/>
+      <c r="BB17" s="66"/>
+      <c r="BC17" s="66"/>
+      <c r="BD17" s="66"/>
+      <c r="BE17" s="66"/>
+      <c r="BF17" s="66"/>
+      <c r="BG17" s="66"/>
+      <c r="BH17" s="66"/>
+      <c r="BI17" s="66"/>
+      <c r="BJ17" s="66"/>
+      <c r="BK17" s="66"/>
+      <c r="BL17" s="68"/>
+      <c r="BR17" s="64"/>
+      <c r="BT17" s="64"/>
+    </row>
+    <row r="18" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A18" s="56"/>
+      <c r="C18" s="73"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="132" t="s">
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="M18" s="131"/>
-      <c r="N18" s="131"/>
-      <c r="O18" s="131"/>
-      <c r="P18" s="131"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="131"/>
-      <c r="S18" s="131"/>
-      <c r="T18" s="131"/>
-      <c r="U18" s="131"/>
-      <c r="V18" s="131"/>
-      <c r="W18" s="131"/>
-      <c r="X18" s="131"/>
-      <c r="Y18" s="131"/>
-      <c r="Z18" s="131"/>
-      <c r="AA18" s="131"/>
-      <c r="AB18" s="131"/>
-      <c r="AC18" s="131"/>
-      <c r="AD18" s="131"/>
-      <c r="AE18" s="131"/>
-      <c r="AF18" s="131"/>
-      <c r="AG18" s="131"/>
-      <c r="AH18" s="131"/>
-      <c r="AI18" s="131"/>
-      <c r="AJ18" s="131"/>
-      <c r="AK18" s="131"/>
-      <c r="AL18" s="131"/>
-      <c r="AM18" s="131"/>
-      <c r="AN18" s="131"/>
-      <c r="AO18" s="131"/>
-      <c r="AP18" s="131"/>
-      <c r="AQ18" s="131"/>
-      <c r="AR18" s="131"/>
-      <c r="AS18" s="131"/>
-      <c r="AT18" s="131"/>
-      <c r="AU18" s="131"/>
-      <c r="AV18" s="131"/>
-      <c r="AW18" s="131"/>
-      <c r="AX18" s="131"/>
-      <c r="AY18" s="131"/>
-      <c r="AZ18" s="131"/>
-      <c r="BA18" s="131"/>
-      <c r="BB18" s="131"/>
-      <c r="BC18" s="131"/>
-      <c r="BD18" s="131"/>
-      <c r="BE18" s="131"/>
-      <c r="BF18" s="131"/>
-      <c r="BG18" s="131"/>
-      <c r="BH18" s="131"/>
-      <c r="BI18" s="131"/>
-      <c r="BJ18" s="131"/>
-      <c r="BK18" s="131"/>
-      <c r="BL18" s="133"/>
-      <c r="BR18" s="127"/>
-      <c r="BT18" s="127"/>
-    </row>
-    <row r="19" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="C19" s="138"/>
-      <c r="E19" s="141"/>
-      <c r="BR19" s="127"/>
-      <c r="BT19" s="127"/>
-    </row>
-    <row r="20" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="119"/>
-      <c r="C20" s="138"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="120" t="s">
+      <c r="M18" s="66"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="66"/>
+      <c r="X18" s="66"/>
+      <c r="Y18" s="66"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="66"/>
+      <c r="AC18" s="66"/>
+      <c r="AD18" s="66"/>
+      <c r="AE18" s="66"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="66"/>
+      <c r="AH18" s="66"/>
+      <c r="AI18" s="66"/>
+      <c r="AJ18" s="66"/>
+      <c r="AK18" s="66"/>
+      <c r="AL18" s="66"/>
+      <c r="AM18" s="66"/>
+      <c r="AN18" s="66"/>
+      <c r="AO18" s="66"/>
+      <c r="AP18" s="66"/>
+      <c r="AQ18" s="66"/>
+      <c r="AR18" s="66"/>
+      <c r="AS18" s="66"/>
+      <c r="AT18" s="66"/>
+      <c r="AU18" s="66"/>
+      <c r="AV18" s="66"/>
+      <c r="AW18" s="66"/>
+      <c r="AX18" s="66"/>
+      <c r="AY18" s="66"/>
+      <c r="AZ18" s="66"/>
+      <c r="BA18" s="66"/>
+      <c r="BB18" s="66"/>
+      <c r="BC18" s="66"/>
+      <c r="BD18" s="66"/>
+      <c r="BE18" s="66"/>
+      <c r="BF18" s="66"/>
+      <c r="BG18" s="66"/>
+      <c r="BH18" s="66"/>
+      <c r="BI18" s="66"/>
+      <c r="BJ18" s="66"/>
+      <c r="BK18" s="66"/>
+      <c r="BL18" s="68"/>
+      <c r="BR18" s="64"/>
+      <c r="BT18" s="64"/>
+    </row>
+    <row r="19" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A19" s="56"/>
+      <c r="C19" s="73"/>
+      <c r="E19" s="76"/>
+      <c r="BR19" s="64"/>
+      <c r="BT19" s="64"/>
+    </row>
+    <row r="20" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="56"/>
+      <c r="C20" s="73"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="BR20" s="127"/>
-      <c r="BT20" s="127"/>
-    </row>
-    <row r="21" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="119"/>
-      <c r="C21" s="138"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="143" t="s">
+      <c r="BR20" s="64"/>
+      <c r="BT20" s="64"/>
+    </row>
+    <row r="21" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A21" s="56"/>
+      <c r="C21" s="73"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="144"/>
-      <c r="S21" s="144"/>
-      <c r="T21" s="144"/>
-      <c r="U21" s="144"/>
-      <c r="V21" s="144"/>
-      <c r="W21" s="144"/>
-      <c r="X21" s="144"/>
-      <c r="Y21" s="144"/>
-      <c r="Z21" s="144"/>
-      <c r="AA21" s="144"/>
-      <c r="AB21" s="144"/>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="144"/>
-      <c r="AG21" s="144"/>
-      <c r="AH21" s="144"/>
-      <c r="AI21" s="144"/>
-      <c r="AJ21" s="144"/>
-      <c r="AK21" s="144"/>
-      <c r="AL21" s="144"/>
-      <c r="AM21" s="144"/>
-      <c r="AN21" s="144"/>
-      <c r="AO21" s="144"/>
-      <c r="AP21" s="144"/>
-      <c r="AQ21" s="144"/>
-      <c r="AR21" s="144"/>
-      <c r="AS21" s="144"/>
-      <c r="AT21" s="144"/>
-      <c r="AU21" s="144"/>
-      <c r="AV21" s="144"/>
-      <c r="AW21" s="144"/>
-      <c r="AX21" s="144"/>
-      <c r="AY21" s="144"/>
-      <c r="AZ21" s="144"/>
-      <c r="BA21" s="144"/>
-      <c r="BB21" s="144"/>
-      <c r="BC21" s="144"/>
-      <c r="BD21" s="144"/>
-      <c r="BE21" s="144"/>
-      <c r="BF21" s="144"/>
-      <c r="BG21" s="144"/>
-      <c r="BH21" s="144"/>
-      <c r="BI21" s="144"/>
-      <c r="BJ21" s="144"/>
-      <c r="BK21" s="144"/>
-      <c r="BL21" s="145"/>
-      <c r="BR21" s="127"/>
-      <c r="BT21" s="127"/>
-    </row>
-    <row r="22" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A22" s="119"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="138"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="146" t="s">
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
+      <c r="W21" s="79"/>
+      <c r="X21" s="79"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="79"/>
+      <c r="AA21" s="79"/>
+      <c r="AB21" s="79"/>
+      <c r="AC21" s="79"/>
+      <c r="AD21" s="79"/>
+      <c r="AE21" s="79"/>
+      <c r="AF21" s="79"/>
+      <c r="AG21" s="79"/>
+      <c r="AH21" s="79"/>
+      <c r="AI21" s="79"/>
+      <c r="AJ21" s="79"/>
+      <c r="AK21" s="79"/>
+      <c r="AL21" s="79"/>
+      <c r="AM21" s="79"/>
+      <c r="AN21" s="79"/>
+      <c r="AO21" s="79"/>
+      <c r="AP21" s="79"/>
+      <c r="AQ21" s="79"/>
+      <c r="AR21" s="79"/>
+      <c r="AS21" s="79"/>
+      <c r="AT21" s="79"/>
+      <c r="AU21" s="79"/>
+      <c r="AV21" s="79"/>
+      <c r="AW21" s="79"/>
+      <c r="AX21" s="79"/>
+      <c r="AY21" s="79"/>
+      <c r="AZ21" s="79"/>
+      <c r="BA21" s="79"/>
+      <c r="BB21" s="79"/>
+      <c r="BC21" s="79"/>
+      <c r="BD21" s="79"/>
+      <c r="BE21" s="79"/>
+      <c r="BF21" s="79"/>
+      <c r="BG21" s="79"/>
+      <c r="BH21" s="79"/>
+      <c r="BI21" s="79"/>
+      <c r="BJ21" s="79"/>
+      <c r="BK21" s="79"/>
+      <c r="BL21" s="80"/>
+      <c r="BR21" s="64"/>
+      <c r="BT21" s="64"/>
+    </row>
+    <row r="22" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A22" s="56"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="73"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="147"/>
-      <c r="H22" s="147"/>
-      <c r="I22" s="147"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="148"/>
-      <c r="L22" s="132" t="s">
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
-      <c r="P22" s="131"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
-      <c r="S22" s="131"/>
-      <c r="T22" s="131"/>
-      <c r="U22" s="131"/>
-      <c r="V22" s="131"/>
-      <c r="W22" s="131"/>
-      <c r="X22" s="131"/>
-      <c r="Y22" s="131"/>
-      <c r="Z22" s="131"/>
-      <c r="AA22" s="131"/>
-      <c r="AB22" s="131"/>
-      <c r="AC22" s="131"/>
-      <c r="AD22" s="131"/>
-      <c r="AE22" s="131"/>
-      <c r="AF22" s="131"/>
-      <c r="AG22" s="131"/>
-      <c r="AH22" s="131"/>
-      <c r="AI22" s="131"/>
-      <c r="AJ22" s="131"/>
-      <c r="AK22" s="131"/>
-      <c r="AL22" s="131"/>
-      <c r="AM22" s="131"/>
-      <c r="AN22" s="131"/>
-      <c r="AO22" s="131"/>
-      <c r="AP22" s="131"/>
-      <c r="AQ22" s="131"/>
-      <c r="AR22" s="131"/>
-      <c r="AS22" s="131"/>
-      <c r="AT22" s="131"/>
-      <c r="AU22" s="131"/>
-      <c r="AV22" s="131"/>
-      <c r="AW22" s="131"/>
-      <c r="AX22" s="131"/>
-      <c r="AY22" s="131"/>
-      <c r="AZ22" s="131"/>
-      <c r="BA22" s="131"/>
-      <c r="BB22" s="131"/>
-      <c r="BC22" s="131"/>
-      <c r="BD22" s="131"/>
-      <c r="BE22" s="131"/>
-      <c r="BF22" s="131"/>
-      <c r="BG22" s="131"/>
-      <c r="BH22" s="131"/>
-      <c r="BI22" s="131"/>
-      <c r="BJ22" s="131"/>
-      <c r="BK22" s="131"/>
-      <c r="BL22" s="133"/>
-      <c r="BR22" s="149"/>
-      <c r="BT22" s="127"/>
-    </row>
-    <row r="23" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="138"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="156" t="s">
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="66"/>
+      <c r="AI22" s="66"/>
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="66"/>
+      <c r="AT22" s="66"/>
+      <c r="AU22" s="66"/>
+      <c r="AV22" s="66"/>
+      <c r="AW22" s="66"/>
+      <c r="AX22" s="66"/>
+      <c r="AY22" s="66"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="66"/>
+      <c r="BB22" s="66"/>
+      <c r="BC22" s="66"/>
+      <c r="BD22" s="66"/>
+      <c r="BE22" s="66"/>
+      <c r="BF22" s="66"/>
+      <c r="BG22" s="66"/>
+      <c r="BH22" s="66"/>
+      <c r="BI22" s="66"/>
+      <c r="BJ22" s="66"/>
+      <c r="BK22" s="66"/>
+      <c r="BL22" s="68"/>
+      <c r="BR22" s="84"/>
+      <c r="BT22" s="64"/>
+    </row>
+    <row r="23" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A23" s="56"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="73"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="158"/>
-      <c r="L23" s="132" t="s">
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M23" s="131"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
-      <c r="S23" s="131"/>
-      <c r="T23" s="131"/>
-      <c r="U23" s="131"/>
-      <c r="V23" s="131"/>
-      <c r="W23" s="131"/>
-      <c r="X23" s="131"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="131"/>
-      <c r="AA23" s="131"/>
-      <c r="AB23" s="131"/>
-      <c r="AC23" s="131"/>
-      <c r="AD23" s="131"/>
-      <c r="AE23" s="131"/>
-      <c r="AF23" s="131"/>
-      <c r="AG23" s="131"/>
-      <c r="AH23" s="131"/>
-      <c r="AI23" s="131"/>
-      <c r="AJ23" s="131"/>
-      <c r="AK23" s="132" t="s">
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="66"/>
+      <c r="AE23" s="66"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="66"/>
+      <c r="AH23" s="66"/>
+      <c r="AI23" s="66"/>
+      <c r="AJ23" s="66"/>
+      <c r="AK23" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="AL23" s="131"/>
-      <c r="AM23" s="131"/>
-      <c r="AN23" s="131"/>
-      <c r="AO23" s="131"/>
-      <c r="AP23" s="131"/>
-      <c r="AQ23" s="131"/>
-      <c r="AR23" s="131"/>
-      <c r="AS23" s="131"/>
-      <c r="AT23" s="131"/>
-      <c r="AU23" s="131"/>
-      <c r="AV23" s="131"/>
-      <c r="AW23" s="131"/>
-      <c r="AX23" s="131"/>
-      <c r="AY23" s="131"/>
-      <c r="AZ23" s="131"/>
-      <c r="BA23" s="131"/>
-      <c r="BB23" s="131"/>
-      <c r="BC23" s="131"/>
-      <c r="BD23" s="131"/>
-      <c r="BE23" s="131"/>
-      <c r="BF23" s="131"/>
-      <c r="BG23" s="131"/>
-      <c r="BH23" s="131"/>
-      <c r="BI23" s="131"/>
-      <c r="BJ23" s="131"/>
-      <c r="BK23" s="131"/>
-      <c r="BL23" s="133"/>
-      <c r="BR23" s="149"/>
-      <c r="BT23" s="127"/>
-    </row>
-    <row r="24" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A24" s="119"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="138"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="146" t="s">
+      <c r="AL23" s="66"/>
+      <c r="AM23" s="66"/>
+      <c r="AN23" s="66"/>
+      <c r="AO23" s="66"/>
+      <c r="AP23" s="66"/>
+      <c r="AQ23" s="66"/>
+      <c r="AR23" s="66"/>
+      <c r="AS23" s="66"/>
+      <c r="AT23" s="66"/>
+      <c r="AU23" s="66"/>
+      <c r="AV23" s="66"/>
+      <c r="AW23" s="66"/>
+      <c r="AX23" s="66"/>
+      <c r="AY23" s="66"/>
+      <c r="AZ23" s="66"/>
+      <c r="BA23" s="66"/>
+      <c r="BB23" s="66"/>
+      <c r="BC23" s="66"/>
+      <c r="BD23" s="66"/>
+      <c r="BE23" s="66"/>
+      <c r="BF23" s="66"/>
+      <c r="BG23" s="66"/>
+      <c r="BH23" s="66"/>
+      <c r="BI23" s="66"/>
+      <c r="BJ23" s="66"/>
+      <c r="BK23" s="66"/>
+      <c r="BL23" s="68"/>
+      <c r="BR23" s="84"/>
+      <c r="BT23" s="64"/>
+    </row>
+    <row r="24" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A24" s="56"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="73"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="147"/>
-      <c r="H24" s="147"/>
-      <c r="I24" s="147"/>
-      <c r="J24" s="147"/>
-      <c r="K24" s="148"/>
-      <c r="L24" s="132" t="s">
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="M24" s="131"/>
-      <c r="N24" s="131"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="131"/>
-      <c r="S24" s="131"/>
-      <c r="T24" s="131"/>
-      <c r="U24" s="131"/>
-      <c r="V24" s="131"/>
-      <c r="W24" s="131"/>
-      <c r="X24" s="131"/>
-      <c r="Y24" s="131"/>
-      <c r="Z24" s="131"/>
-      <c r="AA24" s="131"/>
-      <c r="AB24" s="131"/>
-      <c r="AC24" s="131"/>
-      <c r="AD24" s="131"/>
-      <c r="AE24" s="131"/>
-      <c r="AF24" s="131"/>
-      <c r="AG24" s="131"/>
-      <c r="AH24" s="131"/>
-      <c r="AI24" s="131"/>
-      <c r="AJ24" s="131"/>
-      <c r="AK24" s="131"/>
-      <c r="AL24" s="131"/>
-      <c r="AM24" s="131"/>
-      <c r="AN24" s="131"/>
-      <c r="AO24" s="131"/>
-      <c r="AP24" s="131"/>
-      <c r="AQ24" s="131"/>
-      <c r="AR24" s="131"/>
-      <c r="AS24" s="131"/>
-      <c r="AT24" s="131"/>
-      <c r="AU24" s="131"/>
-      <c r="AV24" s="131"/>
-      <c r="AW24" s="131"/>
-      <c r="AX24" s="131"/>
-      <c r="AY24" s="131"/>
-      <c r="AZ24" s="131"/>
-      <c r="BA24" s="131"/>
-      <c r="BB24" s="131"/>
-      <c r="BC24" s="131"/>
-      <c r="BD24" s="131"/>
-      <c r="BE24" s="131"/>
-      <c r="BF24" s="131"/>
-      <c r="BG24" s="131"/>
-      <c r="BH24" s="131"/>
-      <c r="BI24" s="131"/>
-      <c r="BJ24" s="131"/>
-      <c r="BK24" s="131"/>
-      <c r="BL24" s="133"/>
-      <c r="BR24" s="149"/>
-      <c r="BT24" s="127"/>
-    </row>
-    <row r="25" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A25" s="119"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="138"/>
-      <c r="E25" s="141"/>
-      <c r="BR25" s="149"/>
-      <c r="BT25" s="127"/>
-    </row>
-    <row r="26" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="138"/>
-      <c r="E26" s="141"/>
-      <c r="G26" s="161"/>
-      <c r="BR26" s="149"/>
-      <c r="BT26" s="127"/>
-    </row>
-    <row r="27" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A27" s="119"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="138"/>
-      <c r="E27" s="141"/>
-      <c r="G27" s="161"/>
-      <c r="BR27" s="149"/>
-      <c r="BT27" s="127"/>
-    </row>
-    <row r="28" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A28" s="119"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="141">
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
+      <c r="AC24" s="66"/>
+      <c r="AD24" s="66"/>
+      <c r="AE24" s="66"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="66"/>
+      <c r="AH24" s="66"/>
+      <c r="AI24" s="66"/>
+      <c r="AJ24" s="66"/>
+      <c r="AK24" s="66"/>
+      <c r="AL24" s="66"/>
+      <c r="AM24" s="66"/>
+      <c r="AN24" s="66"/>
+      <c r="AO24" s="66"/>
+      <c r="AP24" s="66"/>
+      <c r="AQ24" s="66"/>
+      <c r="AR24" s="66"/>
+      <c r="AS24" s="66"/>
+      <c r="AT24" s="66"/>
+      <c r="AU24" s="66"/>
+      <c r="AV24" s="66"/>
+      <c r="AW24" s="66"/>
+      <c r="AX24" s="66"/>
+      <c r="AY24" s="66"/>
+      <c r="AZ24" s="66"/>
+      <c r="BA24" s="66"/>
+      <c r="BB24" s="66"/>
+      <c r="BC24" s="66"/>
+      <c r="BD24" s="66"/>
+      <c r="BE24" s="66"/>
+      <c r="BF24" s="66"/>
+      <c r="BG24" s="66"/>
+      <c r="BH24" s="66"/>
+      <c r="BI24" s="66"/>
+      <c r="BJ24" s="66"/>
+      <c r="BK24" s="66"/>
+      <c r="BL24" s="68"/>
+      <c r="BR24" s="84"/>
+      <c r="BT24" s="64"/>
+    </row>
+    <row r="25" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A25" s="56"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="73"/>
+      <c r="E25" s="76"/>
+      <c r="BR25" s="84"/>
+      <c r="BT25" s="64"/>
+    </row>
+    <row r="26" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A26" s="56"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="73"/>
+      <c r="E26" s="76"/>
+      <c r="G26" s="89"/>
+      <c r="BR26" s="84"/>
+      <c r="BT26" s="64"/>
+    </row>
+    <row r="27" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A27" s="56"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="73"/>
+      <c r="E27" s="76"/>
+      <c r="G27" s="89"/>
+      <c r="BR27" s="84"/>
+      <c r="BT27" s="64"/>
+    </row>
+    <row r="28" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A28" s="56"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="76">
         <v>2</v>
       </c>
-      <c r="E28" s="120" t="s">
+      <c r="E28" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="BR28" s="149"/>
-      <c r="BT28" s="127"/>
-    </row>
-    <row r="29" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A29" s="119"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="146" t="s">
+      <c r="BR28" s="84"/>
+      <c r="BT28" s="64"/>
+    </row>
+    <row r="29" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A29" s="56"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="136"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="132" t="s">
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="L29" s="131"/>
-      <c r="M29" s="131"/>
-      <c r="N29" s="131"/>
-      <c r="O29" s="131"/>
-      <c r="P29" s="131"/>
-      <c r="Q29" s="131"/>
-      <c r="R29" s="131"/>
-      <c r="S29" s="131"/>
-      <c r="T29" s="131"/>
-      <c r="U29" s="131"/>
-      <c r="V29" s="131"/>
-      <c r="W29" s="131"/>
-      <c r="X29" s="131"/>
-      <c r="Y29" s="131"/>
-      <c r="Z29" s="131"/>
-      <c r="AA29" s="131"/>
-      <c r="AB29" s="131"/>
-      <c r="AC29" s="131"/>
-      <c r="AD29" s="131"/>
-      <c r="AE29" s="131"/>
-      <c r="AF29" s="131"/>
-      <c r="AG29" s="131"/>
-      <c r="AH29" s="131"/>
-      <c r="AI29" s="131"/>
-      <c r="AJ29" s="131"/>
-      <c r="AK29" s="131"/>
-      <c r="AL29" s="131"/>
-      <c r="AM29" s="131"/>
-      <c r="AN29" s="131"/>
-      <c r="AO29" s="131"/>
-      <c r="AP29" s="131"/>
-      <c r="AQ29" s="131"/>
-      <c r="AR29" s="131"/>
-      <c r="AS29" s="131"/>
-      <c r="AT29" s="131"/>
-      <c r="AU29" s="131"/>
-      <c r="AV29" s="131"/>
-      <c r="AW29" s="131"/>
-      <c r="AX29" s="131"/>
-      <c r="AY29" s="131"/>
-      <c r="AZ29" s="131"/>
-      <c r="BA29" s="131"/>
-      <c r="BB29" s="131"/>
-      <c r="BC29" s="131"/>
-      <c r="BD29" s="131"/>
-      <c r="BE29" s="131"/>
-      <c r="BF29" s="131"/>
-      <c r="BG29" s="131"/>
-      <c r="BH29" s="131"/>
-      <c r="BI29" s="131"/>
-      <c r="BJ29" s="131"/>
-      <c r="BK29" s="131"/>
-      <c r="BL29" s="133"/>
-      <c r="BR29" s="149"/>
-      <c r="BT29" s="127"/>
-    </row>
-    <row r="30" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="135" t="s">
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="66"/>
+      <c r="U29" s="66"/>
+      <c r="V29" s="66"/>
+      <c r="W29" s="66"/>
+      <c r="X29" s="66"/>
+      <c r="Y29" s="66"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="66"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="66"/>
+      <c r="AI29" s="66"/>
+      <c r="AJ29" s="66"/>
+      <c r="AK29" s="66"/>
+      <c r="AL29" s="66"/>
+      <c r="AM29" s="66"/>
+      <c r="AN29" s="66"/>
+      <c r="AO29" s="66"/>
+      <c r="AP29" s="66"/>
+      <c r="AQ29" s="66"/>
+      <c r="AR29" s="66"/>
+      <c r="AS29" s="66"/>
+      <c r="AT29" s="66"/>
+      <c r="AU29" s="66"/>
+      <c r="AV29" s="66"/>
+      <c r="AW29" s="66"/>
+      <c r="AX29" s="66"/>
+      <c r="AY29" s="66"/>
+      <c r="AZ29" s="66"/>
+      <c r="BA29" s="66"/>
+      <c r="BB29" s="66"/>
+      <c r="BC29" s="66"/>
+      <c r="BD29" s="66"/>
+      <c r="BE29" s="66"/>
+      <c r="BF29" s="66"/>
+      <c r="BG29" s="66"/>
+      <c r="BH29" s="66"/>
+      <c r="BI29" s="66"/>
+      <c r="BJ29" s="66"/>
+      <c r="BK29" s="66"/>
+      <c r="BL29" s="68"/>
+      <c r="BR29" s="84"/>
+      <c r="BT29" s="64"/>
+    </row>
+    <row r="30" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A30" s="56"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="135" t="s">
+      <c r="F30" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="136"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="136"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="136"/>
-      <c r="R30" s="136"/>
-      <c r="S30" s="136"/>
-      <c r="T30" s="136"/>
-      <c r="U30" s="135" t="s">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="V30" s="136"/>
-      <c r="W30" s="136"/>
-      <c r="X30" s="136"/>
-      <c r="Y30" s="136"/>
-      <c r="Z30" s="136"/>
-      <c r="AA30" s="136"/>
-      <c r="AB30" s="136"/>
-      <c r="AC30" s="136"/>
-      <c r="AD30" s="136"/>
-      <c r="AE30" s="136"/>
-      <c r="AF30" s="137"/>
-      <c r="AG30" s="135" t="s">
+      <c r="V30" s="71"/>
+      <c r="W30" s="71"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="71"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="71"/>
+      <c r="AC30" s="71"/>
+      <c r="AD30" s="71"/>
+      <c r="AE30" s="71"/>
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="AH30" s="136"/>
-      <c r="AI30" s="136"/>
-      <c r="AJ30" s="136"/>
-      <c r="AK30" s="136"/>
-      <c r="AL30" s="136"/>
-      <c r="AM30" s="136"/>
-      <c r="AN30" s="136"/>
-      <c r="AO30" s="136"/>
-      <c r="AP30" s="136"/>
-      <c r="AQ30" s="136"/>
-      <c r="AR30" s="137"/>
-      <c r="AS30" s="136" t="s">
+      <c r="AH30" s="71"/>
+      <c r="AI30" s="71"/>
+      <c r="AJ30" s="71"/>
+      <c r="AK30" s="71"/>
+      <c r="AL30" s="71"/>
+      <c r="AM30" s="71"/>
+      <c r="AN30" s="71"/>
+      <c r="AO30" s="71"/>
+      <c r="AP30" s="71"/>
+      <c r="AQ30" s="71"/>
+      <c r="AR30" s="72"/>
+      <c r="AS30" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="AT30" s="136"/>
-      <c r="AU30" s="136"/>
-      <c r="AV30" s="136"/>
-      <c r="AW30" s="136"/>
-      <c r="AX30" s="136"/>
-      <c r="AY30" s="136"/>
-      <c r="AZ30" s="136"/>
-      <c r="BA30" s="136"/>
-      <c r="BB30" s="136"/>
-      <c r="BC30" s="136"/>
-      <c r="BD30" s="136"/>
-      <c r="BE30" s="136"/>
-      <c r="BF30" s="136"/>
-      <c r="BG30" s="136"/>
-      <c r="BH30" s="136"/>
-      <c r="BI30" s="136"/>
-      <c r="BJ30" s="136"/>
-      <c r="BK30" s="136"/>
-      <c r="BL30" s="137"/>
-      <c r="BR30" s="149"/>
-      <c r="BT30" s="127"/>
-    </row>
-    <row r="31" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="159">
+      <c r="AT30" s="71"/>
+      <c r="AU30" s="71"/>
+      <c r="AV30" s="71"/>
+      <c r="AW30" s="71"/>
+      <c r="AX30" s="71"/>
+      <c r="AY30" s="71"/>
+      <c r="AZ30" s="71"/>
+      <c r="BA30" s="71"/>
+      <c r="BB30" s="71"/>
+      <c r="BC30" s="71"/>
+      <c r="BD30" s="71"/>
+      <c r="BE30" s="71"/>
+      <c r="BF30" s="71"/>
+      <c r="BG30" s="71"/>
+      <c r="BH30" s="71"/>
+      <c r="BI30" s="71"/>
+      <c r="BJ30" s="71"/>
+      <c r="BK30" s="71"/>
+      <c r="BL30" s="72"/>
+      <c r="BR30" s="84"/>
+      <c r="BT30" s="64"/>
+    </row>
+    <row r="31" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A31" s="56"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="88">
         <v>1</v>
       </c>
-      <c r="F31" s="162" t="s">
+      <c r="F31" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
-      <c r="L31" s="131"/>
-      <c r="M31" s="131"/>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
-      <c r="P31" s="131"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="131"/>
-      <c r="S31" s="131"/>
-      <c r="T31" s="133"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="68"/>
       <c r="U31" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="V31" s="163"/>
-      <c r="W31" s="163"/>
-      <c r="X31" s="163"/>
-      <c r="Y31" s="163"/>
-      <c r="Z31" s="163"/>
-      <c r="AA31" s="163"/>
-      <c r="AB31" s="163"/>
-      <c r="AC31" s="163"/>
-      <c r="AD31" s="163"/>
-      <c r="AE31" s="163"/>
-      <c r="AF31" s="164"/>
+      <c r="V31" s="161"/>
+      <c r="W31" s="161"/>
+      <c r="X31" s="161"/>
+      <c r="Y31" s="161"/>
+      <c r="Z31" s="161"/>
+      <c r="AA31" s="161"/>
+      <c r="AB31" s="161"/>
+      <c r="AC31" s="161"/>
+      <c r="AD31" s="161"/>
+      <c r="AE31" s="161"/>
+      <c r="AF31" s="162"/>
       <c r="AG31" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="AH31" s="163"/>
-      <c r="AI31" s="163"/>
-      <c r="AJ31" s="163"/>
-      <c r="AK31" s="163"/>
-      <c r="AL31" s="163"/>
-      <c r="AM31" s="163"/>
-      <c r="AN31" s="163"/>
-      <c r="AO31" s="163"/>
-      <c r="AP31" s="163"/>
-      <c r="AQ31" s="163"/>
-      <c r="AR31" s="164"/>
-      <c r="AS31" s="165" t="s">
+      <c r="AH31" s="161"/>
+      <c r="AI31" s="161"/>
+      <c r="AJ31" s="161"/>
+      <c r="AK31" s="161"/>
+      <c r="AL31" s="161"/>
+      <c r="AM31" s="161"/>
+      <c r="AN31" s="161"/>
+      <c r="AO31" s="161"/>
+      <c r="AP31" s="161"/>
+      <c r="AQ31" s="161"/>
+      <c r="AR31" s="162"/>
+      <c r="AS31" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="AT31" s="166"/>
-      <c r="AU31" s="166"/>
-      <c r="AV31" s="166"/>
-      <c r="AW31" s="166"/>
-      <c r="AX31" s="166"/>
-      <c r="AY31" s="166"/>
-      <c r="AZ31" s="166"/>
-      <c r="BA31" s="166"/>
-      <c r="BB31" s="166"/>
-      <c r="BC31" s="166"/>
-      <c r="BD31" s="166"/>
-      <c r="BE31" s="166"/>
-      <c r="BF31" s="166"/>
-      <c r="BG31" s="166"/>
-      <c r="BH31" s="166"/>
-      <c r="BI31" s="166"/>
-      <c r="BJ31" s="166"/>
-      <c r="BK31" s="166"/>
-      <c r="BL31" s="167"/>
-      <c r="BR31" s="149"/>
-      <c r="BT31" s="127"/>
-    </row>
-    <row r="32" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A32" s="119"/>
-      <c r="B32" s="134"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="159">
+      <c r="AT31" s="164"/>
+      <c r="AU31" s="164"/>
+      <c r="AV31" s="164"/>
+      <c r="AW31" s="164"/>
+      <c r="AX31" s="164"/>
+      <c r="AY31" s="164"/>
+      <c r="AZ31" s="164"/>
+      <c r="BA31" s="164"/>
+      <c r="BB31" s="164"/>
+      <c r="BC31" s="164"/>
+      <c r="BD31" s="164"/>
+      <c r="BE31" s="164"/>
+      <c r="BF31" s="164"/>
+      <c r="BG31" s="164"/>
+      <c r="BH31" s="164"/>
+      <c r="BI31" s="164"/>
+      <c r="BJ31" s="164"/>
+      <c r="BK31" s="164"/>
+      <c r="BL31" s="165"/>
+      <c r="BR31" s="84"/>
+      <c r="BT31" s="64"/>
+    </row>
+    <row r="32" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A32" s="56"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="88">
         <v>2</v>
       </c>
-      <c r="F32" s="162" t="s">
+      <c r="F32" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="131"/>
-      <c r="K32" s="131"/>
-      <c r="L32" s="131"/>
-      <c r="M32" s="131"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="131"/>
-      <c r="P32" s="131"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="131"/>
-      <c r="S32" s="131"/>
-      <c r="T32" s="133"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="68"/>
       <c r="U32" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="V32" s="163"/>
-      <c r="W32" s="163"/>
-      <c r="X32" s="163"/>
-      <c r="Y32" s="163"/>
-      <c r="Z32" s="163"/>
-      <c r="AA32" s="163"/>
-      <c r="AB32" s="163"/>
-      <c r="AC32" s="163"/>
-      <c r="AD32" s="163"/>
-      <c r="AE32" s="163"/>
-      <c r="AF32" s="164"/>
+      <c r="V32" s="161"/>
+      <c r="W32" s="161"/>
+      <c r="X32" s="161"/>
+      <c r="Y32" s="161"/>
+      <c r="Z32" s="161"/>
+      <c r="AA32" s="161"/>
+      <c r="AB32" s="161"/>
+      <c r="AC32" s="161"/>
+      <c r="AD32" s="161"/>
+      <c r="AE32" s="161"/>
+      <c r="AF32" s="162"/>
       <c r="AG32" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="AH32" s="163"/>
-      <c r="AI32" s="163"/>
-      <c r="AJ32" s="163"/>
-      <c r="AK32" s="163"/>
-      <c r="AL32" s="163"/>
-      <c r="AM32" s="163"/>
-      <c r="AN32" s="163"/>
-      <c r="AO32" s="163"/>
-      <c r="AP32" s="163"/>
-      <c r="AQ32" s="163"/>
-      <c r="AR32" s="164"/>
-      <c r="AS32" s="165" t="s">
+      <c r="AH32" s="161"/>
+      <c r="AI32" s="161"/>
+      <c r="AJ32" s="161"/>
+      <c r="AK32" s="161"/>
+      <c r="AL32" s="161"/>
+      <c r="AM32" s="161"/>
+      <c r="AN32" s="161"/>
+      <c r="AO32" s="161"/>
+      <c r="AP32" s="161"/>
+      <c r="AQ32" s="161"/>
+      <c r="AR32" s="162"/>
+      <c r="AS32" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="AT32" s="166"/>
-      <c r="AU32" s="166"/>
-      <c r="AV32" s="166"/>
-      <c r="AW32" s="166"/>
-      <c r="AX32" s="166"/>
-      <c r="AY32" s="166"/>
-      <c r="AZ32" s="166"/>
-      <c r="BA32" s="166"/>
-      <c r="BB32" s="166"/>
-      <c r="BC32" s="166"/>
-      <c r="BD32" s="166"/>
-      <c r="BE32" s="166"/>
-      <c r="BF32" s="166"/>
-      <c r="BG32" s="166"/>
-      <c r="BH32" s="166"/>
-      <c r="BI32" s="166"/>
-      <c r="BJ32" s="166"/>
-      <c r="BK32" s="166"/>
-      <c r="BL32" s="167"/>
-      <c r="BR32" s="149"/>
-      <c r="BT32" s="127"/>
-    </row>
-    <row r="33" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A33" s="119"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="170"/>
-      <c r="F33" s="170"/>
-      <c r="G33" s="170"/>
-      <c r="H33" s="170"/>
-      <c r="I33" s="170"/>
-      <c r="J33" s="170"/>
-      <c r="K33" s="170"/>
-      <c r="L33" s="170"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="170"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="170"/>
-      <c r="Q33" s="170"/>
-      <c r="R33" s="170"/>
-      <c r="S33" s="170"/>
-      <c r="T33" s="170"/>
-      <c r="U33" s="170"/>
-      <c r="V33" s="170"/>
-      <c r="W33" s="170"/>
-      <c r="X33" s="170"/>
-      <c r="Y33" s="170"/>
-      <c r="Z33" s="170"/>
-      <c r="AA33" s="170"/>
-      <c r="AB33" s="170"/>
-      <c r="AC33" s="170"/>
-      <c r="AD33" s="170"/>
-      <c r="AE33" s="170"/>
-      <c r="AF33" s="170"/>
-      <c r="AG33" s="171"/>
-      <c r="AH33" s="171"/>
-      <c r="AI33" s="171"/>
-      <c r="AJ33" s="171"/>
-      <c r="AK33" s="171"/>
-      <c r="AL33" s="171"/>
-      <c r="AM33" s="171"/>
-      <c r="AN33" s="171"/>
-      <c r="AO33" s="171"/>
-      <c r="AP33" s="171"/>
-      <c r="AQ33" s="171"/>
-      <c r="AR33" s="171"/>
-      <c r="AS33" s="171"/>
-      <c r="AT33" s="171"/>
-      <c r="AU33" s="170"/>
-      <c r="AV33" s="170"/>
-      <c r="AW33" s="170"/>
-      <c r="AX33" s="171"/>
-      <c r="AY33" s="171"/>
-      <c r="AZ33" s="171"/>
-      <c r="BA33" s="171"/>
-      <c r="BB33" s="171"/>
-      <c r="BC33" s="170"/>
-      <c r="BD33" s="170"/>
-      <c r="BE33" s="170"/>
-      <c r="BF33" s="171"/>
-      <c r="BG33" s="171"/>
-      <c r="BH33" s="171"/>
-      <c r="BI33" s="171"/>
-      <c r="BJ33" s="171"/>
-      <c r="BK33" s="170"/>
-      <c r="BL33" s="170"/>
-      <c r="BM33" s="170"/>
-      <c r="BN33" s="170"/>
-      <c r="BO33" s="170"/>
-      <c r="BP33" s="170"/>
-      <c r="BQ33" s="170"/>
-      <c r="BR33" s="172"/>
-      <c r="BT33" s="127"/>
-    </row>
-    <row r="34" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A34" s="119"/>
-      <c r="C34" s="173"/>
-      <c r="BT34" s="127"/>
-    </row>
-    <row r="35" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A35" s="177"/>
-      <c r="C35" s="173"/>
-      <c r="BT35" s="177"/>
-    </row>
-    <row r="36" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A36" s="119"/>
-      <c r="C36" s="121" t="s">
+      <c r="AT32" s="164"/>
+      <c r="AU32" s="164"/>
+      <c r="AV32" s="164"/>
+      <c r="AW32" s="164"/>
+      <c r="AX32" s="164"/>
+      <c r="AY32" s="164"/>
+      <c r="AZ32" s="164"/>
+      <c r="BA32" s="164"/>
+      <c r="BB32" s="164"/>
+      <c r="BC32" s="164"/>
+      <c r="BD32" s="164"/>
+      <c r="BE32" s="164"/>
+      <c r="BF32" s="164"/>
+      <c r="BG32" s="164"/>
+      <c r="BH32" s="164"/>
+      <c r="BI32" s="164"/>
+      <c r="BJ32" s="164"/>
+      <c r="BK32" s="164"/>
+      <c r="BL32" s="165"/>
+      <c r="BR32" s="84"/>
+      <c r="BT32" s="64"/>
+    </row>
+    <row r="33" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A33" s="56"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
+      <c r="P33" s="93"/>
+      <c r="Q33" s="93"/>
+      <c r="R33" s="93"/>
+      <c r="S33" s="93"/>
+      <c r="T33" s="93"/>
+      <c r="U33" s="93"/>
+      <c r="V33" s="93"/>
+      <c r="W33" s="93"/>
+      <c r="X33" s="93"/>
+      <c r="Y33" s="93"/>
+      <c r="Z33" s="93"/>
+      <c r="AA33" s="93"/>
+      <c r="AB33" s="93"/>
+      <c r="AC33" s="93"/>
+      <c r="AD33" s="93"/>
+      <c r="AE33" s="93"/>
+      <c r="AF33" s="93"/>
+      <c r="AG33" s="94"/>
+      <c r="AH33" s="94"/>
+      <c r="AI33" s="94"/>
+      <c r="AJ33" s="94"/>
+      <c r="AK33" s="94"/>
+      <c r="AL33" s="94"/>
+      <c r="AM33" s="94"/>
+      <c r="AN33" s="94"/>
+      <c r="AO33" s="94"/>
+      <c r="AP33" s="94"/>
+      <c r="AQ33" s="94"/>
+      <c r="AR33" s="94"/>
+      <c r="AS33" s="94"/>
+      <c r="AT33" s="94"/>
+      <c r="AU33" s="93"/>
+      <c r="AV33" s="93"/>
+      <c r="AW33" s="93"/>
+      <c r="AX33" s="94"/>
+      <c r="AY33" s="94"/>
+      <c r="AZ33" s="94"/>
+      <c r="BA33" s="94"/>
+      <c r="BB33" s="94"/>
+      <c r="BC33" s="93"/>
+      <c r="BD33" s="93"/>
+      <c r="BE33" s="93"/>
+      <c r="BF33" s="94"/>
+      <c r="BG33" s="94"/>
+      <c r="BH33" s="94"/>
+      <c r="BI33" s="94"/>
+      <c r="BJ33" s="94"/>
+      <c r="BK33" s="93"/>
+      <c r="BL33" s="93"/>
+      <c r="BM33" s="93"/>
+      <c r="BN33" s="93"/>
+      <c r="BO33" s="93"/>
+      <c r="BP33" s="93"/>
+      <c r="BQ33" s="93"/>
+      <c r="BR33" s="95"/>
+      <c r="BT33" s="64"/>
+    </row>
+    <row r="34" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A34" s="56"/>
+      <c r="C34" s="96"/>
+      <c r="BT34" s="64"/>
+    </row>
+    <row r="35" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="C35" s="96"/>
+    </row>
+    <row r="36" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A36" s="56"/>
+      <c r="C36" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="122"/>
-      <c r="E36" s="123" t="s">
+      <c r="D36" s="59"/>
+      <c r="E36" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
-      <c r="AF36" s="124"/>
-      <c r="AG36" s="124"/>
-      <c r="AH36" s="124"/>
-      <c r="AI36" s="124"/>
-      <c r="AJ36" s="125" t="s">
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="AK36" s="124"/>
-      <c r="AL36" s="124"/>
-      <c r="AM36" s="124"/>
-      <c r="AN36" s="124"/>
-      <c r="AO36" s="124"/>
-      <c r="AP36" s="124"/>
-      <c r="AQ36" s="124"/>
-      <c r="AR36" s="124"/>
-      <c r="AS36" s="124"/>
-      <c r="AT36" s="124"/>
-      <c r="AU36" s="124"/>
-      <c r="AV36" s="124"/>
-      <c r="AW36" s="124"/>
-      <c r="AX36" s="124"/>
-      <c r="AY36" s="124"/>
-      <c r="AZ36" s="124"/>
-      <c r="BA36" s="124"/>
-      <c r="BB36" s="125" t="s">
+      <c r="AK36" s="61"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="61"/>
+      <c r="AN36" s="61"/>
+      <c r="AO36" s="61"/>
+      <c r="AP36" s="61"/>
+      <c r="AQ36" s="61"/>
+      <c r="AR36" s="61"/>
+      <c r="AS36" s="61"/>
+      <c r="AT36" s="61"/>
+      <c r="AU36" s="61"/>
+      <c r="AV36" s="61"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
+      <c r="BB36" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="BC36" s="124"/>
-      <c r="BD36" s="124"/>
-      <c r="BE36" s="124"/>
-      <c r="BF36" s="124"/>
-      <c r="BG36" s="124"/>
-      <c r="BH36" s="124"/>
-      <c r="BI36" s="124"/>
-      <c r="BJ36" s="124"/>
-      <c r="BK36" s="124"/>
-      <c r="BL36" s="124"/>
-      <c r="BM36" s="124"/>
-      <c r="BN36" s="124"/>
-      <c r="BO36" s="124"/>
-      <c r="BP36" s="124"/>
-      <c r="BQ36" s="124"/>
-      <c r="BR36" s="126"/>
-      <c r="BT36" s="127"/>
-    </row>
-    <row r="37" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A37" s="119"/>
-      <c r="C37" s="128">
+      <c r="BC36" s="61"/>
+      <c r="BD36" s="61"/>
+      <c r="BE36" s="61"/>
+      <c r="BF36" s="61"/>
+      <c r="BG36" s="61"/>
+      <c r="BH36" s="61"/>
+      <c r="BI36" s="61"/>
+      <c r="BJ36" s="61"/>
+      <c r="BK36" s="61"/>
+      <c r="BL36" s="61"/>
+      <c r="BM36" s="61"/>
+      <c r="BN36" s="61"/>
+      <c r="BO36" s="61"/>
+      <c r="BP36" s="61"/>
+      <c r="BQ36" s="61"/>
+      <c r="BR36" s="63"/>
+      <c r="BT36" s="64"/>
+    </row>
+    <row r="37" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A37" s="56"/>
+      <c r="C37" s="166">
         <v>1</v>
       </c>
-      <c r="D37" s="129"/>
-      <c r="E37" s="130" t="s">
+      <c r="D37" s="167"/>
+      <c r="E37" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="F37" s="131"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="131"/>
-      <c r="J37" s="131"/>
-      <c r="K37" s="131"/>
-      <c r="L37" s="131"/>
-      <c r="M37" s="131"/>
-      <c r="N37" s="131"/>
-      <c r="O37" s="131"/>
-      <c r="P37" s="131"/>
-      <c r="Q37" s="131"/>
-      <c r="R37" s="131"/>
-      <c r="S37" s="131"/>
-      <c r="T37" s="131"/>
-      <c r="U37" s="131"/>
-      <c r="V37" s="131"/>
-      <c r="W37" s="131"/>
-      <c r="X37" s="131"/>
-      <c r="Y37" s="131"/>
-      <c r="Z37" s="131"/>
-      <c r="AA37" s="131"/>
-      <c r="AB37" s="131"/>
-      <c r="AC37" s="131"/>
-      <c r="AD37" s="131"/>
-      <c r="AE37" s="131"/>
-      <c r="AF37" s="131"/>
-      <c r="AG37" s="131"/>
-      <c r="AH37" s="131"/>
-      <c r="AI37" s="131"/>
-      <c r="AJ37" s="132" t="s">
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="66"/>
+      <c r="M37" s="66"/>
+      <c r="N37" s="66"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="66"/>
+      <c r="S37" s="66"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="66"/>
+      <c r="V37" s="66"/>
+      <c r="W37" s="66"/>
+      <c r="X37" s="66"/>
+      <c r="Y37" s="66"/>
+      <c r="Z37" s="66"/>
+      <c r="AA37" s="66"/>
+      <c r="AB37" s="66"/>
+      <c r="AC37" s="66"/>
+      <c r="AD37" s="66"/>
+      <c r="AE37" s="66"/>
+      <c r="AF37" s="66"/>
+      <c r="AG37" s="66"/>
+      <c r="AH37" s="66"/>
+      <c r="AI37" s="66"/>
+      <c r="AJ37" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AK37" s="131"/>
-      <c r="AL37" s="131"/>
-      <c r="AM37" s="131"/>
-      <c r="AN37" s="131"/>
-      <c r="AO37" s="131"/>
-      <c r="AP37" s="131"/>
-      <c r="AQ37" s="131"/>
-      <c r="AR37" s="131"/>
-      <c r="AS37" s="131"/>
-      <c r="AT37" s="131"/>
-      <c r="AU37" s="131"/>
-      <c r="AV37" s="131"/>
-      <c r="AW37" s="131"/>
-      <c r="AX37" s="131"/>
-      <c r="AY37" s="131"/>
-      <c r="AZ37" s="131"/>
-      <c r="BA37" s="131"/>
-      <c r="BB37" s="132" t="s">
+      <c r="AK37" s="66"/>
+      <c r="AL37" s="66"/>
+      <c r="AM37" s="66"/>
+      <c r="AN37" s="66"/>
+      <c r="AO37" s="66"/>
+      <c r="AP37" s="66"/>
+      <c r="AQ37" s="66"/>
+      <c r="AR37" s="66"/>
+      <c r="AS37" s="66"/>
+      <c r="AT37" s="66"/>
+      <c r="AU37" s="66"/>
+      <c r="AV37" s="66"/>
+      <c r="AW37" s="66"/>
+      <c r="AX37" s="66"/>
+      <c r="AY37" s="66"/>
+      <c r="AZ37" s="66"/>
+      <c r="BA37" s="66"/>
+      <c r="BB37" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="BC37" s="131"/>
-      <c r="BD37" s="131"/>
-      <c r="BE37" s="131"/>
-      <c r="BF37" s="131"/>
-      <c r="BG37" s="131"/>
-      <c r="BH37" s="131"/>
-      <c r="BI37" s="131"/>
-      <c r="BJ37" s="131"/>
-      <c r="BK37" s="131"/>
-      <c r="BL37" s="131"/>
-      <c r="BM37" s="131"/>
-      <c r="BN37" s="131"/>
-      <c r="BO37" s="131"/>
-      <c r="BP37" s="131"/>
-      <c r="BQ37" s="131"/>
-      <c r="BR37" s="133"/>
-      <c r="BT37" s="127"/>
-    </row>
-    <row r="38" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A38" s="119"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="135" t="s">
+      <c r="BC37" s="66"/>
+      <c r="BD37" s="66"/>
+      <c r="BE37" s="66"/>
+      <c r="BF37" s="66"/>
+      <c r="BG37" s="66"/>
+      <c r="BH37" s="66"/>
+      <c r="BI37" s="66"/>
+      <c r="BJ37" s="66"/>
+      <c r="BK37" s="66"/>
+      <c r="BL37" s="66"/>
+      <c r="BM37" s="66"/>
+      <c r="BN37" s="66"/>
+      <c r="BO37" s="66"/>
+      <c r="BP37" s="66"/>
+      <c r="BQ37" s="66"/>
+      <c r="BR37" s="68"/>
+      <c r="BT37" s="64"/>
+    </row>
+    <row r="38" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A38" s="56"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="137"/>
-      <c r="M38" s="131" t="s">
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="N38" s="131"/>
-      <c r="O38" s="131"/>
-      <c r="P38" s="131"/>
-      <c r="Q38" s="131"/>
-      <c r="R38" s="131"/>
-      <c r="S38" s="131"/>
-      <c r="T38" s="131"/>
-      <c r="U38" s="131"/>
-      <c r="V38" s="131"/>
-      <c r="W38" s="131"/>
-      <c r="X38" s="131"/>
-      <c r="Y38" s="131"/>
-      <c r="Z38" s="131"/>
-      <c r="AA38" s="131"/>
-      <c r="AB38" s="131"/>
-      <c r="AC38" s="131"/>
-      <c r="AD38" s="131"/>
-      <c r="AE38" s="131"/>
-      <c r="AF38" s="131"/>
-      <c r="AG38" s="131"/>
-      <c r="AH38" s="131"/>
-      <c r="AI38" s="131"/>
-      <c r="AJ38" s="131"/>
-      <c r="AK38" s="131"/>
-      <c r="AL38" s="131"/>
-      <c r="AM38" s="131"/>
-      <c r="AN38" s="131"/>
-      <c r="AO38" s="131"/>
-      <c r="AP38" s="131"/>
-      <c r="AQ38" s="131"/>
-      <c r="AR38" s="131"/>
-      <c r="AS38" s="131"/>
-      <c r="AT38" s="131"/>
-      <c r="AU38" s="131"/>
-      <c r="AV38" s="131"/>
-      <c r="AW38" s="131"/>
-      <c r="AX38" s="131"/>
-      <c r="AY38" s="131"/>
-      <c r="AZ38" s="131"/>
-      <c r="BA38" s="131"/>
-      <c r="BB38" s="131"/>
-      <c r="BC38" s="131"/>
-      <c r="BD38" s="131"/>
-      <c r="BE38" s="131"/>
-      <c r="BF38" s="131"/>
-      <c r="BG38" s="131"/>
-      <c r="BH38" s="131"/>
-      <c r="BI38" s="131"/>
-      <c r="BJ38" s="131"/>
-      <c r="BK38" s="131"/>
-      <c r="BL38" s="131"/>
-      <c r="BM38" s="131"/>
-      <c r="BN38" s="131"/>
-      <c r="BO38" s="131"/>
-      <c r="BP38" s="131"/>
-      <c r="BQ38" s="131"/>
-      <c r="BR38" s="133"/>
-    </row>
-    <row r="39" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A39" s="119"/>
-      <c r="B39" s="134"/>
-      <c r="C39" s="135" t="s">
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="66"/>
+      <c r="W38" s="66"/>
+      <c r="X38" s="66"/>
+      <c r="Y38" s="66"/>
+      <c r="Z38" s="66"/>
+      <c r="AA38" s="66"/>
+      <c r="AB38" s="66"/>
+      <c r="AC38" s="66"/>
+      <c r="AD38" s="66"/>
+      <c r="AE38" s="66"/>
+      <c r="AF38" s="66"/>
+      <c r="AG38" s="66"/>
+      <c r="AH38" s="66"/>
+      <c r="AI38" s="66"/>
+      <c r="AJ38" s="66"/>
+      <c r="AK38" s="66"/>
+      <c r="AL38" s="66"/>
+      <c r="AM38" s="66"/>
+      <c r="AN38" s="66"/>
+      <c r="AO38" s="66"/>
+      <c r="AP38" s="66"/>
+      <c r="AQ38" s="66"/>
+      <c r="AR38" s="66"/>
+      <c r="AS38" s="66"/>
+      <c r="AT38" s="66"/>
+      <c r="AU38" s="66"/>
+      <c r="AV38" s="66"/>
+      <c r="AW38" s="66"/>
+      <c r="AX38" s="66"/>
+      <c r="AY38" s="66"/>
+      <c r="AZ38" s="66"/>
+      <c r="BA38" s="66"/>
+      <c r="BB38" s="66"/>
+      <c r="BC38" s="66"/>
+      <c r="BD38" s="66"/>
+      <c r="BE38" s="66"/>
+      <c r="BF38" s="66"/>
+      <c r="BG38" s="66"/>
+      <c r="BH38" s="66"/>
+      <c r="BI38" s="66"/>
+      <c r="BJ38" s="66"/>
+      <c r="BK38" s="66"/>
+      <c r="BL38" s="66"/>
+      <c r="BM38" s="66"/>
+      <c r="BN38" s="66"/>
+      <c r="BO38" s="66"/>
+      <c r="BP38" s="66"/>
+      <c r="BQ38" s="66"/>
+      <c r="BR38" s="68"/>
+    </row>
+    <row r="39" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A39" s="56"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="136"/>
-      <c r="E39" s="136"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="136"/>
-      <c r="H39" s="136"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="137"/>
-      <c r="M39" s="131" t="s">
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="N39" s="131"/>
-      <c r="O39" s="131"/>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="131"/>
-      <c r="R39" s="131"/>
-      <c r="S39" s="131"/>
-      <c r="T39" s="131"/>
-      <c r="U39" s="131"/>
-      <c r="V39" s="131"/>
-      <c r="W39" s="131"/>
-      <c r="X39" s="131"/>
-      <c r="Y39" s="131"/>
-      <c r="Z39" s="131"/>
-      <c r="AA39" s="131"/>
-      <c r="AB39" s="131"/>
-      <c r="AC39" s="131"/>
-      <c r="AD39" s="131"/>
-      <c r="AE39" s="131"/>
-      <c r="AF39" s="131"/>
-      <c r="AG39" s="131"/>
-      <c r="AH39" s="131"/>
-      <c r="AI39" s="131"/>
-      <c r="AJ39" s="131"/>
-      <c r="AK39" s="131"/>
-      <c r="AL39" s="131"/>
-      <c r="AM39" s="131"/>
-      <c r="AN39" s="131"/>
-      <c r="AO39" s="131"/>
-      <c r="AP39" s="131"/>
-      <c r="AQ39" s="131"/>
-      <c r="AR39" s="131"/>
-      <c r="AS39" s="131"/>
-      <c r="AT39" s="131"/>
-      <c r="AU39" s="131"/>
-      <c r="AV39" s="131"/>
-      <c r="AW39" s="131"/>
-      <c r="AX39" s="131"/>
-      <c r="AY39" s="131"/>
-      <c r="AZ39" s="131"/>
-      <c r="BA39" s="131"/>
-      <c r="BB39" s="131"/>
-      <c r="BC39" s="131"/>
-      <c r="BD39" s="131"/>
-      <c r="BE39" s="131"/>
-      <c r="BF39" s="131"/>
-      <c r="BG39" s="131"/>
-      <c r="BH39" s="131"/>
-      <c r="BI39" s="131"/>
-      <c r="BJ39" s="131"/>
-      <c r="BK39" s="131"/>
-      <c r="BL39" s="131"/>
-      <c r="BM39" s="131"/>
-      <c r="BN39" s="131"/>
-      <c r="BO39" s="131"/>
-      <c r="BP39" s="131"/>
-      <c r="BQ39" s="131"/>
-      <c r="BR39" s="133"/>
-    </row>
-    <row r="40" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A40" s="119"/>
-      <c r="B40" s="134"/>
-      <c r="C40" s="138"/>
-      <c r="D40" s="139"/>
-      <c r="BR40" s="140"/>
-      <c r="BT40" s="127"/>
-    </row>
-    <row r="41" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A41" s="119"/>
-      <c r="B41" s="134"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="120" t="s">
+      <c r="N39" s="66"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="66"/>
+      <c r="Q39" s="66"/>
+      <c r="R39" s="66"/>
+      <c r="S39" s="66"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="66"/>
+      <c r="V39" s="66"/>
+      <c r="W39" s="66"/>
+      <c r="X39" s="66"/>
+      <c r="Y39" s="66"/>
+      <c r="Z39" s="66"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="66"/>
+      <c r="AC39" s="66"/>
+      <c r="AD39" s="66"/>
+      <c r="AE39" s="66"/>
+      <c r="AF39" s="66"/>
+      <c r="AG39" s="66"/>
+      <c r="AH39" s="66"/>
+      <c r="AI39" s="66"/>
+      <c r="AJ39" s="66"/>
+      <c r="AK39" s="66"/>
+      <c r="AL39" s="66"/>
+      <c r="AM39" s="66"/>
+      <c r="AN39" s="66"/>
+      <c r="AO39" s="66"/>
+      <c r="AP39" s="66"/>
+      <c r="AQ39" s="66"/>
+      <c r="AR39" s="66"/>
+      <c r="AS39" s="66"/>
+      <c r="AT39" s="66"/>
+      <c r="AU39" s="66"/>
+      <c r="AV39" s="66"/>
+      <c r="AW39" s="66"/>
+      <c r="AX39" s="66"/>
+      <c r="AY39" s="66"/>
+      <c r="AZ39" s="66"/>
+      <c r="BA39" s="66"/>
+      <c r="BB39" s="66"/>
+      <c r="BC39" s="66"/>
+      <c r="BD39" s="66"/>
+      <c r="BE39" s="66"/>
+      <c r="BF39" s="66"/>
+      <c r="BG39" s="66"/>
+      <c r="BH39" s="66"/>
+      <c r="BI39" s="66"/>
+      <c r="BJ39" s="66"/>
+      <c r="BK39" s="66"/>
+      <c r="BL39" s="66"/>
+      <c r="BM39" s="66"/>
+      <c r="BN39" s="66"/>
+      <c r="BO39" s="66"/>
+      <c r="BP39" s="66"/>
+      <c r="BQ39" s="66"/>
+      <c r="BR39" s="68"/>
+    </row>
+    <row r="40" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A40" s="56"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="74"/>
+      <c r="BR40" s="75"/>
+      <c r="BT40" s="64"/>
+    </row>
+    <row r="41" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A41" s="56"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="BR41" s="127"/>
-      <c r="BT41" s="127"/>
-    </row>
-    <row r="42" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A42" s="119"/>
-      <c r="B42" s="134"/>
-      <c r="C42" s="138"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="120" t="s">
+      <c r="BR41" s="64"/>
+      <c r="BT41" s="64"/>
+    </row>
+    <row r="42" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A42" s="56"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="73"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="BR42" s="127"/>
-      <c r="BT42" s="127"/>
-    </row>
-    <row r="43" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A43" s="119"/>
-      <c r="C43" s="138"/>
-      <c r="E43" s="142"/>
-      <c r="F43" s="143" t="s">
+      <c r="BR42" s="64"/>
+      <c r="BT42" s="64"/>
+    </row>
+    <row r="43" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A43" s="56"/>
+      <c r="C43" s="73"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G43" s="144"/>
-      <c r="H43" s="144"/>
-      <c r="I43" s="144"/>
-      <c r="J43" s="144"/>
-      <c r="K43" s="144"/>
-      <c r="L43" s="144"/>
-      <c r="M43" s="144"/>
-      <c r="N43" s="144"/>
-      <c r="O43" s="144"/>
-      <c r="P43" s="144"/>
-      <c r="Q43" s="144"/>
-      <c r="R43" s="144"/>
-      <c r="S43" s="144"/>
-      <c r="T43" s="144"/>
-      <c r="U43" s="144"/>
-      <c r="V43" s="144"/>
-      <c r="W43" s="144"/>
-      <c r="X43" s="144"/>
-      <c r="Y43" s="144"/>
-      <c r="Z43" s="144"/>
-      <c r="AA43" s="144"/>
-      <c r="AB43" s="144"/>
-      <c r="AC43" s="144"/>
-      <c r="AD43" s="144"/>
-      <c r="AE43" s="144"/>
-      <c r="AF43" s="144"/>
-      <c r="AG43" s="144"/>
-      <c r="AH43" s="144"/>
-      <c r="AI43" s="144"/>
-      <c r="AJ43" s="144"/>
-      <c r="AK43" s="144"/>
-      <c r="AL43" s="144"/>
-      <c r="AM43" s="144"/>
-      <c r="AN43" s="144"/>
-      <c r="AO43" s="144"/>
-      <c r="AP43" s="144"/>
-      <c r="AQ43" s="144"/>
-      <c r="AR43" s="144"/>
-      <c r="AS43" s="144"/>
-      <c r="AT43" s="144"/>
-      <c r="AU43" s="144"/>
-      <c r="AV43" s="144"/>
-      <c r="AW43" s="144"/>
-      <c r="AX43" s="144"/>
-      <c r="AY43" s="144"/>
-      <c r="AZ43" s="144"/>
-      <c r="BA43" s="144"/>
-      <c r="BB43" s="144"/>
-      <c r="BC43" s="144"/>
-      <c r="BD43" s="144"/>
-      <c r="BE43" s="144"/>
-      <c r="BF43" s="144"/>
-      <c r="BG43" s="144"/>
-      <c r="BH43" s="144"/>
-      <c r="BI43" s="144"/>
-      <c r="BJ43" s="144"/>
-      <c r="BK43" s="144"/>
-      <c r="BL43" s="145"/>
-      <c r="BR43" s="127"/>
-      <c r="BT43" s="127"/>
-    </row>
-    <row r="44" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A44" s="119"/>
-      <c r="C44" s="138"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="146" t="s">
+      <c r="G43" s="79"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="79"/>
+      <c r="R43" s="79"/>
+      <c r="S43" s="79"/>
+      <c r="T43" s="79"/>
+      <c r="U43" s="79"/>
+      <c r="V43" s="79"/>
+      <c r="W43" s="79"/>
+      <c r="X43" s="79"/>
+      <c r="Y43" s="79"/>
+      <c r="Z43" s="79"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="79"/>
+      <c r="AC43" s="79"/>
+      <c r="AD43" s="79"/>
+      <c r="AE43" s="79"/>
+      <c r="AF43" s="79"/>
+      <c r="AG43" s="79"/>
+      <c r="AH43" s="79"/>
+      <c r="AI43" s="79"/>
+      <c r="AJ43" s="79"/>
+      <c r="AK43" s="79"/>
+      <c r="AL43" s="79"/>
+      <c r="AM43" s="79"/>
+      <c r="AN43" s="79"/>
+      <c r="AO43" s="79"/>
+      <c r="AP43" s="79"/>
+      <c r="AQ43" s="79"/>
+      <c r="AR43" s="79"/>
+      <c r="AS43" s="79"/>
+      <c r="AT43" s="79"/>
+      <c r="AU43" s="79"/>
+      <c r="AV43" s="79"/>
+      <c r="AW43" s="79"/>
+      <c r="AX43" s="79"/>
+      <c r="AY43" s="79"/>
+      <c r="AZ43" s="79"/>
+      <c r="BA43" s="79"/>
+      <c r="BB43" s="79"/>
+      <c r="BC43" s="79"/>
+      <c r="BD43" s="79"/>
+      <c r="BE43" s="79"/>
+      <c r="BF43" s="79"/>
+      <c r="BG43" s="79"/>
+      <c r="BH43" s="79"/>
+      <c r="BI43" s="79"/>
+      <c r="BJ43" s="79"/>
+      <c r="BK43" s="79"/>
+      <c r="BL43" s="80"/>
+      <c r="BR43" s="64"/>
+      <c r="BT43" s="64"/>
+    </row>
+    <row r="44" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A44" s="56"/>
+      <c r="C44" s="73"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G44" s="147"/>
-      <c r="H44" s="147"/>
-      <c r="I44" s="147"/>
-      <c r="J44" s="147"/>
-      <c r="K44" s="148"/>
-      <c r="L44" s="132" t="s">
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="M44" s="131"/>
-      <c r="N44" s="131"/>
-      <c r="O44" s="131"/>
-      <c r="P44" s="131"/>
-      <c r="Q44" s="131"/>
-      <c r="R44" s="131"/>
-      <c r="S44" s="131"/>
-      <c r="T44" s="131"/>
-      <c r="U44" s="131"/>
-      <c r="V44" s="131"/>
-      <c r="W44" s="131"/>
-      <c r="X44" s="131"/>
-      <c r="Y44" s="131"/>
-      <c r="Z44" s="131"/>
-      <c r="AA44" s="131"/>
-      <c r="AB44" s="131"/>
-      <c r="AC44" s="131"/>
-      <c r="AD44" s="131"/>
-      <c r="AE44" s="131"/>
-      <c r="AF44" s="131"/>
-      <c r="AG44" s="131"/>
-      <c r="AH44" s="131"/>
-      <c r="AI44" s="131"/>
-      <c r="AJ44" s="131"/>
-      <c r="AK44" s="131"/>
-      <c r="AL44" s="131"/>
-      <c r="AM44" s="131"/>
-      <c r="AN44" s="131"/>
-      <c r="AO44" s="131"/>
-      <c r="AP44" s="131"/>
-      <c r="AQ44" s="131"/>
-      <c r="AR44" s="131"/>
-      <c r="AS44" s="131"/>
-      <c r="AT44" s="131"/>
-      <c r="AU44" s="131"/>
-      <c r="AV44" s="131"/>
-      <c r="AW44" s="131"/>
-      <c r="AX44" s="131"/>
-      <c r="AY44" s="131"/>
-      <c r="AZ44" s="131"/>
-      <c r="BA44" s="131"/>
-      <c r="BB44" s="131"/>
-      <c r="BC44" s="131"/>
-      <c r="BD44" s="131"/>
-      <c r="BE44" s="131"/>
-      <c r="BF44" s="131"/>
-      <c r="BG44" s="131"/>
-      <c r="BH44" s="131"/>
-      <c r="BI44" s="131"/>
-      <c r="BJ44" s="131"/>
-      <c r="BK44" s="131"/>
-      <c r="BL44" s="133"/>
-      <c r="BR44" s="149"/>
-      <c r="BT44" s="127"/>
-    </row>
-    <row r="45" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A45" s="119"/>
-      <c r="C45" s="138"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="150" t="s">
+      <c r="M44" s="66"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="66"/>
+      <c r="T44" s="66"/>
+      <c r="U44" s="66"/>
+      <c r="V44" s="66"/>
+      <c r="W44" s="66"/>
+      <c r="X44" s="66"/>
+      <c r="Y44" s="66"/>
+      <c r="Z44" s="66"/>
+      <c r="AA44" s="66"/>
+      <c r="AB44" s="66"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="66"/>
+      <c r="AE44" s="66"/>
+      <c r="AF44" s="66"/>
+      <c r="AG44" s="66"/>
+      <c r="AH44" s="66"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="66"/>
+      <c r="AK44" s="66"/>
+      <c r="AL44" s="66"/>
+      <c r="AM44" s="66"/>
+      <c r="AN44" s="66"/>
+      <c r="AO44" s="66"/>
+      <c r="AP44" s="66"/>
+      <c r="AQ44" s="66"/>
+      <c r="AR44" s="66"/>
+      <c r="AS44" s="66"/>
+      <c r="AT44" s="66"/>
+      <c r="AU44" s="66"/>
+      <c r="AV44" s="66"/>
+      <c r="AW44" s="66"/>
+      <c r="AX44" s="66"/>
+      <c r="AY44" s="66"/>
+      <c r="AZ44" s="66"/>
+      <c r="BA44" s="66"/>
+      <c r="BB44" s="66"/>
+      <c r="BC44" s="66"/>
+      <c r="BD44" s="66"/>
+      <c r="BE44" s="66"/>
+      <c r="BF44" s="66"/>
+      <c r="BG44" s="66"/>
+      <c r="BH44" s="66"/>
+      <c r="BI44" s="66"/>
+      <c r="BJ44" s="66"/>
+      <c r="BK44" s="66"/>
+      <c r="BL44" s="68"/>
+      <c r="BR44" s="84"/>
+      <c r="BT44" s="64"/>
+    </row>
+    <row r="45" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A45" s="56"/>
+      <c r="C45" s="73"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="168" t="s">
         <v>68</v>
       </c>
-      <c r="G45" s="151"/>
-      <c r="H45" s="151"/>
-      <c r="I45" s="151"/>
-      <c r="J45" s="151"/>
-      <c r="K45" s="152"/>
-      <c r="L45" s="132" t="s">
+      <c r="G45" s="169"/>
+      <c r="H45" s="169"/>
+      <c r="I45" s="169"/>
+      <c r="J45" s="169"/>
+      <c r="K45" s="170"/>
+      <c r="L45" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="M45" s="131"/>
-      <c r="N45" s="131"/>
-      <c r="O45" s="131"/>
-      <c r="P45" s="131"/>
-      <c r="Q45" s="131"/>
-      <c r="R45" s="131"/>
-      <c r="S45" s="131"/>
-      <c r="T45" s="131"/>
-      <c r="U45" s="131"/>
-      <c r="V45" s="131"/>
-      <c r="W45" s="131"/>
-      <c r="X45" s="131"/>
-      <c r="Y45" s="131"/>
-      <c r="Z45" s="131"/>
-      <c r="AA45" s="131"/>
-      <c r="AB45" s="131"/>
-      <c r="AC45" s="131"/>
-      <c r="AD45" s="131"/>
-      <c r="AE45" s="131"/>
-      <c r="AF45" s="131"/>
-      <c r="AG45" s="131"/>
-      <c r="AH45" s="131"/>
-      <c r="AI45" s="131"/>
-      <c r="AJ45" s="131"/>
-      <c r="AK45" s="132" t="s">
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="66"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="66"/>
+      <c r="U45" s="66"/>
+      <c r="V45" s="66"/>
+      <c r="W45" s="66"/>
+      <c r="X45" s="66"/>
+      <c r="Y45" s="66"/>
+      <c r="Z45" s="66"/>
+      <c r="AA45" s="66"/>
+      <c r="AB45" s="66"/>
+      <c r="AC45" s="66"/>
+      <c r="AD45" s="66"/>
+      <c r="AE45" s="66"/>
+      <c r="AF45" s="66"/>
+      <c r="AG45" s="66"/>
+      <c r="AH45" s="66"/>
+      <c r="AI45" s="66"/>
+      <c r="AJ45" s="66"/>
+      <c r="AK45" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AL45" s="131"/>
-      <c r="AM45" s="131"/>
-      <c r="AN45" s="131"/>
-      <c r="AO45" s="131"/>
-      <c r="AP45" s="131"/>
-      <c r="AQ45" s="131"/>
-      <c r="AR45" s="131"/>
-      <c r="AS45" s="131"/>
-      <c r="AT45" s="131"/>
-      <c r="AU45" s="131"/>
-      <c r="AV45" s="131"/>
-      <c r="AW45" s="131"/>
-      <c r="AX45" s="131"/>
-      <c r="AY45" s="131"/>
-      <c r="AZ45" s="131"/>
-      <c r="BA45" s="131"/>
-      <c r="BB45" s="131"/>
-      <c r="BC45" s="131"/>
-      <c r="BD45" s="131"/>
-      <c r="BE45" s="131"/>
-      <c r="BF45" s="131"/>
-      <c r="BG45" s="131"/>
-      <c r="BH45" s="131"/>
-      <c r="BI45" s="131"/>
-      <c r="BJ45" s="131"/>
-      <c r="BK45" s="131"/>
-      <c r="BL45" s="133"/>
-      <c r="BR45" s="127"/>
-      <c r="BT45" s="127"/>
-    </row>
-    <row r="46" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A46" s="119"/>
-      <c r="C46" s="138"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="154"/>
-      <c r="J46" s="154"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="132" t="s">
+      <c r="AL45" s="66"/>
+      <c r="AM45" s="66"/>
+      <c r="AN45" s="66"/>
+      <c r="AO45" s="66"/>
+      <c r="AP45" s="66"/>
+      <c r="AQ45" s="66"/>
+      <c r="AR45" s="66"/>
+      <c r="AS45" s="66"/>
+      <c r="AT45" s="66"/>
+      <c r="AU45" s="66"/>
+      <c r="AV45" s="66"/>
+      <c r="AW45" s="66"/>
+      <c r="AX45" s="66"/>
+      <c r="AY45" s="66"/>
+      <c r="AZ45" s="66"/>
+      <c r="BA45" s="66"/>
+      <c r="BB45" s="66"/>
+      <c r="BC45" s="66"/>
+      <c r="BD45" s="66"/>
+      <c r="BE45" s="66"/>
+      <c r="BF45" s="66"/>
+      <c r="BG45" s="66"/>
+      <c r="BH45" s="66"/>
+      <c r="BI45" s="66"/>
+      <c r="BJ45" s="66"/>
+      <c r="BK45" s="66"/>
+      <c r="BL45" s="68"/>
+      <c r="BR45" s="64"/>
+      <c r="BT45" s="64"/>
+    </row>
+    <row r="46" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A46" s="56"/>
+      <c r="C46" s="73"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="171"/>
+      <c r="G46" s="172"/>
+      <c r="H46" s="172"/>
+      <c r="I46" s="172"/>
+      <c r="J46" s="172"/>
+      <c r="K46" s="173"/>
+      <c r="L46" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="M46" s="131"/>
-      <c r="N46" s="131"/>
-      <c r="O46" s="131"/>
-      <c r="P46" s="131"/>
-      <c r="Q46" s="131"/>
-      <c r="R46" s="131"/>
-      <c r="S46" s="131"/>
-      <c r="T46" s="131"/>
-      <c r="U46" s="131"/>
-      <c r="V46" s="131"/>
-      <c r="W46" s="131"/>
-      <c r="X46" s="131"/>
-      <c r="Y46" s="131"/>
-      <c r="Z46" s="131"/>
-      <c r="AA46" s="131"/>
-      <c r="AB46" s="131"/>
-      <c r="AC46" s="131"/>
-      <c r="AD46" s="131"/>
-      <c r="AE46" s="131"/>
-      <c r="AF46" s="131"/>
-      <c r="AG46" s="131"/>
-      <c r="AH46" s="131"/>
-      <c r="AI46" s="131"/>
-      <c r="AJ46" s="131"/>
-      <c r="AK46" s="132" t="s">
+      <c r="M46" s="66"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="66"/>
+      <c r="Q46" s="66"/>
+      <c r="R46" s="66"/>
+      <c r="S46" s="66"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="66"/>
+      <c r="V46" s="66"/>
+      <c r="W46" s="66"/>
+      <c r="X46" s="66"/>
+      <c r="Y46" s="66"/>
+      <c r="Z46" s="66"/>
+      <c r="AA46" s="66"/>
+      <c r="AB46" s="66"/>
+      <c r="AC46" s="66"/>
+      <c r="AD46" s="66"/>
+      <c r="AE46" s="66"/>
+      <c r="AF46" s="66"/>
+      <c r="AG46" s="66"/>
+      <c r="AH46" s="66"/>
+      <c r="AI46" s="66"/>
+      <c r="AJ46" s="66"/>
+      <c r="AK46" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AL46" s="131"/>
-      <c r="AM46" s="131"/>
-      <c r="AN46" s="131"/>
-      <c r="AO46" s="131"/>
-      <c r="AP46" s="131"/>
-      <c r="AQ46" s="131"/>
-      <c r="AR46" s="131"/>
-      <c r="AS46" s="131"/>
-      <c r="AT46" s="131"/>
-      <c r="AU46" s="131"/>
-      <c r="AV46" s="131"/>
-      <c r="AW46" s="131"/>
-      <c r="AX46" s="131"/>
-      <c r="AY46" s="131"/>
-      <c r="AZ46" s="131"/>
-      <c r="BA46" s="131"/>
-      <c r="BB46" s="131"/>
-      <c r="BC46" s="131"/>
-      <c r="BD46" s="131"/>
-      <c r="BE46" s="131"/>
-      <c r="BF46" s="131"/>
-      <c r="BG46" s="131"/>
-      <c r="BH46" s="131"/>
-      <c r="BI46" s="131"/>
-      <c r="BJ46" s="131"/>
-      <c r="BK46" s="131"/>
-      <c r="BL46" s="133"/>
-      <c r="BR46" s="127"/>
-      <c r="BT46" s="127"/>
-    </row>
-    <row r="47" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A47" s="119"/>
-      <c r="C47" s="138"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="146" t="s">
+      <c r="AL46" s="66"/>
+      <c r="AM46" s="66"/>
+      <c r="AN46" s="66"/>
+      <c r="AO46" s="66"/>
+      <c r="AP46" s="66"/>
+      <c r="AQ46" s="66"/>
+      <c r="AR46" s="66"/>
+      <c r="AS46" s="66"/>
+      <c r="AT46" s="66"/>
+      <c r="AU46" s="66"/>
+      <c r="AV46" s="66"/>
+      <c r="AW46" s="66"/>
+      <c r="AX46" s="66"/>
+      <c r="AY46" s="66"/>
+      <c r="AZ46" s="66"/>
+      <c r="BA46" s="66"/>
+      <c r="BB46" s="66"/>
+      <c r="BC46" s="66"/>
+      <c r="BD46" s="66"/>
+      <c r="BE46" s="66"/>
+      <c r="BF46" s="66"/>
+      <c r="BG46" s="66"/>
+      <c r="BH46" s="66"/>
+      <c r="BI46" s="66"/>
+      <c r="BJ46" s="66"/>
+      <c r="BK46" s="66"/>
+      <c r="BL46" s="68"/>
+      <c r="BR46" s="64"/>
+      <c r="BT46" s="64"/>
+    </row>
+    <row r="47" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A47" s="56"/>
+      <c r="C47" s="73"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="147"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="148"/>
-      <c r="L47" s="132" t="s">
+      <c r="G47" s="82"/>
+      <c r="H47" s="82"/>
+      <c r="I47" s="82"/>
+      <c r="J47" s="82"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="M47" s="131"/>
-      <c r="N47" s="131"/>
-      <c r="O47" s="131"/>
-      <c r="P47" s="131"/>
-      <c r="Q47" s="131"/>
-      <c r="R47" s="131"/>
-      <c r="S47" s="131"/>
-      <c r="T47" s="131"/>
-      <c r="U47" s="131"/>
-      <c r="V47" s="131"/>
-      <c r="W47" s="131"/>
-      <c r="X47" s="131"/>
-      <c r="Y47" s="131"/>
-      <c r="Z47" s="131"/>
-      <c r="AA47" s="131"/>
-      <c r="AB47" s="131"/>
-      <c r="AC47" s="131"/>
-      <c r="AD47" s="131"/>
-      <c r="AE47" s="131"/>
-      <c r="AF47" s="131"/>
-      <c r="AG47" s="131"/>
-      <c r="AH47" s="131"/>
-      <c r="AI47" s="131"/>
-      <c r="AJ47" s="131"/>
-      <c r="AK47" s="131"/>
-      <c r="AL47" s="131"/>
-      <c r="AM47" s="131"/>
-      <c r="AN47" s="131"/>
-      <c r="AO47" s="131"/>
-      <c r="AP47" s="131"/>
-      <c r="AQ47" s="131"/>
-      <c r="AR47" s="131"/>
-      <c r="AS47" s="131"/>
-      <c r="AT47" s="131"/>
-      <c r="AU47" s="131"/>
-      <c r="AV47" s="131"/>
-      <c r="AW47" s="131"/>
-      <c r="AX47" s="131"/>
-      <c r="AY47" s="131"/>
-      <c r="AZ47" s="131"/>
-      <c r="BA47" s="131"/>
-      <c r="BB47" s="131"/>
-      <c r="BC47" s="131"/>
-      <c r="BD47" s="131"/>
-      <c r="BE47" s="131"/>
-      <c r="BF47" s="131"/>
-      <c r="BG47" s="131"/>
-      <c r="BH47" s="131"/>
-      <c r="BI47" s="131"/>
-      <c r="BJ47" s="131"/>
-      <c r="BK47" s="131"/>
-      <c r="BL47" s="133"/>
-      <c r="BR47" s="127"/>
-      <c r="BT47" s="127"/>
-    </row>
-    <row r="48" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A48" s="119"/>
-      <c r="C48" s="138"/>
-      <c r="E48" s="141"/>
-      <c r="BR48" s="127"/>
-      <c r="BT48" s="127"/>
-    </row>
-    <row r="49" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A49" s="119"/>
-      <c r="C49" s="138"/>
-      <c r="E49" s="141"/>
-      <c r="F49" s="120" t="s">
+      <c r="M47" s="66"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="66"/>
+      <c r="S47" s="66"/>
+      <c r="T47" s="66"/>
+      <c r="U47" s="66"/>
+      <c r="V47" s="66"/>
+      <c r="W47" s="66"/>
+      <c r="X47" s="66"/>
+      <c r="Y47" s="66"/>
+      <c r="Z47" s="66"/>
+      <c r="AA47" s="66"/>
+      <c r="AB47" s="66"/>
+      <c r="AC47" s="66"/>
+      <c r="AD47" s="66"/>
+      <c r="AE47" s="66"/>
+      <c r="AF47" s="66"/>
+      <c r="AG47" s="66"/>
+      <c r="AH47" s="66"/>
+      <c r="AI47" s="66"/>
+      <c r="AJ47" s="66"/>
+      <c r="AK47" s="66"/>
+      <c r="AL47" s="66"/>
+      <c r="AM47" s="66"/>
+      <c r="AN47" s="66"/>
+      <c r="AO47" s="66"/>
+      <c r="AP47" s="66"/>
+      <c r="AQ47" s="66"/>
+      <c r="AR47" s="66"/>
+      <c r="AS47" s="66"/>
+      <c r="AT47" s="66"/>
+      <c r="AU47" s="66"/>
+      <c r="AV47" s="66"/>
+      <c r="AW47" s="66"/>
+      <c r="AX47" s="66"/>
+      <c r="AY47" s="66"/>
+      <c r="AZ47" s="66"/>
+      <c r="BA47" s="66"/>
+      <c r="BB47" s="66"/>
+      <c r="BC47" s="66"/>
+      <c r="BD47" s="66"/>
+      <c r="BE47" s="66"/>
+      <c r="BF47" s="66"/>
+      <c r="BG47" s="66"/>
+      <c r="BH47" s="66"/>
+      <c r="BI47" s="66"/>
+      <c r="BJ47" s="66"/>
+      <c r="BK47" s="66"/>
+      <c r="BL47" s="68"/>
+      <c r="BR47" s="64"/>
+      <c r="BT47" s="64"/>
+    </row>
+    <row r="48" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A48" s="56"/>
+      <c r="C48" s="73"/>
+      <c r="E48" s="76"/>
+      <c r="BR48" s="64"/>
+      <c r="BT48" s="64"/>
+    </row>
+    <row r="49" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A49" s="56"/>
+      <c r="C49" s="73"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="BR49" s="127"/>
-      <c r="BT49" s="127"/>
-    </row>
-    <row r="50" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A50" s="119"/>
-      <c r="C50" s="138"/>
-      <c r="E50" s="141"/>
-      <c r="F50" s="143" t="s">
+      <c r="BR49" s="64"/>
+      <c r="BT49" s="64"/>
+    </row>
+    <row r="50" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A50" s="56"/>
+      <c r="C50" s="73"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G50" s="144"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="144"/>
-      <c r="J50" s="144"/>
-      <c r="K50" s="144"/>
-      <c r="L50" s="144"/>
-      <c r="M50" s="144"/>
-      <c r="N50" s="144"/>
-      <c r="O50" s="144"/>
-      <c r="P50" s="144"/>
-      <c r="Q50" s="144"/>
-      <c r="R50" s="144"/>
-      <c r="S50" s="144"/>
-      <c r="T50" s="144"/>
-      <c r="U50" s="144"/>
-      <c r="V50" s="144"/>
-      <c r="W50" s="144"/>
-      <c r="X50" s="144"/>
-      <c r="Y50" s="144"/>
-      <c r="Z50" s="144"/>
-      <c r="AA50" s="144"/>
-      <c r="AB50" s="144"/>
-      <c r="AC50" s="144"/>
-      <c r="AD50" s="144"/>
-      <c r="AE50" s="144"/>
-      <c r="AF50" s="144"/>
-      <c r="AG50" s="144"/>
-      <c r="AH50" s="144"/>
-      <c r="AI50" s="144"/>
-      <c r="AJ50" s="144"/>
-      <c r="AK50" s="144"/>
-      <c r="AL50" s="144"/>
-      <c r="AM50" s="144"/>
-      <c r="AN50" s="144"/>
-      <c r="AO50" s="144"/>
-      <c r="AP50" s="144"/>
-      <c r="AQ50" s="144"/>
-      <c r="AR50" s="144"/>
-      <c r="AS50" s="144"/>
-      <c r="AT50" s="144"/>
-      <c r="AU50" s="144"/>
-      <c r="AV50" s="144"/>
-      <c r="AW50" s="144"/>
-      <c r="AX50" s="144"/>
-      <c r="AY50" s="144"/>
-      <c r="AZ50" s="144"/>
-      <c r="BA50" s="144"/>
-      <c r="BB50" s="144"/>
-      <c r="BC50" s="144"/>
-      <c r="BD50" s="144"/>
-      <c r="BE50" s="144"/>
-      <c r="BF50" s="144"/>
-      <c r="BG50" s="144"/>
-      <c r="BH50" s="144"/>
-      <c r="BI50" s="144"/>
-      <c r="BJ50" s="144"/>
-      <c r="BK50" s="144"/>
-      <c r="BL50" s="145"/>
-      <c r="BR50" s="127"/>
-      <c r="BT50" s="127"/>
-    </row>
-    <row r="51" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A51" s="119"/>
-      <c r="B51" s="134"/>
-      <c r="C51" s="138"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="146" t="s">
+      <c r="G50" s="79"/>
+      <c r="H50" s="79"/>
+      <c r="I50" s="79"/>
+      <c r="J50" s="79"/>
+      <c r="K50" s="79"/>
+      <c r="L50" s="79"/>
+      <c r="M50" s="79"/>
+      <c r="N50" s="79"/>
+      <c r="O50" s="79"/>
+      <c r="P50" s="79"/>
+      <c r="Q50" s="79"/>
+      <c r="R50" s="79"/>
+      <c r="S50" s="79"/>
+      <c r="T50" s="79"/>
+      <c r="U50" s="79"/>
+      <c r="V50" s="79"/>
+      <c r="W50" s="79"/>
+      <c r="X50" s="79"/>
+      <c r="Y50" s="79"/>
+      <c r="Z50" s="79"/>
+      <c r="AA50" s="79"/>
+      <c r="AB50" s="79"/>
+      <c r="AC50" s="79"/>
+      <c r="AD50" s="79"/>
+      <c r="AE50" s="79"/>
+      <c r="AF50" s="79"/>
+      <c r="AG50" s="79"/>
+      <c r="AH50" s="79"/>
+      <c r="AI50" s="79"/>
+      <c r="AJ50" s="79"/>
+      <c r="AK50" s="79"/>
+      <c r="AL50" s="79"/>
+      <c r="AM50" s="79"/>
+      <c r="AN50" s="79"/>
+      <c r="AO50" s="79"/>
+      <c r="AP50" s="79"/>
+      <c r="AQ50" s="79"/>
+      <c r="AR50" s="79"/>
+      <c r="AS50" s="79"/>
+      <c r="AT50" s="79"/>
+      <c r="AU50" s="79"/>
+      <c r="AV50" s="79"/>
+      <c r="AW50" s="79"/>
+      <c r="AX50" s="79"/>
+      <c r="AY50" s="79"/>
+      <c r="AZ50" s="79"/>
+      <c r="BA50" s="79"/>
+      <c r="BB50" s="79"/>
+      <c r="BC50" s="79"/>
+      <c r="BD50" s="79"/>
+      <c r="BE50" s="79"/>
+      <c r="BF50" s="79"/>
+      <c r="BG50" s="79"/>
+      <c r="BH50" s="79"/>
+      <c r="BI50" s="79"/>
+      <c r="BJ50" s="79"/>
+      <c r="BK50" s="79"/>
+      <c r="BL50" s="80"/>
+      <c r="BR50" s="64"/>
+      <c r="BT50" s="64"/>
+    </row>
+    <row r="51" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A51" s="56"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="73"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G51" s="147"/>
-      <c r="H51" s="147"/>
-      <c r="I51" s="147"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="148"/>
-      <c r="L51" s="132" t="s">
+      <c r="G51" s="82"/>
+      <c r="H51" s="82"/>
+      <c r="I51" s="82"/>
+      <c r="J51" s="82"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M51" s="131"/>
-      <c r="N51" s="131"/>
-      <c r="O51" s="131"/>
-      <c r="P51" s="131"/>
-      <c r="Q51" s="131"/>
-      <c r="R51" s="131"/>
-      <c r="S51" s="131"/>
-      <c r="T51" s="131"/>
-      <c r="U51" s="131"/>
-      <c r="V51" s="131"/>
-      <c r="W51" s="131"/>
-      <c r="X51" s="131"/>
-      <c r="Y51" s="131"/>
-      <c r="Z51" s="131"/>
-      <c r="AA51" s="131"/>
-      <c r="AB51" s="131"/>
-      <c r="AC51" s="131"/>
-      <c r="AD51" s="131"/>
-      <c r="AE51" s="131"/>
-      <c r="AF51" s="131"/>
-      <c r="AG51" s="131"/>
-      <c r="AH51" s="131"/>
-      <c r="AI51" s="131"/>
-      <c r="AJ51" s="131"/>
-      <c r="AK51" s="131"/>
-      <c r="AL51" s="131"/>
-      <c r="AM51" s="131"/>
-      <c r="AN51" s="131"/>
-      <c r="AO51" s="131"/>
-      <c r="AP51" s="131"/>
-      <c r="AQ51" s="131"/>
-      <c r="AR51" s="131"/>
-      <c r="AS51" s="131"/>
-      <c r="AT51" s="131"/>
-      <c r="AU51" s="131"/>
-      <c r="AV51" s="131"/>
-      <c r="AW51" s="131"/>
-      <c r="AX51" s="131"/>
-      <c r="AY51" s="131"/>
-      <c r="AZ51" s="131"/>
-      <c r="BA51" s="131"/>
-      <c r="BB51" s="131"/>
-      <c r="BC51" s="131"/>
-      <c r="BD51" s="131"/>
-      <c r="BE51" s="131"/>
-      <c r="BF51" s="131"/>
-      <c r="BG51" s="131"/>
-      <c r="BH51" s="131"/>
-      <c r="BI51" s="131"/>
-      <c r="BJ51" s="131"/>
-      <c r="BK51" s="131"/>
-      <c r="BL51" s="133"/>
-      <c r="BR51" s="149"/>
-      <c r="BT51" s="127"/>
-    </row>
-    <row r="52" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A52" s="119"/>
-      <c r="B52" s="134"/>
-      <c r="C52" s="138"/>
-      <c r="E52" s="141"/>
-      <c r="F52" s="156" t="s">
+      <c r="M51" s="66"/>
+      <c r="N51" s="66"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="66"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="66"/>
+      <c r="U51" s="66"/>
+      <c r="V51" s="66"/>
+      <c r="W51" s="66"/>
+      <c r="X51" s="66"/>
+      <c r="Y51" s="66"/>
+      <c r="Z51" s="66"/>
+      <c r="AA51" s="66"/>
+      <c r="AB51" s="66"/>
+      <c r="AC51" s="66"/>
+      <c r="AD51" s="66"/>
+      <c r="AE51" s="66"/>
+      <c r="AF51" s="66"/>
+      <c r="AG51" s="66"/>
+      <c r="AH51" s="66"/>
+      <c r="AI51" s="66"/>
+      <c r="AJ51" s="66"/>
+      <c r="AK51" s="66"/>
+      <c r="AL51" s="66"/>
+      <c r="AM51" s="66"/>
+      <c r="AN51" s="66"/>
+      <c r="AO51" s="66"/>
+      <c r="AP51" s="66"/>
+      <c r="AQ51" s="66"/>
+      <c r="AR51" s="66"/>
+      <c r="AS51" s="66"/>
+      <c r="AT51" s="66"/>
+      <c r="AU51" s="66"/>
+      <c r="AV51" s="66"/>
+      <c r="AW51" s="66"/>
+      <c r="AX51" s="66"/>
+      <c r="AY51" s="66"/>
+      <c r="AZ51" s="66"/>
+      <c r="BA51" s="66"/>
+      <c r="BB51" s="66"/>
+      <c r="BC51" s="66"/>
+      <c r="BD51" s="66"/>
+      <c r="BE51" s="66"/>
+      <c r="BF51" s="66"/>
+      <c r="BG51" s="66"/>
+      <c r="BH51" s="66"/>
+      <c r="BI51" s="66"/>
+      <c r="BJ51" s="66"/>
+      <c r="BK51" s="66"/>
+      <c r="BL51" s="68"/>
+      <c r="BR51" s="84"/>
+      <c r="BT51" s="64"/>
+    </row>
+    <row r="52" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A52" s="56"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="73"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="G52" s="157"/>
-      <c r="H52" s="157"/>
-      <c r="I52" s="157"/>
-      <c r="J52" s="157"/>
-      <c r="K52" s="158"/>
-      <c r="L52" s="132" t="s">
+      <c r="G52" s="86"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="86"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M52" s="131"/>
-      <c r="N52" s="131"/>
-      <c r="O52" s="131"/>
-      <c r="P52" s="131"/>
-      <c r="Q52" s="131"/>
-      <c r="R52" s="131"/>
-      <c r="S52" s="131"/>
-      <c r="T52" s="131"/>
-      <c r="U52" s="131"/>
-      <c r="V52" s="131"/>
-      <c r="W52" s="131"/>
-      <c r="X52" s="131"/>
-      <c r="Y52" s="131"/>
-      <c r="Z52" s="131"/>
-      <c r="AA52" s="131"/>
-      <c r="AB52" s="131"/>
-      <c r="AC52" s="131"/>
-      <c r="AD52" s="131"/>
-      <c r="AE52" s="131"/>
-      <c r="AF52" s="131"/>
-      <c r="AG52" s="131"/>
-      <c r="AH52" s="131"/>
-      <c r="AI52" s="131"/>
-      <c r="AJ52" s="131"/>
-      <c r="AK52" s="132" t="s">
+      <c r="M52" s="66"/>
+      <c r="N52" s="66"/>
+      <c r="O52" s="66"/>
+      <c r="P52" s="66"/>
+      <c r="Q52" s="66"/>
+      <c r="R52" s="66"/>
+      <c r="S52" s="66"/>
+      <c r="T52" s="66"/>
+      <c r="U52" s="66"/>
+      <c r="V52" s="66"/>
+      <c r="W52" s="66"/>
+      <c r="X52" s="66"/>
+      <c r="Y52" s="66"/>
+      <c r="Z52" s="66"/>
+      <c r="AA52" s="66"/>
+      <c r="AB52" s="66"/>
+      <c r="AC52" s="66"/>
+      <c r="AD52" s="66"/>
+      <c r="AE52" s="66"/>
+      <c r="AF52" s="66"/>
+      <c r="AG52" s="66"/>
+      <c r="AH52" s="66"/>
+      <c r="AI52" s="66"/>
+      <c r="AJ52" s="66"/>
+      <c r="AK52" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="AL52" s="131"/>
-      <c r="AM52" s="131"/>
-      <c r="AN52" s="131"/>
-      <c r="AO52" s="131"/>
-      <c r="AP52" s="131"/>
-      <c r="AQ52" s="131"/>
-      <c r="AR52" s="131"/>
-      <c r="AS52" s="131"/>
-      <c r="AT52" s="131"/>
-      <c r="AU52" s="131"/>
-      <c r="AV52" s="131"/>
-      <c r="AW52" s="131"/>
-      <c r="AX52" s="131"/>
-      <c r="AY52" s="131"/>
-      <c r="AZ52" s="131"/>
-      <c r="BA52" s="131"/>
-      <c r="BB52" s="131"/>
-      <c r="BC52" s="131"/>
-      <c r="BD52" s="131"/>
-      <c r="BE52" s="131"/>
-      <c r="BF52" s="131"/>
-      <c r="BG52" s="131"/>
-      <c r="BH52" s="131"/>
-      <c r="BI52" s="131"/>
-      <c r="BJ52" s="131"/>
-      <c r="BK52" s="131"/>
-      <c r="BL52" s="133"/>
-      <c r="BR52" s="149"/>
-      <c r="BT52" s="127"/>
-    </row>
-    <row r="53" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A53" s="119"/>
-      <c r="B53" s="134"/>
-      <c r="C53" s="138"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="146" t="s">
+      <c r="AL52" s="66"/>
+      <c r="AM52" s="66"/>
+      <c r="AN52" s="66"/>
+      <c r="AO52" s="66"/>
+      <c r="AP52" s="66"/>
+      <c r="AQ52" s="66"/>
+      <c r="AR52" s="66"/>
+      <c r="AS52" s="66"/>
+      <c r="AT52" s="66"/>
+      <c r="AU52" s="66"/>
+      <c r="AV52" s="66"/>
+      <c r="AW52" s="66"/>
+      <c r="AX52" s="66"/>
+      <c r="AY52" s="66"/>
+      <c r="AZ52" s="66"/>
+      <c r="BA52" s="66"/>
+      <c r="BB52" s="66"/>
+      <c r="BC52" s="66"/>
+      <c r="BD52" s="66"/>
+      <c r="BE52" s="66"/>
+      <c r="BF52" s="66"/>
+      <c r="BG52" s="66"/>
+      <c r="BH52" s="66"/>
+      <c r="BI52" s="66"/>
+      <c r="BJ52" s="66"/>
+      <c r="BK52" s="66"/>
+      <c r="BL52" s="68"/>
+      <c r="BR52" s="84"/>
+      <c r="BT52" s="64"/>
+    </row>
+    <row r="53" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A53" s="56"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="73"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G53" s="147"/>
-      <c r="H53" s="147"/>
-      <c r="I53" s="147"/>
-      <c r="J53" s="147"/>
-      <c r="K53" s="148"/>
-      <c r="L53" s="132" t="s">
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="M53" s="131"/>
-      <c r="N53" s="131"/>
-      <c r="O53" s="131"/>
-      <c r="P53" s="131"/>
-      <c r="Q53" s="131"/>
-      <c r="R53" s="131"/>
-      <c r="S53" s="131"/>
-      <c r="T53" s="131"/>
-      <c r="U53" s="131"/>
-      <c r="V53" s="131"/>
-      <c r="W53" s="131"/>
-      <c r="X53" s="131"/>
-      <c r="Y53" s="131"/>
-      <c r="Z53" s="131"/>
-      <c r="AA53" s="131"/>
-      <c r="AB53" s="131"/>
-      <c r="AC53" s="131"/>
-      <c r="AD53" s="131"/>
-      <c r="AE53" s="131"/>
-      <c r="AF53" s="131"/>
-      <c r="AG53" s="131"/>
-      <c r="AH53" s="131"/>
-      <c r="AI53" s="131"/>
-      <c r="AJ53" s="131"/>
-      <c r="AK53" s="131"/>
-      <c r="AL53" s="131"/>
-      <c r="AM53" s="131"/>
-      <c r="AN53" s="131"/>
-      <c r="AO53" s="131"/>
-      <c r="AP53" s="131"/>
-      <c r="AQ53" s="131"/>
-      <c r="AR53" s="131"/>
-      <c r="AS53" s="131"/>
-      <c r="AT53" s="131"/>
-      <c r="AU53" s="131"/>
-      <c r="AV53" s="131"/>
-      <c r="AW53" s="131"/>
-      <c r="AX53" s="131"/>
-      <c r="AY53" s="131"/>
-      <c r="AZ53" s="131"/>
-      <c r="BA53" s="131"/>
-      <c r="BB53" s="131"/>
-      <c r="BC53" s="131"/>
-      <c r="BD53" s="131"/>
-      <c r="BE53" s="131"/>
-      <c r="BF53" s="131"/>
-      <c r="BG53" s="131"/>
-      <c r="BH53" s="131"/>
-      <c r="BI53" s="131"/>
-      <c r="BJ53" s="131"/>
-      <c r="BK53" s="131"/>
-      <c r="BL53" s="133"/>
-      <c r="BR53" s="149"/>
-      <c r="BT53" s="127"/>
-    </row>
-    <row r="54" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A54" s="119"/>
-      <c r="B54" s="134"/>
-      <c r="C54" s="138"/>
-      <c r="E54" s="141"/>
-      <c r="BR54" s="149"/>
-      <c r="BT54" s="127"/>
-    </row>
-    <row r="55" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A55" s="119"/>
-      <c r="B55" s="134"/>
-      <c r="C55" s="138"/>
-      <c r="E55" s="141"/>
-      <c r="G55" s="161"/>
-      <c r="BR55" s="149"/>
-      <c r="BT55" s="127"/>
-    </row>
-    <row r="56" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A56" s="119"/>
-      <c r="B56" s="134"/>
-      <c r="C56" s="138"/>
-      <c r="E56" s="141"/>
-      <c r="G56" s="161"/>
-      <c r="BR56" s="149"/>
-      <c r="BT56" s="127"/>
-    </row>
-    <row r="57" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A57" s="119"/>
-      <c r="B57" s="134"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="141">
+      <c r="M53" s="66"/>
+      <c r="N53" s="66"/>
+      <c r="O53" s="66"/>
+      <c r="P53" s="66"/>
+      <c r="Q53" s="66"/>
+      <c r="R53" s="66"/>
+      <c r="S53" s="66"/>
+      <c r="T53" s="66"/>
+      <c r="U53" s="66"/>
+      <c r="V53" s="66"/>
+      <c r="W53" s="66"/>
+      <c r="X53" s="66"/>
+      <c r="Y53" s="66"/>
+      <c r="Z53" s="66"/>
+      <c r="AA53" s="66"/>
+      <c r="AB53" s="66"/>
+      <c r="AC53" s="66"/>
+      <c r="AD53" s="66"/>
+      <c r="AE53" s="66"/>
+      <c r="AF53" s="66"/>
+      <c r="AG53" s="66"/>
+      <c r="AH53" s="66"/>
+      <c r="AI53" s="66"/>
+      <c r="AJ53" s="66"/>
+      <c r="AK53" s="66"/>
+      <c r="AL53" s="66"/>
+      <c r="AM53" s="66"/>
+      <c r="AN53" s="66"/>
+      <c r="AO53" s="66"/>
+      <c r="AP53" s="66"/>
+      <c r="AQ53" s="66"/>
+      <c r="AR53" s="66"/>
+      <c r="AS53" s="66"/>
+      <c r="AT53" s="66"/>
+      <c r="AU53" s="66"/>
+      <c r="AV53" s="66"/>
+      <c r="AW53" s="66"/>
+      <c r="AX53" s="66"/>
+      <c r="AY53" s="66"/>
+      <c r="AZ53" s="66"/>
+      <c r="BA53" s="66"/>
+      <c r="BB53" s="66"/>
+      <c r="BC53" s="66"/>
+      <c r="BD53" s="66"/>
+      <c r="BE53" s="66"/>
+      <c r="BF53" s="66"/>
+      <c r="BG53" s="66"/>
+      <c r="BH53" s="66"/>
+      <c r="BI53" s="66"/>
+      <c r="BJ53" s="66"/>
+      <c r="BK53" s="66"/>
+      <c r="BL53" s="68"/>
+      <c r="BR53" s="84"/>
+      <c r="BT53" s="64"/>
+    </row>
+    <row r="54" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A54" s="56"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="73"/>
+      <c r="E54" s="76"/>
+      <c r="BR54" s="84"/>
+      <c r="BT54" s="64"/>
+    </row>
+    <row r="55" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A55" s="56"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="73"/>
+      <c r="E55" s="76"/>
+      <c r="G55" s="89"/>
+      <c r="BR55" s="84"/>
+      <c r="BT55" s="64"/>
+    </row>
+    <row r="56" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A56" s="56"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="73"/>
+      <c r="E56" s="76"/>
+      <c r="G56" s="89"/>
+      <c r="BR56" s="84"/>
+      <c r="BT56" s="64"/>
+    </row>
+    <row r="57" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A57" s="56"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="76">
         <v>2</v>
       </c>
-      <c r="E57" s="120" t="s">
+      <c r="E57" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="BR57" s="149"/>
-      <c r="BT57" s="127"/>
-    </row>
-    <row r="58" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A58" s="119"/>
-      <c r="B58" s="134"/>
-      <c r="C58" s="138"/>
-      <c r="D58" s="141"/>
-      <c r="E58" s="146" t="s">
+      <c r="BR57" s="84"/>
+      <c r="BT57" s="64"/>
+    </row>
+    <row r="58" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A58" s="56"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="136"/>
-      <c r="G58" s="136"/>
-      <c r="H58" s="136"/>
-      <c r="I58" s="136"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="132" t="s">
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="71"/>
+      <c r="K58" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="L58" s="131"/>
-      <c r="M58" s="131"/>
-      <c r="N58" s="131"/>
-      <c r="O58" s="131"/>
-      <c r="P58" s="131"/>
-      <c r="Q58" s="131"/>
-      <c r="R58" s="131"/>
-      <c r="S58" s="131"/>
-      <c r="T58" s="131"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="131"/>
-      <c r="W58" s="131"/>
-      <c r="X58" s="131"/>
-      <c r="Y58" s="131"/>
-      <c r="Z58" s="131"/>
-      <c r="AA58" s="131"/>
-      <c r="AB58" s="131"/>
-      <c r="AC58" s="131"/>
-      <c r="AD58" s="131"/>
-      <c r="AE58" s="131"/>
-      <c r="AF58" s="131"/>
-      <c r="AG58" s="131"/>
-      <c r="AH58" s="131"/>
-      <c r="AI58" s="131"/>
-      <c r="AJ58" s="131"/>
-      <c r="AK58" s="131"/>
-      <c r="AL58" s="131"/>
-      <c r="AM58" s="131"/>
-      <c r="AN58" s="131"/>
-      <c r="AO58" s="131"/>
-      <c r="AP58" s="131"/>
-      <c r="AQ58" s="131"/>
-      <c r="AR58" s="131"/>
-      <c r="AS58" s="131"/>
-      <c r="AT58" s="131"/>
-      <c r="AU58" s="131"/>
-      <c r="AV58" s="131"/>
-      <c r="AW58" s="131"/>
-      <c r="AX58" s="131"/>
-      <c r="AY58" s="131"/>
-      <c r="AZ58" s="131"/>
-      <c r="BA58" s="131"/>
-      <c r="BB58" s="131"/>
-      <c r="BC58" s="131"/>
-      <c r="BD58" s="131"/>
-      <c r="BE58" s="131"/>
-      <c r="BF58" s="131"/>
-      <c r="BG58" s="131"/>
-      <c r="BH58" s="131"/>
-      <c r="BI58" s="131"/>
-      <c r="BJ58" s="131"/>
-      <c r="BK58" s="131"/>
-      <c r="BL58" s="133"/>
-      <c r="BR58" s="149"/>
-      <c r="BT58" s="127"/>
-    </row>
-    <row r="59" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A59" s="119"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="138"/>
-      <c r="D59" s="141"/>
-      <c r="E59" s="135" t="s">
+      <c r="L58" s="66"/>
+      <c r="M58" s="66"/>
+      <c r="N58" s="66"/>
+      <c r="O58" s="66"/>
+      <c r="P58" s="66"/>
+      <c r="Q58" s="66"/>
+      <c r="R58" s="66"/>
+      <c r="S58" s="66"/>
+      <c r="T58" s="66"/>
+      <c r="U58" s="66"/>
+      <c r="V58" s="66"/>
+      <c r="W58" s="66"/>
+      <c r="X58" s="66"/>
+      <c r="Y58" s="66"/>
+      <c r="Z58" s="66"/>
+      <c r="AA58" s="66"/>
+      <c r="AB58" s="66"/>
+      <c r="AC58" s="66"/>
+      <c r="AD58" s="66"/>
+      <c r="AE58" s="66"/>
+      <c r="AF58" s="66"/>
+      <c r="AG58" s="66"/>
+      <c r="AH58" s="66"/>
+      <c r="AI58" s="66"/>
+      <c r="AJ58" s="66"/>
+      <c r="AK58" s="66"/>
+      <c r="AL58" s="66"/>
+      <c r="AM58" s="66"/>
+      <c r="AN58" s="66"/>
+      <c r="AO58" s="66"/>
+      <c r="AP58" s="66"/>
+      <c r="AQ58" s="66"/>
+      <c r="AR58" s="66"/>
+      <c r="AS58" s="66"/>
+      <c r="AT58" s="66"/>
+      <c r="AU58" s="66"/>
+      <c r="AV58" s="66"/>
+      <c r="AW58" s="66"/>
+      <c r="AX58" s="66"/>
+      <c r="AY58" s="66"/>
+      <c r="AZ58" s="66"/>
+      <c r="BA58" s="66"/>
+      <c r="BB58" s="66"/>
+      <c r="BC58" s="66"/>
+      <c r="BD58" s="66"/>
+      <c r="BE58" s="66"/>
+      <c r="BF58" s="66"/>
+      <c r="BG58" s="66"/>
+      <c r="BH58" s="66"/>
+      <c r="BI58" s="66"/>
+      <c r="BJ58" s="66"/>
+      <c r="BK58" s="66"/>
+      <c r="BL58" s="68"/>
+      <c r="BR58" s="84"/>
+      <c r="BT58" s="64"/>
+    </row>
+    <row r="59" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A59" s="56"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F59" s="135" t="s">
+      <c r="F59" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G59" s="136"/>
-      <c r="H59" s="136"/>
-      <c r="I59" s="136"/>
-      <c r="J59" s="136"/>
-      <c r="K59" s="136"/>
-      <c r="L59" s="136"/>
-      <c r="M59" s="136"/>
-      <c r="N59" s="136"/>
-      <c r="O59" s="136"/>
-      <c r="P59" s="136"/>
-      <c r="Q59" s="136"/>
-      <c r="R59" s="136"/>
-      <c r="S59" s="136"/>
-      <c r="T59" s="136"/>
-      <c r="U59" s="135" t="s">
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="71"/>
+      <c r="K59" s="71"/>
+      <c r="L59" s="71"/>
+      <c r="M59" s="71"/>
+      <c r="N59" s="71"/>
+      <c r="O59" s="71"/>
+      <c r="P59" s="71"/>
+      <c r="Q59" s="71"/>
+      <c r="R59" s="71"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="71"/>
+      <c r="U59" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="V59" s="136"/>
-      <c r="W59" s="136"/>
-      <c r="X59" s="136"/>
-      <c r="Y59" s="136"/>
-      <c r="Z59" s="136"/>
-      <c r="AA59" s="136"/>
-      <c r="AB59" s="136"/>
-      <c r="AC59" s="136"/>
-      <c r="AD59" s="136"/>
-      <c r="AE59" s="136"/>
-      <c r="AF59" s="137"/>
-      <c r="AG59" s="135" t="s">
+      <c r="V59" s="71"/>
+      <c r="W59" s="71"/>
+      <c r="X59" s="71"/>
+      <c r="Y59" s="71"/>
+      <c r="Z59" s="71"/>
+      <c r="AA59" s="71"/>
+      <c r="AB59" s="71"/>
+      <c r="AC59" s="71"/>
+      <c r="AD59" s="71"/>
+      <c r="AE59" s="71"/>
+      <c r="AF59" s="72"/>
+      <c r="AG59" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="AH59" s="136"/>
-      <c r="AI59" s="136"/>
-      <c r="AJ59" s="136"/>
-      <c r="AK59" s="136"/>
-      <c r="AL59" s="136"/>
-      <c r="AM59" s="136"/>
-      <c r="AN59" s="136"/>
-      <c r="AO59" s="136"/>
-      <c r="AP59" s="136"/>
-      <c r="AQ59" s="136"/>
-      <c r="AR59" s="137"/>
-      <c r="AS59" s="136" t="s">
+      <c r="AH59" s="71"/>
+      <c r="AI59" s="71"/>
+      <c r="AJ59" s="71"/>
+      <c r="AK59" s="71"/>
+      <c r="AL59" s="71"/>
+      <c r="AM59" s="71"/>
+      <c r="AN59" s="71"/>
+      <c r="AO59" s="71"/>
+      <c r="AP59" s="71"/>
+      <c r="AQ59" s="71"/>
+      <c r="AR59" s="72"/>
+      <c r="AS59" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="AT59" s="136"/>
-      <c r="AU59" s="136"/>
-      <c r="AV59" s="136"/>
-      <c r="AW59" s="136"/>
-      <c r="AX59" s="136"/>
-      <c r="AY59" s="136"/>
-      <c r="AZ59" s="136"/>
-      <c r="BA59" s="136"/>
-      <c r="BB59" s="136"/>
-      <c r="BC59" s="136"/>
-      <c r="BD59" s="136"/>
-      <c r="BE59" s="136"/>
-      <c r="BF59" s="136"/>
-      <c r="BG59" s="136"/>
-      <c r="BH59" s="136"/>
-      <c r="BI59" s="136"/>
-      <c r="BJ59" s="136"/>
-      <c r="BK59" s="136"/>
-      <c r="BL59" s="137"/>
-      <c r="BR59" s="149"/>
-      <c r="BT59" s="127"/>
-    </row>
-    <row r="60" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A60" s="119"/>
-      <c r="B60" s="134"/>
-      <c r="C60" s="138"/>
-      <c r="D60" s="141"/>
-      <c r="E60" s="159">
+      <c r="AT59" s="71"/>
+      <c r="AU59" s="71"/>
+      <c r="AV59" s="71"/>
+      <c r="AW59" s="71"/>
+      <c r="AX59" s="71"/>
+      <c r="AY59" s="71"/>
+      <c r="AZ59" s="71"/>
+      <c r="BA59" s="71"/>
+      <c r="BB59" s="71"/>
+      <c r="BC59" s="71"/>
+      <c r="BD59" s="71"/>
+      <c r="BE59" s="71"/>
+      <c r="BF59" s="71"/>
+      <c r="BG59" s="71"/>
+      <c r="BH59" s="71"/>
+      <c r="BI59" s="71"/>
+      <c r="BJ59" s="71"/>
+      <c r="BK59" s="71"/>
+      <c r="BL59" s="72"/>
+      <c r="BR59" s="84"/>
+      <c r="BT59" s="64"/>
+    </row>
+    <row r="60" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A60" s="56"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="88">
         <v>1</v>
       </c>
-      <c r="F60" s="162" t="s">
+      <c r="F60" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="G60" s="131"/>
-      <c r="H60" s="131"/>
-      <c r="I60" s="131"/>
-      <c r="J60" s="131"/>
-      <c r="K60" s="131"/>
-      <c r="L60" s="131"/>
-      <c r="M60" s="131"/>
-      <c r="N60" s="131"/>
-      <c r="O60" s="131"/>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="131"/>
-      <c r="R60" s="131"/>
-      <c r="S60" s="131"/>
-      <c r="T60" s="133"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="66"/>
+      <c r="K60" s="66"/>
+      <c r="L60" s="66"/>
+      <c r="M60" s="66"/>
+      <c r="N60" s="66"/>
+      <c r="O60" s="66"/>
+      <c r="P60" s="66"/>
+      <c r="Q60" s="66"/>
+      <c r="R60" s="66"/>
+      <c r="S60" s="66"/>
+      <c r="T60" s="68"/>
       <c r="U60" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="V60" s="163"/>
-      <c r="W60" s="163"/>
-      <c r="X60" s="163"/>
-      <c r="Y60" s="163"/>
-      <c r="Z60" s="163"/>
-      <c r="AA60" s="163"/>
-      <c r="AB60" s="163"/>
-      <c r="AC60" s="163"/>
-      <c r="AD60" s="163"/>
-      <c r="AE60" s="163"/>
-      <c r="AF60" s="164"/>
+      <c r="V60" s="161"/>
+      <c r="W60" s="161"/>
+      <c r="X60" s="161"/>
+      <c r="Y60" s="161"/>
+      <c r="Z60" s="161"/>
+      <c r="AA60" s="161"/>
+      <c r="AB60" s="161"/>
+      <c r="AC60" s="161"/>
+      <c r="AD60" s="161"/>
+      <c r="AE60" s="161"/>
+      <c r="AF60" s="162"/>
       <c r="AG60" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="AH60" s="163"/>
-      <c r="AI60" s="163"/>
-      <c r="AJ60" s="163"/>
-      <c r="AK60" s="163"/>
-      <c r="AL60" s="163"/>
-      <c r="AM60" s="163"/>
-      <c r="AN60" s="163"/>
-      <c r="AO60" s="163"/>
-      <c r="AP60" s="163"/>
-      <c r="AQ60" s="163"/>
-      <c r="AR60" s="164"/>
-      <c r="AS60" s="165" t="s">
+      <c r="AH60" s="161"/>
+      <c r="AI60" s="161"/>
+      <c r="AJ60" s="161"/>
+      <c r="AK60" s="161"/>
+      <c r="AL60" s="161"/>
+      <c r="AM60" s="161"/>
+      <c r="AN60" s="161"/>
+      <c r="AO60" s="161"/>
+      <c r="AP60" s="161"/>
+      <c r="AQ60" s="161"/>
+      <c r="AR60" s="162"/>
+      <c r="AS60" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="AT60" s="166"/>
-      <c r="AU60" s="166"/>
-      <c r="AV60" s="166"/>
-      <c r="AW60" s="166"/>
-      <c r="AX60" s="166"/>
-      <c r="AY60" s="166"/>
-      <c r="AZ60" s="166"/>
-      <c r="BA60" s="166"/>
-      <c r="BB60" s="166"/>
-      <c r="BC60" s="166"/>
-      <c r="BD60" s="166"/>
-      <c r="BE60" s="166"/>
-      <c r="BF60" s="166"/>
-      <c r="BG60" s="166"/>
-      <c r="BH60" s="166"/>
-      <c r="BI60" s="166"/>
-      <c r="BJ60" s="166"/>
-      <c r="BK60" s="166"/>
-      <c r="BL60" s="167"/>
-      <c r="BR60" s="149"/>
-      <c r="BT60" s="127"/>
-    </row>
-    <row r="61" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A61" s="119"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="138"/>
-      <c r="D61" s="141"/>
-      <c r="E61" s="159">
+      <c r="AT60" s="164"/>
+      <c r="AU60" s="164"/>
+      <c r="AV60" s="164"/>
+      <c r="AW60" s="164"/>
+      <c r="AX60" s="164"/>
+      <c r="AY60" s="164"/>
+      <c r="AZ60" s="164"/>
+      <c r="BA60" s="164"/>
+      <c r="BB60" s="164"/>
+      <c r="BC60" s="164"/>
+      <c r="BD60" s="164"/>
+      <c r="BE60" s="164"/>
+      <c r="BF60" s="164"/>
+      <c r="BG60" s="164"/>
+      <c r="BH60" s="164"/>
+      <c r="BI60" s="164"/>
+      <c r="BJ60" s="164"/>
+      <c r="BK60" s="164"/>
+      <c r="BL60" s="165"/>
+      <c r="BR60" s="84"/>
+      <c r="BT60" s="64"/>
+    </row>
+    <row r="61" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A61" s="56"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="88">
         <v>2</v>
       </c>
-      <c r="F61" s="162" t="s">
+      <c r="F61" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="G61" s="131"/>
-      <c r="H61" s="131"/>
-      <c r="I61" s="131"/>
-      <c r="J61" s="131"/>
-      <c r="K61" s="131"/>
-      <c r="L61" s="131"/>
-      <c r="M61" s="131"/>
-      <c r="N61" s="131"/>
-      <c r="O61" s="131"/>
-      <c r="P61" s="131"/>
-      <c r="Q61" s="131"/>
-      <c r="R61" s="131"/>
-      <c r="S61" s="131"/>
-      <c r="T61" s="133"/>
+      <c r="G61" s="66"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
+      <c r="M61" s="66"/>
+      <c r="N61" s="66"/>
+      <c r="O61" s="66"/>
+      <c r="P61" s="66"/>
+      <c r="Q61" s="66"/>
+      <c r="R61" s="66"/>
+      <c r="S61" s="66"/>
+      <c r="T61" s="68"/>
       <c r="U61" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="V61" s="163"/>
-      <c r="W61" s="163"/>
-      <c r="X61" s="163"/>
-      <c r="Y61" s="163"/>
-      <c r="Z61" s="163"/>
-      <c r="AA61" s="163"/>
-      <c r="AB61" s="163"/>
-      <c r="AC61" s="163"/>
-      <c r="AD61" s="163"/>
-      <c r="AE61" s="163"/>
-      <c r="AF61" s="164"/>
+      <c r="V61" s="161"/>
+      <c r="W61" s="161"/>
+      <c r="X61" s="161"/>
+      <c r="Y61" s="161"/>
+      <c r="Z61" s="161"/>
+      <c r="AA61" s="161"/>
+      <c r="AB61" s="161"/>
+      <c r="AC61" s="161"/>
+      <c r="AD61" s="161"/>
+      <c r="AE61" s="161"/>
+      <c r="AF61" s="162"/>
       <c r="AG61" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="AH61" s="163"/>
-      <c r="AI61" s="163"/>
-      <c r="AJ61" s="163"/>
-      <c r="AK61" s="163"/>
-      <c r="AL61" s="163"/>
-      <c r="AM61" s="163"/>
-      <c r="AN61" s="163"/>
-      <c r="AO61" s="163"/>
-      <c r="AP61" s="163"/>
-      <c r="AQ61" s="163"/>
-      <c r="AR61" s="164"/>
-      <c r="AS61" s="165" t="s">
+      <c r="AH61" s="161"/>
+      <c r="AI61" s="161"/>
+      <c r="AJ61" s="161"/>
+      <c r="AK61" s="161"/>
+      <c r="AL61" s="161"/>
+      <c r="AM61" s="161"/>
+      <c r="AN61" s="161"/>
+      <c r="AO61" s="161"/>
+      <c r="AP61" s="161"/>
+      <c r="AQ61" s="161"/>
+      <c r="AR61" s="162"/>
+      <c r="AS61" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="AT61" s="166"/>
-      <c r="AU61" s="166"/>
-      <c r="AV61" s="166"/>
-      <c r="AW61" s="166"/>
-      <c r="AX61" s="166"/>
-      <c r="AY61" s="166"/>
-      <c r="AZ61" s="166"/>
-      <c r="BA61" s="166"/>
-      <c r="BB61" s="166"/>
-      <c r="BC61" s="166"/>
-      <c r="BD61" s="166"/>
-      <c r="BE61" s="166"/>
-      <c r="BF61" s="166"/>
-      <c r="BG61" s="166"/>
-      <c r="BH61" s="166"/>
-      <c r="BI61" s="166"/>
-      <c r="BJ61" s="166"/>
-      <c r="BK61" s="166"/>
-      <c r="BL61" s="167"/>
-      <c r="BR61" s="149"/>
-      <c r="BT61" s="127"/>
-    </row>
-    <row r="62" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A62" s="119"/>
-      <c r="B62" s="134"/>
-      <c r="C62" s="168"/>
-      <c r="D62" s="169"/>
-      <c r="E62" s="170"/>
-      <c r="F62" s="170"/>
-      <c r="G62" s="170"/>
-      <c r="H62" s="170"/>
-      <c r="I62" s="170"/>
-      <c r="J62" s="170"/>
-      <c r="K62" s="170"/>
-      <c r="L62" s="170"/>
-      <c r="M62" s="170"/>
-      <c r="N62" s="170"/>
-      <c r="O62" s="170"/>
-      <c r="P62" s="170"/>
-      <c r="Q62" s="170"/>
-      <c r="R62" s="170"/>
-      <c r="S62" s="170"/>
-      <c r="T62" s="170"/>
-      <c r="U62" s="170"/>
-      <c r="V62" s="170"/>
-      <c r="W62" s="170"/>
-      <c r="X62" s="170"/>
-      <c r="Y62" s="170"/>
-      <c r="Z62" s="170"/>
-      <c r="AA62" s="170"/>
-      <c r="AB62" s="170"/>
-      <c r="AC62" s="170"/>
-      <c r="AD62" s="170"/>
-      <c r="AE62" s="170"/>
-      <c r="AF62" s="170"/>
-      <c r="AG62" s="171"/>
-      <c r="AH62" s="171"/>
-      <c r="AI62" s="171"/>
-      <c r="AJ62" s="171"/>
-      <c r="AK62" s="171"/>
-      <c r="AL62" s="171"/>
-      <c r="AM62" s="171"/>
-      <c r="AN62" s="171"/>
-      <c r="AO62" s="171"/>
-      <c r="AP62" s="171"/>
-      <c r="AQ62" s="171"/>
-      <c r="AR62" s="171"/>
-      <c r="AS62" s="171"/>
-      <c r="AT62" s="171"/>
-      <c r="AU62" s="170"/>
-      <c r="AV62" s="170"/>
-      <c r="AW62" s="170"/>
-      <c r="AX62" s="171"/>
-      <c r="AY62" s="171"/>
-      <c r="AZ62" s="171"/>
-      <c r="BA62" s="171"/>
-      <c r="BB62" s="171"/>
-      <c r="BC62" s="170"/>
-      <c r="BD62" s="170"/>
-      <c r="BE62" s="170"/>
-      <c r="BF62" s="171"/>
-      <c r="BG62" s="171"/>
-      <c r="BH62" s="171"/>
-      <c r="BI62" s="171"/>
-      <c r="BJ62" s="171"/>
-      <c r="BK62" s="170"/>
-      <c r="BL62" s="170"/>
-      <c r="BM62" s="170"/>
-      <c r="BN62" s="170"/>
-      <c r="BO62" s="170"/>
-      <c r="BP62" s="170"/>
-      <c r="BQ62" s="170"/>
-      <c r="BR62" s="172"/>
-      <c r="BT62" s="127"/>
+      <c r="AT61" s="164"/>
+      <c r="AU61" s="164"/>
+      <c r="AV61" s="164"/>
+      <c r="AW61" s="164"/>
+      <c r="AX61" s="164"/>
+      <c r="AY61" s="164"/>
+      <c r="AZ61" s="164"/>
+      <c r="BA61" s="164"/>
+      <c r="BB61" s="164"/>
+      <c r="BC61" s="164"/>
+      <c r="BD61" s="164"/>
+      <c r="BE61" s="164"/>
+      <c r="BF61" s="164"/>
+      <c r="BG61" s="164"/>
+      <c r="BH61" s="164"/>
+      <c r="BI61" s="164"/>
+      <c r="BJ61" s="164"/>
+      <c r="BK61" s="164"/>
+      <c r="BL61" s="165"/>
+      <c r="BR61" s="84"/>
+      <c r="BT61" s="64"/>
+    </row>
+    <row r="62" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A62" s="56"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="93"/>
+      <c r="F62" s="93"/>
+      <c r="G62" s="93"/>
+      <c r="H62" s="93"/>
+      <c r="I62" s="93"/>
+      <c r="J62" s="93"/>
+      <c r="K62" s="93"/>
+      <c r="L62" s="93"/>
+      <c r="M62" s="93"/>
+      <c r="N62" s="93"/>
+      <c r="O62" s="93"/>
+      <c r="P62" s="93"/>
+      <c r="Q62" s="93"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="93"/>
+      <c r="T62" s="93"/>
+      <c r="U62" s="93"/>
+      <c r="V62" s="93"/>
+      <c r="W62" s="93"/>
+      <c r="X62" s="93"/>
+      <c r="Y62" s="93"/>
+      <c r="Z62" s="93"/>
+      <c r="AA62" s="93"/>
+      <c r="AB62" s="93"/>
+      <c r="AC62" s="93"/>
+      <c r="AD62" s="93"/>
+      <c r="AE62" s="93"/>
+      <c r="AF62" s="93"/>
+      <c r="AG62" s="94"/>
+      <c r="AH62" s="94"/>
+      <c r="AI62" s="94"/>
+      <c r="AJ62" s="94"/>
+      <c r="AK62" s="94"/>
+      <c r="AL62" s="94"/>
+      <c r="AM62" s="94"/>
+      <c r="AN62" s="94"/>
+      <c r="AO62" s="94"/>
+      <c r="AP62" s="94"/>
+      <c r="AQ62" s="94"/>
+      <c r="AR62" s="94"/>
+      <c r="AS62" s="94"/>
+      <c r="AT62" s="94"/>
+      <c r="AU62" s="93"/>
+      <c r="AV62" s="93"/>
+      <c r="AW62" s="93"/>
+      <c r="AX62" s="94"/>
+      <c r="AY62" s="94"/>
+      <c r="AZ62" s="94"/>
+      <c r="BA62" s="94"/>
+      <c r="BB62" s="94"/>
+      <c r="BC62" s="93"/>
+      <c r="BD62" s="93"/>
+      <c r="BE62" s="93"/>
+      <c r="BF62" s="94"/>
+      <c r="BG62" s="94"/>
+      <c r="BH62" s="94"/>
+      <c r="BI62" s="94"/>
+      <c r="BJ62" s="94"/>
+      <c r="BK62" s="93"/>
+      <c r="BL62" s="93"/>
+      <c r="BM62" s="93"/>
+      <c r="BN62" s="93"/>
+      <c r="BO62" s="93"/>
+      <c r="BP62" s="93"/>
+      <c r="BQ62" s="93"/>
+      <c r="BR62" s="95"/>
+      <c r="BT62" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="U61:AF61"/>
-    <mergeCell ref="AG61:AR61"/>
-    <mergeCell ref="AS61:BL61"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F45:K46"/>
-    <mergeCell ref="U60:AF60"/>
-    <mergeCell ref="AG60:AR60"/>
-    <mergeCell ref="AS60:BL60"/>
-    <mergeCell ref="BC1:BT1"/>
-    <mergeCell ref="BC2:BT2"/>
-    <mergeCell ref="U32:AF32"/>
-    <mergeCell ref="AG32:AR32"/>
-    <mergeCell ref="AS32:BL32"/>
-    <mergeCell ref="U31:AF31"/>
-    <mergeCell ref="AG31:AR31"/>
-    <mergeCell ref="AS31:BL31"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F16:K17"/>
     <mergeCell ref="AE1:AI1"/>
@@ -8795,15 +8779,31 @@
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:AD2"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="BC1:BT1"/>
+    <mergeCell ref="BC2:BT2"/>
+    <mergeCell ref="U32:AF32"/>
+    <mergeCell ref="AG32:AR32"/>
+    <mergeCell ref="AS32:BL32"/>
+    <mergeCell ref="U31:AF31"/>
+    <mergeCell ref="AG31:AR31"/>
+    <mergeCell ref="AS31:BL31"/>
     <mergeCell ref="AJ1:AM1"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="AE2:AI2"/>
     <mergeCell ref="AJ2:AM2"/>
     <mergeCell ref="AN2:AR2"/>
     <mergeCell ref="AS2:AW2"/>
     <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="U61:AF61"/>
+    <mergeCell ref="AG61:AR61"/>
+    <mergeCell ref="AS61:BL61"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F45:K46"/>
+    <mergeCell ref="U60:AF60"/>
+    <mergeCell ref="AG60:AR60"/>
+    <mergeCell ref="AS60:BL60"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/design-detail/DD_Staff_v1.0.xlsx
+++ b/design-detail/DD_Staff_v1.0.xlsx
@@ -8,47 +8,49 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\design-detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD1B36A-68EA-4B7E-8CB6-D354639FEC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA9ABA2-1DEB-4ADC-88FF-76C482C73E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="His" sheetId="32" r:id="rId1"/>
-    <sheet name="Overview" sheetId="28" r:id="rId2"/>
-    <sheet name="SQL" sheetId="35" r:id="rId3"/>
-    <sheet name="ClassDiagram" sheetId="42" r:id="rId4"/>
-    <sheet name="SequenceDiagram" sheetId="43" r:id="rId5"/>
-    <sheet name="APIs" sheetId="36" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="34" state="hidden" r:id="rId7"/>
+    <sheet name="Layout" sheetId="45" r:id="rId2"/>
+    <sheet name="Overview" sheetId="28" r:id="rId3"/>
+    <sheet name="SQL" sheetId="35" r:id="rId4"/>
+    <sheet name="ClassDiagram" sheetId="42" r:id="rId5"/>
+    <sheet name="SequenceDiagram" sheetId="43" r:id="rId6"/>
+    <sheet name="APIs" sheetId="36" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="34" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_Key1" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Key1" localSheetId="4" hidden="1">#REF!</definedName>
+    <definedName name="_Key1" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="_Key1" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Key1" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
+    <definedName name="_Regression_X" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Regression_X" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Regression_X" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Regression_X" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" hidden="1">#REF!</definedName>
+    <definedName name="_Sort" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Sort" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="_Sort" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Sort" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Sort" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Sort" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">APIs!$A$1:$BT$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">ClassDiagram!$A$1:$BG$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">APIs!$A$1:$BT$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">ClassDiagram!$A$1:$BG$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">His!$A$1:$E$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">SequenceDiagram!$A$1:$BG$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">SQL!$A$1:$BG$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Layout!$A$1:$BL$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">SequenceDiagram!$A$1:$BG$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SQL!$A$1:$BG$26</definedName>
+    <definedName name="関連表" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="関連表" localSheetId="4" hidden="1">#REF!</definedName>
+    <definedName name="関連表" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="関連表" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="関連表" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="関連表" hidden="1">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -67,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
   <si>
     <t>Label</t>
   </si>
@@ -401,6 +403,9 @@
   </si>
   <si>
     <t>Update</t>
+  </si>
+  <si>
+    <t>figma</t>
   </si>
 </sst>
 </file>
@@ -2093,6 +2098,147 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="38" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="29" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="28" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="41" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="43" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="40" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="39" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2105,145 +2251,13 @@
     <xf numFmtId="49" fontId="47" fillId="0" borderId="42" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="38" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="29" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="28" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="41" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="43" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="40" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2264,14 +2278,38 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="16" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2290,39 +2328,6 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="16" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="144">
@@ -2493,6 +2498,55 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>30939</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>7950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C0CD704-5B59-716D-15CC-16A198511146}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="998220" y="1531620"/>
+          <a:ext cx="5296359" cy="3810330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>45720</xdr:colOff>
       <xdr:row>12</xdr:row>
@@ -2538,7 +2592,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2587,7 +2641,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3182,11 +3236,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222134E3-A126-43B4-9320-68F74CBADA6F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BM25"/>
+  <dimension ref="A1:BM9"/>
   <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="3.109375" style="2" customWidth="1"/>
@@ -3203,248 +3257,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="5" customFormat="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="134" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="139" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="140" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="140" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="141"/>
-      <c r="AE1" s="141"/>
-      <c r="AF1" s="141"/>
-      <c r="AG1" s="141"/>
-      <c r="AH1" s="142"/>
-      <c r="AI1" s="148" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AJ1" s="149"/>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="148" t="s">
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="150"/>
-      <c r="AS1" s="148" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
-      <c r="AW1" s="150"/>
-      <c r="AX1" s="134" t="s">
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AY1" s="136"/>
-      <c r="AZ1" s="136"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="137"/>
-      <c r="BC1" s="134" t="s">
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="109"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="BD1" s="135"/>
-      <c r="BE1" s="135"/>
-      <c r="BF1" s="136"/>
-      <c r="BG1" s="137"/>
-      <c r="BH1" s="130" t="s">
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="109"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BI1" s="131"/>
-      <c r="BJ1" s="132"/>
-      <c r="BK1" s="132"/>
-      <c r="BL1" s="133"/>
+      <c r="BI1" s="104"/>
+      <c r="BJ1" s="105"/>
+      <c r="BK1" s="105"/>
+      <c r="BL1" s="106"/>
       <c r="BM1" s="2"/>
     </row>
     <row r="2" spans="1:65" s="5" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="116" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="105" t="s">
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="104" t="s">
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="104" t="s">
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
-      <c r="AA2" s="105"/>
-      <c r="AB2" s="105"/>
-      <c r="AC2" s="105"/>
-      <c r="AD2" s="105"/>
-      <c r="AE2" s="105"/>
-      <c r="AF2" s="105"/>
-      <c r="AG2" s="105"/>
-      <c r="AH2" s="106"/>
-      <c r="AI2" s="110">
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="111">
         <v>45701</v>
       </c>
-      <c r="AJ2" s="111"/>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="112"/>
-      <c r="AN2" s="116" t="s">
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="112"/>
+      <c r="AL2" s="112"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="117"/>
-      <c r="AS2" s="110">
+      <c r="AO2" s="144"/>
+      <c r="AP2" s="144"/>
+      <c r="AQ2" s="144"/>
+      <c r="AR2" s="144"/>
+      <c r="AS2" s="111">
         <v>45707</v>
       </c>
-      <c r="AT2" s="111"/>
-      <c r="AU2" s="111"/>
-      <c r="AV2" s="111"/>
-      <c r="AW2" s="112"/>
-      <c r="AX2" s="120" t="s">
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="AY2" s="120"/>
-      <c r="AZ2" s="120"/>
-      <c r="BA2" s="120"/>
-      <c r="BB2" s="120"/>
-      <c r="BC2" s="110">
+      <c r="AY2" s="117"/>
+      <c r="AZ2" s="117"/>
+      <c r="BA2" s="117"/>
+      <c r="BB2" s="117"/>
+      <c r="BC2" s="111">
         <v>45701</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
-      <c r="BH2" s="120" t="s">
+      <c r="BD2" s="112"/>
+      <c r="BE2" s="112"/>
+      <c r="BF2" s="112"/>
+      <c r="BG2" s="113"/>
+      <c r="BH2" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="BI2" s="120"/>
-      <c r="BJ2" s="120"/>
-      <c r="BK2" s="120"/>
-      <c r="BL2" s="120"/>
+      <c r="BI2" s="117"/>
+      <c r="BJ2" s="117"/>
+      <c r="BK2" s="117"/>
+      <c r="BL2" s="117"/>
       <c r="BM2" s="2"/>
     </row>
     <row r="3" spans="1:65" s="5" customFormat="1" ht="10.5" customHeight="1">
-      <c r="A3" s="145"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="147"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="107"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="107"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108"/>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108"/>
-      <c r="AA3" s="108"/>
-      <c r="AB3" s="108"/>
-      <c r="AC3" s="108"/>
-      <c r="AD3" s="108"/>
-      <c r="AE3" s="108"/>
-      <c r="AF3" s="108"/>
-      <c r="AG3" s="108"/>
-      <c r="AH3" s="109"/>
-      <c r="AI3" s="113"/>
-      <c r="AJ3" s="114"/>
-      <c r="AK3" s="114"/>
-      <c r="AL3" s="114"/>
-      <c r="AM3" s="115"/>
-      <c r="AN3" s="118"/>
-      <c r="AO3" s="119"/>
-      <c r="AP3" s="119"/>
-      <c r="AQ3" s="119"/>
-      <c r="AR3" s="119"/>
-      <c r="AS3" s="113"/>
-      <c r="AT3" s="114"/>
-      <c r="AU3" s="114"/>
-      <c r="AV3" s="114"/>
-      <c r="AW3" s="115"/>
-      <c r="AX3" s="120"/>
-      <c r="AY3" s="120"/>
-      <c r="AZ3" s="120"/>
-      <c r="BA3" s="120"/>
-      <c r="BB3" s="120"/>
-      <c r="BC3" s="113"/>
-      <c r="BD3" s="114"/>
-      <c r="BE3" s="114"/>
-      <c r="BF3" s="114"/>
-      <c r="BG3" s="115"/>
-      <c r="BH3" s="120"/>
-      <c r="BI3" s="120"/>
-      <c r="BJ3" s="120"/>
-      <c r="BK3" s="120"/>
-      <c r="BL3" s="120"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="132"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+      <c r="AF3" s="131"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="116"/>
+      <c r="AN3" s="145"/>
+      <c r="AO3" s="146"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="146"/>
+      <c r="AR3" s="146"/>
+      <c r="AS3" s="114"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="117"/>
+      <c r="AY3" s="117"/>
+      <c r="AZ3" s="117"/>
+      <c r="BA3" s="117"/>
+      <c r="BB3" s="117"/>
+      <c r="BC3" s="114"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="115"/>
+      <c r="BF3" s="115"/>
+      <c r="BG3" s="116"/>
+      <c r="BH3" s="117"/>
+      <c r="BI3" s="117"/>
+      <c r="BJ3" s="117"/>
+      <c r="BK3" s="117"/>
+      <c r="BL3" s="117"/>
       <c r="BM3" s="2"/>
     </row>
     <row r="4" spans="1:65" s="5" customFormat="1" ht="9.75" customHeight="1">
@@ -3660,6 +3714,523 @@
       <c r="BL8" s="15"/>
     </row>
     <row r="9" spans="1:65">
+      <c r="B9" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="AS2:AW3"/>
+    <mergeCell ref="AX2:BB3"/>
+    <mergeCell ref="BC2:BG3"/>
+    <mergeCell ref="BH2:BL3"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BG1"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="A2:E3"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K2:O3"/>
+    <mergeCell ref="P2:T3"/>
+    <mergeCell ref="U2:AH3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AH1"/>
+    <mergeCell ref="AI1:AM1"/>
+  </mergeCells>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;P/&amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BM25"/>
+  <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="2" width="3.109375" style="2" customWidth="1"/>
+    <col min="3" max="5" width="2.77734375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="2.33203125" style="2"/>
+    <col min="8" max="8" width="2.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="3" style="2" customWidth="1"/>
+    <col min="10" max="10" width="3.44140625" style="2" customWidth="1"/>
+    <col min="11" max="46" width="2.33203125" style="2"/>
+    <col min="47" max="47" width="2.88671875" style="2" customWidth="1"/>
+    <col min="48" max="48" width="2.6640625" style="2" customWidth="1"/>
+    <col min="49" max="49" width="2.77734375" style="2" customWidth="1"/>
+    <col min="50" max="16384" width="2.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:65" s="5" customFormat="1">
+      <c r="A1" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="133" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="109"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="109"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="BI1" s="104"/>
+      <c r="BJ1" s="105"/>
+      <c r="BK1" s="105"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="2"/>
+    </row>
+    <row r="2" spans="1:65" s="5" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A2" s="123" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="129" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="111">
+        <v>45701</v>
+      </c>
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="112"/>
+      <c r="AL2" s="112"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="123" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO2" s="144"/>
+      <c r="AP2" s="144"/>
+      <c r="AQ2" s="144"/>
+      <c r="AR2" s="144"/>
+      <c r="AS2" s="111">
+        <v>45707</v>
+      </c>
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY2" s="117"/>
+      <c r="AZ2" s="117"/>
+      <c r="BA2" s="117"/>
+      <c r="BB2" s="117"/>
+      <c r="BC2" s="111">
+        <v>45701</v>
+      </c>
+      <c r="BD2" s="112"/>
+      <c r="BE2" s="112"/>
+      <c r="BF2" s="112"/>
+      <c r="BG2" s="113"/>
+      <c r="BH2" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="BI2" s="117"/>
+      <c r="BJ2" s="117"/>
+      <c r="BK2" s="117"/>
+      <c r="BL2" s="117"/>
+      <c r="BM2" s="2"/>
+    </row>
+    <row r="3" spans="1:65" s="5" customFormat="1" ht="10.5" customHeight="1">
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="132"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+      <c r="AF3" s="131"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="116"/>
+      <c r="AN3" s="145"/>
+      <c r="AO3" s="146"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="146"/>
+      <c r="AR3" s="146"/>
+      <c r="AS3" s="114"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="117"/>
+      <c r="AY3" s="117"/>
+      <c r="AZ3" s="117"/>
+      <c r="BA3" s="117"/>
+      <c r="BB3" s="117"/>
+      <c r="BC3" s="114"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="115"/>
+      <c r="BF3" s="115"/>
+      <c r="BG3" s="116"/>
+      <c r="BH3" s="117"/>
+      <c r="BI3" s="117"/>
+      <c r="BJ3" s="117"/>
+      <c r="BK3" s="117"/>
+      <c r="BL3" s="117"/>
+      <c r="BM3" s="2"/>
+    </row>
+    <row r="4" spans="1:65" s="5" customFormat="1" ht="9.75" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="42"/>
+      <c r="AM4" s="42"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="42"/>
+      <c r="AU4" s="42"/>
+      <c r="AV4" s="42"/>
+      <c r="AW4" s="42"/>
+      <c r="AX4" s="52"/>
+      <c r="AY4" s="52"/>
+      <c r="AZ4" s="52"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="52"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="44"/>
+      <c r="BH4" s="47"/>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="43"/>
+      <c r="BK4" s="43"/>
+      <c r="BL4" s="45"/>
+      <c r="BM4" s="2"/>
+    </row>
+    <row r="5" spans="1:65">
+      <c r="A5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="10"/>
+      <c r="AN5" s="10"/>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="10"/>
+      <c r="AS5" s="10"/>
+      <c r="AT5" s="10"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="10"/>
+      <c r="AW5" s="10"/>
+      <c r="AX5" s="10"/>
+      <c r="AY5" s="10"/>
+      <c r="AZ5" s="10"/>
+      <c r="BA5" s="10"/>
+      <c r="BB5" s="10"/>
+      <c r="BC5" s="10"/>
+      <c r="BD5" s="10"/>
+      <c r="BE5" s="10"/>
+      <c r="BF5" s="10"/>
+      <c r="BG5" s="10"/>
+      <c r="BH5" s="10"/>
+      <c r="BI5" s="10"/>
+      <c r="BJ5" s="10"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="11"/>
+    </row>
+    <row r="6" spans="1:65">
+      <c r="A6" s="13"/>
+      <c r="BL6" s="3"/>
+    </row>
+    <row r="7" spans="1:65">
+      <c r="A7" s="13"/>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="BL7" s="3"/>
+    </row>
+    <row r="8" spans="1:65">
+      <c r="A8" s="14"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+      <c r="BI8" s="12"/>
+      <c r="BJ8" s="12"/>
+      <c r="BK8" s="12"/>
+      <c r="BL8" s="15"/>
+    </row>
+    <row r="9" spans="1:65">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -3701,23 +4272,23 @@
         <v>24</v>
       </c>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="121" t="s">
+      <c r="AO10" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="AP10" s="122"/>
-      <c r="AQ10" s="122"/>
-      <c r="AR10" s="122"/>
-      <c r="AS10" s="122"/>
-      <c r="AT10" s="122"/>
-      <c r="AU10" s="122"/>
-      <c r="AV10" s="122"/>
-      <c r="AW10" s="122"/>
-      <c r="AX10" s="122"/>
-      <c r="AY10" s="122"/>
-      <c r="AZ10" s="122"/>
-      <c r="BA10" s="122"/>
-      <c r="BB10" s="122"/>
-      <c r="BC10" s="123"/>
+      <c r="AP10" s="137"/>
+      <c r="AQ10" s="137"/>
+      <c r="AR10" s="137"/>
+      <c r="AS10" s="137"/>
+      <c r="AT10" s="137"/>
+      <c r="AU10" s="137"/>
+      <c r="AV10" s="137"/>
+      <c r="AW10" s="137"/>
+      <c r="AX10" s="137"/>
+      <c r="AY10" s="137"/>
+      <c r="AZ10" s="137"/>
+      <c r="BA10" s="137"/>
+      <c r="BB10" s="137"/>
+      <c r="BC10" s="138"/>
       <c r="BD10" s="21" t="s">
         <v>5</v>
       </c>
@@ -3727,31 +4298,31 @@
     </row>
     <row r="11" spans="1:65" ht="15" customHeight="1">
       <c r="A11" s="13"/>
-      <c r="AM11" s="100" t="s">
+      <c r="AM11" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="AN11" s="101"/>
-      <c r="AO11" s="124" t="s">
+      <c r="AN11" s="148"/>
+      <c r="AO11" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="AP11" s="125"/>
-      <c r="AQ11" s="125"/>
-      <c r="AR11" s="125"/>
-      <c r="AS11" s="125"/>
-      <c r="AT11" s="125"/>
-      <c r="AU11" s="125"/>
-      <c r="AV11" s="125"/>
-      <c r="AW11" s="125"/>
-      <c r="AX11" s="125"/>
-      <c r="AY11" s="125"/>
-      <c r="AZ11" s="125"/>
-      <c r="BA11" s="125"/>
-      <c r="BB11" s="125"/>
-      <c r="BC11" s="126"/>
-      <c r="BD11" s="102" t="s">
+      <c r="AP11" s="101"/>
+      <c r="AQ11" s="101"/>
+      <c r="AR11" s="101"/>
+      <c r="AS11" s="101"/>
+      <c r="AT11" s="101"/>
+      <c r="AU11" s="101"/>
+      <c r="AV11" s="101"/>
+      <c r="AW11" s="101"/>
+      <c r="AX11" s="101"/>
+      <c r="AY11" s="101"/>
+      <c r="AZ11" s="101"/>
+      <c r="BA11" s="101"/>
+      <c r="BB11" s="101"/>
+      <c r="BC11" s="102"/>
+      <c r="BD11" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="BE11" s="103"/>
+      <c r="BE11" s="150"/>
       <c r="BF11" s="13"/>
       <c r="BL11" s="3"/>
     </row>
@@ -3760,61 +4331,61 @@
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM12" s="100" t="s">
+      <c r="AM12" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="AN12" s="101"/>
-      <c r="AO12" s="127" t="s">
+      <c r="AN12" s="148"/>
+      <c r="AO12" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="AP12" s="128"/>
-      <c r="AQ12" s="128"/>
-      <c r="AR12" s="128"/>
-      <c r="AS12" s="128"/>
-      <c r="AT12" s="128"/>
-      <c r="AU12" s="128"/>
-      <c r="AV12" s="128"/>
-      <c r="AW12" s="128"/>
-      <c r="AX12" s="128"/>
-      <c r="AY12" s="128"/>
-      <c r="AZ12" s="128"/>
-      <c r="BA12" s="128"/>
-      <c r="BB12" s="128"/>
-      <c r="BC12" s="129"/>
-      <c r="BD12" s="102" t="s">
+      <c r="AP12" s="140"/>
+      <c r="AQ12" s="140"/>
+      <c r="AR12" s="140"/>
+      <c r="AS12" s="140"/>
+      <c r="AT12" s="140"/>
+      <c r="AU12" s="140"/>
+      <c r="AV12" s="140"/>
+      <c r="AW12" s="140"/>
+      <c r="AX12" s="140"/>
+      <c r="AY12" s="140"/>
+      <c r="AZ12" s="140"/>
+      <c r="BA12" s="140"/>
+      <c r="BB12" s="140"/>
+      <c r="BC12" s="141"/>
+      <c r="BD12" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="BE12" s="103"/>
+      <c r="BE12" s="150"/>
       <c r="BF12" s="13"/>
       <c r="BL12" s="3"/>
     </row>
     <row r="13" spans="1:65" ht="15" customHeight="1">
       <c r="A13" s="13"/>
-      <c r="AM13" s="100" t="s">
+      <c r="AM13" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="AN13" s="101"/>
-      <c r="AO13" s="127" t="s">
+      <c r="AN13" s="148"/>
+      <c r="AO13" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="AP13" s="128"/>
-      <c r="AQ13" s="128"/>
-      <c r="AR13" s="128"/>
-      <c r="AS13" s="128"/>
-      <c r="AT13" s="128"/>
-      <c r="AU13" s="128"/>
-      <c r="AV13" s="128"/>
-      <c r="AW13" s="128"/>
-      <c r="AX13" s="128"/>
-      <c r="AY13" s="128"/>
-      <c r="AZ13" s="128"/>
-      <c r="BA13" s="128"/>
-      <c r="BB13" s="128"/>
-      <c r="BC13" s="129"/>
-      <c r="BD13" s="102" t="s">
+      <c r="AP13" s="140"/>
+      <c r="AQ13" s="140"/>
+      <c r="AR13" s="140"/>
+      <c r="AS13" s="140"/>
+      <c r="AT13" s="140"/>
+      <c r="AU13" s="140"/>
+      <c r="AV13" s="140"/>
+      <c r="AW13" s="140"/>
+      <c r="AX13" s="140"/>
+      <c r="AY13" s="140"/>
+      <c r="AZ13" s="140"/>
+      <c r="BA13" s="140"/>
+      <c r="BB13" s="140"/>
+      <c r="BC13" s="141"/>
+      <c r="BD13" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="BE13" s="103"/>
+      <c r="BE13" s="150"/>
       <c r="BF13" s="13"/>
       <c r="BL13" s="3"/>
     </row>
@@ -3822,21 +4393,21 @@
       <c r="A14" s="13"/>
       <c r="AM14" s="27"/>
       <c r="AN14" s="28"/>
-      <c r="AO14" s="124"/>
-      <c r="AP14" s="125"/>
-      <c r="AQ14" s="125"/>
-      <c r="AR14" s="125"/>
-      <c r="AS14" s="125"/>
-      <c r="AT14" s="125"/>
-      <c r="AU14" s="125"/>
-      <c r="AV14" s="125"/>
-      <c r="AW14" s="125"/>
-      <c r="AX14" s="125"/>
-      <c r="AY14" s="125"/>
-      <c r="AZ14" s="125"/>
-      <c r="BA14" s="125"/>
-      <c r="BB14" s="125"/>
-      <c r="BC14" s="126"/>
+      <c r="AO14" s="100"/>
+      <c r="AP14" s="101"/>
+      <c r="AQ14" s="101"/>
+      <c r="AR14" s="101"/>
+      <c r="AS14" s="101"/>
+      <c r="AT14" s="101"/>
+      <c r="AU14" s="101"/>
+      <c r="AV14" s="101"/>
+      <c r="AW14" s="101"/>
+      <c r="AX14" s="101"/>
+      <c r="AY14" s="101"/>
+      <c r="AZ14" s="101"/>
+      <c r="BA14" s="101"/>
+      <c r="BB14" s="101"/>
+      <c r="BC14" s="102"/>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="13"/>
@@ -3846,21 +4417,21 @@
       <c r="A15" s="13"/>
       <c r="AM15" s="27"/>
       <c r="AN15" s="28"/>
-      <c r="AO15" s="124"/>
-      <c r="AP15" s="125"/>
-      <c r="AQ15" s="125"/>
-      <c r="AR15" s="125"/>
-      <c r="AS15" s="125"/>
-      <c r="AT15" s="125"/>
-      <c r="AU15" s="125"/>
-      <c r="AV15" s="125"/>
-      <c r="AW15" s="125"/>
-      <c r="AX15" s="125"/>
-      <c r="AY15" s="125"/>
-      <c r="AZ15" s="125"/>
-      <c r="BA15" s="125"/>
-      <c r="BB15" s="125"/>
-      <c r="BC15" s="126"/>
+      <c r="AO15" s="100"/>
+      <c r="AP15" s="101"/>
+      <c r="AQ15" s="101"/>
+      <c r="AR15" s="101"/>
+      <c r="AS15" s="101"/>
+      <c r="AT15" s="101"/>
+      <c r="AU15" s="101"/>
+      <c r="AV15" s="101"/>
+      <c r="AW15" s="101"/>
+      <c r="AX15" s="101"/>
+      <c r="AY15" s="101"/>
+      <c r="AZ15" s="101"/>
+      <c r="BA15" s="101"/>
+      <c r="BB15" s="101"/>
+      <c r="BC15" s="102"/>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="13"/>
@@ -3870,21 +4441,21 @@
       <c r="A16" s="13"/>
       <c r="AM16" s="27"/>
       <c r="AN16" s="28"/>
-      <c r="AO16" s="124"/>
-      <c r="AP16" s="125"/>
-      <c r="AQ16" s="125"/>
-      <c r="AR16" s="125"/>
-      <c r="AS16" s="125"/>
-      <c r="AT16" s="125"/>
-      <c r="AU16" s="125"/>
-      <c r="AV16" s="125"/>
-      <c r="AW16" s="125"/>
-      <c r="AX16" s="125"/>
-      <c r="AY16" s="125"/>
-      <c r="AZ16" s="125"/>
-      <c r="BA16" s="125"/>
-      <c r="BB16" s="125"/>
-      <c r="BC16" s="126"/>
+      <c r="AO16" s="100"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="101"/>
+      <c r="AS16" s="101"/>
+      <c r="AT16" s="101"/>
+      <c r="AU16" s="101"/>
+      <c r="AV16" s="101"/>
+      <c r="AW16" s="101"/>
+      <c r="AX16" s="101"/>
+      <c r="AY16" s="101"/>
+      <c r="AZ16" s="101"/>
+      <c r="BA16" s="101"/>
+      <c r="BB16" s="101"/>
+      <c r="BC16" s="102"/>
       <c r="BD16" s="31"/>
       <c r="BE16" s="32"/>
       <c r="BF16" s="13"/>
@@ -3894,21 +4465,21 @@
       <c r="A17" s="13"/>
       <c r="AM17" s="27"/>
       <c r="AN17" s="28"/>
-      <c r="AO17" s="124"/>
-      <c r="AP17" s="125"/>
-      <c r="AQ17" s="125"/>
-      <c r="AR17" s="125"/>
-      <c r="AS17" s="125"/>
-      <c r="AT17" s="125"/>
-      <c r="AU17" s="125"/>
-      <c r="AV17" s="125"/>
-      <c r="AW17" s="125"/>
-      <c r="AX17" s="125"/>
-      <c r="AY17" s="125"/>
-      <c r="AZ17" s="125"/>
-      <c r="BA17" s="125"/>
-      <c r="BB17" s="125"/>
-      <c r="BC17" s="126"/>
+      <c r="AO17" s="100"/>
+      <c r="AP17" s="101"/>
+      <c r="AQ17" s="101"/>
+      <c r="AR17" s="101"/>
+      <c r="AS17" s="101"/>
+      <c r="AT17" s="101"/>
+      <c r="AU17" s="101"/>
+      <c r="AV17" s="101"/>
+      <c r="AW17" s="101"/>
+      <c r="AX17" s="101"/>
+      <c r="AY17" s="101"/>
+      <c r="AZ17" s="101"/>
+      <c r="BA17" s="101"/>
+      <c r="BB17" s="101"/>
+      <c r="BC17" s="102"/>
       <c r="BD17" s="31"/>
       <c r="BE17" s="32"/>
       <c r="BF17" s="13"/>
@@ -3918,21 +4489,21 @@
       <c r="A18" s="13"/>
       <c r="AM18" s="27"/>
       <c r="AN18" s="28"/>
-      <c r="AO18" s="124"/>
-      <c r="AP18" s="125"/>
-      <c r="AQ18" s="125"/>
-      <c r="AR18" s="125"/>
-      <c r="AS18" s="125"/>
-      <c r="AT18" s="125"/>
-      <c r="AU18" s="125"/>
-      <c r="AV18" s="125"/>
-      <c r="AW18" s="125"/>
-      <c r="AX18" s="125"/>
-      <c r="AY18" s="125"/>
-      <c r="AZ18" s="125"/>
-      <c r="BA18" s="125"/>
-      <c r="BB18" s="125"/>
-      <c r="BC18" s="126"/>
+      <c r="AO18" s="100"/>
+      <c r="AP18" s="101"/>
+      <c r="AQ18" s="101"/>
+      <c r="AR18" s="101"/>
+      <c r="AS18" s="101"/>
+      <c r="AT18" s="101"/>
+      <c r="AU18" s="101"/>
+      <c r="AV18" s="101"/>
+      <c r="AW18" s="101"/>
+      <c r="AX18" s="101"/>
+      <c r="AY18" s="101"/>
+      <c r="AZ18" s="101"/>
+      <c r="BA18" s="101"/>
+      <c r="BB18" s="101"/>
+      <c r="BC18" s="102"/>
       <c r="BD18" s="34"/>
       <c r="BE18" s="35"/>
       <c r="BF18" s="13"/>
@@ -4124,11 +4695,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="AO14:BC14"/>
-    <mergeCell ref="AO18:BC18"/>
-    <mergeCell ref="AO15:BC15"/>
-    <mergeCell ref="AO16:BC16"/>
-    <mergeCell ref="AO17:BC17"/>
+    <mergeCell ref="AM11:AN11"/>
+    <mergeCell ref="BD11:BE11"/>
+    <mergeCell ref="AM12:AN12"/>
+    <mergeCell ref="BD12:BE12"/>
+    <mergeCell ref="AM13:AN13"/>
+    <mergeCell ref="BD13:BE13"/>
+    <mergeCell ref="P2:T3"/>
+    <mergeCell ref="U2:AH3"/>
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="AS2:AW3"/>
+    <mergeCell ref="AX2:BB3"/>
+    <mergeCell ref="AO10:BC10"/>
+    <mergeCell ref="AO11:BC11"/>
+    <mergeCell ref="AO12:BC12"/>
+    <mergeCell ref="AO13:BC13"/>
     <mergeCell ref="BH1:BL1"/>
     <mergeCell ref="BC1:BG1"/>
     <mergeCell ref="BC2:BG3"/>
@@ -4145,22 +4727,11 @@
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="AX2:BB3"/>
-    <mergeCell ref="AO10:BC10"/>
-    <mergeCell ref="AO11:BC11"/>
-    <mergeCell ref="AO12:BC12"/>
-    <mergeCell ref="AO13:BC13"/>
-    <mergeCell ref="P2:T3"/>
-    <mergeCell ref="U2:AH3"/>
-    <mergeCell ref="AI2:AM3"/>
-    <mergeCell ref="AN2:AR3"/>
-    <mergeCell ref="AS2:AW3"/>
-    <mergeCell ref="AM11:AN11"/>
-    <mergeCell ref="BD11:BE11"/>
-    <mergeCell ref="AM12:AN12"/>
-    <mergeCell ref="BD12:BE12"/>
-    <mergeCell ref="AM13:AN13"/>
-    <mergeCell ref="BD13:BE13"/>
+    <mergeCell ref="AO14:BC14"/>
+    <mergeCell ref="AO18:BC18"/>
+    <mergeCell ref="AO15:BC15"/>
+    <mergeCell ref="AO16:BC16"/>
+    <mergeCell ref="AO17:BC17"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4171,7 +4742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4193,182 +4764,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="134" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="139" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="140" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="140" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="148" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="148" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="148" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="150"/>
-      <c r="AS1" s="134" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="137"/>
-      <c r="AX1" s="134" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="137"/>
-      <c r="BC1" s="130" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="132"/>
-      <c r="BF1" s="132"/>
-      <c r="BG1" s="133"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="151" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="151" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="156" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="156" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="157">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="158"/>
-      <c r="AG2" s="158"/>
-      <c r="AH2" s="158"/>
-      <c r="AI2" s="159"/>
-      <c r="AJ2" s="151" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="152"/>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="157">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="158"/>
-      <c r="AP2" s="158"/>
-      <c r="AQ2" s="158"/>
-      <c r="AR2" s="159"/>
-      <c r="AS2" s="120" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="120"/>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="157">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="158"/>
-      <c r="AZ2" s="158"/>
-      <c r="BA2" s="158"/>
-      <c r="BB2" s="159"/>
-      <c r="BC2" s="151" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="153"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -4625,28 +5196,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="BC2:BG2"/>
     <mergeCell ref="AJ1:AM1"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AW1"/>
     <mergeCell ref="AX1:BB1"/>
     <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="AE1:AI1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -4656,7 +5227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567342E5-F899-48BD-974B-0DC0FF996026}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4678,182 +5249,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="134" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="139" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="140" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="140" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="148" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="148" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="148" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="150"/>
-      <c r="AS1" s="134" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="137"/>
-      <c r="AX1" s="134" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="137"/>
-      <c r="BC1" s="130" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="132"/>
-      <c r="BF1" s="132"/>
-      <c r="BG1" s="133"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="151" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="151" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="156" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="156" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="157">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="158"/>
-      <c r="AG2" s="158"/>
-      <c r="AH2" s="158"/>
-      <c r="AI2" s="159"/>
-      <c r="AJ2" s="151" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="152"/>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="157">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="158"/>
-      <c r="AP2" s="158"/>
-      <c r="AQ2" s="158"/>
-      <c r="AR2" s="159"/>
-      <c r="AS2" s="120" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="120"/>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="157">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="158"/>
-      <c r="AZ2" s="158"/>
-      <c r="BA2" s="158"/>
-      <c r="BB2" s="159"/>
-      <c r="BC2" s="151" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="153"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5050,28 +5621,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="BC2:BG2"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BG1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="BC2:BG2"/>
-    <mergeCell ref="AJ1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5082,7 +5653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B661F1-2324-49A4-A317-7CE94BF662B6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5104,182 +5675,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="134" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="139" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="140" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="140" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="148" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="148" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="148" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="150"/>
-      <c r="AS1" s="134" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="137"/>
-      <c r="AX1" s="134" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="137"/>
-      <c r="BC1" s="130" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="132"/>
-      <c r="BF1" s="132"/>
-      <c r="BG1" s="133"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="151" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="151" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="156" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="156" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="157">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="158"/>
-      <c r="AG2" s="158"/>
-      <c r="AH2" s="158"/>
-      <c r="AI2" s="159"/>
-      <c r="AJ2" s="151" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="152"/>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="157">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="158"/>
-      <c r="AP2" s="158"/>
-      <c r="AQ2" s="158"/>
-      <c r="AR2" s="159"/>
-      <c r="AS2" s="120" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="120"/>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="157">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="158"/>
-      <c r="AZ2" s="158"/>
-      <c r="BA2" s="158"/>
-      <c r="BB2" s="159"/>
-      <c r="BC2" s="151" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="153"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5476,28 +6047,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
+    <mergeCell ref="BC2:BG2"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BG1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
     <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="BC2:BG2"/>
-    <mergeCell ref="AJ1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="BC1:BG1"/>
-    <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5508,7 +6079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5534,207 +6105,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="134" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="139" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="140" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="142"/>
-      <c r="U1" s="140" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="148" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="149"/>
-      <c r="AG1" s="149"/>
-      <c r="AH1" s="149"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="148" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="149"/>
-      <c r="AL1" s="149"/>
-      <c r="AM1" s="150"/>
-      <c r="AN1" s="148" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="149"/>
-      <c r="AP1" s="149"/>
-      <c r="AQ1" s="149"/>
-      <c r="AR1" s="150"/>
-      <c r="AS1" s="134" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="137"/>
-      <c r="AX1" s="134" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="135"/>
-      <c r="BA1" s="136"/>
-      <c r="BB1" s="137"/>
-      <c r="BC1" s="174" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="168" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="175"/>
-      <c r="BE1" s="175"/>
-      <c r="BF1" s="175"/>
-      <c r="BG1" s="175"/>
-      <c r="BH1" s="175"/>
-      <c r="BI1" s="175"/>
-      <c r="BJ1" s="175"/>
-      <c r="BK1" s="175"/>
-      <c r="BL1" s="175"/>
-      <c r="BM1" s="175"/>
-      <c r="BN1" s="175"/>
-      <c r="BO1" s="175"/>
-      <c r="BP1" s="175"/>
-      <c r="BQ1" s="175"/>
-      <c r="BR1" s="175"/>
-      <c r="BS1" s="175"/>
-      <c r="BT1" s="175"/>
+      <c r="BD1" s="169"/>
+      <c r="BE1" s="169"/>
+      <c r="BF1" s="169"/>
+      <c r="BG1" s="169"/>
+      <c r="BH1" s="169"/>
+      <c r="BI1" s="169"/>
+      <c r="BJ1" s="169"/>
+      <c r="BK1" s="169"/>
+      <c r="BL1" s="169"/>
+      <c r="BM1" s="169"/>
+      <c r="BN1" s="169"/>
+      <c r="BO1" s="169"/>
+      <c r="BP1" s="169"/>
+      <c r="BQ1" s="169"/>
+      <c r="BR1" s="169"/>
+      <c r="BS1" s="169"/>
+      <c r="BT1" s="169"/>
     </row>
     <row r="2" spans="1:72" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="151" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="151" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="156" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="154"/>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="156" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="154"/>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="157">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="158"/>
-      <c r="AG2" s="158"/>
-      <c r="AH2" s="158"/>
-      <c r="AI2" s="159"/>
-      <c r="AJ2" s="151" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="152"/>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="157">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="158"/>
-      <c r="AP2" s="158"/>
-      <c r="AQ2" s="158"/>
-      <c r="AR2" s="159"/>
-      <c r="AS2" s="120" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="120"/>
-      <c r="AU2" s="120"/>
-      <c r="AV2" s="120"/>
-      <c r="AW2" s="120"/>
-      <c r="AX2" s="157">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="158"/>
-      <c r="AZ2" s="158"/>
-      <c r="BA2" s="158"/>
-      <c r="BB2" s="159"/>
-      <c r="BC2" s="176" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="170" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="176"/>
-      <c r="BE2" s="176"/>
-      <c r="BF2" s="176"/>
-      <c r="BG2" s="176"/>
-      <c r="BH2" s="176"/>
-      <c r="BI2" s="176"/>
-      <c r="BJ2" s="176"/>
-      <c r="BK2" s="176"/>
-      <c r="BL2" s="176"/>
-      <c r="BM2" s="176"/>
-      <c r="BN2" s="176"/>
-      <c r="BO2" s="176"/>
-      <c r="BP2" s="176"/>
-      <c r="BQ2" s="176"/>
-      <c r="BR2" s="176"/>
-      <c r="BS2" s="176"/>
-      <c r="BT2" s="176"/>
+      <c r="BD2" s="170"/>
+      <c r="BE2" s="170"/>
+      <c r="BF2" s="170"/>
+      <c r="BG2" s="170"/>
+      <c r="BH2" s="170"/>
+      <c r="BI2" s="170"/>
+      <c r="BJ2" s="170"/>
+      <c r="BK2" s="170"/>
+      <c r="BL2" s="170"/>
+      <c r="BM2" s="170"/>
+      <c r="BN2" s="170"/>
+      <c r="BO2" s="170"/>
+      <c r="BP2" s="170"/>
+      <c r="BQ2" s="170"/>
+      <c r="BR2" s="170"/>
+      <c r="BS2" s="170"/>
+      <c r="BT2" s="170"/>
     </row>
     <row r="3" spans="1:72" s="4" customFormat="1" ht="10.5" customHeight="1">
       <c r="A3" s="2"/>
@@ -6018,10 +6589,10 @@
     </row>
     <row r="8" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
       <c r="A8" s="56"/>
-      <c r="C8" s="166">
+      <c r="C8" s="160">
         <v>1</v>
       </c>
-      <c r="D8" s="167"/>
+      <c r="D8" s="161"/>
       <c r="E8" s="65" t="s">
         <v>93</v>
       </c>
@@ -6420,14 +6991,14 @@
       <c r="A16" s="56"/>
       <c r="C16" s="73"/>
       <c r="E16" s="76"/>
-      <c r="F16" s="168" t="s">
+      <c r="F16" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="169"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="169"/>
-      <c r="J16" s="169"/>
-      <c r="K16" s="170"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
+      <c r="I16" s="163"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
       <c r="L16" s="67" t="s">
         <v>89</v>
       </c>
@@ -6492,12 +7063,12 @@
       <c r="A17" s="56"/>
       <c r="C17" s="73"/>
       <c r="E17" s="76"/>
-      <c r="F17" s="171"/>
-      <c r="G17" s="172"/>
-      <c r="H17" s="172"/>
-      <c r="I17" s="172"/>
-      <c r="J17" s="172"/>
-      <c r="K17" s="173"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="166"/>
+      <c r="K17" s="167"/>
       <c r="L17" s="67" t="s">
         <v>90</v>
       </c>
@@ -7142,56 +7713,56 @@
       <c r="R31" s="66"/>
       <c r="S31" s="66"/>
       <c r="T31" s="68"/>
-      <c r="U31" s="160" t="s">
+      <c r="U31" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V31" s="161"/>
-      <c r="W31" s="161"/>
-      <c r="X31" s="161"/>
-      <c r="Y31" s="161"/>
-      <c r="Z31" s="161"/>
-      <c r="AA31" s="161"/>
-      <c r="AB31" s="161"/>
-      <c r="AC31" s="161"/>
-      <c r="AD31" s="161"/>
-      <c r="AE31" s="161"/>
-      <c r="AF31" s="162"/>
-      <c r="AG31" s="160" t="s">
+      <c r="V31" s="172"/>
+      <c r="W31" s="172"/>
+      <c r="X31" s="172"/>
+      <c r="Y31" s="172"/>
+      <c r="Z31" s="172"/>
+      <c r="AA31" s="172"/>
+      <c r="AB31" s="172"/>
+      <c r="AC31" s="172"/>
+      <c r="AD31" s="172"/>
+      <c r="AE31" s="172"/>
+      <c r="AF31" s="173"/>
+      <c r="AG31" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH31" s="161"/>
-      <c r="AI31" s="161"/>
-      <c r="AJ31" s="161"/>
-      <c r="AK31" s="161"/>
-      <c r="AL31" s="161"/>
-      <c r="AM31" s="161"/>
-      <c r="AN31" s="161"/>
-      <c r="AO31" s="161"/>
-      <c r="AP31" s="161"/>
-      <c r="AQ31" s="161"/>
-      <c r="AR31" s="162"/>
-      <c r="AS31" s="163" t="s">
+      <c r="AH31" s="172"/>
+      <c r="AI31" s="172"/>
+      <c r="AJ31" s="172"/>
+      <c r="AK31" s="172"/>
+      <c r="AL31" s="172"/>
+      <c r="AM31" s="172"/>
+      <c r="AN31" s="172"/>
+      <c r="AO31" s="172"/>
+      <c r="AP31" s="172"/>
+      <c r="AQ31" s="172"/>
+      <c r="AR31" s="173"/>
+      <c r="AS31" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT31" s="164"/>
-      <c r="AU31" s="164"/>
-      <c r="AV31" s="164"/>
-      <c r="AW31" s="164"/>
-      <c r="AX31" s="164"/>
-      <c r="AY31" s="164"/>
-      <c r="AZ31" s="164"/>
-      <c r="BA31" s="164"/>
-      <c r="BB31" s="164"/>
-      <c r="BC31" s="164"/>
-      <c r="BD31" s="164"/>
-      <c r="BE31" s="164"/>
-      <c r="BF31" s="164"/>
-      <c r="BG31" s="164"/>
-      <c r="BH31" s="164"/>
-      <c r="BI31" s="164"/>
-      <c r="BJ31" s="164"/>
-      <c r="BK31" s="164"/>
-      <c r="BL31" s="165"/>
+      <c r="AT31" s="175"/>
+      <c r="AU31" s="175"/>
+      <c r="AV31" s="175"/>
+      <c r="AW31" s="175"/>
+      <c r="AX31" s="175"/>
+      <c r="AY31" s="175"/>
+      <c r="AZ31" s="175"/>
+      <c r="BA31" s="175"/>
+      <c r="BB31" s="175"/>
+      <c r="BC31" s="175"/>
+      <c r="BD31" s="175"/>
+      <c r="BE31" s="175"/>
+      <c r="BF31" s="175"/>
+      <c r="BG31" s="175"/>
+      <c r="BH31" s="175"/>
+      <c r="BI31" s="175"/>
+      <c r="BJ31" s="175"/>
+      <c r="BK31" s="175"/>
+      <c r="BL31" s="176"/>
       <c r="BR31" s="84"/>
       <c r="BT31" s="64"/>
     </row>
@@ -7220,56 +7791,56 @@
       <c r="R32" s="66"/>
       <c r="S32" s="66"/>
       <c r="T32" s="68"/>
-      <c r="U32" s="160" t="s">
+      <c r="U32" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V32" s="161"/>
-      <c r="W32" s="161"/>
-      <c r="X32" s="161"/>
-      <c r="Y32" s="161"/>
-      <c r="Z32" s="161"/>
-      <c r="AA32" s="161"/>
-      <c r="AB32" s="161"/>
-      <c r="AC32" s="161"/>
-      <c r="AD32" s="161"/>
-      <c r="AE32" s="161"/>
-      <c r="AF32" s="162"/>
-      <c r="AG32" s="160" t="s">
+      <c r="V32" s="172"/>
+      <c r="W32" s="172"/>
+      <c r="X32" s="172"/>
+      <c r="Y32" s="172"/>
+      <c r="Z32" s="172"/>
+      <c r="AA32" s="172"/>
+      <c r="AB32" s="172"/>
+      <c r="AC32" s="172"/>
+      <c r="AD32" s="172"/>
+      <c r="AE32" s="172"/>
+      <c r="AF32" s="173"/>
+      <c r="AG32" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH32" s="161"/>
-      <c r="AI32" s="161"/>
-      <c r="AJ32" s="161"/>
-      <c r="AK32" s="161"/>
-      <c r="AL32" s="161"/>
-      <c r="AM32" s="161"/>
-      <c r="AN32" s="161"/>
-      <c r="AO32" s="161"/>
-      <c r="AP32" s="161"/>
-      <c r="AQ32" s="161"/>
-      <c r="AR32" s="162"/>
-      <c r="AS32" s="163" t="s">
+      <c r="AH32" s="172"/>
+      <c r="AI32" s="172"/>
+      <c r="AJ32" s="172"/>
+      <c r="AK32" s="172"/>
+      <c r="AL32" s="172"/>
+      <c r="AM32" s="172"/>
+      <c r="AN32" s="172"/>
+      <c r="AO32" s="172"/>
+      <c r="AP32" s="172"/>
+      <c r="AQ32" s="172"/>
+      <c r="AR32" s="173"/>
+      <c r="AS32" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT32" s="164"/>
-      <c r="AU32" s="164"/>
-      <c r="AV32" s="164"/>
-      <c r="AW32" s="164"/>
-      <c r="AX32" s="164"/>
-      <c r="AY32" s="164"/>
-      <c r="AZ32" s="164"/>
-      <c r="BA32" s="164"/>
-      <c r="BB32" s="164"/>
-      <c r="BC32" s="164"/>
-      <c r="BD32" s="164"/>
-      <c r="BE32" s="164"/>
-      <c r="BF32" s="164"/>
-      <c r="BG32" s="164"/>
-      <c r="BH32" s="164"/>
-      <c r="BI32" s="164"/>
-      <c r="BJ32" s="164"/>
-      <c r="BK32" s="164"/>
-      <c r="BL32" s="165"/>
+      <c r="AT32" s="175"/>
+      <c r="AU32" s="175"/>
+      <c r="AV32" s="175"/>
+      <c r="AW32" s="175"/>
+      <c r="AX32" s="175"/>
+      <c r="AY32" s="175"/>
+      <c r="AZ32" s="175"/>
+      <c r="BA32" s="175"/>
+      <c r="BB32" s="175"/>
+      <c r="BC32" s="175"/>
+      <c r="BD32" s="175"/>
+      <c r="BE32" s="175"/>
+      <c r="BF32" s="175"/>
+      <c r="BG32" s="175"/>
+      <c r="BH32" s="175"/>
+      <c r="BI32" s="175"/>
+      <c r="BJ32" s="175"/>
+      <c r="BK32" s="175"/>
+      <c r="BL32" s="176"/>
       <c r="BR32" s="84"/>
       <c r="BT32" s="64"/>
     </row>
@@ -7436,10 +8007,10 @@
     </row>
     <row r="37" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
       <c r="A37" s="56"/>
-      <c r="C37" s="166">
+      <c r="C37" s="160">
         <v>1</v>
       </c>
-      <c r="D37" s="167"/>
+      <c r="D37" s="161"/>
       <c r="E37" s="65" t="s">
         <v>96</v>
       </c>
@@ -7838,14 +8409,14 @@
       <c r="A45" s="56"/>
       <c r="C45" s="73"/>
       <c r="E45" s="76"/>
-      <c r="F45" s="168" t="s">
+      <c r="F45" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169"/>
-      <c r="I45" s="169"/>
-      <c r="J45" s="169"/>
-      <c r="K45" s="170"/>
+      <c r="G45" s="163"/>
+      <c r="H45" s="163"/>
+      <c r="I45" s="163"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
       <c r="L45" s="67" t="s">
         <v>89</v>
       </c>
@@ -7910,12 +8481,12 @@
       <c r="A46" s="56"/>
       <c r="C46" s="73"/>
       <c r="E46" s="76"/>
-      <c r="F46" s="171"/>
-      <c r="G46" s="172"/>
-      <c r="H46" s="172"/>
-      <c r="I46" s="172"/>
-      <c r="J46" s="172"/>
-      <c r="K46" s="173"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="166"/>
+      <c r="H46" s="166"/>
+      <c r="I46" s="166"/>
+      <c r="J46" s="166"/>
+      <c r="K46" s="167"/>
       <c r="L46" s="67" t="s">
         <v>90</v>
       </c>
@@ -8560,56 +9131,56 @@
       <c r="R60" s="66"/>
       <c r="S60" s="66"/>
       <c r="T60" s="68"/>
-      <c r="U60" s="160" t="s">
+      <c r="U60" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V60" s="161"/>
-      <c r="W60" s="161"/>
-      <c r="X60" s="161"/>
-      <c r="Y60" s="161"/>
-      <c r="Z60" s="161"/>
-      <c r="AA60" s="161"/>
-      <c r="AB60" s="161"/>
-      <c r="AC60" s="161"/>
-      <c r="AD60" s="161"/>
-      <c r="AE60" s="161"/>
-      <c r="AF60" s="162"/>
-      <c r="AG60" s="160" t="s">
+      <c r="V60" s="172"/>
+      <c r="W60" s="172"/>
+      <c r="X60" s="172"/>
+      <c r="Y60" s="172"/>
+      <c r="Z60" s="172"/>
+      <c r="AA60" s="172"/>
+      <c r="AB60" s="172"/>
+      <c r="AC60" s="172"/>
+      <c r="AD60" s="172"/>
+      <c r="AE60" s="172"/>
+      <c r="AF60" s="173"/>
+      <c r="AG60" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH60" s="161"/>
-      <c r="AI60" s="161"/>
-      <c r="AJ60" s="161"/>
-      <c r="AK60" s="161"/>
-      <c r="AL60" s="161"/>
-      <c r="AM60" s="161"/>
-      <c r="AN60" s="161"/>
-      <c r="AO60" s="161"/>
-      <c r="AP60" s="161"/>
-      <c r="AQ60" s="161"/>
-      <c r="AR60" s="162"/>
-      <c r="AS60" s="163" t="s">
+      <c r="AH60" s="172"/>
+      <c r="AI60" s="172"/>
+      <c r="AJ60" s="172"/>
+      <c r="AK60" s="172"/>
+      <c r="AL60" s="172"/>
+      <c r="AM60" s="172"/>
+      <c r="AN60" s="172"/>
+      <c r="AO60" s="172"/>
+      <c r="AP60" s="172"/>
+      <c r="AQ60" s="172"/>
+      <c r="AR60" s="173"/>
+      <c r="AS60" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT60" s="164"/>
-      <c r="AU60" s="164"/>
-      <c r="AV60" s="164"/>
-      <c r="AW60" s="164"/>
-      <c r="AX60" s="164"/>
-      <c r="AY60" s="164"/>
-      <c r="AZ60" s="164"/>
-      <c r="BA60" s="164"/>
-      <c r="BB60" s="164"/>
-      <c r="BC60" s="164"/>
-      <c r="BD60" s="164"/>
-      <c r="BE60" s="164"/>
-      <c r="BF60" s="164"/>
-      <c r="BG60" s="164"/>
-      <c r="BH60" s="164"/>
-      <c r="BI60" s="164"/>
-      <c r="BJ60" s="164"/>
-      <c r="BK60" s="164"/>
-      <c r="BL60" s="165"/>
+      <c r="AT60" s="175"/>
+      <c r="AU60" s="175"/>
+      <c r="AV60" s="175"/>
+      <c r="AW60" s="175"/>
+      <c r="AX60" s="175"/>
+      <c r="AY60" s="175"/>
+      <c r="AZ60" s="175"/>
+      <c r="BA60" s="175"/>
+      <c r="BB60" s="175"/>
+      <c r="BC60" s="175"/>
+      <c r="BD60" s="175"/>
+      <c r="BE60" s="175"/>
+      <c r="BF60" s="175"/>
+      <c r="BG60" s="175"/>
+      <c r="BH60" s="175"/>
+      <c r="BI60" s="175"/>
+      <c r="BJ60" s="175"/>
+      <c r="BK60" s="175"/>
+      <c r="BL60" s="176"/>
       <c r="BR60" s="84"/>
       <c r="BT60" s="64"/>
     </row>
@@ -8638,56 +9209,56 @@
       <c r="R61" s="66"/>
       <c r="S61" s="66"/>
       <c r="T61" s="68"/>
-      <c r="U61" s="160" t="s">
+      <c r="U61" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V61" s="161"/>
-      <c r="W61" s="161"/>
-      <c r="X61" s="161"/>
-      <c r="Y61" s="161"/>
-      <c r="Z61" s="161"/>
-      <c r="AA61" s="161"/>
-      <c r="AB61" s="161"/>
-      <c r="AC61" s="161"/>
-      <c r="AD61" s="161"/>
-      <c r="AE61" s="161"/>
-      <c r="AF61" s="162"/>
-      <c r="AG61" s="160" t="s">
+      <c r="V61" s="172"/>
+      <c r="W61" s="172"/>
+      <c r="X61" s="172"/>
+      <c r="Y61" s="172"/>
+      <c r="Z61" s="172"/>
+      <c r="AA61" s="172"/>
+      <c r="AB61" s="172"/>
+      <c r="AC61" s="172"/>
+      <c r="AD61" s="172"/>
+      <c r="AE61" s="172"/>
+      <c r="AF61" s="173"/>
+      <c r="AG61" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH61" s="161"/>
-      <c r="AI61" s="161"/>
-      <c r="AJ61" s="161"/>
-      <c r="AK61" s="161"/>
-      <c r="AL61" s="161"/>
-      <c r="AM61" s="161"/>
-      <c r="AN61" s="161"/>
-      <c r="AO61" s="161"/>
-      <c r="AP61" s="161"/>
-      <c r="AQ61" s="161"/>
-      <c r="AR61" s="162"/>
-      <c r="AS61" s="163" t="s">
+      <c r="AH61" s="172"/>
+      <c r="AI61" s="172"/>
+      <c r="AJ61" s="172"/>
+      <c r="AK61" s="172"/>
+      <c r="AL61" s="172"/>
+      <c r="AM61" s="172"/>
+      <c r="AN61" s="172"/>
+      <c r="AO61" s="172"/>
+      <c r="AP61" s="172"/>
+      <c r="AQ61" s="172"/>
+      <c r="AR61" s="173"/>
+      <c r="AS61" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT61" s="164"/>
-      <c r="AU61" s="164"/>
-      <c r="AV61" s="164"/>
-      <c r="AW61" s="164"/>
-      <c r="AX61" s="164"/>
-      <c r="AY61" s="164"/>
-      <c r="AZ61" s="164"/>
-      <c r="BA61" s="164"/>
-      <c r="BB61" s="164"/>
-      <c r="BC61" s="164"/>
-      <c r="BD61" s="164"/>
-      <c r="BE61" s="164"/>
-      <c r="BF61" s="164"/>
-      <c r="BG61" s="164"/>
-      <c r="BH61" s="164"/>
-      <c r="BI61" s="164"/>
-      <c r="BJ61" s="164"/>
-      <c r="BK61" s="164"/>
-      <c r="BL61" s="165"/>
+      <c r="AT61" s="175"/>
+      <c r="AU61" s="175"/>
+      <c r="AV61" s="175"/>
+      <c r="AW61" s="175"/>
+      <c r="AX61" s="175"/>
+      <c r="AY61" s="175"/>
+      <c r="AZ61" s="175"/>
+      <c r="BA61" s="175"/>
+      <c r="BB61" s="175"/>
+      <c r="BC61" s="175"/>
+      <c r="BD61" s="175"/>
+      <c r="BE61" s="175"/>
+      <c r="BF61" s="175"/>
+      <c r="BG61" s="175"/>
+      <c r="BH61" s="175"/>
+      <c r="BI61" s="175"/>
+      <c r="BJ61" s="175"/>
+      <c r="BK61" s="175"/>
+      <c r="BL61" s="176"/>
       <c r="BR61" s="84"/>
       <c r="BT61" s="64"/>
     </row>
@@ -8766,20 +9337,14 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F16:K17"/>
-    <mergeCell ref="AE1:AI1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:O2"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="U61:AF61"/>
+    <mergeCell ref="AG61:AR61"/>
+    <mergeCell ref="AS61:BL61"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F45:K46"/>
+    <mergeCell ref="U60:AF60"/>
+    <mergeCell ref="AG60:AR60"/>
+    <mergeCell ref="AS60:BL60"/>
     <mergeCell ref="BC1:BT1"/>
     <mergeCell ref="BC2:BT2"/>
     <mergeCell ref="U32:AF32"/>
@@ -8796,14 +9361,20 @@
     <mergeCell ref="AN2:AR2"/>
     <mergeCell ref="AS2:AW2"/>
     <mergeCell ref="AX2:BB2"/>
-    <mergeCell ref="U61:AF61"/>
-    <mergeCell ref="AG61:AR61"/>
-    <mergeCell ref="AS61:BL61"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F45:K46"/>
-    <mergeCell ref="U60:AF60"/>
-    <mergeCell ref="AG60:AR60"/>
-    <mergeCell ref="AS60:BL60"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F16:K17"/>
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AD1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="U2:AD2"/>
+    <mergeCell ref="AE2:AI2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8813,7 +9384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:B12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>

--- a/design-detail/DD_Staff_v1.0.xlsx
+++ b/design-detail/DD_Staff_v1.0.xlsx
@@ -5,50 +5,52 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Document\Detail-design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\design-detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728A4DF6-2E26-42CA-BFDB-5A04330B25B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA9ABA2-1DEB-4ADC-88FF-76C482C73E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="His" sheetId="32" r:id="rId1"/>
-    <sheet name="Overview" sheetId="28" r:id="rId2"/>
-    <sheet name="SQL" sheetId="35" r:id="rId3"/>
-    <sheet name="ClassDiagram" sheetId="42" r:id="rId4"/>
-    <sheet name="SequenceDiagram" sheetId="43" r:id="rId5"/>
-    <sheet name="APIs" sheetId="36" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="34" state="hidden" r:id="rId7"/>
+    <sheet name="Layout" sheetId="45" r:id="rId2"/>
+    <sheet name="Overview" sheetId="28" r:id="rId3"/>
+    <sheet name="SQL" sheetId="35" r:id="rId4"/>
+    <sheet name="ClassDiagram" sheetId="42" r:id="rId5"/>
+    <sheet name="SequenceDiagram" sheetId="43" r:id="rId6"/>
+    <sheet name="APIs" sheetId="36" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="34" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_Key1" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Key1" localSheetId="4" hidden="1">#REF!</definedName>
+    <definedName name="_Key1" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="_Key1" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Key1" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Key1" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
+    <definedName name="_Regression_X" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Regression_X" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Regression_X" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Regression_X" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Regression_X" hidden="1">#REF!</definedName>
+    <definedName name="_Sort" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="_Sort" localSheetId="4" hidden="1">#REF!</definedName>
     <definedName name="_Sort" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="_Sort" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="_Sort" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="_Sort" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">APIs!$A$1:$BT$66</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">ClassDiagram!$A$1:$BG$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">APIs!$A$1:$BT$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">ClassDiagram!$A$1:$BG$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">His!$A$1:$E$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">SequenceDiagram!$A$1:$BG$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">SQL!$A$1:$BG$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Layout!$A$1:$BL$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">SequenceDiagram!$A$1:$BG$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">SQL!$A$1:$BG$26</definedName>
+    <definedName name="関連表" localSheetId="6" hidden="1">#REF!</definedName>
+    <definedName name="関連表" localSheetId="4" hidden="1">#REF!</definedName>
+    <definedName name="関連表" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="関連表" localSheetId="5" hidden="1">#REF!</definedName>
     <definedName name="関連表" localSheetId="3" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="4" hidden="1">#REF!</definedName>
-    <definedName name="関連表" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="関連表" hidden="1">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -67,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="111">
   <si>
     <t>Label</t>
   </si>
@@ -398,6 +400,12 @@
   </si>
   <si>
     <t>where ST.FIRST_NAME = %s order by ST.CREATED_DATE desc limit 1</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>figma</t>
   </si>
 </sst>
 </file>
@@ -1789,7 +1797,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1958,6 +1966,129 @@
     <xf numFmtId="14" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="40" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="133" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1967,6 +2098,147 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="38" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="29" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="28" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="41" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="43" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="40" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="39" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1979,146 +2251,14 @@
     <xf numFmtId="49" fontId="47" fillId="0" borderId="42" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="38" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="29" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="28" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="41" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="43" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="40" xfId="76" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="20" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="4" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="21" xfId="130" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="24" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="22" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="23" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="18" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="15" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="19" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="23" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="37" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="26" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="4" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="38" borderId="25" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="24" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="22" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -2138,108 +2278,12 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="130" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="20" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="4" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="21" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="40" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="20" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="4" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="21" xfId="133" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="17" xfId="133" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2258,27 +2302,18 @@
     <xf numFmtId="0" fontId="51" fillId="40" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="16" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2293,36 +2328,6 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="21" xfId="133" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="16" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="37" borderId="0" xfId="130" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="8" xfId="130" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="144">
@@ -2493,6 +2498,55 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>30939</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>7950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C0CD704-5B59-716D-15CC-16A198511146}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="998220" y="1531620"/>
+          <a:ext cx="5296359" cy="3810330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>45720</xdr:colOff>
       <xdr:row>12</xdr:row>
@@ -2538,7 +2592,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2587,7 +2641,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3021,12 +3075,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
     </row>
     <row r="3" spans="2:5">
       <c r="B3" s="48" t="s">
@@ -3060,7 +3114,9 @@
       <c r="B5" s="53"/>
       <c r="C5" s="55"/>
       <c r="D5" s="54"/>
-      <c r="E5" s="41"/>
+      <c r="E5" s="41" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="41"/>
@@ -3180,11 +3236,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222134E3-A126-43B4-9320-68F74CBADA6F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BM25"/>
+  <dimension ref="A1:BM9"/>
   <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="3.109375" style="2" customWidth="1"/>
@@ -3201,248 +3257,248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:65" s="5" customFormat="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="87"/>
-      <c r="AE1" s="87"/>
-      <c r="AF1" s="87"/>
-      <c r="AG1" s="87"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="99" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AJ1" s="100"/>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="99" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AT1" s="100"/>
-      <c r="AU1" s="100"/>
-      <c r="AV1" s="100"/>
-      <c r="AW1" s="101"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="75"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="73" t="s">
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="109"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="BD1" s="74"/>
-      <c r="BE1" s="74"/>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="69" t="s">
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="109"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BI1" s="70"/>
-      <c r="BJ1" s="71"/>
-      <c r="BK1" s="71"/>
-      <c r="BL1" s="72"/>
+      <c r="BI1" s="104"/>
+      <c r="BJ1" s="105"/>
+      <c r="BK1" s="105"/>
+      <c r="BL1" s="106"/>
       <c r="BM1" s="2"/>
     </row>
     <row r="2" spans="1:65" s="5" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="89" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="95" t="s">
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="105" t="s">
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="96"/>
-      <c r="U2" s="105" t="s">
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="96"/>
-      <c r="AI2" s="77">
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="111">
         <v>45701</v>
       </c>
-      <c r="AJ2" s="78"/>
-      <c r="AK2" s="78"/>
-      <c r="AL2" s="78"/>
-      <c r="AM2" s="79"/>
-      <c r="AN2" s="89" t="s">
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="112"/>
+      <c r="AL2" s="112"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="123" t="s">
         <v>56</v>
       </c>
-      <c r="AO2" s="107"/>
-      <c r="AP2" s="107"/>
-      <c r="AQ2" s="107"/>
-      <c r="AR2" s="107"/>
-      <c r="AS2" s="77">
+      <c r="AO2" s="144"/>
+      <c r="AP2" s="144"/>
+      <c r="AQ2" s="144"/>
+      <c r="AR2" s="144"/>
+      <c r="AS2" s="111">
         <v>45707</v>
       </c>
-      <c r="AT2" s="78"/>
-      <c r="AU2" s="78"/>
-      <c r="AV2" s="78"/>
-      <c r="AW2" s="79"/>
-      <c r="AX2" s="83" t="s">
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="AY2" s="83"/>
-      <c r="AZ2" s="83"/>
-      <c r="BA2" s="83"/>
-      <c r="BB2" s="83"/>
-      <c r="BC2" s="77">
+      <c r="AY2" s="117"/>
+      <c r="AZ2" s="117"/>
+      <c r="BA2" s="117"/>
+      <c r="BB2" s="117"/>
+      <c r="BC2" s="111">
         <v>45701</v>
       </c>
-      <c r="BD2" s="78"/>
-      <c r="BE2" s="78"/>
-      <c r="BF2" s="78"/>
-      <c r="BG2" s="79"/>
-      <c r="BH2" s="83" t="s">
+      <c r="BD2" s="112"/>
+      <c r="BE2" s="112"/>
+      <c r="BF2" s="112"/>
+      <c r="BG2" s="113"/>
+      <c r="BH2" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="BI2" s="83"/>
-      <c r="BJ2" s="83"/>
-      <c r="BK2" s="83"/>
-      <c r="BL2" s="83"/>
+      <c r="BI2" s="117"/>
+      <c r="BJ2" s="117"/>
+      <c r="BK2" s="117"/>
+      <c r="BL2" s="117"/>
       <c r="BM2" s="2"/>
     </row>
     <row r="3" spans="1:65" s="5" customFormat="1" ht="10.5" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="94"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="97"/>
-      <c r="Y3" s="97"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="97"/>
-      <c r="AC3" s="97"/>
-      <c r="AD3" s="97"/>
-      <c r="AE3" s="97"/>
-      <c r="AF3" s="97"/>
-      <c r="AG3" s="97"/>
-      <c r="AH3" s="98"/>
-      <c r="AI3" s="80"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="82"/>
-      <c r="AN3" s="108"/>
-      <c r="AO3" s="109"/>
-      <c r="AP3" s="109"/>
-      <c r="AQ3" s="109"/>
-      <c r="AR3" s="109"/>
-      <c r="AS3" s="80"/>
-      <c r="AT3" s="81"/>
-      <c r="AU3" s="81"/>
-      <c r="AV3" s="81"/>
-      <c r="AW3" s="82"/>
-      <c r="AX3" s="83"/>
-      <c r="AY3" s="83"/>
-      <c r="AZ3" s="83"/>
-      <c r="BA3" s="83"/>
-      <c r="BB3" s="83"/>
-      <c r="BC3" s="80"/>
-      <c r="BD3" s="81"/>
-      <c r="BE3" s="81"/>
-      <c r="BF3" s="81"/>
-      <c r="BG3" s="82"/>
-      <c r="BH3" s="83"/>
-      <c r="BI3" s="83"/>
-      <c r="BJ3" s="83"/>
-      <c r="BK3" s="83"/>
-      <c r="BL3" s="83"/>
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="132"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+      <c r="AF3" s="131"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="116"/>
+      <c r="AN3" s="145"/>
+      <c r="AO3" s="146"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="146"/>
+      <c r="AR3" s="146"/>
+      <c r="AS3" s="114"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="117"/>
+      <c r="AY3" s="117"/>
+      <c r="AZ3" s="117"/>
+      <c r="BA3" s="117"/>
+      <c r="BB3" s="117"/>
+      <c r="BC3" s="114"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="115"/>
+      <c r="BF3" s="115"/>
+      <c r="BG3" s="116"/>
+      <c r="BH3" s="117"/>
+      <c r="BI3" s="117"/>
+      <c r="BJ3" s="117"/>
+      <c r="BK3" s="117"/>
+      <c r="BL3" s="117"/>
       <c r="BM3" s="2"/>
     </row>
     <row r="4" spans="1:65" s="5" customFormat="1" ht="9.75" customHeight="1">
@@ -3658,6 +3714,523 @@
       <c r="BL8" s="15"/>
     </row>
     <row r="9" spans="1:65">
+      <c r="B9" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="AI2:AM3"/>
+    <mergeCell ref="AN2:AR3"/>
+    <mergeCell ref="AS2:AW3"/>
+    <mergeCell ref="AX2:BB3"/>
+    <mergeCell ref="BC2:BG3"/>
+    <mergeCell ref="BH2:BL3"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BG1"/>
+    <mergeCell ref="BH1:BL1"/>
+    <mergeCell ref="A2:E3"/>
+    <mergeCell ref="F2:J3"/>
+    <mergeCell ref="K2:O3"/>
+    <mergeCell ref="P2:T3"/>
+    <mergeCell ref="U2:AH3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="U1:AH1"/>
+    <mergeCell ref="AI1:AM1"/>
+  </mergeCells>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;P/&amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BM25"/>
+  <sheetFormatPr defaultColWidth="2.33203125" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="2" width="3.109375" style="2" customWidth="1"/>
+    <col min="3" max="5" width="2.77734375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="2.33203125" style="2"/>
+    <col min="8" max="8" width="2.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="3" style="2" customWidth="1"/>
+    <col min="10" max="10" width="3.44140625" style="2" customWidth="1"/>
+    <col min="11" max="46" width="2.33203125" style="2"/>
+    <col min="47" max="47" width="2.88671875" style="2" customWidth="1"/>
+    <col min="48" max="48" width="2.6640625" style="2" customWidth="1"/>
+    <col min="49" max="49" width="2.77734375" style="2" customWidth="1"/>
+    <col min="50" max="16384" width="2.33203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:65" s="5" customFormat="1">
+      <c r="A1" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="122"/>
+      <c r="AI1" s="133" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="133" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="135"/>
+      <c r="AX1" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY1" s="109"/>
+      <c r="AZ1" s="109"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="109"/>
+      <c r="BG1" s="110"/>
+      <c r="BH1" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="BI1" s="104"/>
+      <c r="BJ1" s="105"/>
+      <c r="BK1" s="105"/>
+      <c r="BL1" s="106"/>
+      <c r="BM1" s="2"/>
+    </row>
+    <row r="2" spans="1:65" s="5" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A2" s="123" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="123" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="129" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="130"/>
+      <c r="U2" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
+      <c r="X2" s="129"/>
+      <c r="Y2" s="129"/>
+      <c r="Z2" s="129"/>
+      <c r="AA2" s="129"/>
+      <c r="AB2" s="129"/>
+      <c r="AC2" s="129"/>
+      <c r="AD2" s="129"/>
+      <c r="AE2" s="129"/>
+      <c r="AF2" s="129"/>
+      <c r="AG2" s="129"/>
+      <c r="AH2" s="130"/>
+      <c r="AI2" s="111">
+        <v>45701</v>
+      </c>
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="112"/>
+      <c r="AL2" s="112"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="123" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO2" s="144"/>
+      <c r="AP2" s="144"/>
+      <c r="AQ2" s="144"/>
+      <c r="AR2" s="144"/>
+      <c r="AS2" s="111">
+        <v>45707</v>
+      </c>
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="112"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY2" s="117"/>
+      <c r="AZ2" s="117"/>
+      <c r="BA2" s="117"/>
+      <c r="BB2" s="117"/>
+      <c r="BC2" s="111">
+        <v>45701</v>
+      </c>
+      <c r="BD2" s="112"/>
+      <c r="BE2" s="112"/>
+      <c r="BF2" s="112"/>
+      <c r="BG2" s="113"/>
+      <c r="BH2" s="117" t="s">
+        <v>56</v>
+      </c>
+      <c r="BI2" s="117"/>
+      <c r="BJ2" s="117"/>
+      <c r="BK2" s="117"/>
+      <c r="BL2" s="117"/>
+      <c r="BM2" s="2"/>
+    </row>
+    <row r="3" spans="1:65" s="5" customFormat="1" ht="10.5" customHeight="1">
+      <c r="A3" s="126"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="131"/>
+      <c r="S3" s="131"/>
+      <c r="T3" s="132"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="131"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="131"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="131"/>
+      <c r="AF3" s="131"/>
+      <c r="AG3" s="131"/>
+      <c r="AH3" s="132"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="115"/>
+      <c r="AK3" s="115"/>
+      <c r="AL3" s="115"/>
+      <c r="AM3" s="116"/>
+      <c r="AN3" s="145"/>
+      <c r="AO3" s="146"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="146"/>
+      <c r="AR3" s="146"/>
+      <c r="AS3" s="114"/>
+      <c r="AT3" s="115"/>
+      <c r="AU3" s="115"/>
+      <c r="AV3" s="115"/>
+      <c r="AW3" s="116"/>
+      <c r="AX3" s="117"/>
+      <c r="AY3" s="117"/>
+      <c r="AZ3" s="117"/>
+      <c r="BA3" s="117"/>
+      <c r="BB3" s="117"/>
+      <c r="BC3" s="114"/>
+      <c r="BD3" s="115"/>
+      <c r="BE3" s="115"/>
+      <c r="BF3" s="115"/>
+      <c r="BG3" s="116"/>
+      <c r="BH3" s="117"/>
+      <c r="BI3" s="117"/>
+      <c r="BJ3" s="117"/>
+      <c r="BK3" s="117"/>
+      <c r="BL3" s="117"/>
+      <c r="BM3" s="2"/>
+    </row>
+    <row r="4" spans="1:65" s="5" customFormat="1" ht="9.75" customHeight="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="42"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="42"/>
+      <c r="AM4" s="42"/>
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="42"/>
+      <c r="AU4" s="42"/>
+      <c r="AV4" s="42"/>
+      <c r="AW4" s="42"/>
+      <c r="AX4" s="52"/>
+      <c r="AY4" s="52"/>
+      <c r="AZ4" s="52"/>
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="52"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="44"/>
+      <c r="BH4" s="47"/>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="43"/>
+      <c r="BK4" s="43"/>
+      <c r="BL4" s="45"/>
+      <c r="BM4" s="2"/>
+    </row>
+    <row r="5" spans="1:65">
+      <c r="A5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="10"/>
+      <c r="AH5" s="10"/>
+      <c r="AI5" s="10"/>
+      <c r="AJ5" s="10"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="10"/>
+      <c r="AN5" s="10"/>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="10"/>
+      <c r="AS5" s="10"/>
+      <c r="AT5" s="10"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="10"/>
+      <c r="AW5" s="10"/>
+      <c r="AX5" s="10"/>
+      <c r="AY5" s="10"/>
+      <c r="AZ5" s="10"/>
+      <c r="BA5" s="10"/>
+      <c r="BB5" s="10"/>
+      <c r="BC5" s="10"/>
+      <c r="BD5" s="10"/>
+      <c r="BE5" s="10"/>
+      <c r="BF5" s="10"/>
+      <c r="BG5" s="10"/>
+      <c r="BH5" s="10"/>
+      <c r="BI5" s="10"/>
+      <c r="BJ5" s="10"/>
+      <c r="BK5" s="10"/>
+      <c r="BL5" s="11"/>
+    </row>
+    <row r="6" spans="1:65">
+      <c r="A6" s="13"/>
+      <c r="BL6" s="3"/>
+    </row>
+    <row r="7" spans="1:65">
+      <c r="A7" s="13"/>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="BL7" s="3"/>
+    </row>
+    <row r="8" spans="1:65">
+      <c r="A8" s="14"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+      <c r="BI8" s="12"/>
+      <c r="BJ8" s="12"/>
+      <c r="BK8" s="12"/>
+      <c r="BL8" s="15"/>
+    </row>
+    <row r="9" spans="1:65">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -3699,23 +4272,23 @@
         <v>24</v>
       </c>
       <c r="AN10" s="19"/>
-      <c r="AO10" s="102" t="s">
+      <c r="AO10" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="AP10" s="103"/>
-      <c r="AQ10" s="103"/>
-      <c r="AR10" s="103"/>
-      <c r="AS10" s="103"/>
-      <c r="AT10" s="103"/>
-      <c r="AU10" s="103"/>
-      <c r="AV10" s="103"/>
-      <c r="AW10" s="103"/>
-      <c r="AX10" s="103"/>
-      <c r="AY10" s="103"/>
-      <c r="AZ10" s="103"/>
-      <c r="BA10" s="103"/>
-      <c r="BB10" s="103"/>
-      <c r="BC10" s="104"/>
+      <c r="AP10" s="137"/>
+      <c r="AQ10" s="137"/>
+      <c r="AR10" s="137"/>
+      <c r="AS10" s="137"/>
+      <c r="AT10" s="137"/>
+      <c r="AU10" s="137"/>
+      <c r="AV10" s="137"/>
+      <c r="AW10" s="137"/>
+      <c r="AX10" s="137"/>
+      <c r="AY10" s="137"/>
+      <c r="AZ10" s="137"/>
+      <c r="BA10" s="137"/>
+      <c r="BB10" s="137"/>
+      <c r="BC10" s="138"/>
       <c r="BD10" s="21" t="s">
         <v>5</v>
       </c>
@@ -3725,31 +4298,31 @@
     </row>
     <row r="11" spans="1:65" ht="15" customHeight="1">
       <c r="A11" s="13"/>
-      <c r="AM11" s="59" t="s">
+      <c r="AM11" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="AN11" s="60"/>
-      <c r="AO11" s="63" t="s">
+      <c r="AN11" s="148"/>
+      <c r="AO11" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="AP11" s="64"/>
-      <c r="AQ11" s="64"/>
-      <c r="AR11" s="64"/>
-      <c r="AS11" s="64"/>
-      <c r="AT11" s="64"/>
-      <c r="AU11" s="64"/>
-      <c r="AV11" s="64"/>
-      <c r="AW11" s="64"/>
-      <c r="AX11" s="64"/>
-      <c r="AY11" s="64"/>
-      <c r="AZ11" s="64"/>
-      <c r="BA11" s="64"/>
-      <c r="BB11" s="64"/>
-      <c r="BC11" s="65"/>
-      <c r="BD11" s="61" t="s">
+      <c r="AP11" s="101"/>
+      <c r="AQ11" s="101"/>
+      <c r="AR11" s="101"/>
+      <c r="AS11" s="101"/>
+      <c r="AT11" s="101"/>
+      <c r="AU11" s="101"/>
+      <c r="AV11" s="101"/>
+      <c r="AW11" s="101"/>
+      <c r="AX11" s="101"/>
+      <c r="AY11" s="101"/>
+      <c r="AZ11" s="101"/>
+      <c r="BA11" s="101"/>
+      <c r="BB11" s="101"/>
+      <c r="BC11" s="102"/>
+      <c r="BD11" s="149" t="s">
         <v>47</v>
       </c>
-      <c r="BE11" s="62"/>
+      <c r="BE11" s="150"/>
       <c r="BF11" s="13"/>
       <c r="BL11" s="3"/>
     </row>
@@ -3758,61 +4331,61 @@
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AM12" s="59" t="s">
+      <c r="AM12" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="AN12" s="60"/>
-      <c r="AO12" s="66" t="s">
+      <c r="AN12" s="148"/>
+      <c r="AO12" s="139" t="s">
         <v>50</v>
       </c>
-      <c r="AP12" s="67"/>
-      <c r="AQ12" s="67"/>
-      <c r="AR12" s="67"/>
-      <c r="AS12" s="67"/>
-      <c r="AT12" s="67"/>
-      <c r="AU12" s="67"/>
-      <c r="AV12" s="67"/>
-      <c r="AW12" s="67"/>
-      <c r="AX12" s="67"/>
-      <c r="AY12" s="67"/>
-      <c r="AZ12" s="67"/>
-      <c r="BA12" s="67"/>
-      <c r="BB12" s="67"/>
-      <c r="BC12" s="68"/>
-      <c r="BD12" s="61" t="s">
+      <c r="AP12" s="140"/>
+      <c r="AQ12" s="140"/>
+      <c r="AR12" s="140"/>
+      <c r="AS12" s="140"/>
+      <c r="AT12" s="140"/>
+      <c r="AU12" s="140"/>
+      <c r="AV12" s="140"/>
+      <c r="AW12" s="140"/>
+      <c r="AX12" s="140"/>
+      <c r="AY12" s="140"/>
+      <c r="AZ12" s="140"/>
+      <c r="BA12" s="140"/>
+      <c r="BB12" s="140"/>
+      <c r="BC12" s="141"/>
+      <c r="BD12" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="BE12" s="62"/>
+      <c r="BE12" s="150"/>
       <c r="BF12" s="13"/>
       <c r="BL12" s="3"/>
     </row>
     <row r="13" spans="1:65" ht="15" customHeight="1">
       <c r="A13" s="13"/>
-      <c r="AM13" s="59" t="s">
+      <c r="AM13" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="AN13" s="60"/>
-      <c r="AO13" s="66" t="s">
+      <c r="AN13" s="148"/>
+      <c r="AO13" s="139" t="s">
         <v>51</v>
       </c>
-      <c r="AP13" s="67"/>
-      <c r="AQ13" s="67"/>
-      <c r="AR13" s="67"/>
-      <c r="AS13" s="67"/>
-      <c r="AT13" s="67"/>
-      <c r="AU13" s="67"/>
-      <c r="AV13" s="67"/>
-      <c r="AW13" s="67"/>
-      <c r="AX13" s="67"/>
-      <c r="AY13" s="67"/>
-      <c r="AZ13" s="67"/>
-      <c r="BA13" s="67"/>
-      <c r="BB13" s="67"/>
-      <c r="BC13" s="68"/>
-      <c r="BD13" s="61" t="s">
+      <c r="AP13" s="140"/>
+      <c r="AQ13" s="140"/>
+      <c r="AR13" s="140"/>
+      <c r="AS13" s="140"/>
+      <c r="AT13" s="140"/>
+      <c r="AU13" s="140"/>
+      <c r="AV13" s="140"/>
+      <c r="AW13" s="140"/>
+      <c r="AX13" s="140"/>
+      <c r="AY13" s="140"/>
+      <c r="AZ13" s="140"/>
+      <c r="BA13" s="140"/>
+      <c r="BB13" s="140"/>
+      <c r="BC13" s="141"/>
+      <c r="BD13" s="149" t="s">
         <v>42</v>
       </c>
-      <c r="BE13" s="62"/>
+      <c r="BE13" s="150"/>
       <c r="BF13" s="13"/>
       <c r="BL13" s="3"/>
     </row>
@@ -3820,21 +4393,21 @@
       <c r="A14" s="13"/>
       <c r="AM14" s="27"/>
       <c r="AN14" s="28"/>
-      <c r="AO14" s="63"/>
-      <c r="AP14" s="64"/>
-      <c r="AQ14" s="64"/>
-      <c r="AR14" s="64"/>
-      <c r="AS14" s="64"/>
-      <c r="AT14" s="64"/>
-      <c r="AU14" s="64"/>
-      <c r="AV14" s="64"/>
-      <c r="AW14" s="64"/>
-      <c r="AX14" s="64"/>
-      <c r="AY14" s="64"/>
-      <c r="AZ14" s="64"/>
-      <c r="BA14" s="64"/>
-      <c r="BB14" s="64"/>
-      <c r="BC14" s="65"/>
+      <c r="AO14" s="100"/>
+      <c r="AP14" s="101"/>
+      <c r="AQ14" s="101"/>
+      <c r="AR14" s="101"/>
+      <c r="AS14" s="101"/>
+      <c r="AT14" s="101"/>
+      <c r="AU14" s="101"/>
+      <c r="AV14" s="101"/>
+      <c r="AW14" s="101"/>
+      <c r="AX14" s="101"/>
+      <c r="AY14" s="101"/>
+      <c r="AZ14" s="101"/>
+      <c r="BA14" s="101"/>
+      <c r="BB14" s="101"/>
+      <c r="BC14" s="102"/>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="13"/>
@@ -3844,21 +4417,21 @@
       <c r="A15" s="13"/>
       <c r="AM15" s="27"/>
       <c r="AN15" s="28"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="64"/>
-      <c r="AQ15" s="64"/>
-      <c r="AR15" s="64"/>
-      <c r="AS15" s="64"/>
-      <c r="AT15" s="64"/>
-      <c r="AU15" s="64"/>
-      <c r="AV15" s="64"/>
-      <c r="AW15" s="64"/>
-      <c r="AX15" s="64"/>
-      <c r="AY15" s="64"/>
-      <c r="AZ15" s="64"/>
-      <c r="BA15" s="64"/>
-      <c r="BB15" s="64"/>
-      <c r="BC15" s="65"/>
+      <c r="AO15" s="100"/>
+      <c r="AP15" s="101"/>
+      <c r="AQ15" s="101"/>
+      <c r="AR15" s="101"/>
+      <c r="AS15" s="101"/>
+      <c r="AT15" s="101"/>
+      <c r="AU15" s="101"/>
+      <c r="AV15" s="101"/>
+      <c r="AW15" s="101"/>
+      <c r="AX15" s="101"/>
+      <c r="AY15" s="101"/>
+      <c r="AZ15" s="101"/>
+      <c r="BA15" s="101"/>
+      <c r="BB15" s="101"/>
+      <c r="BC15" s="102"/>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="13"/>
@@ -3868,21 +4441,21 @@
       <c r="A16" s="13"/>
       <c r="AM16" s="27"/>
       <c r="AN16" s="28"/>
-      <c r="AO16" s="63"/>
-      <c r="AP16" s="64"/>
-      <c r="AQ16" s="64"/>
-      <c r="AR16" s="64"/>
-      <c r="AS16" s="64"/>
-      <c r="AT16" s="64"/>
-      <c r="AU16" s="64"/>
-      <c r="AV16" s="64"/>
-      <c r="AW16" s="64"/>
-      <c r="AX16" s="64"/>
-      <c r="AY16" s="64"/>
-      <c r="AZ16" s="64"/>
-      <c r="BA16" s="64"/>
-      <c r="BB16" s="64"/>
-      <c r="BC16" s="65"/>
+      <c r="AO16" s="100"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="101"/>
+      <c r="AS16" s="101"/>
+      <c r="AT16" s="101"/>
+      <c r="AU16" s="101"/>
+      <c r="AV16" s="101"/>
+      <c r="AW16" s="101"/>
+      <c r="AX16" s="101"/>
+      <c r="AY16" s="101"/>
+      <c r="AZ16" s="101"/>
+      <c r="BA16" s="101"/>
+      <c r="BB16" s="101"/>
+      <c r="BC16" s="102"/>
       <c r="BD16" s="31"/>
       <c r="BE16" s="32"/>
       <c r="BF16" s="13"/>
@@ -3892,21 +4465,21 @@
       <c r="A17" s="13"/>
       <c r="AM17" s="27"/>
       <c r="AN17" s="28"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="64"/>
-      <c r="AQ17" s="64"/>
-      <c r="AR17" s="64"/>
-      <c r="AS17" s="64"/>
-      <c r="AT17" s="64"/>
-      <c r="AU17" s="64"/>
-      <c r="AV17" s="64"/>
-      <c r="AW17" s="64"/>
-      <c r="AX17" s="64"/>
-      <c r="AY17" s="64"/>
-      <c r="AZ17" s="64"/>
-      <c r="BA17" s="64"/>
-      <c r="BB17" s="64"/>
-      <c r="BC17" s="65"/>
+      <c r="AO17" s="100"/>
+      <c r="AP17" s="101"/>
+      <c r="AQ17" s="101"/>
+      <c r="AR17" s="101"/>
+      <c r="AS17" s="101"/>
+      <c r="AT17" s="101"/>
+      <c r="AU17" s="101"/>
+      <c r="AV17" s="101"/>
+      <c r="AW17" s="101"/>
+      <c r="AX17" s="101"/>
+      <c r="AY17" s="101"/>
+      <c r="AZ17" s="101"/>
+      <c r="BA17" s="101"/>
+      <c r="BB17" s="101"/>
+      <c r="BC17" s="102"/>
       <c r="BD17" s="31"/>
       <c r="BE17" s="32"/>
       <c r="BF17" s="13"/>
@@ -3916,21 +4489,21 @@
       <c r="A18" s="13"/>
       <c r="AM18" s="27"/>
       <c r="AN18" s="28"/>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="64"/>
-      <c r="AQ18" s="64"/>
-      <c r="AR18" s="64"/>
-      <c r="AS18" s="64"/>
-      <c r="AT18" s="64"/>
-      <c r="AU18" s="64"/>
-      <c r="AV18" s="64"/>
-      <c r="AW18" s="64"/>
-      <c r="AX18" s="64"/>
-      <c r="AY18" s="64"/>
-      <c r="AZ18" s="64"/>
-      <c r="BA18" s="64"/>
-      <c r="BB18" s="64"/>
-      <c r="BC18" s="65"/>
+      <c r="AO18" s="100"/>
+      <c r="AP18" s="101"/>
+      <c r="AQ18" s="101"/>
+      <c r="AR18" s="101"/>
+      <c r="AS18" s="101"/>
+      <c r="AT18" s="101"/>
+      <c r="AU18" s="101"/>
+      <c r="AV18" s="101"/>
+      <c r="AW18" s="101"/>
+      <c r="AX18" s="101"/>
+      <c r="AY18" s="101"/>
+      <c r="AZ18" s="101"/>
+      <c r="BA18" s="101"/>
+      <c r="BB18" s="101"/>
+      <c r="BC18" s="102"/>
       <c r="BD18" s="34"/>
       <c r="BE18" s="35"/>
       <c r="BF18" s="13"/>
@@ -4169,7 +4742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4191,182 +4764,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -4654,7 +5227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567342E5-F899-48BD-974B-0DC0FF996026}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4676,182 +5249,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5064,12 +5637,12 @@
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:AD2"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5080,7 +5653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B661F1-2324-49A4-A317-7CE94BF662B6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5102,182 +5675,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="69" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="70"/>
-      <c r="BE1" s="71"/>
-      <c r="BF1" s="71"/>
-      <c r="BG1" s="72"/>
+      <c r="BD1" s="104"/>
+      <c r="BE1" s="105"/>
+      <c r="BF1" s="105"/>
+      <c r="BG1" s="106"/>
       <c r="BH1" s="2"/>
     </row>
     <row r="2" spans="1:60" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="110" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="111"/>
-      <c r="BE2" s="111"/>
-      <c r="BF2" s="111"/>
-      <c r="BG2" s="112"/>
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="156"/>
       <c r="BH2" s="2"/>
     </row>
     <row r="3" spans="1:60" s="4" customFormat="1" ht="10.5" customHeight="1">
@@ -5490,12 +6063,12 @@
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:AD2"/>
+    <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:AD1"/>
-    <mergeCell ref="AE1:AI1"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -5506,7 +6079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5532,207 +6105,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="73" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="85" t="s">
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="86" t="s">
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="87"/>
-      <c r="R1" s="87"/>
-      <c r="S1" s="87"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="86" t="s">
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="87"/>
-      <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="87"/>
-      <c r="AA1" s="87"/>
-      <c r="AB1" s="87"/>
-      <c r="AC1" s="87"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="99" t="s">
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="122"/>
+      <c r="AE1" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="101"/>
-      <c r="AJ1" s="99" t="s">
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="135"/>
+      <c r="AJ1" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="101"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AK1" s="134"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="135"/>
+      <c r="AN1" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="101"/>
-      <c r="AS1" s="73" t="s">
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="135"/>
+      <c r="AS1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="73" t="s">
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
+      <c r="AV1" s="109"/>
+      <c r="AW1" s="110"/>
+      <c r="AX1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AY1" s="74"/>
-      <c r="AZ1" s="74"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="174" t="s">
+      <c r="AY1" s="108"/>
+      <c r="AZ1" s="108"/>
+      <c r="BA1" s="109"/>
+      <c r="BB1" s="110"/>
+      <c r="BC1" s="168" t="s">
         <v>21</v>
       </c>
-      <c r="BD1" s="175"/>
-      <c r="BE1" s="175"/>
-      <c r="BF1" s="175"/>
-      <c r="BG1" s="175"/>
-      <c r="BH1" s="175"/>
-      <c r="BI1" s="175"/>
-      <c r="BJ1" s="175"/>
-      <c r="BK1" s="175"/>
-      <c r="BL1" s="175"/>
-      <c r="BM1" s="175"/>
-      <c r="BN1" s="175"/>
-      <c r="BO1" s="175"/>
-      <c r="BP1" s="175"/>
-      <c r="BQ1" s="175"/>
-      <c r="BR1" s="175"/>
-      <c r="BS1" s="175"/>
-      <c r="BT1" s="175"/>
+      <c r="BD1" s="169"/>
+      <c r="BE1" s="169"/>
+      <c r="BF1" s="169"/>
+      <c r="BG1" s="169"/>
+      <c r="BH1" s="169"/>
+      <c r="BI1" s="169"/>
+      <c r="BJ1" s="169"/>
+      <c r="BK1" s="169"/>
+      <c r="BL1" s="169"/>
+      <c r="BM1" s="169"/>
+      <c r="BN1" s="169"/>
+      <c r="BO1" s="169"/>
+      <c r="BP1" s="169"/>
+      <c r="BQ1" s="169"/>
+      <c r="BR1" s="169"/>
+      <c r="BS1" s="169"/>
+      <c r="BT1" s="169"/>
     </row>
     <row r="2" spans="1:72" s="5" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A2" s="110" t="str">
+      <c r="A2" s="154" t="str">
         <f>Overview!A2</f>
         <v>EduLearn</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="111"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="110" t="str">
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="154" t="str">
         <f>Overview!F2</f>
         <v>Courses</v>
       </c>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="113" t="str">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="157" t="str">
         <f>Overview!K2</f>
         <v>SC001</v>
       </c>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115" t="str">
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="159" t="str">
         <f>Overview!P2</f>
         <v>SC Name</v>
       </c>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="115" t="str">
+      <c r="Q2" s="157"/>
+      <c r="R2" s="157"/>
+      <c r="S2" s="157"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="159" t="str">
         <f>Overview!U2</f>
         <v>Template_DD_v1.0.xlsx</v>
       </c>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="116">
+      <c r="V2" s="157"/>
+      <c r="W2" s="157"/>
+      <c r="X2" s="157"/>
+      <c r="Y2" s="157"/>
+      <c r="Z2" s="157"/>
+      <c r="AA2" s="157"/>
+      <c r="AB2" s="157"/>
+      <c r="AC2" s="157"/>
+      <c r="AD2" s="158"/>
+      <c r="AE2" s="151">
         <f>Overview!AI2</f>
         <v>45701</v>
       </c>
-      <c r="AF2" s="117"/>
-      <c r="AG2" s="117"/>
-      <c r="AH2" s="117"/>
-      <c r="AI2" s="118"/>
-      <c r="AJ2" s="110" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="154" t="str">
         <f>Overview!AN2</f>
         <v>BangNT</v>
       </c>
-      <c r="AK2" s="111"/>
-      <c r="AL2" s="111"/>
-      <c r="AM2" s="111"/>
-      <c r="AN2" s="116">
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="151">
         <f>Overview!AS2</f>
         <v>45707</v>
       </c>
-      <c r="AO2" s="117"/>
-      <c r="AP2" s="117"/>
-      <c r="AQ2" s="117"/>
-      <c r="AR2" s="118"/>
-      <c r="AS2" s="83" t="str">
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="117" t="str">
         <f>Overview!AX2</f>
         <v>BangNT</v>
       </c>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AX2" s="116">
+      <c r="AT2" s="117"/>
+      <c r="AU2" s="117"/>
+      <c r="AV2" s="117"/>
+      <c r="AW2" s="117"/>
+      <c r="AX2" s="151">
         <f>Overview!BC2</f>
         <v>45701</v>
       </c>
-      <c r="AY2" s="117"/>
-      <c r="AZ2" s="117"/>
-      <c r="BA2" s="117"/>
-      <c r="BB2" s="118"/>
-      <c r="BC2" s="176" t="str">
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="152"/>
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="170" t="str">
         <f>Overview!BH2</f>
         <v>BangNT</v>
       </c>
-      <c r="BD2" s="176"/>
-      <c r="BE2" s="176"/>
-      <c r="BF2" s="176"/>
-      <c r="BG2" s="176"/>
-      <c r="BH2" s="176"/>
-      <c r="BI2" s="176"/>
-      <c r="BJ2" s="176"/>
-      <c r="BK2" s="176"/>
-      <c r="BL2" s="176"/>
-      <c r="BM2" s="176"/>
-      <c r="BN2" s="176"/>
-      <c r="BO2" s="176"/>
-      <c r="BP2" s="176"/>
-      <c r="BQ2" s="176"/>
-      <c r="BR2" s="176"/>
-      <c r="BS2" s="176"/>
-      <c r="BT2" s="176"/>
+      <c r="BD2" s="170"/>
+      <c r="BE2" s="170"/>
+      <c r="BF2" s="170"/>
+      <c r="BG2" s="170"/>
+      <c r="BH2" s="170"/>
+      <c r="BI2" s="170"/>
+      <c r="BJ2" s="170"/>
+      <c r="BK2" s="170"/>
+      <c r="BL2" s="170"/>
+      <c r="BM2" s="170"/>
+      <c r="BN2" s="170"/>
+      <c r="BO2" s="170"/>
+      <c r="BP2" s="170"/>
+      <c r="BQ2" s="170"/>
+      <c r="BR2" s="170"/>
+      <c r="BS2" s="170"/>
+      <c r="BT2" s="170"/>
     </row>
     <row r="3" spans="1:72" s="4" customFormat="1" ht="10.5" customHeight="1">
       <c r="A3" s="2"/>
@@ -5934,2835 +6507,2833 @@
       <c r="BS5" s="49"/>
       <c r="BT5" s="50"/>
     </row>
-    <row r="7" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A7" s="119"/>
-      <c r="C7" s="121" t="s">
+    <row r="7" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A7" s="56"/>
+      <c r="C7" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123" t="s">
+      <c r="D7" s="59"/>
+      <c r="E7" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="124"/>
-      <c r="S7" s="124"/>
-      <c r="T7" s="124"/>
-      <c r="U7" s="124"/>
-      <c r="V7" s="124"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="124"/>
-      <c r="Z7" s="124"/>
-      <c r="AA7" s="124"/>
-      <c r="AB7" s="124"/>
-      <c r="AC7" s="124"/>
-      <c r="AD7" s="124"/>
-      <c r="AE7" s="124"/>
-      <c r="AF7" s="124"/>
-      <c r="AG7" s="124"/>
-      <c r="AH7" s="124"/>
-      <c r="AI7" s="124"/>
-      <c r="AJ7" s="125" t="s">
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="61"/>
+      <c r="U7" s="61"/>
+      <c r="V7" s="61"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="61"/>
+      <c r="Y7" s="61"/>
+      <c r="Z7" s="61"/>
+      <c r="AA7" s="61"/>
+      <c r="AB7" s="61"/>
+      <c r="AC7" s="61"/>
+      <c r="AD7" s="61"/>
+      <c r="AE7" s="61"/>
+      <c r="AF7" s="61"/>
+      <c r="AG7" s="61"/>
+      <c r="AH7" s="61"/>
+      <c r="AI7" s="61"/>
+      <c r="AJ7" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="AK7" s="124"/>
-      <c r="AL7" s="124"/>
-      <c r="AM7" s="124"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="124"/>
-      <c r="AP7" s="124"/>
-      <c r="AQ7" s="124"/>
-      <c r="AR7" s="124"/>
-      <c r="AS7" s="124"/>
-      <c r="AT7" s="124"/>
-      <c r="AU7" s="124"/>
-      <c r="AV7" s="124"/>
-      <c r="AW7" s="124"/>
-      <c r="AX7" s="124"/>
-      <c r="AY7" s="124"/>
-      <c r="AZ7" s="124"/>
-      <c r="BA7" s="124"/>
-      <c r="BB7" s="125" t="s">
+      <c r="AK7" s="61"/>
+      <c r="AL7" s="61"/>
+      <c r="AM7" s="61"/>
+      <c r="AN7" s="61"/>
+      <c r="AO7" s="61"/>
+      <c r="AP7" s="61"/>
+      <c r="AQ7" s="61"/>
+      <c r="AR7" s="61"/>
+      <c r="AS7" s="61"/>
+      <c r="AT7" s="61"/>
+      <c r="AU7" s="61"/>
+      <c r="AV7" s="61"/>
+      <c r="AW7" s="61"/>
+      <c r="AX7" s="61"/>
+      <c r="AY7" s="61"/>
+      <c r="AZ7" s="61"/>
+      <c r="BA7" s="61"/>
+      <c r="BB7" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="BC7" s="124"/>
-      <c r="BD7" s="124"/>
-      <c r="BE7" s="124"/>
-      <c r="BF7" s="124"/>
-      <c r="BG7" s="124"/>
-      <c r="BH7" s="124"/>
-      <c r="BI7" s="124"/>
-      <c r="BJ7" s="124"/>
-      <c r="BK7" s="124"/>
-      <c r="BL7" s="124"/>
-      <c r="BM7" s="124"/>
-      <c r="BN7" s="124"/>
-      <c r="BO7" s="124"/>
-      <c r="BP7" s="124"/>
-      <c r="BQ7" s="124"/>
-      <c r="BR7" s="126"/>
-      <c r="BT7" s="127"/>
-    </row>
-    <row r="8" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="C8" s="128">
+      <c r="BC7" s="61"/>
+      <c r="BD7" s="61"/>
+      <c r="BE7" s="61"/>
+      <c r="BF7" s="61"/>
+      <c r="BG7" s="61"/>
+      <c r="BH7" s="61"/>
+      <c r="BI7" s="61"/>
+      <c r="BJ7" s="61"/>
+      <c r="BK7" s="61"/>
+      <c r="BL7" s="61"/>
+      <c r="BM7" s="61"/>
+      <c r="BN7" s="61"/>
+      <c r="BO7" s="61"/>
+      <c r="BP7" s="61"/>
+      <c r="BQ7" s="61"/>
+      <c r="BR7" s="63"/>
+      <c r="BT7" s="64"/>
+    </row>
+    <row r="8" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="C8" s="160">
         <v>1</v>
       </c>
-      <c r="D8" s="129"/>
-      <c r="E8" s="130" t="s">
+      <c r="D8" s="161"/>
+      <c r="E8" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131"/>
-      <c r="K8" s="131"/>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="131"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131"/>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="131"/>
-      <c r="AB8" s="131"/>
-      <c r="AC8" s="131"/>
-      <c r="AD8" s="131"/>
-      <c r="AE8" s="131"/>
-      <c r="AF8" s="131"/>
-      <c r="AG8" s="131"/>
-      <c r="AH8" s="131"/>
-      <c r="AI8" s="131"/>
-      <c r="AJ8" s="132" t="s">
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="66"/>
+      <c r="W8" s="66"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="AK8" s="131"/>
-      <c r="AL8" s="131"/>
-      <c r="AM8" s="131"/>
-      <c r="AN8" s="131"/>
-      <c r="AO8" s="131"/>
-      <c r="AP8" s="131"/>
-      <c r="AQ8" s="131"/>
-      <c r="AR8" s="131"/>
-      <c r="AS8" s="131"/>
-      <c r="AT8" s="131"/>
-      <c r="AU8" s="131"/>
-      <c r="AV8" s="131"/>
-      <c r="AW8" s="131"/>
-      <c r="AX8" s="131"/>
-      <c r="AY8" s="131"/>
-      <c r="AZ8" s="131"/>
-      <c r="BA8" s="131"/>
-      <c r="BB8" s="132" t="s">
+      <c r="AK8" s="66"/>
+      <c r="AL8" s="66"/>
+      <c r="AM8" s="66"/>
+      <c r="AN8" s="66"/>
+      <c r="AO8" s="66"/>
+      <c r="AP8" s="66"/>
+      <c r="AQ8" s="66"/>
+      <c r="AR8" s="66"/>
+      <c r="AS8" s="66"/>
+      <c r="AT8" s="66"/>
+      <c r="AU8" s="66"/>
+      <c r="AV8" s="66"/>
+      <c r="AW8" s="66"/>
+      <c r="AX8" s="66"/>
+      <c r="AY8" s="66"/>
+      <c r="AZ8" s="66"/>
+      <c r="BA8" s="66"/>
+      <c r="BB8" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="BC8" s="131"/>
-      <c r="BD8" s="131"/>
-      <c r="BE8" s="131"/>
-      <c r="BF8" s="131"/>
-      <c r="BG8" s="131"/>
-      <c r="BH8" s="131"/>
-      <c r="BI8" s="131"/>
-      <c r="BJ8" s="131"/>
-      <c r="BK8" s="131"/>
-      <c r="BL8" s="131"/>
-      <c r="BM8" s="131"/>
-      <c r="BN8" s="131"/>
-      <c r="BO8" s="131"/>
-      <c r="BP8" s="131"/>
-      <c r="BQ8" s="131"/>
-      <c r="BR8" s="133"/>
-      <c r="BT8" s="127"/>
-    </row>
-    <row r="9" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135" t="s">
+      <c r="BC8" s="66"/>
+      <c r="BD8" s="66"/>
+      <c r="BE8" s="66"/>
+      <c r="BF8" s="66"/>
+      <c r="BG8" s="66"/>
+      <c r="BH8" s="66"/>
+      <c r="BI8" s="66"/>
+      <c r="BJ8" s="66"/>
+      <c r="BK8" s="66"/>
+      <c r="BL8" s="66"/>
+      <c r="BM8" s="66"/>
+      <c r="BN8" s="66"/>
+      <c r="BO8" s="66"/>
+      <c r="BP8" s="66"/>
+      <c r="BQ8" s="66"/>
+      <c r="BR8" s="68"/>
+      <c r="BT8" s="64"/>
+    </row>
+    <row r="9" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="131" t="s">
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="131"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131"/>
-      <c r="U9" s="131"/>
-      <c r="V9" s="131"/>
-      <c r="W9" s="131"/>
-      <c r="X9" s="131"/>
-      <c r="Y9" s="131"/>
-      <c r="Z9" s="131"/>
-      <c r="AA9" s="131"/>
-      <c r="AB9" s="131"/>
-      <c r="AC9" s="131"/>
-      <c r="AD9" s="131"/>
-      <c r="AE9" s="131"/>
-      <c r="AF9" s="131"/>
-      <c r="AG9" s="131"/>
-      <c r="AH9" s="131"/>
-      <c r="AI9" s="131"/>
-      <c r="AJ9" s="131"/>
-      <c r="AK9" s="131"/>
-      <c r="AL9" s="131"/>
-      <c r="AM9" s="131"/>
-      <c r="AN9" s="131"/>
-      <c r="AO9" s="131"/>
-      <c r="AP9" s="131"/>
-      <c r="AQ9" s="131"/>
-      <c r="AR9" s="131"/>
-      <c r="AS9" s="131"/>
-      <c r="AT9" s="131"/>
-      <c r="AU9" s="131"/>
-      <c r="AV9" s="131"/>
-      <c r="AW9" s="131"/>
-      <c r="AX9" s="131"/>
-      <c r="AY9" s="131"/>
-      <c r="AZ9" s="131"/>
-      <c r="BA9" s="131"/>
-      <c r="BB9" s="131"/>
-      <c r="BC9" s="131"/>
-      <c r="BD9" s="131"/>
-      <c r="BE9" s="131"/>
-      <c r="BF9" s="131"/>
-      <c r="BG9" s="131"/>
-      <c r="BH9" s="131"/>
-      <c r="BI9" s="131"/>
-      <c r="BJ9" s="131"/>
-      <c r="BK9" s="131"/>
-      <c r="BL9" s="131"/>
-      <c r="BM9" s="131"/>
-      <c r="BN9" s="131"/>
-      <c r="BO9" s="131"/>
-      <c r="BP9" s="131"/>
-      <c r="BQ9" s="131"/>
-      <c r="BR9" s="133"/>
-    </row>
-    <row r="10" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="135" t="s">
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="66"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
+      <c r="AC9" s="66"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="66"/>
+      <c r="AG9" s="66"/>
+      <c r="AH9" s="66"/>
+      <c r="AI9" s="66"/>
+      <c r="AJ9" s="66"/>
+      <c r="AK9" s="66"/>
+      <c r="AL9" s="66"/>
+      <c r="AM9" s="66"/>
+      <c r="AN9" s="66"/>
+      <c r="AO9" s="66"/>
+      <c r="AP9" s="66"/>
+      <c r="AQ9" s="66"/>
+      <c r="AR9" s="66"/>
+      <c r="AS9" s="66"/>
+      <c r="AT9" s="66"/>
+      <c r="AU9" s="66"/>
+      <c r="AV9" s="66"/>
+      <c r="AW9" s="66"/>
+      <c r="AX9" s="66"/>
+      <c r="AY9" s="66"/>
+      <c r="AZ9" s="66"/>
+      <c r="BA9" s="66"/>
+      <c r="BB9" s="66"/>
+      <c r="BC9" s="66"/>
+      <c r="BD9" s="66"/>
+      <c r="BE9" s="66"/>
+      <c r="BF9" s="66"/>
+      <c r="BG9" s="66"/>
+      <c r="BH9" s="66"/>
+      <c r="BI9" s="66"/>
+      <c r="BJ9" s="66"/>
+      <c r="BK9" s="66"/>
+      <c r="BL9" s="66"/>
+      <c r="BM9" s="66"/>
+      <c r="BN9" s="66"/>
+      <c r="BO9" s="66"/>
+      <c r="BP9" s="66"/>
+      <c r="BQ9" s="66"/>
+      <c r="BR9" s="68"/>
+    </row>
+    <row r="10" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="136"/>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="131" t="s">
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="131"/>
-      <c r="W10" s="131"/>
-      <c r="X10" s="131"/>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="131"/>
-      <c r="AB10" s="131"/>
-      <c r="AC10" s="131"/>
-      <c r="AD10" s="131"/>
-      <c r="AE10" s="131"/>
-      <c r="AF10" s="131"/>
-      <c r="AG10" s="131"/>
-      <c r="AH10" s="131"/>
-      <c r="AI10" s="131"/>
-      <c r="AJ10" s="131"/>
-      <c r="AK10" s="131"/>
-      <c r="AL10" s="131"/>
-      <c r="AM10" s="131"/>
-      <c r="AN10" s="131"/>
-      <c r="AO10" s="131"/>
-      <c r="AP10" s="131"/>
-      <c r="AQ10" s="131"/>
-      <c r="AR10" s="131"/>
-      <c r="AS10" s="131"/>
-      <c r="AT10" s="131"/>
-      <c r="AU10" s="131"/>
-      <c r="AV10" s="131"/>
-      <c r="AW10" s="131"/>
-      <c r="AX10" s="131"/>
-      <c r="AY10" s="131"/>
-      <c r="AZ10" s="131"/>
-      <c r="BA10" s="131"/>
-      <c r="BB10" s="131"/>
-      <c r="BC10" s="131"/>
-      <c r="BD10" s="131"/>
-      <c r="BE10" s="131"/>
-      <c r="BF10" s="131"/>
-      <c r="BG10" s="131"/>
-      <c r="BH10" s="131"/>
-      <c r="BI10" s="131"/>
-      <c r="BJ10" s="131"/>
-      <c r="BK10" s="131"/>
-      <c r="BL10" s="131"/>
-      <c r="BM10" s="131"/>
-      <c r="BN10" s="131"/>
-      <c r="BO10" s="131"/>
-      <c r="BP10" s="131"/>
-      <c r="BQ10" s="131"/>
-      <c r="BR10" s="133"/>
-    </row>
-    <row r="11" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="138"/>
-      <c r="D11" s="139"/>
-      <c r="BR11" s="140"/>
-      <c r="BT11" s="127"/>
-    </row>
-    <row r="12" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A12" s="119"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="120" t="s">
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="66"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="66"/>
+      <c r="AI10" s="66"/>
+      <c r="AJ10" s="66"/>
+      <c r="AK10" s="66"/>
+      <c r="AL10" s="66"/>
+      <c r="AM10" s="66"/>
+      <c r="AN10" s="66"/>
+      <c r="AO10" s="66"/>
+      <c r="AP10" s="66"/>
+      <c r="AQ10" s="66"/>
+      <c r="AR10" s="66"/>
+      <c r="AS10" s="66"/>
+      <c r="AT10" s="66"/>
+      <c r="AU10" s="66"/>
+      <c r="AV10" s="66"/>
+      <c r="AW10" s="66"/>
+      <c r="AX10" s="66"/>
+      <c r="AY10" s="66"/>
+      <c r="AZ10" s="66"/>
+      <c r="BA10" s="66"/>
+      <c r="BB10" s="66"/>
+      <c r="BC10" s="66"/>
+      <c r="BD10" s="66"/>
+      <c r="BE10" s="66"/>
+      <c r="BF10" s="66"/>
+      <c r="BG10" s="66"/>
+      <c r="BH10" s="66"/>
+      <c r="BI10" s="66"/>
+      <c r="BJ10" s="66"/>
+      <c r="BK10" s="66"/>
+      <c r="BL10" s="66"/>
+      <c r="BM10" s="66"/>
+      <c r="BN10" s="66"/>
+      <c r="BO10" s="66"/>
+      <c r="BP10" s="66"/>
+      <c r="BQ10" s="66"/>
+      <c r="BR10" s="68"/>
+    </row>
+    <row r="11" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="BR11" s="75"/>
+      <c r="BT11" s="64"/>
+    </row>
+    <row r="12" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="BR12" s="127"/>
-      <c r="BT12" s="127"/>
-    </row>
-    <row r="13" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A13" s="119"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="138"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="120" t="s">
+      <c r="BR12" s="64"/>
+      <c r="BT12" s="64"/>
+    </row>
+    <row r="13" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="73"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="BR13" s="127"/>
-      <c r="BT13" s="127"/>
-    </row>
-    <row r="14" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A14" s="119"/>
-      <c r="C14" s="138"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="143" t="s">
+      <c r="BR13" s="64"/>
+      <c r="BT13" s="64"/>
+    </row>
+    <row r="14" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A14" s="56"/>
+      <c r="C14" s="73"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
-      <c r="P14" s="144"/>
-      <c r="Q14" s="144"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="144"/>
-      <c r="T14" s="144"/>
-      <c r="U14" s="144"/>
-      <c r="V14" s="144"/>
-      <c r="W14" s="144"/>
-      <c r="X14" s="144"/>
-      <c r="Y14" s="144"/>
-      <c r="Z14" s="144"/>
-      <c r="AA14" s="144"/>
-      <c r="AB14" s="144"/>
-      <c r="AC14" s="144"/>
-      <c r="AD14" s="144"/>
-      <c r="AE14" s="144"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="144"/>
-      <c r="AH14" s="144"/>
-      <c r="AI14" s="144"/>
-      <c r="AJ14" s="144"/>
-      <c r="AK14" s="144"/>
-      <c r="AL14" s="144"/>
-      <c r="AM14" s="144"/>
-      <c r="AN14" s="144"/>
-      <c r="AO14" s="144"/>
-      <c r="AP14" s="144"/>
-      <c r="AQ14" s="144"/>
-      <c r="AR14" s="144"/>
-      <c r="AS14" s="144"/>
-      <c r="AT14" s="144"/>
-      <c r="AU14" s="144"/>
-      <c r="AV14" s="144"/>
-      <c r="AW14" s="144"/>
-      <c r="AX14" s="144"/>
-      <c r="AY14" s="144"/>
-      <c r="AZ14" s="144"/>
-      <c r="BA14" s="144"/>
-      <c r="BB14" s="144"/>
-      <c r="BC14" s="144"/>
-      <c r="BD14" s="144"/>
-      <c r="BE14" s="144"/>
-      <c r="BF14" s="144"/>
-      <c r="BG14" s="144"/>
-      <c r="BH14" s="144"/>
-      <c r="BI14" s="144"/>
-      <c r="BJ14" s="144"/>
-      <c r="BK14" s="144"/>
-      <c r="BL14" s="145"/>
-      <c r="BR14" s="127"/>
-      <c r="BT14" s="127"/>
-    </row>
-    <row r="15" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A15" s="119"/>
-      <c r="C15" s="138"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="146" t="s">
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="79"/>
+      <c r="R14" s="79"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="79"/>
+      <c r="U14" s="79"/>
+      <c r="V14" s="79"/>
+      <c r="W14" s="79"/>
+      <c r="X14" s="79"/>
+      <c r="Y14" s="79"/>
+      <c r="Z14" s="79"/>
+      <c r="AA14" s="79"/>
+      <c r="AB14" s="79"/>
+      <c r="AC14" s="79"/>
+      <c r="AD14" s="79"/>
+      <c r="AE14" s="79"/>
+      <c r="AF14" s="79"/>
+      <c r="AG14" s="79"/>
+      <c r="AH14" s="79"/>
+      <c r="AI14" s="79"/>
+      <c r="AJ14" s="79"/>
+      <c r="AK14" s="79"/>
+      <c r="AL14" s="79"/>
+      <c r="AM14" s="79"/>
+      <c r="AN14" s="79"/>
+      <c r="AO14" s="79"/>
+      <c r="AP14" s="79"/>
+      <c r="AQ14" s="79"/>
+      <c r="AR14" s="79"/>
+      <c r="AS14" s="79"/>
+      <c r="AT14" s="79"/>
+      <c r="AU14" s="79"/>
+      <c r="AV14" s="79"/>
+      <c r="AW14" s="79"/>
+      <c r="AX14" s="79"/>
+      <c r="AY14" s="79"/>
+      <c r="AZ14" s="79"/>
+      <c r="BA14" s="79"/>
+      <c r="BB14" s="79"/>
+      <c r="BC14" s="79"/>
+      <c r="BD14" s="79"/>
+      <c r="BE14" s="79"/>
+      <c r="BF14" s="79"/>
+      <c r="BG14" s="79"/>
+      <c r="BH14" s="79"/>
+      <c r="BI14" s="79"/>
+      <c r="BJ14" s="79"/>
+      <c r="BK14" s="79"/>
+      <c r="BL14" s="80"/>
+      <c r="BR14" s="64"/>
+      <c r="BT14" s="64"/>
+    </row>
+    <row r="15" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A15" s="56"/>
+      <c r="C15" s="73"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="147"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="148"/>
-      <c r="L15" s="132" t="s">
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="M15" s="131"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="131"/>
-      <c r="R15" s="131"/>
-      <c r="S15" s="131"/>
-      <c r="T15" s="131"/>
-      <c r="U15" s="131"/>
-      <c r="V15" s="131"/>
-      <c r="W15" s="131"/>
-      <c r="X15" s="131"/>
-      <c r="Y15" s="131"/>
-      <c r="Z15" s="131"/>
-      <c r="AA15" s="131"/>
-      <c r="AB15" s="131"/>
-      <c r="AC15" s="131"/>
-      <c r="AD15" s="131"/>
-      <c r="AE15" s="131"/>
-      <c r="AF15" s="131"/>
-      <c r="AG15" s="131"/>
-      <c r="AH15" s="131"/>
-      <c r="AI15" s="131"/>
-      <c r="AJ15" s="131"/>
-      <c r="AK15" s="131"/>
-      <c r="AL15" s="131"/>
-      <c r="AM15" s="131"/>
-      <c r="AN15" s="131"/>
-      <c r="AO15" s="131"/>
-      <c r="AP15" s="131"/>
-      <c r="AQ15" s="131"/>
-      <c r="AR15" s="131"/>
-      <c r="AS15" s="131"/>
-      <c r="AT15" s="131"/>
-      <c r="AU15" s="131"/>
-      <c r="AV15" s="131"/>
-      <c r="AW15" s="131"/>
-      <c r="AX15" s="131"/>
-      <c r="AY15" s="131"/>
-      <c r="AZ15" s="131"/>
-      <c r="BA15" s="131"/>
-      <c r="BB15" s="131"/>
-      <c r="BC15" s="131"/>
-      <c r="BD15" s="131"/>
-      <c r="BE15" s="131"/>
-      <c r="BF15" s="131"/>
-      <c r="BG15" s="131"/>
-      <c r="BH15" s="131"/>
-      <c r="BI15" s="131"/>
-      <c r="BJ15" s="131"/>
-      <c r="BK15" s="131"/>
-      <c r="BL15" s="133"/>
-      <c r="BR15" s="149"/>
-      <c r="BT15" s="127"/>
-    </row>
-    <row r="16" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A16" s="119"/>
-      <c r="C16" s="138"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="150" t="s">
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="66"/>
+      <c r="AC15" s="66"/>
+      <c r="AD15" s="66"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="66"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="66"/>
+      <c r="AK15" s="66"/>
+      <c r="AL15" s="66"/>
+      <c r="AM15" s="66"/>
+      <c r="AN15" s="66"/>
+      <c r="AO15" s="66"/>
+      <c r="AP15" s="66"/>
+      <c r="AQ15" s="66"/>
+      <c r="AR15" s="66"/>
+      <c r="AS15" s="66"/>
+      <c r="AT15" s="66"/>
+      <c r="AU15" s="66"/>
+      <c r="AV15" s="66"/>
+      <c r="AW15" s="66"/>
+      <c r="AX15" s="66"/>
+      <c r="AY15" s="66"/>
+      <c r="AZ15" s="66"/>
+      <c r="BA15" s="66"/>
+      <c r="BB15" s="66"/>
+      <c r="BC15" s="66"/>
+      <c r="BD15" s="66"/>
+      <c r="BE15" s="66"/>
+      <c r="BF15" s="66"/>
+      <c r="BG15" s="66"/>
+      <c r="BH15" s="66"/>
+      <c r="BI15" s="66"/>
+      <c r="BJ15" s="66"/>
+      <c r="BK15" s="66"/>
+      <c r="BL15" s="68"/>
+      <c r="BR15" s="84"/>
+      <c r="BT15" s="64"/>
+    </row>
+    <row r="16" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A16" s="56"/>
+      <c r="C16" s="73"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="152"/>
-      <c r="L16" s="132" t="s">
+      <c r="G16" s="163"/>
+      <c r="H16" s="163"/>
+      <c r="I16" s="163"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="131"/>
-      <c r="S16" s="131"/>
-      <c r="T16" s="131"/>
-      <c r="U16" s="131"/>
-      <c r="V16" s="131"/>
-      <c r="W16" s="131"/>
-      <c r="X16" s="131"/>
-      <c r="Y16" s="131"/>
-      <c r="Z16" s="131"/>
-      <c r="AA16" s="131"/>
-      <c r="AB16" s="131"/>
-      <c r="AC16" s="131"/>
-      <c r="AD16" s="131"/>
-      <c r="AE16" s="131"/>
-      <c r="AF16" s="131"/>
-      <c r="AG16" s="131"/>
-      <c r="AH16" s="131"/>
-      <c r="AI16" s="131"/>
-      <c r="AJ16" s="131"/>
-      <c r="AK16" s="132" t="s">
+      <c r="M16" s="66"/>
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="66"/>
+      <c r="X16" s="66"/>
+      <c r="Y16" s="66"/>
+      <c r="Z16" s="66"/>
+      <c r="AA16" s="66"/>
+      <c r="AB16" s="66"/>
+      <c r="AC16" s="66"/>
+      <c r="AD16" s="66"/>
+      <c r="AE16" s="66"/>
+      <c r="AF16" s="66"/>
+      <c r="AG16" s="66"/>
+      <c r="AH16" s="66"/>
+      <c r="AI16" s="66"/>
+      <c r="AJ16" s="66"/>
+      <c r="AK16" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AL16" s="131"/>
-      <c r="AM16" s="131"/>
-      <c r="AN16" s="131"/>
-      <c r="AO16" s="131"/>
-      <c r="AP16" s="131"/>
-      <c r="AQ16" s="131"/>
-      <c r="AR16" s="131"/>
-      <c r="AS16" s="131"/>
-      <c r="AT16" s="131"/>
-      <c r="AU16" s="131"/>
-      <c r="AV16" s="131"/>
-      <c r="AW16" s="131"/>
-      <c r="AX16" s="131"/>
-      <c r="AY16" s="131"/>
-      <c r="AZ16" s="131"/>
-      <c r="BA16" s="131"/>
-      <c r="BB16" s="131"/>
-      <c r="BC16" s="131"/>
-      <c r="BD16" s="131"/>
-      <c r="BE16" s="131"/>
-      <c r="BF16" s="131"/>
-      <c r="BG16" s="131"/>
-      <c r="BH16" s="131"/>
-      <c r="BI16" s="131"/>
-      <c r="BJ16" s="131"/>
-      <c r="BK16" s="131"/>
-      <c r="BL16" s="133"/>
-      <c r="BR16" s="127"/>
-      <c r="BT16" s="127"/>
-    </row>
-    <row r="17" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A17" s="119"/>
-      <c r="C17" s="138"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="153"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="154"/>
-      <c r="K17" s="155"/>
-      <c r="L17" s="132" t="s">
+      <c r="AL16" s="66"/>
+      <c r="AM16" s="66"/>
+      <c r="AN16" s="66"/>
+      <c r="AO16" s="66"/>
+      <c r="AP16" s="66"/>
+      <c r="AQ16" s="66"/>
+      <c r="AR16" s="66"/>
+      <c r="AS16" s="66"/>
+      <c r="AT16" s="66"/>
+      <c r="AU16" s="66"/>
+      <c r="AV16" s="66"/>
+      <c r="AW16" s="66"/>
+      <c r="AX16" s="66"/>
+      <c r="AY16" s="66"/>
+      <c r="AZ16" s="66"/>
+      <c r="BA16" s="66"/>
+      <c r="BB16" s="66"/>
+      <c r="BC16" s="66"/>
+      <c r="BD16" s="66"/>
+      <c r="BE16" s="66"/>
+      <c r="BF16" s="66"/>
+      <c r="BG16" s="66"/>
+      <c r="BH16" s="66"/>
+      <c r="BI16" s="66"/>
+      <c r="BJ16" s="66"/>
+      <c r="BK16" s="66"/>
+      <c r="BL16" s="68"/>
+      <c r="BR16" s="64"/>
+      <c r="BT16" s="64"/>
+    </row>
+    <row r="17" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A17" s="56"/>
+      <c r="C17" s="73"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="166"/>
+      <c r="H17" s="166"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="166"/>
+      <c r="K17" s="167"/>
+      <c r="L17" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="M17" s="131"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="131"/>
-      <c r="R17" s="131"/>
-      <c r="S17" s="131"/>
-      <c r="T17" s="131"/>
-      <c r="U17" s="131"/>
-      <c r="V17" s="131"/>
-      <c r="W17" s="131"/>
-      <c r="X17" s="131"/>
-      <c r="Y17" s="131"/>
-      <c r="Z17" s="131"/>
-      <c r="AA17" s="131"/>
-      <c r="AB17" s="131"/>
-      <c r="AC17" s="131"/>
-      <c r="AD17" s="131"/>
-      <c r="AE17" s="131"/>
-      <c r="AF17" s="131"/>
-      <c r="AG17" s="131"/>
-      <c r="AH17" s="131"/>
-      <c r="AI17" s="131"/>
-      <c r="AJ17" s="131"/>
-      <c r="AK17" s="132" t="s">
+      <c r="M17" s="66"/>
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="66"/>
+      <c r="Y17" s="66"/>
+      <c r="Z17" s="66"/>
+      <c r="AA17" s="66"/>
+      <c r="AB17" s="66"/>
+      <c r="AC17" s="66"/>
+      <c r="AD17" s="66"/>
+      <c r="AE17" s="66"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="66"/>
+      <c r="AH17" s="66"/>
+      <c r="AI17" s="66"/>
+      <c r="AJ17" s="66"/>
+      <c r="AK17" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AL17" s="131"/>
-      <c r="AM17" s="131"/>
-      <c r="AN17" s="131"/>
-      <c r="AO17" s="131"/>
-      <c r="AP17" s="131"/>
-      <c r="AQ17" s="131"/>
-      <c r="AR17" s="131"/>
-      <c r="AS17" s="131"/>
-      <c r="AT17" s="131"/>
-      <c r="AU17" s="131"/>
-      <c r="AV17" s="131"/>
-      <c r="AW17" s="131"/>
-      <c r="AX17" s="131"/>
-      <c r="AY17" s="131"/>
-      <c r="AZ17" s="131"/>
-      <c r="BA17" s="131"/>
-      <c r="BB17" s="131"/>
-      <c r="BC17" s="131"/>
-      <c r="BD17" s="131"/>
-      <c r="BE17" s="131"/>
-      <c r="BF17" s="131"/>
-      <c r="BG17" s="131"/>
-      <c r="BH17" s="131"/>
-      <c r="BI17" s="131"/>
-      <c r="BJ17" s="131"/>
-      <c r="BK17" s="131"/>
-      <c r="BL17" s="133"/>
-      <c r="BR17" s="127"/>
-      <c r="BT17" s="127"/>
-    </row>
-    <row r="18" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A18" s="119"/>
-      <c r="C18" s="138"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="146" t="s">
+      <c r="AL17" s="66"/>
+      <c r="AM17" s="66"/>
+      <c r="AN17" s="66"/>
+      <c r="AO17" s="66"/>
+      <c r="AP17" s="66"/>
+      <c r="AQ17" s="66"/>
+      <c r="AR17" s="66"/>
+      <c r="AS17" s="66"/>
+      <c r="AT17" s="66"/>
+      <c r="AU17" s="66"/>
+      <c r="AV17" s="66"/>
+      <c r="AW17" s="66"/>
+      <c r="AX17" s="66"/>
+      <c r="AY17" s="66"/>
+      <c r="AZ17" s="66"/>
+      <c r="BA17" s="66"/>
+      <c r="BB17" s="66"/>
+      <c r="BC17" s="66"/>
+      <c r="BD17" s="66"/>
+      <c r="BE17" s="66"/>
+      <c r="BF17" s="66"/>
+      <c r="BG17" s="66"/>
+      <c r="BH17" s="66"/>
+      <c r="BI17" s="66"/>
+      <c r="BJ17" s="66"/>
+      <c r="BK17" s="66"/>
+      <c r="BL17" s="68"/>
+      <c r="BR17" s="64"/>
+      <c r="BT17" s="64"/>
+    </row>
+    <row r="18" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A18" s="56"/>
+      <c r="C18" s="73"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="147"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="147"/>
-      <c r="J18" s="147"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="132" t="s">
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="M18" s="131"/>
-      <c r="N18" s="131"/>
-      <c r="O18" s="131"/>
-      <c r="P18" s="131"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="131"/>
-      <c r="S18" s="131"/>
-      <c r="T18" s="131"/>
-      <c r="U18" s="131"/>
-      <c r="V18" s="131"/>
-      <c r="W18" s="131"/>
-      <c r="X18" s="131"/>
-      <c r="Y18" s="131"/>
-      <c r="Z18" s="131"/>
-      <c r="AA18" s="131"/>
-      <c r="AB18" s="131"/>
-      <c r="AC18" s="131"/>
-      <c r="AD18" s="131"/>
-      <c r="AE18" s="131"/>
-      <c r="AF18" s="131"/>
-      <c r="AG18" s="131"/>
-      <c r="AH18" s="131"/>
-      <c r="AI18" s="131"/>
-      <c r="AJ18" s="131"/>
-      <c r="AK18" s="131"/>
-      <c r="AL18" s="131"/>
-      <c r="AM18" s="131"/>
-      <c r="AN18" s="131"/>
-      <c r="AO18" s="131"/>
-      <c r="AP18" s="131"/>
-      <c r="AQ18" s="131"/>
-      <c r="AR18" s="131"/>
-      <c r="AS18" s="131"/>
-      <c r="AT18" s="131"/>
-      <c r="AU18" s="131"/>
-      <c r="AV18" s="131"/>
-      <c r="AW18" s="131"/>
-      <c r="AX18" s="131"/>
-      <c r="AY18" s="131"/>
-      <c r="AZ18" s="131"/>
-      <c r="BA18" s="131"/>
-      <c r="BB18" s="131"/>
-      <c r="BC18" s="131"/>
-      <c r="BD18" s="131"/>
-      <c r="BE18" s="131"/>
-      <c r="BF18" s="131"/>
-      <c r="BG18" s="131"/>
-      <c r="BH18" s="131"/>
-      <c r="BI18" s="131"/>
-      <c r="BJ18" s="131"/>
-      <c r="BK18" s="131"/>
-      <c r="BL18" s="133"/>
-      <c r="BR18" s="127"/>
-      <c r="BT18" s="127"/>
-    </row>
-    <row r="19" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="119"/>
-      <c r="C19" s="138"/>
-      <c r="E19" s="141"/>
-      <c r="BR19" s="127"/>
-      <c r="BT19" s="127"/>
-    </row>
-    <row r="20" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A20" s="119"/>
-      <c r="C20" s="138"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="120" t="s">
+      <c r="M18" s="66"/>
+      <c r="N18" s="66"/>
+      <c r="O18" s="66"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="66"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="66"/>
+      <c r="X18" s="66"/>
+      <c r="Y18" s="66"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="66"/>
+      <c r="AB18" s="66"/>
+      <c r="AC18" s="66"/>
+      <c r="AD18" s="66"/>
+      <c r="AE18" s="66"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="66"/>
+      <c r="AH18" s="66"/>
+      <c r="AI18" s="66"/>
+      <c r="AJ18" s="66"/>
+      <c r="AK18" s="66"/>
+      <c r="AL18" s="66"/>
+      <c r="AM18" s="66"/>
+      <c r="AN18" s="66"/>
+      <c r="AO18" s="66"/>
+      <c r="AP18" s="66"/>
+      <c r="AQ18" s="66"/>
+      <c r="AR18" s="66"/>
+      <c r="AS18" s="66"/>
+      <c r="AT18" s="66"/>
+      <c r="AU18" s="66"/>
+      <c r="AV18" s="66"/>
+      <c r="AW18" s="66"/>
+      <c r="AX18" s="66"/>
+      <c r="AY18" s="66"/>
+      <c r="AZ18" s="66"/>
+      <c r="BA18" s="66"/>
+      <c r="BB18" s="66"/>
+      <c r="BC18" s="66"/>
+      <c r="BD18" s="66"/>
+      <c r="BE18" s="66"/>
+      <c r="BF18" s="66"/>
+      <c r="BG18" s="66"/>
+      <c r="BH18" s="66"/>
+      <c r="BI18" s="66"/>
+      <c r="BJ18" s="66"/>
+      <c r="BK18" s="66"/>
+      <c r="BL18" s="68"/>
+      <c r="BR18" s="64"/>
+      <c r="BT18" s="64"/>
+    </row>
+    <row r="19" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A19" s="56"/>
+      <c r="C19" s="73"/>
+      <c r="E19" s="76"/>
+      <c r="BR19" s="64"/>
+      <c r="BT19" s="64"/>
+    </row>
+    <row r="20" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A20" s="56"/>
+      <c r="C20" s="73"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="BR20" s="127"/>
-      <c r="BT20" s="127"/>
-    </row>
-    <row r="21" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A21" s="119"/>
-      <c r="C21" s="138"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="143" t="s">
+      <c r="BR20" s="64"/>
+      <c r="BT20" s="64"/>
+    </row>
+    <row r="21" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A21" s="56"/>
+      <c r="C21" s="73"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="144"/>
-      <c r="O21" s="144"/>
-      <c r="P21" s="144"/>
-      <c r="Q21" s="144"/>
-      <c r="R21" s="144"/>
-      <c r="S21" s="144"/>
-      <c r="T21" s="144"/>
-      <c r="U21" s="144"/>
-      <c r="V21" s="144"/>
-      <c r="W21" s="144"/>
-      <c r="X21" s="144"/>
-      <c r="Y21" s="144"/>
-      <c r="Z21" s="144"/>
-      <c r="AA21" s="144"/>
-      <c r="AB21" s="144"/>
-      <c r="AC21" s="144"/>
-      <c r="AD21" s="144"/>
-      <c r="AE21" s="144"/>
-      <c r="AF21" s="144"/>
-      <c r="AG21" s="144"/>
-      <c r="AH21" s="144"/>
-      <c r="AI21" s="144"/>
-      <c r="AJ21" s="144"/>
-      <c r="AK21" s="144"/>
-      <c r="AL21" s="144"/>
-      <c r="AM21" s="144"/>
-      <c r="AN21" s="144"/>
-      <c r="AO21" s="144"/>
-      <c r="AP21" s="144"/>
-      <c r="AQ21" s="144"/>
-      <c r="AR21" s="144"/>
-      <c r="AS21" s="144"/>
-      <c r="AT21" s="144"/>
-      <c r="AU21" s="144"/>
-      <c r="AV21" s="144"/>
-      <c r="AW21" s="144"/>
-      <c r="AX21" s="144"/>
-      <c r="AY21" s="144"/>
-      <c r="AZ21" s="144"/>
-      <c r="BA21" s="144"/>
-      <c r="BB21" s="144"/>
-      <c r="BC21" s="144"/>
-      <c r="BD21" s="144"/>
-      <c r="BE21" s="144"/>
-      <c r="BF21" s="144"/>
-      <c r="BG21" s="144"/>
-      <c r="BH21" s="144"/>
-      <c r="BI21" s="144"/>
-      <c r="BJ21" s="144"/>
-      <c r="BK21" s="144"/>
-      <c r="BL21" s="145"/>
-      <c r="BR21" s="127"/>
-      <c r="BT21" s="127"/>
-    </row>
-    <row r="22" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A22" s="119"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="138"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="146" t="s">
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="79"/>
+      <c r="U21" s="79"/>
+      <c r="V21" s="79"/>
+      <c r="W21" s="79"/>
+      <c r="X21" s="79"/>
+      <c r="Y21" s="79"/>
+      <c r="Z21" s="79"/>
+      <c r="AA21" s="79"/>
+      <c r="AB21" s="79"/>
+      <c r="AC21" s="79"/>
+      <c r="AD21" s="79"/>
+      <c r="AE21" s="79"/>
+      <c r="AF21" s="79"/>
+      <c r="AG21" s="79"/>
+      <c r="AH21" s="79"/>
+      <c r="AI21" s="79"/>
+      <c r="AJ21" s="79"/>
+      <c r="AK21" s="79"/>
+      <c r="AL21" s="79"/>
+      <c r="AM21" s="79"/>
+      <c r="AN21" s="79"/>
+      <c r="AO21" s="79"/>
+      <c r="AP21" s="79"/>
+      <c r="AQ21" s="79"/>
+      <c r="AR21" s="79"/>
+      <c r="AS21" s="79"/>
+      <c r="AT21" s="79"/>
+      <c r="AU21" s="79"/>
+      <c r="AV21" s="79"/>
+      <c r="AW21" s="79"/>
+      <c r="AX21" s="79"/>
+      <c r="AY21" s="79"/>
+      <c r="AZ21" s="79"/>
+      <c r="BA21" s="79"/>
+      <c r="BB21" s="79"/>
+      <c r="BC21" s="79"/>
+      <c r="BD21" s="79"/>
+      <c r="BE21" s="79"/>
+      <c r="BF21" s="79"/>
+      <c r="BG21" s="79"/>
+      <c r="BH21" s="79"/>
+      <c r="BI21" s="79"/>
+      <c r="BJ21" s="79"/>
+      <c r="BK21" s="79"/>
+      <c r="BL21" s="80"/>
+      <c r="BR21" s="64"/>
+      <c r="BT21" s="64"/>
+    </row>
+    <row r="22" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A22" s="56"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="73"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G22" s="147"/>
-      <c r="H22" s="147"/>
-      <c r="I22" s="147"/>
-      <c r="J22" s="147"/>
-      <c r="K22" s="148"/>
-      <c r="L22" s="132" t="s">
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="82"/>
+      <c r="K22" s="83"/>
+      <c r="L22" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
-      <c r="P22" s="131"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
-      <c r="S22" s="131"/>
-      <c r="T22" s="131"/>
-      <c r="U22" s="131"/>
-      <c r="V22" s="131"/>
-      <c r="W22" s="131"/>
-      <c r="X22" s="131"/>
-      <c r="Y22" s="131"/>
-      <c r="Z22" s="131"/>
-      <c r="AA22" s="131"/>
-      <c r="AB22" s="131"/>
-      <c r="AC22" s="131"/>
-      <c r="AD22" s="131"/>
-      <c r="AE22" s="131"/>
-      <c r="AF22" s="131"/>
-      <c r="AG22" s="131"/>
-      <c r="AH22" s="131"/>
-      <c r="AI22" s="131"/>
-      <c r="AJ22" s="131"/>
-      <c r="AK22" s="131"/>
-      <c r="AL22" s="131"/>
-      <c r="AM22" s="131"/>
-      <c r="AN22" s="131"/>
-      <c r="AO22" s="131"/>
-      <c r="AP22" s="131"/>
-      <c r="AQ22" s="131"/>
-      <c r="AR22" s="131"/>
-      <c r="AS22" s="131"/>
-      <c r="AT22" s="131"/>
-      <c r="AU22" s="131"/>
-      <c r="AV22" s="131"/>
-      <c r="AW22" s="131"/>
-      <c r="AX22" s="131"/>
-      <c r="AY22" s="131"/>
-      <c r="AZ22" s="131"/>
-      <c r="BA22" s="131"/>
-      <c r="BB22" s="131"/>
-      <c r="BC22" s="131"/>
-      <c r="BD22" s="131"/>
-      <c r="BE22" s="131"/>
-      <c r="BF22" s="131"/>
-      <c r="BG22" s="131"/>
-      <c r="BH22" s="131"/>
-      <c r="BI22" s="131"/>
-      <c r="BJ22" s="131"/>
-      <c r="BK22" s="131"/>
-      <c r="BL22" s="133"/>
-      <c r="BR22" s="149"/>
-      <c r="BT22" s="127"/>
-    </row>
-    <row r="23" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="138"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="156" t="s">
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="66"/>
+      <c r="AI22" s="66"/>
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="66"/>
+      <c r="AT22" s="66"/>
+      <c r="AU22" s="66"/>
+      <c r="AV22" s="66"/>
+      <c r="AW22" s="66"/>
+      <c r="AX22" s="66"/>
+      <c r="AY22" s="66"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="66"/>
+      <c r="BB22" s="66"/>
+      <c r="BC22" s="66"/>
+      <c r="BD22" s="66"/>
+      <c r="BE22" s="66"/>
+      <c r="BF22" s="66"/>
+      <c r="BG22" s="66"/>
+      <c r="BH22" s="66"/>
+      <c r="BI22" s="66"/>
+      <c r="BJ22" s="66"/>
+      <c r="BK22" s="66"/>
+      <c r="BL22" s="68"/>
+      <c r="BR22" s="84"/>
+      <c r="BT22" s="64"/>
+    </row>
+    <row r="23" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A23" s="56"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="73"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="158"/>
-      <c r="L23" s="132" t="s">
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="87"/>
+      <c r="L23" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M23" s="131"/>
-      <c r="N23" s="131"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="131"/>
-      <c r="R23" s="131"/>
-      <c r="S23" s="131"/>
-      <c r="T23" s="131"/>
-      <c r="U23" s="131"/>
-      <c r="V23" s="131"/>
-      <c r="W23" s="131"/>
-      <c r="X23" s="131"/>
-      <c r="Y23" s="131"/>
-      <c r="Z23" s="131"/>
-      <c r="AA23" s="131"/>
-      <c r="AB23" s="131"/>
-      <c r="AC23" s="131"/>
-      <c r="AD23" s="131"/>
-      <c r="AE23" s="131"/>
-      <c r="AF23" s="131"/>
-      <c r="AG23" s="131"/>
-      <c r="AH23" s="131"/>
-      <c r="AI23" s="131"/>
-      <c r="AJ23" s="131"/>
-      <c r="AK23" s="132" t="s">
+      <c r="M23" s="66"/>
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66"/>
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="66"/>
+      <c r="AE23" s="66"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="66"/>
+      <c r="AH23" s="66"/>
+      <c r="AI23" s="66"/>
+      <c r="AJ23" s="66"/>
+      <c r="AK23" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="AL23" s="131"/>
-      <c r="AM23" s="131"/>
-      <c r="AN23" s="131"/>
-      <c r="AO23" s="131"/>
-      <c r="AP23" s="131"/>
-      <c r="AQ23" s="131"/>
-      <c r="AR23" s="131"/>
-      <c r="AS23" s="131"/>
-      <c r="AT23" s="131"/>
-      <c r="AU23" s="131"/>
-      <c r="AV23" s="131"/>
-      <c r="AW23" s="131"/>
-      <c r="AX23" s="131"/>
-      <c r="AY23" s="131"/>
-      <c r="AZ23" s="131"/>
-      <c r="BA23" s="131"/>
-      <c r="BB23" s="131"/>
-      <c r="BC23" s="131"/>
-      <c r="BD23" s="131"/>
-      <c r="BE23" s="131"/>
-      <c r="BF23" s="131"/>
-      <c r="BG23" s="131"/>
-      <c r="BH23" s="131"/>
-      <c r="BI23" s="131"/>
-      <c r="BJ23" s="131"/>
-      <c r="BK23" s="131"/>
-      <c r="BL23" s="133"/>
-      <c r="BR23" s="149"/>
-      <c r="BT23" s="127"/>
-    </row>
-    <row r="24" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A24" s="119"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="138"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="146" t="s">
+      <c r="AL23" s="66"/>
+      <c r="AM23" s="66"/>
+      <c r="AN23" s="66"/>
+      <c r="AO23" s="66"/>
+      <c r="AP23" s="66"/>
+      <c r="AQ23" s="66"/>
+      <c r="AR23" s="66"/>
+      <c r="AS23" s="66"/>
+      <c r="AT23" s="66"/>
+      <c r="AU23" s="66"/>
+      <c r="AV23" s="66"/>
+      <c r="AW23" s="66"/>
+      <c r="AX23" s="66"/>
+      <c r="AY23" s="66"/>
+      <c r="AZ23" s="66"/>
+      <c r="BA23" s="66"/>
+      <c r="BB23" s="66"/>
+      <c r="BC23" s="66"/>
+      <c r="BD23" s="66"/>
+      <c r="BE23" s="66"/>
+      <c r="BF23" s="66"/>
+      <c r="BG23" s="66"/>
+      <c r="BH23" s="66"/>
+      <c r="BI23" s="66"/>
+      <c r="BJ23" s="66"/>
+      <c r="BK23" s="66"/>
+      <c r="BL23" s="68"/>
+      <c r="BR23" s="84"/>
+      <c r="BT23" s="64"/>
+    </row>
+    <row r="24" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A24" s="56"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="73"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="147"/>
-      <c r="H24" s="147"/>
-      <c r="I24" s="147"/>
-      <c r="J24" s="147"/>
-      <c r="K24" s="148"/>
-      <c r="L24" s="132" t="s">
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="83"/>
+      <c r="L24" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="M24" s="131"/>
-      <c r="N24" s="131"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="131"/>
-      <c r="S24" s="131"/>
-      <c r="T24" s="131"/>
-      <c r="U24" s="131"/>
-      <c r="V24" s="131"/>
-      <c r="W24" s="131"/>
-      <c r="X24" s="131"/>
-      <c r="Y24" s="131"/>
-      <c r="Z24" s="131"/>
-      <c r="AA24" s="131"/>
-      <c r="AB24" s="131"/>
-      <c r="AC24" s="131"/>
-      <c r="AD24" s="131"/>
-      <c r="AE24" s="131"/>
-      <c r="AF24" s="131"/>
-      <c r="AG24" s="131"/>
-      <c r="AH24" s="131"/>
-      <c r="AI24" s="131"/>
-      <c r="AJ24" s="131"/>
-      <c r="AK24" s="131"/>
-      <c r="AL24" s="131"/>
-      <c r="AM24" s="131"/>
-      <c r="AN24" s="131"/>
-      <c r="AO24" s="131"/>
-      <c r="AP24" s="131"/>
-      <c r="AQ24" s="131"/>
-      <c r="AR24" s="131"/>
-      <c r="AS24" s="131"/>
-      <c r="AT24" s="131"/>
-      <c r="AU24" s="131"/>
-      <c r="AV24" s="131"/>
-      <c r="AW24" s="131"/>
-      <c r="AX24" s="131"/>
-      <c r="AY24" s="131"/>
-      <c r="AZ24" s="131"/>
-      <c r="BA24" s="131"/>
-      <c r="BB24" s="131"/>
-      <c r="BC24" s="131"/>
-      <c r="BD24" s="131"/>
-      <c r="BE24" s="131"/>
-      <c r="BF24" s="131"/>
-      <c r="BG24" s="131"/>
-      <c r="BH24" s="131"/>
-      <c r="BI24" s="131"/>
-      <c r="BJ24" s="131"/>
-      <c r="BK24" s="131"/>
-      <c r="BL24" s="133"/>
-      <c r="BR24" s="149"/>
-      <c r="BT24" s="127"/>
-    </row>
-    <row r="25" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A25" s="119"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="138"/>
-      <c r="E25" s="141"/>
-      <c r="BR25" s="149"/>
-      <c r="BT25" s="127"/>
-    </row>
-    <row r="26" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A26" s="119"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="138"/>
-      <c r="E26" s="141"/>
-      <c r="G26" s="161"/>
-      <c r="BR26" s="149"/>
-      <c r="BT26" s="127"/>
-    </row>
-    <row r="27" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A27" s="119"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="138"/>
-      <c r="E27" s="141"/>
-      <c r="G27" s="161"/>
-      <c r="BR27" s="149"/>
-      <c r="BT27" s="127"/>
-    </row>
-    <row r="28" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A28" s="119"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="141">
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
+      <c r="AC24" s="66"/>
+      <c r="AD24" s="66"/>
+      <c r="AE24" s="66"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="66"/>
+      <c r="AH24" s="66"/>
+      <c r="AI24" s="66"/>
+      <c r="AJ24" s="66"/>
+      <c r="AK24" s="66"/>
+      <c r="AL24" s="66"/>
+      <c r="AM24" s="66"/>
+      <c r="AN24" s="66"/>
+      <c r="AO24" s="66"/>
+      <c r="AP24" s="66"/>
+      <c r="AQ24" s="66"/>
+      <c r="AR24" s="66"/>
+      <c r="AS24" s="66"/>
+      <c r="AT24" s="66"/>
+      <c r="AU24" s="66"/>
+      <c r="AV24" s="66"/>
+      <c r="AW24" s="66"/>
+      <c r="AX24" s="66"/>
+      <c r="AY24" s="66"/>
+      <c r="AZ24" s="66"/>
+      <c r="BA24" s="66"/>
+      <c r="BB24" s="66"/>
+      <c r="BC24" s="66"/>
+      <c r="BD24" s="66"/>
+      <c r="BE24" s="66"/>
+      <c r="BF24" s="66"/>
+      <c r="BG24" s="66"/>
+      <c r="BH24" s="66"/>
+      <c r="BI24" s="66"/>
+      <c r="BJ24" s="66"/>
+      <c r="BK24" s="66"/>
+      <c r="BL24" s="68"/>
+      <c r="BR24" s="84"/>
+      <c r="BT24" s="64"/>
+    </row>
+    <row r="25" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A25" s="56"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="73"/>
+      <c r="E25" s="76"/>
+      <c r="BR25" s="84"/>
+      <c r="BT25" s="64"/>
+    </row>
+    <row r="26" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A26" s="56"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="73"/>
+      <c r="E26" s="76"/>
+      <c r="G26" s="89"/>
+      <c r="BR26" s="84"/>
+      <c r="BT26" s="64"/>
+    </row>
+    <row r="27" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A27" s="56"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="73"/>
+      <c r="E27" s="76"/>
+      <c r="G27" s="89"/>
+      <c r="BR27" s="84"/>
+      <c r="BT27" s="64"/>
+    </row>
+    <row r="28" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A28" s="56"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="76">
         <v>2</v>
       </c>
-      <c r="E28" s="120" t="s">
+      <c r="E28" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="BR28" s="149"/>
-      <c r="BT28" s="127"/>
-    </row>
-    <row r="29" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A29" s="119"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="146" t="s">
+      <c r="BR28" s="84"/>
+      <c r="BT28" s="64"/>
+    </row>
+    <row r="29" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A29" s="56"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="F29" s="136"/>
-      <c r="G29" s="136"/>
-      <c r="H29" s="136"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="132" t="s">
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="L29" s="131"/>
-      <c r="M29" s="131"/>
-      <c r="N29" s="131"/>
-      <c r="O29" s="131"/>
-      <c r="P29" s="131"/>
-      <c r="Q29" s="131"/>
-      <c r="R29" s="131"/>
-      <c r="S29" s="131"/>
-      <c r="T29" s="131"/>
-      <c r="U29" s="131"/>
-      <c r="V29" s="131"/>
-      <c r="W29" s="131"/>
-      <c r="X29" s="131"/>
-      <c r="Y29" s="131"/>
-      <c r="Z29" s="131"/>
-      <c r="AA29" s="131"/>
-      <c r="AB29" s="131"/>
-      <c r="AC29" s="131"/>
-      <c r="AD29" s="131"/>
-      <c r="AE29" s="131"/>
-      <c r="AF29" s="131"/>
-      <c r="AG29" s="131"/>
-      <c r="AH29" s="131"/>
-      <c r="AI29" s="131"/>
-      <c r="AJ29" s="131"/>
-      <c r="AK29" s="131"/>
-      <c r="AL29" s="131"/>
-      <c r="AM29" s="131"/>
-      <c r="AN29" s="131"/>
-      <c r="AO29" s="131"/>
-      <c r="AP29" s="131"/>
-      <c r="AQ29" s="131"/>
-      <c r="AR29" s="131"/>
-      <c r="AS29" s="131"/>
-      <c r="AT29" s="131"/>
-      <c r="AU29" s="131"/>
-      <c r="AV29" s="131"/>
-      <c r="AW29" s="131"/>
-      <c r="AX29" s="131"/>
-      <c r="AY29" s="131"/>
-      <c r="AZ29" s="131"/>
-      <c r="BA29" s="131"/>
-      <c r="BB29" s="131"/>
-      <c r="BC29" s="131"/>
-      <c r="BD29" s="131"/>
-      <c r="BE29" s="131"/>
-      <c r="BF29" s="131"/>
-      <c r="BG29" s="131"/>
-      <c r="BH29" s="131"/>
-      <c r="BI29" s="131"/>
-      <c r="BJ29" s="131"/>
-      <c r="BK29" s="131"/>
-      <c r="BL29" s="133"/>
-      <c r="BR29" s="149"/>
-      <c r="BT29" s="127"/>
-    </row>
-    <row r="30" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="135" t="s">
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="66"/>
+      <c r="U29" s="66"/>
+      <c r="V29" s="66"/>
+      <c r="W29" s="66"/>
+      <c r="X29" s="66"/>
+      <c r="Y29" s="66"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="66"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="66"/>
+      <c r="AI29" s="66"/>
+      <c r="AJ29" s="66"/>
+      <c r="AK29" s="66"/>
+      <c r="AL29" s="66"/>
+      <c r="AM29" s="66"/>
+      <c r="AN29" s="66"/>
+      <c r="AO29" s="66"/>
+      <c r="AP29" s="66"/>
+      <c r="AQ29" s="66"/>
+      <c r="AR29" s="66"/>
+      <c r="AS29" s="66"/>
+      <c r="AT29" s="66"/>
+      <c r="AU29" s="66"/>
+      <c r="AV29" s="66"/>
+      <c r="AW29" s="66"/>
+      <c r="AX29" s="66"/>
+      <c r="AY29" s="66"/>
+      <c r="AZ29" s="66"/>
+      <c r="BA29" s="66"/>
+      <c r="BB29" s="66"/>
+      <c r="BC29" s="66"/>
+      <c r="BD29" s="66"/>
+      <c r="BE29" s="66"/>
+      <c r="BF29" s="66"/>
+      <c r="BG29" s="66"/>
+      <c r="BH29" s="66"/>
+      <c r="BI29" s="66"/>
+      <c r="BJ29" s="66"/>
+      <c r="BK29" s="66"/>
+      <c r="BL29" s="68"/>
+      <c r="BR29" s="84"/>
+      <c r="BT29" s="64"/>
+    </row>
+    <row r="30" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A30" s="56"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="135" t="s">
+      <c r="F30" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="136"/>
-      <c r="H30" s="136"/>
-      <c r="I30" s="136"/>
-      <c r="J30" s="136"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="136"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="136"/>
-      <c r="Q30" s="136"/>
-      <c r="R30" s="136"/>
-      <c r="S30" s="136"/>
-      <c r="T30" s="136"/>
-      <c r="U30" s="135" t="s">
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="V30" s="136"/>
-      <c r="W30" s="136"/>
-      <c r="X30" s="136"/>
-      <c r="Y30" s="136"/>
-      <c r="Z30" s="136"/>
-      <c r="AA30" s="136"/>
-      <c r="AB30" s="136"/>
-      <c r="AC30" s="136"/>
-      <c r="AD30" s="136"/>
-      <c r="AE30" s="136"/>
-      <c r="AF30" s="137"/>
-      <c r="AG30" s="135" t="s">
+      <c r="V30" s="71"/>
+      <c r="W30" s="71"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="71"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="71"/>
+      <c r="AC30" s="71"/>
+      <c r="AD30" s="71"/>
+      <c r="AE30" s="71"/>
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="AH30" s="136"/>
-      <c r="AI30" s="136"/>
-      <c r="AJ30" s="136"/>
-      <c r="AK30" s="136"/>
-      <c r="AL30" s="136"/>
-      <c r="AM30" s="136"/>
-      <c r="AN30" s="136"/>
-      <c r="AO30" s="136"/>
-      <c r="AP30" s="136"/>
-      <c r="AQ30" s="136"/>
-      <c r="AR30" s="137"/>
-      <c r="AS30" s="136" t="s">
+      <c r="AH30" s="71"/>
+      <c r="AI30" s="71"/>
+      <c r="AJ30" s="71"/>
+      <c r="AK30" s="71"/>
+      <c r="AL30" s="71"/>
+      <c r="AM30" s="71"/>
+      <c r="AN30" s="71"/>
+      <c r="AO30" s="71"/>
+      <c r="AP30" s="71"/>
+      <c r="AQ30" s="71"/>
+      <c r="AR30" s="72"/>
+      <c r="AS30" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="AT30" s="136"/>
-      <c r="AU30" s="136"/>
-      <c r="AV30" s="136"/>
-      <c r="AW30" s="136"/>
-      <c r="AX30" s="136"/>
-      <c r="AY30" s="136"/>
-      <c r="AZ30" s="136"/>
-      <c r="BA30" s="136"/>
-      <c r="BB30" s="136"/>
-      <c r="BC30" s="136"/>
-      <c r="BD30" s="136"/>
-      <c r="BE30" s="136"/>
-      <c r="BF30" s="136"/>
-      <c r="BG30" s="136"/>
-      <c r="BH30" s="136"/>
-      <c r="BI30" s="136"/>
-      <c r="BJ30" s="136"/>
-      <c r="BK30" s="136"/>
-      <c r="BL30" s="137"/>
-      <c r="BR30" s="149"/>
-      <c r="BT30" s="127"/>
-    </row>
-    <row r="31" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A31" s="119"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="159">
+      <c r="AT30" s="71"/>
+      <c r="AU30" s="71"/>
+      <c r="AV30" s="71"/>
+      <c r="AW30" s="71"/>
+      <c r="AX30" s="71"/>
+      <c r="AY30" s="71"/>
+      <c r="AZ30" s="71"/>
+      <c r="BA30" s="71"/>
+      <c r="BB30" s="71"/>
+      <c r="BC30" s="71"/>
+      <c r="BD30" s="71"/>
+      <c r="BE30" s="71"/>
+      <c r="BF30" s="71"/>
+      <c r="BG30" s="71"/>
+      <c r="BH30" s="71"/>
+      <c r="BI30" s="71"/>
+      <c r="BJ30" s="71"/>
+      <c r="BK30" s="71"/>
+      <c r="BL30" s="72"/>
+      <c r="BR30" s="84"/>
+      <c r="BT30" s="64"/>
+    </row>
+    <row r="31" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A31" s="56"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="88">
         <v>1</v>
       </c>
-      <c r="F31" s="162" t="s">
+      <c r="F31" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
-      <c r="L31" s="131"/>
-      <c r="M31" s="131"/>
-      <c r="N31" s="131"/>
-      <c r="O31" s="131"/>
-      <c r="P31" s="131"/>
-      <c r="Q31" s="131"/>
-      <c r="R31" s="131"/>
-      <c r="S31" s="131"/>
-      <c r="T31" s="133"/>
-      <c r="U31" s="160" t="s">
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="68"/>
+      <c r="U31" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V31" s="163"/>
-      <c r="W31" s="163"/>
-      <c r="X31" s="163"/>
-      <c r="Y31" s="163"/>
-      <c r="Z31" s="163"/>
-      <c r="AA31" s="163"/>
-      <c r="AB31" s="163"/>
-      <c r="AC31" s="163"/>
-      <c r="AD31" s="163"/>
-      <c r="AE31" s="163"/>
-      <c r="AF31" s="164"/>
-      <c r="AG31" s="160" t="s">
+      <c r="V31" s="172"/>
+      <c r="W31" s="172"/>
+      <c r="X31" s="172"/>
+      <c r="Y31" s="172"/>
+      <c r="Z31" s="172"/>
+      <c r="AA31" s="172"/>
+      <c r="AB31" s="172"/>
+      <c r="AC31" s="172"/>
+      <c r="AD31" s="172"/>
+      <c r="AE31" s="172"/>
+      <c r="AF31" s="173"/>
+      <c r="AG31" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH31" s="163"/>
-      <c r="AI31" s="163"/>
-      <c r="AJ31" s="163"/>
-      <c r="AK31" s="163"/>
-      <c r="AL31" s="163"/>
-      <c r="AM31" s="163"/>
-      <c r="AN31" s="163"/>
-      <c r="AO31" s="163"/>
-      <c r="AP31" s="163"/>
-      <c r="AQ31" s="163"/>
-      <c r="AR31" s="164"/>
-      <c r="AS31" s="165" t="s">
+      <c r="AH31" s="172"/>
+      <c r="AI31" s="172"/>
+      <c r="AJ31" s="172"/>
+      <c r="AK31" s="172"/>
+      <c r="AL31" s="172"/>
+      <c r="AM31" s="172"/>
+      <c r="AN31" s="172"/>
+      <c r="AO31" s="172"/>
+      <c r="AP31" s="172"/>
+      <c r="AQ31" s="172"/>
+      <c r="AR31" s="173"/>
+      <c r="AS31" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT31" s="166"/>
-      <c r="AU31" s="166"/>
-      <c r="AV31" s="166"/>
-      <c r="AW31" s="166"/>
-      <c r="AX31" s="166"/>
-      <c r="AY31" s="166"/>
-      <c r="AZ31" s="166"/>
-      <c r="BA31" s="166"/>
-      <c r="BB31" s="166"/>
-      <c r="BC31" s="166"/>
-      <c r="BD31" s="166"/>
-      <c r="BE31" s="166"/>
-      <c r="BF31" s="166"/>
-      <c r="BG31" s="166"/>
-      <c r="BH31" s="166"/>
-      <c r="BI31" s="166"/>
-      <c r="BJ31" s="166"/>
-      <c r="BK31" s="166"/>
-      <c r="BL31" s="167"/>
-      <c r="BR31" s="149"/>
-      <c r="BT31" s="127"/>
-    </row>
-    <row r="32" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A32" s="119"/>
-      <c r="B32" s="134"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="159">
+      <c r="AT31" s="175"/>
+      <c r="AU31" s="175"/>
+      <c r="AV31" s="175"/>
+      <c r="AW31" s="175"/>
+      <c r="AX31" s="175"/>
+      <c r="AY31" s="175"/>
+      <c r="AZ31" s="175"/>
+      <c r="BA31" s="175"/>
+      <c r="BB31" s="175"/>
+      <c r="BC31" s="175"/>
+      <c r="BD31" s="175"/>
+      <c r="BE31" s="175"/>
+      <c r="BF31" s="175"/>
+      <c r="BG31" s="175"/>
+      <c r="BH31" s="175"/>
+      <c r="BI31" s="175"/>
+      <c r="BJ31" s="175"/>
+      <c r="BK31" s="175"/>
+      <c r="BL31" s="176"/>
+      <c r="BR31" s="84"/>
+      <c r="BT31" s="64"/>
+    </row>
+    <row r="32" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A32" s="56"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="88">
         <v>2</v>
       </c>
-      <c r="F32" s="162" t="s">
+      <c r="F32" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="131"/>
-      <c r="K32" s="131"/>
-      <c r="L32" s="131"/>
-      <c r="M32" s="131"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="131"/>
-      <c r="P32" s="131"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="131"/>
-      <c r="S32" s="131"/>
-      <c r="T32" s="133"/>
-      <c r="U32" s="160" t="s">
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="66"/>
+      <c r="O32" s="66"/>
+      <c r="P32" s="66"/>
+      <c r="Q32" s="66"/>
+      <c r="R32" s="66"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V32" s="163"/>
-      <c r="W32" s="163"/>
-      <c r="X32" s="163"/>
-      <c r="Y32" s="163"/>
-      <c r="Z32" s="163"/>
-      <c r="AA32" s="163"/>
-      <c r="AB32" s="163"/>
-      <c r="AC32" s="163"/>
-      <c r="AD32" s="163"/>
-      <c r="AE32" s="163"/>
-      <c r="AF32" s="164"/>
-      <c r="AG32" s="160" t="s">
+      <c r="V32" s="172"/>
+      <c r="W32" s="172"/>
+      <c r="X32" s="172"/>
+      <c r="Y32" s="172"/>
+      <c r="Z32" s="172"/>
+      <c r="AA32" s="172"/>
+      <c r="AB32" s="172"/>
+      <c r="AC32" s="172"/>
+      <c r="AD32" s="172"/>
+      <c r="AE32" s="172"/>
+      <c r="AF32" s="173"/>
+      <c r="AG32" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH32" s="163"/>
-      <c r="AI32" s="163"/>
-      <c r="AJ32" s="163"/>
-      <c r="AK32" s="163"/>
-      <c r="AL32" s="163"/>
-      <c r="AM32" s="163"/>
-      <c r="AN32" s="163"/>
-      <c r="AO32" s="163"/>
-      <c r="AP32" s="163"/>
-      <c r="AQ32" s="163"/>
-      <c r="AR32" s="164"/>
-      <c r="AS32" s="165" t="s">
+      <c r="AH32" s="172"/>
+      <c r="AI32" s="172"/>
+      <c r="AJ32" s="172"/>
+      <c r="AK32" s="172"/>
+      <c r="AL32" s="172"/>
+      <c r="AM32" s="172"/>
+      <c r="AN32" s="172"/>
+      <c r="AO32" s="172"/>
+      <c r="AP32" s="172"/>
+      <c r="AQ32" s="172"/>
+      <c r="AR32" s="173"/>
+      <c r="AS32" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT32" s="166"/>
-      <c r="AU32" s="166"/>
-      <c r="AV32" s="166"/>
-      <c r="AW32" s="166"/>
-      <c r="AX32" s="166"/>
-      <c r="AY32" s="166"/>
-      <c r="AZ32" s="166"/>
-      <c r="BA32" s="166"/>
-      <c r="BB32" s="166"/>
-      <c r="BC32" s="166"/>
-      <c r="BD32" s="166"/>
-      <c r="BE32" s="166"/>
-      <c r="BF32" s="166"/>
-      <c r="BG32" s="166"/>
-      <c r="BH32" s="166"/>
-      <c r="BI32" s="166"/>
-      <c r="BJ32" s="166"/>
-      <c r="BK32" s="166"/>
-      <c r="BL32" s="167"/>
-      <c r="BR32" s="149"/>
-      <c r="BT32" s="127"/>
-    </row>
-    <row r="33" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A33" s="119"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="169"/>
-      <c r="E33" s="170"/>
-      <c r="F33" s="170"/>
-      <c r="G33" s="170"/>
-      <c r="H33" s="170"/>
-      <c r="I33" s="170"/>
-      <c r="J33" s="170"/>
-      <c r="K33" s="170"/>
-      <c r="L33" s="170"/>
-      <c r="M33" s="170"/>
-      <c r="N33" s="170"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="170"/>
-      <c r="Q33" s="170"/>
-      <c r="R33" s="170"/>
-      <c r="S33" s="170"/>
-      <c r="T33" s="170"/>
-      <c r="U33" s="170"/>
-      <c r="V33" s="170"/>
-      <c r="W33" s="170"/>
-      <c r="X33" s="170"/>
-      <c r="Y33" s="170"/>
-      <c r="Z33" s="170"/>
-      <c r="AA33" s="170"/>
-      <c r="AB33" s="170"/>
-      <c r="AC33" s="170"/>
-      <c r="AD33" s="170"/>
-      <c r="AE33" s="170"/>
-      <c r="AF33" s="170"/>
-      <c r="AG33" s="171"/>
-      <c r="AH33" s="171"/>
-      <c r="AI33" s="171"/>
-      <c r="AJ33" s="171"/>
-      <c r="AK33" s="171"/>
-      <c r="AL33" s="171"/>
-      <c r="AM33" s="171"/>
-      <c r="AN33" s="171"/>
-      <c r="AO33" s="171"/>
-      <c r="AP33" s="171"/>
-      <c r="AQ33" s="171"/>
-      <c r="AR33" s="171"/>
-      <c r="AS33" s="171"/>
-      <c r="AT33" s="171"/>
-      <c r="AU33" s="170"/>
-      <c r="AV33" s="170"/>
-      <c r="AW33" s="170"/>
-      <c r="AX33" s="171"/>
-      <c r="AY33" s="171"/>
-      <c r="AZ33" s="171"/>
-      <c r="BA33" s="171"/>
-      <c r="BB33" s="171"/>
-      <c r="BC33" s="170"/>
-      <c r="BD33" s="170"/>
-      <c r="BE33" s="170"/>
-      <c r="BF33" s="171"/>
-      <c r="BG33" s="171"/>
-      <c r="BH33" s="171"/>
-      <c r="BI33" s="171"/>
-      <c r="BJ33" s="171"/>
-      <c r="BK33" s="170"/>
-      <c r="BL33" s="170"/>
-      <c r="BM33" s="170"/>
-      <c r="BN33" s="170"/>
-      <c r="BO33" s="170"/>
-      <c r="BP33" s="170"/>
-      <c r="BQ33" s="170"/>
-      <c r="BR33" s="172"/>
-      <c r="BT33" s="127"/>
-    </row>
-    <row r="34" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A34" s="119"/>
-      <c r="C34" s="173"/>
-      <c r="BT34" s="127"/>
-    </row>
-    <row r="35" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A35" s="177"/>
-      <c r="C35" s="173"/>
-      <c r="BT35" s="177"/>
-    </row>
-    <row r="36" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A36" s="119"/>
-      <c r="C36" s="121" t="s">
+      <c r="AT32" s="175"/>
+      <c r="AU32" s="175"/>
+      <c r="AV32" s="175"/>
+      <c r="AW32" s="175"/>
+      <c r="AX32" s="175"/>
+      <c r="AY32" s="175"/>
+      <c r="AZ32" s="175"/>
+      <c r="BA32" s="175"/>
+      <c r="BB32" s="175"/>
+      <c r="BC32" s="175"/>
+      <c r="BD32" s="175"/>
+      <c r="BE32" s="175"/>
+      <c r="BF32" s="175"/>
+      <c r="BG32" s="175"/>
+      <c r="BH32" s="175"/>
+      <c r="BI32" s="175"/>
+      <c r="BJ32" s="175"/>
+      <c r="BK32" s="175"/>
+      <c r="BL32" s="176"/>
+      <c r="BR32" s="84"/>
+      <c r="BT32" s="64"/>
+    </row>
+    <row r="33" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A33" s="56"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="93"/>
+      <c r="K33" s="93"/>
+      <c r="L33" s="93"/>
+      <c r="M33" s="93"/>
+      <c r="N33" s="93"/>
+      <c r="O33" s="93"/>
+      <c r="P33" s="93"/>
+      <c r="Q33" s="93"/>
+      <c r="R33" s="93"/>
+      <c r="S33" s="93"/>
+      <c r="T33" s="93"/>
+      <c r="U33" s="93"/>
+      <c r="V33" s="93"/>
+      <c r="W33" s="93"/>
+      <c r="X33" s="93"/>
+      <c r="Y33" s="93"/>
+      <c r="Z33" s="93"/>
+      <c r="AA33" s="93"/>
+      <c r="AB33" s="93"/>
+      <c r="AC33" s="93"/>
+      <c r="AD33" s="93"/>
+      <c r="AE33" s="93"/>
+      <c r="AF33" s="93"/>
+      <c r="AG33" s="94"/>
+      <c r="AH33" s="94"/>
+      <c r="AI33" s="94"/>
+      <c r="AJ33" s="94"/>
+      <c r="AK33" s="94"/>
+      <c r="AL33" s="94"/>
+      <c r="AM33" s="94"/>
+      <c r="AN33" s="94"/>
+      <c r="AO33" s="94"/>
+      <c r="AP33" s="94"/>
+      <c r="AQ33" s="94"/>
+      <c r="AR33" s="94"/>
+      <c r="AS33" s="94"/>
+      <c r="AT33" s="94"/>
+      <c r="AU33" s="93"/>
+      <c r="AV33" s="93"/>
+      <c r="AW33" s="93"/>
+      <c r="AX33" s="94"/>
+      <c r="AY33" s="94"/>
+      <c r="AZ33" s="94"/>
+      <c r="BA33" s="94"/>
+      <c r="BB33" s="94"/>
+      <c r="BC33" s="93"/>
+      <c r="BD33" s="93"/>
+      <c r="BE33" s="93"/>
+      <c r="BF33" s="94"/>
+      <c r="BG33" s="94"/>
+      <c r="BH33" s="94"/>
+      <c r="BI33" s="94"/>
+      <c r="BJ33" s="94"/>
+      <c r="BK33" s="93"/>
+      <c r="BL33" s="93"/>
+      <c r="BM33" s="93"/>
+      <c r="BN33" s="93"/>
+      <c r="BO33" s="93"/>
+      <c r="BP33" s="93"/>
+      <c r="BQ33" s="93"/>
+      <c r="BR33" s="95"/>
+      <c r="BT33" s="64"/>
+    </row>
+    <row r="34" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A34" s="56"/>
+      <c r="C34" s="96"/>
+      <c r="BT34" s="64"/>
+    </row>
+    <row r="35" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="C35" s="96"/>
+    </row>
+    <row r="36" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A36" s="56"/>
+      <c r="C36" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="122"/>
-      <c r="E36" s="123" t="s">
+      <c r="D36" s="59"/>
+      <c r="E36" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="124"/>
-      <c r="K36" s="124"/>
-      <c r="L36" s="124"/>
-      <c r="M36" s="124"/>
-      <c r="N36" s="124"/>
-      <c r="O36" s="124"/>
-      <c r="P36" s="124"/>
-      <c r="Q36" s="124"/>
-      <c r="R36" s="124"/>
-      <c r="S36" s="124"/>
-      <c r="T36" s="124"/>
-      <c r="U36" s="124"/>
-      <c r="V36" s="124"/>
-      <c r="W36" s="124"/>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="124"/>
-      <c r="Z36" s="124"/>
-      <c r="AA36" s="124"/>
-      <c r="AB36" s="124"/>
-      <c r="AC36" s="124"/>
-      <c r="AD36" s="124"/>
-      <c r="AE36" s="124"/>
-      <c r="AF36" s="124"/>
-      <c r="AG36" s="124"/>
-      <c r="AH36" s="124"/>
-      <c r="AI36" s="124"/>
-      <c r="AJ36" s="125" t="s">
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="61"/>
+      <c r="Q36" s="61"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="AK36" s="124"/>
-      <c r="AL36" s="124"/>
-      <c r="AM36" s="124"/>
-      <c r="AN36" s="124"/>
-      <c r="AO36" s="124"/>
-      <c r="AP36" s="124"/>
-      <c r="AQ36" s="124"/>
-      <c r="AR36" s="124"/>
-      <c r="AS36" s="124"/>
-      <c r="AT36" s="124"/>
-      <c r="AU36" s="124"/>
-      <c r="AV36" s="124"/>
-      <c r="AW36" s="124"/>
-      <c r="AX36" s="124"/>
-      <c r="AY36" s="124"/>
-      <c r="AZ36" s="124"/>
-      <c r="BA36" s="124"/>
-      <c r="BB36" s="125" t="s">
+      <c r="AK36" s="61"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="61"/>
+      <c r="AN36" s="61"/>
+      <c r="AO36" s="61"/>
+      <c r="AP36" s="61"/>
+      <c r="AQ36" s="61"/>
+      <c r="AR36" s="61"/>
+      <c r="AS36" s="61"/>
+      <c r="AT36" s="61"/>
+      <c r="AU36" s="61"/>
+      <c r="AV36" s="61"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
+      <c r="BB36" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="BC36" s="124"/>
-      <c r="BD36" s="124"/>
-      <c r="BE36" s="124"/>
-      <c r="BF36" s="124"/>
-      <c r="BG36" s="124"/>
-      <c r="BH36" s="124"/>
-      <c r="BI36" s="124"/>
-      <c r="BJ36" s="124"/>
-      <c r="BK36" s="124"/>
-      <c r="BL36" s="124"/>
-      <c r="BM36" s="124"/>
-      <c r="BN36" s="124"/>
-      <c r="BO36" s="124"/>
-      <c r="BP36" s="124"/>
-      <c r="BQ36" s="124"/>
-      <c r="BR36" s="126"/>
-      <c r="BT36" s="127"/>
-    </row>
-    <row r="37" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A37" s="119"/>
-      <c r="C37" s="128">
+      <c r="BC36" s="61"/>
+      <c r="BD36" s="61"/>
+      <c r="BE36" s="61"/>
+      <c r="BF36" s="61"/>
+      <c r="BG36" s="61"/>
+      <c r="BH36" s="61"/>
+      <c r="BI36" s="61"/>
+      <c r="BJ36" s="61"/>
+      <c r="BK36" s="61"/>
+      <c r="BL36" s="61"/>
+      <c r="BM36" s="61"/>
+      <c r="BN36" s="61"/>
+      <c r="BO36" s="61"/>
+      <c r="BP36" s="61"/>
+      <c r="BQ36" s="61"/>
+      <c r="BR36" s="63"/>
+      <c r="BT36" s="64"/>
+    </row>
+    <row r="37" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A37" s="56"/>
+      <c r="C37" s="160">
         <v>1</v>
       </c>
-      <c r="D37" s="129"/>
-      <c r="E37" s="130" t="s">
+      <c r="D37" s="161"/>
+      <c r="E37" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="F37" s="131"/>
-      <c r="G37" s="131"/>
-      <c r="H37" s="131"/>
-      <c r="I37" s="131"/>
-      <c r="J37" s="131"/>
-      <c r="K37" s="131"/>
-      <c r="L37" s="131"/>
-      <c r="M37" s="131"/>
-      <c r="N37" s="131"/>
-      <c r="O37" s="131"/>
-      <c r="P37" s="131"/>
-      <c r="Q37" s="131"/>
-      <c r="R37" s="131"/>
-      <c r="S37" s="131"/>
-      <c r="T37" s="131"/>
-      <c r="U37" s="131"/>
-      <c r="V37" s="131"/>
-      <c r="W37" s="131"/>
-      <c r="X37" s="131"/>
-      <c r="Y37" s="131"/>
-      <c r="Z37" s="131"/>
-      <c r="AA37" s="131"/>
-      <c r="AB37" s="131"/>
-      <c r="AC37" s="131"/>
-      <c r="AD37" s="131"/>
-      <c r="AE37" s="131"/>
-      <c r="AF37" s="131"/>
-      <c r="AG37" s="131"/>
-      <c r="AH37" s="131"/>
-      <c r="AI37" s="131"/>
-      <c r="AJ37" s="132" t="s">
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="66"/>
+      <c r="M37" s="66"/>
+      <c r="N37" s="66"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="66"/>
+      <c r="S37" s="66"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="66"/>
+      <c r="V37" s="66"/>
+      <c r="W37" s="66"/>
+      <c r="X37" s="66"/>
+      <c r="Y37" s="66"/>
+      <c r="Z37" s="66"/>
+      <c r="AA37" s="66"/>
+      <c r="AB37" s="66"/>
+      <c r="AC37" s="66"/>
+      <c r="AD37" s="66"/>
+      <c r="AE37" s="66"/>
+      <c r="AF37" s="66"/>
+      <c r="AG37" s="66"/>
+      <c r="AH37" s="66"/>
+      <c r="AI37" s="66"/>
+      <c r="AJ37" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="AK37" s="131"/>
-      <c r="AL37" s="131"/>
-      <c r="AM37" s="131"/>
-      <c r="AN37" s="131"/>
-      <c r="AO37" s="131"/>
-      <c r="AP37" s="131"/>
-      <c r="AQ37" s="131"/>
-      <c r="AR37" s="131"/>
-      <c r="AS37" s="131"/>
-      <c r="AT37" s="131"/>
-      <c r="AU37" s="131"/>
-      <c r="AV37" s="131"/>
-      <c r="AW37" s="131"/>
-      <c r="AX37" s="131"/>
-      <c r="AY37" s="131"/>
-      <c r="AZ37" s="131"/>
-      <c r="BA37" s="131"/>
-      <c r="BB37" s="132" t="s">
+      <c r="AK37" s="66"/>
+      <c r="AL37" s="66"/>
+      <c r="AM37" s="66"/>
+      <c r="AN37" s="66"/>
+      <c r="AO37" s="66"/>
+      <c r="AP37" s="66"/>
+      <c r="AQ37" s="66"/>
+      <c r="AR37" s="66"/>
+      <c r="AS37" s="66"/>
+      <c r="AT37" s="66"/>
+      <c r="AU37" s="66"/>
+      <c r="AV37" s="66"/>
+      <c r="AW37" s="66"/>
+      <c r="AX37" s="66"/>
+      <c r="AY37" s="66"/>
+      <c r="AZ37" s="66"/>
+      <c r="BA37" s="66"/>
+      <c r="BB37" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="BC37" s="131"/>
-      <c r="BD37" s="131"/>
-      <c r="BE37" s="131"/>
-      <c r="BF37" s="131"/>
-      <c r="BG37" s="131"/>
-      <c r="BH37" s="131"/>
-      <c r="BI37" s="131"/>
-      <c r="BJ37" s="131"/>
-      <c r="BK37" s="131"/>
-      <c r="BL37" s="131"/>
-      <c r="BM37" s="131"/>
-      <c r="BN37" s="131"/>
-      <c r="BO37" s="131"/>
-      <c r="BP37" s="131"/>
-      <c r="BQ37" s="131"/>
-      <c r="BR37" s="133"/>
-      <c r="BT37" s="127"/>
-    </row>
-    <row r="38" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A38" s="119"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="135" t="s">
+      <c r="BC37" s="66"/>
+      <c r="BD37" s="66"/>
+      <c r="BE37" s="66"/>
+      <c r="BF37" s="66"/>
+      <c r="BG37" s="66"/>
+      <c r="BH37" s="66"/>
+      <c r="BI37" s="66"/>
+      <c r="BJ37" s="66"/>
+      <c r="BK37" s="66"/>
+      <c r="BL37" s="66"/>
+      <c r="BM37" s="66"/>
+      <c r="BN37" s="66"/>
+      <c r="BO37" s="66"/>
+      <c r="BP37" s="66"/>
+      <c r="BQ37" s="66"/>
+      <c r="BR37" s="68"/>
+      <c r="BT37" s="64"/>
+    </row>
+    <row r="38" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A38" s="56"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="137"/>
-      <c r="M38" s="131" t="s">
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="N38" s="131"/>
-      <c r="O38" s="131"/>
-      <c r="P38" s="131"/>
-      <c r="Q38" s="131"/>
-      <c r="R38" s="131"/>
-      <c r="S38" s="131"/>
-      <c r="T38" s="131"/>
-      <c r="U38" s="131"/>
-      <c r="V38" s="131"/>
-      <c r="W38" s="131"/>
-      <c r="X38" s="131"/>
-      <c r="Y38" s="131"/>
-      <c r="Z38" s="131"/>
-      <c r="AA38" s="131"/>
-      <c r="AB38" s="131"/>
-      <c r="AC38" s="131"/>
-      <c r="AD38" s="131"/>
-      <c r="AE38" s="131"/>
-      <c r="AF38" s="131"/>
-      <c r="AG38" s="131"/>
-      <c r="AH38" s="131"/>
-      <c r="AI38" s="131"/>
-      <c r="AJ38" s="131"/>
-      <c r="AK38" s="131"/>
-      <c r="AL38" s="131"/>
-      <c r="AM38" s="131"/>
-      <c r="AN38" s="131"/>
-      <c r="AO38" s="131"/>
-      <c r="AP38" s="131"/>
-      <c r="AQ38" s="131"/>
-      <c r="AR38" s="131"/>
-      <c r="AS38" s="131"/>
-      <c r="AT38" s="131"/>
-      <c r="AU38" s="131"/>
-      <c r="AV38" s="131"/>
-      <c r="AW38" s="131"/>
-      <c r="AX38" s="131"/>
-      <c r="AY38" s="131"/>
-      <c r="AZ38" s="131"/>
-      <c r="BA38" s="131"/>
-      <c r="BB38" s="131"/>
-      <c r="BC38" s="131"/>
-      <c r="BD38" s="131"/>
-      <c r="BE38" s="131"/>
-      <c r="BF38" s="131"/>
-      <c r="BG38" s="131"/>
-      <c r="BH38" s="131"/>
-      <c r="BI38" s="131"/>
-      <c r="BJ38" s="131"/>
-      <c r="BK38" s="131"/>
-      <c r="BL38" s="131"/>
-      <c r="BM38" s="131"/>
-      <c r="BN38" s="131"/>
-      <c r="BO38" s="131"/>
-      <c r="BP38" s="131"/>
-      <c r="BQ38" s="131"/>
-      <c r="BR38" s="133"/>
-    </row>
-    <row r="39" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A39" s="119"/>
-      <c r="B39" s="134"/>
-      <c r="C39" s="135" t="s">
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="66"/>
+      <c r="W38" s="66"/>
+      <c r="X38" s="66"/>
+      <c r="Y38" s="66"/>
+      <c r="Z38" s="66"/>
+      <c r="AA38" s="66"/>
+      <c r="AB38" s="66"/>
+      <c r="AC38" s="66"/>
+      <c r="AD38" s="66"/>
+      <c r="AE38" s="66"/>
+      <c r="AF38" s="66"/>
+      <c r="AG38" s="66"/>
+      <c r="AH38" s="66"/>
+      <c r="AI38" s="66"/>
+      <c r="AJ38" s="66"/>
+      <c r="AK38" s="66"/>
+      <c r="AL38" s="66"/>
+      <c r="AM38" s="66"/>
+      <c r="AN38" s="66"/>
+      <c r="AO38" s="66"/>
+      <c r="AP38" s="66"/>
+      <c r="AQ38" s="66"/>
+      <c r="AR38" s="66"/>
+      <c r="AS38" s="66"/>
+      <c r="AT38" s="66"/>
+      <c r="AU38" s="66"/>
+      <c r="AV38" s="66"/>
+      <c r="AW38" s="66"/>
+      <c r="AX38" s="66"/>
+      <c r="AY38" s="66"/>
+      <c r="AZ38" s="66"/>
+      <c r="BA38" s="66"/>
+      <c r="BB38" s="66"/>
+      <c r="BC38" s="66"/>
+      <c r="BD38" s="66"/>
+      <c r="BE38" s="66"/>
+      <c r="BF38" s="66"/>
+      <c r="BG38" s="66"/>
+      <c r="BH38" s="66"/>
+      <c r="BI38" s="66"/>
+      <c r="BJ38" s="66"/>
+      <c r="BK38" s="66"/>
+      <c r="BL38" s="66"/>
+      <c r="BM38" s="66"/>
+      <c r="BN38" s="66"/>
+      <c r="BO38" s="66"/>
+      <c r="BP38" s="66"/>
+      <c r="BQ38" s="66"/>
+      <c r="BR38" s="68"/>
+    </row>
+    <row r="39" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A39" s="56"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="136"/>
-      <c r="E39" s="136"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="136"/>
-      <c r="H39" s="136"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="137"/>
-      <c r="M39" s="131" t="s">
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="N39" s="131"/>
-      <c r="O39" s="131"/>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="131"/>
-      <c r="R39" s="131"/>
-      <c r="S39" s="131"/>
-      <c r="T39" s="131"/>
-      <c r="U39" s="131"/>
-      <c r="V39" s="131"/>
-      <c r="W39" s="131"/>
-      <c r="X39" s="131"/>
-      <c r="Y39" s="131"/>
-      <c r="Z39" s="131"/>
-      <c r="AA39" s="131"/>
-      <c r="AB39" s="131"/>
-      <c r="AC39" s="131"/>
-      <c r="AD39" s="131"/>
-      <c r="AE39" s="131"/>
-      <c r="AF39" s="131"/>
-      <c r="AG39" s="131"/>
-      <c r="AH39" s="131"/>
-      <c r="AI39" s="131"/>
-      <c r="AJ39" s="131"/>
-      <c r="AK39" s="131"/>
-      <c r="AL39" s="131"/>
-      <c r="AM39" s="131"/>
-      <c r="AN39" s="131"/>
-      <c r="AO39" s="131"/>
-      <c r="AP39" s="131"/>
-      <c r="AQ39" s="131"/>
-      <c r="AR39" s="131"/>
-      <c r="AS39" s="131"/>
-      <c r="AT39" s="131"/>
-      <c r="AU39" s="131"/>
-      <c r="AV39" s="131"/>
-      <c r="AW39" s="131"/>
-      <c r="AX39" s="131"/>
-      <c r="AY39" s="131"/>
-      <c r="AZ39" s="131"/>
-      <c r="BA39" s="131"/>
-      <c r="BB39" s="131"/>
-      <c r="BC39" s="131"/>
-      <c r="BD39" s="131"/>
-      <c r="BE39" s="131"/>
-      <c r="BF39" s="131"/>
-      <c r="BG39" s="131"/>
-      <c r="BH39" s="131"/>
-      <c r="BI39" s="131"/>
-      <c r="BJ39" s="131"/>
-      <c r="BK39" s="131"/>
-      <c r="BL39" s="131"/>
-      <c r="BM39" s="131"/>
-      <c r="BN39" s="131"/>
-      <c r="BO39" s="131"/>
-      <c r="BP39" s="131"/>
-      <c r="BQ39" s="131"/>
-      <c r="BR39" s="133"/>
-    </row>
-    <row r="40" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A40" s="119"/>
-      <c r="B40" s="134"/>
-      <c r="C40" s="138"/>
-      <c r="D40" s="139"/>
-      <c r="BR40" s="140"/>
-      <c r="BT40" s="127"/>
-    </row>
-    <row r="41" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A41" s="119"/>
-      <c r="B41" s="134"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="139"/>
-      <c r="E41" s="120" t="s">
+      <c r="N39" s="66"/>
+      <c r="O39" s="66"/>
+      <c r="P39" s="66"/>
+      <c r="Q39" s="66"/>
+      <c r="R39" s="66"/>
+      <c r="S39" s="66"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="66"/>
+      <c r="V39" s="66"/>
+      <c r="W39" s="66"/>
+      <c r="X39" s="66"/>
+      <c r="Y39" s="66"/>
+      <c r="Z39" s="66"/>
+      <c r="AA39" s="66"/>
+      <c r="AB39" s="66"/>
+      <c r="AC39" s="66"/>
+      <c r="AD39" s="66"/>
+      <c r="AE39" s="66"/>
+      <c r="AF39" s="66"/>
+      <c r="AG39" s="66"/>
+      <c r="AH39" s="66"/>
+      <c r="AI39" s="66"/>
+      <c r="AJ39" s="66"/>
+      <c r="AK39" s="66"/>
+      <c r="AL39" s="66"/>
+      <c r="AM39" s="66"/>
+      <c r="AN39" s="66"/>
+      <c r="AO39" s="66"/>
+      <c r="AP39" s="66"/>
+      <c r="AQ39" s="66"/>
+      <c r="AR39" s="66"/>
+      <c r="AS39" s="66"/>
+      <c r="AT39" s="66"/>
+      <c r="AU39" s="66"/>
+      <c r="AV39" s="66"/>
+      <c r="AW39" s="66"/>
+      <c r="AX39" s="66"/>
+      <c r="AY39" s="66"/>
+      <c r="AZ39" s="66"/>
+      <c r="BA39" s="66"/>
+      <c r="BB39" s="66"/>
+      <c r="BC39" s="66"/>
+      <c r="BD39" s="66"/>
+      <c r="BE39" s="66"/>
+      <c r="BF39" s="66"/>
+      <c r="BG39" s="66"/>
+      <c r="BH39" s="66"/>
+      <c r="BI39" s="66"/>
+      <c r="BJ39" s="66"/>
+      <c r="BK39" s="66"/>
+      <c r="BL39" s="66"/>
+      <c r="BM39" s="66"/>
+      <c r="BN39" s="66"/>
+      <c r="BO39" s="66"/>
+      <c r="BP39" s="66"/>
+      <c r="BQ39" s="66"/>
+      <c r="BR39" s="68"/>
+    </row>
+    <row r="40" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A40" s="56"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="74"/>
+      <c r="BR40" s="75"/>
+      <c r="BT40" s="64"/>
+    </row>
+    <row r="41" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A41" s="56"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="BR41" s="127"/>
-      <c r="BT41" s="127"/>
-    </row>
-    <row r="42" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A42" s="119"/>
-      <c r="B42" s="134"/>
-      <c r="C42" s="138"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="120" t="s">
+      <c r="BR41" s="64"/>
+      <c r="BT41" s="64"/>
+    </row>
+    <row r="42" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A42" s="56"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="73"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="BR42" s="127"/>
-      <c r="BT42" s="127"/>
-    </row>
-    <row r="43" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A43" s="119"/>
-      <c r="C43" s="138"/>
-      <c r="E43" s="142"/>
-      <c r="F43" s="143" t="s">
+      <c r="BR42" s="64"/>
+      <c r="BT42" s="64"/>
+    </row>
+    <row r="43" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A43" s="56"/>
+      <c r="C43" s="73"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G43" s="144"/>
-      <c r="H43" s="144"/>
-      <c r="I43" s="144"/>
-      <c r="J43" s="144"/>
-      <c r="K43" s="144"/>
-      <c r="L43" s="144"/>
-      <c r="M43" s="144"/>
-      <c r="N43" s="144"/>
-      <c r="O43" s="144"/>
-      <c r="P43" s="144"/>
-      <c r="Q43" s="144"/>
-      <c r="R43" s="144"/>
-      <c r="S43" s="144"/>
-      <c r="T43" s="144"/>
-      <c r="U43" s="144"/>
-      <c r="V43" s="144"/>
-      <c r="W43" s="144"/>
-      <c r="X43" s="144"/>
-      <c r="Y43" s="144"/>
-      <c r="Z43" s="144"/>
-      <c r="AA43" s="144"/>
-      <c r="AB43" s="144"/>
-      <c r="AC43" s="144"/>
-      <c r="AD43" s="144"/>
-      <c r="AE43" s="144"/>
-      <c r="AF43" s="144"/>
-      <c r="AG43" s="144"/>
-      <c r="AH43" s="144"/>
-      <c r="AI43" s="144"/>
-      <c r="AJ43" s="144"/>
-      <c r="AK43" s="144"/>
-      <c r="AL43" s="144"/>
-      <c r="AM43" s="144"/>
-      <c r="AN43" s="144"/>
-      <c r="AO43" s="144"/>
-      <c r="AP43" s="144"/>
-      <c r="AQ43" s="144"/>
-      <c r="AR43" s="144"/>
-      <c r="AS43" s="144"/>
-      <c r="AT43" s="144"/>
-      <c r="AU43" s="144"/>
-      <c r="AV43" s="144"/>
-      <c r="AW43" s="144"/>
-      <c r="AX43" s="144"/>
-      <c r="AY43" s="144"/>
-      <c r="AZ43" s="144"/>
-      <c r="BA43" s="144"/>
-      <c r="BB43" s="144"/>
-      <c r="BC43" s="144"/>
-      <c r="BD43" s="144"/>
-      <c r="BE43" s="144"/>
-      <c r="BF43" s="144"/>
-      <c r="BG43" s="144"/>
-      <c r="BH43" s="144"/>
-      <c r="BI43" s="144"/>
-      <c r="BJ43" s="144"/>
-      <c r="BK43" s="144"/>
-      <c r="BL43" s="145"/>
-      <c r="BR43" s="127"/>
-      <c r="BT43" s="127"/>
-    </row>
-    <row r="44" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A44" s="119"/>
-      <c r="C44" s="138"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="146" t="s">
+      <c r="G43" s="79"/>
+      <c r="H43" s="79"/>
+      <c r="I43" s="79"/>
+      <c r="J43" s="79"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="79"/>
+      <c r="M43" s="79"/>
+      <c r="N43" s="79"/>
+      <c r="O43" s="79"/>
+      <c r="P43" s="79"/>
+      <c r="Q43" s="79"/>
+      <c r="R43" s="79"/>
+      <c r="S43" s="79"/>
+      <c r="T43" s="79"/>
+      <c r="U43" s="79"/>
+      <c r="V43" s="79"/>
+      <c r="W43" s="79"/>
+      <c r="X43" s="79"/>
+      <c r="Y43" s="79"/>
+      <c r="Z43" s="79"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="79"/>
+      <c r="AC43" s="79"/>
+      <c r="AD43" s="79"/>
+      <c r="AE43" s="79"/>
+      <c r="AF43" s="79"/>
+      <c r="AG43" s="79"/>
+      <c r="AH43" s="79"/>
+      <c r="AI43" s="79"/>
+      <c r="AJ43" s="79"/>
+      <c r="AK43" s="79"/>
+      <c r="AL43" s="79"/>
+      <c r="AM43" s="79"/>
+      <c r="AN43" s="79"/>
+      <c r="AO43" s="79"/>
+      <c r="AP43" s="79"/>
+      <c r="AQ43" s="79"/>
+      <c r="AR43" s="79"/>
+      <c r="AS43" s="79"/>
+      <c r="AT43" s="79"/>
+      <c r="AU43" s="79"/>
+      <c r="AV43" s="79"/>
+      <c r="AW43" s="79"/>
+      <c r="AX43" s="79"/>
+      <c r="AY43" s="79"/>
+      <c r="AZ43" s="79"/>
+      <c r="BA43" s="79"/>
+      <c r="BB43" s="79"/>
+      <c r="BC43" s="79"/>
+      <c r="BD43" s="79"/>
+      <c r="BE43" s="79"/>
+      <c r="BF43" s="79"/>
+      <c r="BG43" s="79"/>
+      <c r="BH43" s="79"/>
+      <c r="BI43" s="79"/>
+      <c r="BJ43" s="79"/>
+      <c r="BK43" s="79"/>
+      <c r="BL43" s="80"/>
+      <c r="BR43" s="64"/>
+      <c r="BT43" s="64"/>
+    </row>
+    <row r="44" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A44" s="56"/>
+      <c r="C44" s="73"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G44" s="147"/>
-      <c r="H44" s="147"/>
-      <c r="I44" s="147"/>
-      <c r="J44" s="147"/>
-      <c r="K44" s="148"/>
-      <c r="L44" s="132" t="s">
+      <c r="G44" s="82"/>
+      <c r="H44" s="82"/>
+      <c r="I44" s="82"/>
+      <c r="J44" s="82"/>
+      <c r="K44" s="83"/>
+      <c r="L44" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="M44" s="131"/>
-      <c r="N44" s="131"/>
-      <c r="O44" s="131"/>
-      <c r="P44" s="131"/>
-      <c r="Q44" s="131"/>
-      <c r="R44" s="131"/>
-      <c r="S44" s="131"/>
-      <c r="T44" s="131"/>
-      <c r="U44" s="131"/>
-      <c r="V44" s="131"/>
-      <c r="W44" s="131"/>
-      <c r="X44" s="131"/>
-      <c r="Y44" s="131"/>
-      <c r="Z44" s="131"/>
-      <c r="AA44" s="131"/>
-      <c r="AB44" s="131"/>
-      <c r="AC44" s="131"/>
-      <c r="AD44" s="131"/>
-      <c r="AE44" s="131"/>
-      <c r="AF44" s="131"/>
-      <c r="AG44" s="131"/>
-      <c r="AH44" s="131"/>
-      <c r="AI44" s="131"/>
-      <c r="AJ44" s="131"/>
-      <c r="AK44" s="131"/>
-      <c r="AL44" s="131"/>
-      <c r="AM44" s="131"/>
-      <c r="AN44" s="131"/>
-      <c r="AO44" s="131"/>
-      <c r="AP44" s="131"/>
-      <c r="AQ44" s="131"/>
-      <c r="AR44" s="131"/>
-      <c r="AS44" s="131"/>
-      <c r="AT44" s="131"/>
-      <c r="AU44" s="131"/>
-      <c r="AV44" s="131"/>
-      <c r="AW44" s="131"/>
-      <c r="AX44" s="131"/>
-      <c r="AY44" s="131"/>
-      <c r="AZ44" s="131"/>
-      <c r="BA44" s="131"/>
-      <c r="BB44" s="131"/>
-      <c r="BC44" s="131"/>
-      <c r="BD44" s="131"/>
-      <c r="BE44" s="131"/>
-      <c r="BF44" s="131"/>
-      <c r="BG44" s="131"/>
-      <c r="BH44" s="131"/>
-      <c r="BI44" s="131"/>
-      <c r="BJ44" s="131"/>
-      <c r="BK44" s="131"/>
-      <c r="BL44" s="133"/>
-      <c r="BR44" s="149"/>
-      <c r="BT44" s="127"/>
-    </row>
-    <row r="45" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A45" s="119"/>
-      <c r="C45" s="138"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="150" t="s">
+      <c r="M44" s="66"/>
+      <c r="N44" s="66"/>
+      <c r="O44" s="66"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="66"/>
+      <c r="T44" s="66"/>
+      <c r="U44" s="66"/>
+      <c r="V44" s="66"/>
+      <c r="W44" s="66"/>
+      <c r="X44" s="66"/>
+      <c r="Y44" s="66"/>
+      <c r="Z44" s="66"/>
+      <c r="AA44" s="66"/>
+      <c r="AB44" s="66"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="66"/>
+      <c r="AE44" s="66"/>
+      <c r="AF44" s="66"/>
+      <c r="AG44" s="66"/>
+      <c r="AH44" s="66"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="66"/>
+      <c r="AK44" s="66"/>
+      <c r="AL44" s="66"/>
+      <c r="AM44" s="66"/>
+      <c r="AN44" s="66"/>
+      <c r="AO44" s="66"/>
+      <c r="AP44" s="66"/>
+      <c r="AQ44" s="66"/>
+      <c r="AR44" s="66"/>
+      <c r="AS44" s="66"/>
+      <c r="AT44" s="66"/>
+      <c r="AU44" s="66"/>
+      <c r="AV44" s="66"/>
+      <c r="AW44" s="66"/>
+      <c r="AX44" s="66"/>
+      <c r="AY44" s="66"/>
+      <c r="AZ44" s="66"/>
+      <c r="BA44" s="66"/>
+      <c r="BB44" s="66"/>
+      <c r="BC44" s="66"/>
+      <c r="BD44" s="66"/>
+      <c r="BE44" s="66"/>
+      <c r="BF44" s="66"/>
+      <c r="BG44" s="66"/>
+      <c r="BH44" s="66"/>
+      <c r="BI44" s="66"/>
+      <c r="BJ44" s="66"/>
+      <c r="BK44" s="66"/>
+      <c r="BL44" s="68"/>
+      <c r="BR44" s="84"/>
+      <c r="BT44" s="64"/>
+    </row>
+    <row r="45" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A45" s="56"/>
+      <c r="C45" s="73"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="162" t="s">
         <v>68</v>
       </c>
-      <c r="G45" s="151"/>
-      <c r="H45" s="151"/>
-      <c r="I45" s="151"/>
-      <c r="J45" s="151"/>
-      <c r="K45" s="152"/>
-      <c r="L45" s="132" t="s">
+      <c r="G45" s="163"/>
+      <c r="H45" s="163"/>
+      <c r="I45" s="163"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="M45" s="131"/>
-      <c r="N45" s="131"/>
-      <c r="O45" s="131"/>
-      <c r="P45" s="131"/>
-      <c r="Q45" s="131"/>
-      <c r="R45" s="131"/>
-      <c r="S45" s="131"/>
-      <c r="T45" s="131"/>
-      <c r="U45" s="131"/>
-      <c r="V45" s="131"/>
-      <c r="W45" s="131"/>
-      <c r="X45" s="131"/>
-      <c r="Y45" s="131"/>
-      <c r="Z45" s="131"/>
-      <c r="AA45" s="131"/>
-      <c r="AB45" s="131"/>
-      <c r="AC45" s="131"/>
-      <c r="AD45" s="131"/>
-      <c r="AE45" s="131"/>
-      <c r="AF45" s="131"/>
-      <c r="AG45" s="131"/>
-      <c r="AH45" s="131"/>
-      <c r="AI45" s="131"/>
-      <c r="AJ45" s="131"/>
-      <c r="AK45" s="132" t="s">
+      <c r="M45" s="66"/>
+      <c r="N45" s="66"/>
+      <c r="O45" s="66"/>
+      <c r="P45" s="66"/>
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="66"/>
+      <c r="U45" s="66"/>
+      <c r="V45" s="66"/>
+      <c r="W45" s="66"/>
+      <c r="X45" s="66"/>
+      <c r="Y45" s="66"/>
+      <c r="Z45" s="66"/>
+      <c r="AA45" s="66"/>
+      <c r="AB45" s="66"/>
+      <c r="AC45" s="66"/>
+      <c r="AD45" s="66"/>
+      <c r="AE45" s="66"/>
+      <c r="AF45" s="66"/>
+      <c r="AG45" s="66"/>
+      <c r="AH45" s="66"/>
+      <c r="AI45" s="66"/>
+      <c r="AJ45" s="66"/>
+      <c r="AK45" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="AL45" s="131"/>
-      <c r="AM45" s="131"/>
-      <c r="AN45" s="131"/>
-      <c r="AO45" s="131"/>
-      <c r="AP45" s="131"/>
-      <c r="AQ45" s="131"/>
-      <c r="AR45" s="131"/>
-      <c r="AS45" s="131"/>
-      <c r="AT45" s="131"/>
-      <c r="AU45" s="131"/>
-      <c r="AV45" s="131"/>
-      <c r="AW45" s="131"/>
-      <c r="AX45" s="131"/>
-      <c r="AY45" s="131"/>
-      <c r="AZ45" s="131"/>
-      <c r="BA45" s="131"/>
-      <c r="BB45" s="131"/>
-      <c r="BC45" s="131"/>
-      <c r="BD45" s="131"/>
-      <c r="BE45" s="131"/>
-      <c r="BF45" s="131"/>
-      <c r="BG45" s="131"/>
-      <c r="BH45" s="131"/>
-      <c r="BI45" s="131"/>
-      <c r="BJ45" s="131"/>
-      <c r="BK45" s="131"/>
-      <c r="BL45" s="133"/>
-      <c r="BR45" s="127"/>
-      <c r="BT45" s="127"/>
-    </row>
-    <row r="46" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A46" s="119"/>
-      <c r="C46" s="138"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="154"/>
-      <c r="J46" s="154"/>
-      <c r="K46" s="155"/>
-      <c r="L46" s="132" t="s">
+      <c r="AL45" s="66"/>
+      <c r="AM45" s="66"/>
+      <c r="AN45" s="66"/>
+      <c r="AO45" s="66"/>
+      <c r="AP45" s="66"/>
+      <c r="AQ45" s="66"/>
+      <c r="AR45" s="66"/>
+      <c r="AS45" s="66"/>
+      <c r="AT45" s="66"/>
+      <c r="AU45" s="66"/>
+      <c r="AV45" s="66"/>
+      <c r="AW45" s="66"/>
+      <c r="AX45" s="66"/>
+      <c r="AY45" s="66"/>
+      <c r="AZ45" s="66"/>
+      <c r="BA45" s="66"/>
+      <c r="BB45" s="66"/>
+      <c r="BC45" s="66"/>
+      <c r="BD45" s="66"/>
+      <c r="BE45" s="66"/>
+      <c r="BF45" s="66"/>
+      <c r="BG45" s="66"/>
+      <c r="BH45" s="66"/>
+      <c r="BI45" s="66"/>
+      <c r="BJ45" s="66"/>
+      <c r="BK45" s="66"/>
+      <c r="BL45" s="68"/>
+      <c r="BR45" s="64"/>
+      <c r="BT45" s="64"/>
+    </row>
+    <row r="46" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A46" s="56"/>
+      <c r="C46" s="73"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="166"/>
+      <c r="H46" s="166"/>
+      <c r="I46" s="166"/>
+      <c r="J46" s="166"/>
+      <c r="K46" s="167"/>
+      <c r="L46" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="M46" s="131"/>
-      <c r="N46" s="131"/>
-      <c r="O46" s="131"/>
-      <c r="P46" s="131"/>
-      <c r="Q46" s="131"/>
-      <c r="R46" s="131"/>
-      <c r="S46" s="131"/>
-      <c r="T46" s="131"/>
-      <c r="U46" s="131"/>
-      <c r="V46" s="131"/>
-      <c r="W46" s="131"/>
-      <c r="X46" s="131"/>
-      <c r="Y46" s="131"/>
-      <c r="Z46" s="131"/>
-      <c r="AA46" s="131"/>
-      <c r="AB46" s="131"/>
-      <c r="AC46" s="131"/>
-      <c r="AD46" s="131"/>
-      <c r="AE46" s="131"/>
-      <c r="AF46" s="131"/>
-      <c r="AG46" s="131"/>
-      <c r="AH46" s="131"/>
-      <c r="AI46" s="131"/>
-      <c r="AJ46" s="131"/>
-      <c r="AK46" s="132" t="s">
+      <c r="M46" s="66"/>
+      <c r="N46" s="66"/>
+      <c r="O46" s="66"/>
+      <c r="P46" s="66"/>
+      <c r="Q46" s="66"/>
+      <c r="R46" s="66"/>
+      <c r="S46" s="66"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="66"/>
+      <c r="V46" s="66"/>
+      <c r="W46" s="66"/>
+      <c r="X46" s="66"/>
+      <c r="Y46" s="66"/>
+      <c r="Z46" s="66"/>
+      <c r="AA46" s="66"/>
+      <c r="AB46" s="66"/>
+      <c r="AC46" s="66"/>
+      <c r="AD46" s="66"/>
+      <c r="AE46" s="66"/>
+      <c r="AF46" s="66"/>
+      <c r="AG46" s="66"/>
+      <c r="AH46" s="66"/>
+      <c r="AI46" s="66"/>
+      <c r="AJ46" s="66"/>
+      <c r="AK46" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="AL46" s="131"/>
-      <c r="AM46" s="131"/>
-      <c r="AN46" s="131"/>
-      <c r="AO46" s="131"/>
-      <c r="AP46" s="131"/>
-      <c r="AQ46" s="131"/>
-      <c r="AR46" s="131"/>
-      <c r="AS46" s="131"/>
-      <c r="AT46" s="131"/>
-      <c r="AU46" s="131"/>
-      <c r="AV46" s="131"/>
-      <c r="AW46" s="131"/>
-      <c r="AX46" s="131"/>
-      <c r="AY46" s="131"/>
-      <c r="AZ46" s="131"/>
-      <c r="BA46" s="131"/>
-      <c r="BB46" s="131"/>
-      <c r="BC46" s="131"/>
-      <c r="BD46" s="131"/>
-      <c r="BE46" s="131"/>
-      <c r="BF46" s="131"/>
-      <c r="BG46" s="131"/>
-      <c r="BH46" s="131"/>
-      <c r="BI46" s="131"/>
-      <c r="BJ46" s="131"/>
-      <c r="BK46" s="131"/>
-      <c r="BL46" s="133"/>
-      <c r="BR46" s="127"/>
-      <c r="BT46" s="127"/>
-    </row>
-    <row r="47" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A47" s="119"/>
-      <c r="C47" s="138"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="146" t="s">
+      <c r="AL46" s="66"/>
+      <c r="AM46" s="66"/>
+      <c r="AN46" s="66"/>
+      <c r="AO46" s="66"/>
+      <c r="AP46" s="66"/>
+      <c r="AQ46" s="66"/>
+      <c r="AR46" s="66"/>
+      <c r="AS46" s="66"/>
+      <c r="AT46" s="66"/>
+      <c r="AU46" s="66"/>
+      <c r="AV46" s="66"/>
+      <c r="AW46" s="66"/>
+      <c r="AX46" s="66"/>
+      <c r="AY46" s="66"/>
+      <c r="AZ46" s="66"/>
+      <c r="BA46" s="66"/>
+      <c r="BB46" s="66"/>
+      <c r="BC46" s="66"/>
+      <c r="BD46" s="66"/>
+      <c r="BE46" s="66"/>
+      <c r="BF46" s="66"/>
+      <c r="BG46" s="66"/>
+      <c r="BH46" s="66"/>
+      <c r="BI46" s="66"/>
+      <c r="BJ46" s="66"/>
+      <c r="BK46" s="66"/>
+      <c r="BL46" s="68"/>
+      <c r="BR46" s="64"/>
+      <c r="BT46" s="64"/>
+    </row>
+    <row r="47" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A47" s="56"/>
+      <c r="C47" s="73"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="147"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="148"/>
-      <c r="L47" s="132" t="s">
+      <c r="G47" s="82"/>
+      <c r="H47" s="82"/>
+      <c r="I47" s="82"/>
+      <c r="J47" s="82"/>
+      <c r="K47" s="83"/>
+      <c r="L47" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="M47" s="131"/>
-      <c r="N47" s="131"/>
-      <c r="O47" s="131"/>
-      <c r="P47" s="131"/>
-      <c r="Q47" s="131"/>
-      <c r="R47" s="131"/>
-      <c r="S47" s="131"/>
-      <c r="T47" s="131"/>
-      <c r="U47" s="131"/>
-      <c r="V47" s="131"/>
-      <c r="W47" s="131"/>
-      <c r="X47" s="131"/>
-      <c r="Y47" s="131"/>
-      <c r="Z47" s="131"/>
-      <c r="AA47" s="131"/>
-      <c r="AB47" s="131"/>
-      <c r="AC47" s="131"/>
-      <c r="AD47" s="131"/>
-      <c r="AE47" s="131"/>
-      <c r="AF47" s="131"/>
-      <c r="AG47" s="131"/>
-      <c r="AH47" s="131"/>
-      <c r="AI47" s="131"/>
-      <c r="AJ47" s="131"/>
-      <c r="AK47" s="131"/>
-      <c r="AL47" s="131"/>
-      <c r="AM47" s="131"/>
-      <c r="AN47" s="131"/>
-      <c r="AO47" s="131"/>
-      <c r="AP47" s="131"/>
-      <c r="AQ47" s="131"/>
-      <c r="AR47" s="131"/>
-      <c r="AS47" s="131"/>
-      <c r="AT47" s="131"/>
-      <c r="AU47" s="131"/>
-      <c r="AV47" s="131"/>
-      <c r="AW47" s="131"/>
-      <c r="AX47" s="131"/>
-      <c r="AY47" s="131"/>
-      <c r="AZ47" s="131"/>
-      <c r="BA47" s="131"/>
-      <c r="BB47" s="131"/>
-      <c r="BC47" s="131"/>
-      <c r="BD47" s="131"/>
-      <c r="BE47" s="131"/>
-      <c r="BF47" s="131"/>
-      <c r="BG47" s="131"/>
-      <c r="BH47" s="131"/>
-      <c r="BI47" s="131"/>
-      <c r="BJ47" s="131"/>
-      <c r="BK47" s="131"/>
-      <c r="BL47" s="133"/>
-      <c r="BR47" s="127"/>
-      <c r="BT47" s="127"/>
-    </row>
-    <row r="48" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A48" s="119"/>
-      <c r="C48" s="138"/>
-      <c r="E48" s="141"/>
-      <c r="BR48" s="127"/>
-      <c r="BT48" s="127"/>
-    </row>
-    <row r="49" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A49" s="119"/>
-      <c r="C49" s="138"/>
-      <c r="E49" s="141"/>
-      <c r="F49" s="120" t="s">
+      <c r="M47" s="66"/>
+      <c r="N47" s="66"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="66"/>
+      <c r="Q47" s="66"/>
+      <c r="R47" s="66"/>
+      <c r="S47" s="66"/>
+      <c r="T47" s="66"/>
+      <c r="U47" s="66"/>
+      <c r="V47" s="66"/>
+      <c r="W47" s="66"/>
+      <c r="X47" s="66"/>
+      <c r="Y47" s="66"/>
+      <c r="Z47" s="66"/>
+      <c r="AA47" s="66"/>
+      <c r="AB47" s="66"/>
+      <c r="AC47" s="66"/>
+      <c r="AD47" s="66"/>
+      <c r="AE47" s="66"/>
+      <c r="AF47" s="66"/>
+      <c r="AG47" s="66"/>
+      <c r="AH47" s="66"/>
+      <c r="AI47" s="66"/>
+      <c r="AJ47" s="66"/>
+      <c r="AK47" s="66"/>
+      <c r="AL47" s="66"/>
+      <c r="AM47" s="66"/>
+      <c r="AN47" s="66"/>
+      <c r="AO47" s="66"/>
+      <c r="AP47" s="66"/>
+      <c r="AQ47" s="66"/>
+      <c r="AR47" s="66"/>
+      <c r="AS47" s="66"/>
+      <c r="AT47" s="66"/>
+      <c r="AU47" s="66"/>
+      <c r="AV47" s="66"/>
+      <c r="AW47" s="66"/>
+      <c r="AX47" s="66"/>
+      <c r="AY47" s="66"/>
+      <c r="AZ47" s="66"/>
+      <c r="BA47" s="66"/>
+      <c r="BB47" s="66"/>
+      <c r="BC47" s="66"/>
+      <c r="BD47" s="66"/>
+      <c r="BE47" s="66"/>
+      <c r="BF47" s="66"/>
+      <c r="BG47" s="66"/>
+      <c r="BH47" s="66"/>
+      <c r="BI47" s="66"/>
+      <c r="BJ47" s="66"/>
+      <c r="BK47" s="66"/>
+      <c r="BL47" s="68"/>
+      <c r="BR47" s="64"/>
+      <c r="BT47" s="64"/>
+    </row>
+    <row r="48" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A48" s="56"/>
+      <c r="C48" s="73"/>
+      <c r="E48" s="76"/>
+      <c r="BR48" s="64"/>
+      <c r="BT48" s="64"/>
+    </row>
+    <row r="49" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A49" s="56"/>
+      <c r="C49" s="73"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="BR49" s="127"/>
-      <c r="BT49" s="127"/>
-    </row>
-    <row r="50" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A50" s="119"/>
-      <c r="C50" s="138"/>
-      <c r="E50" s="141"/>
-      <c r="F50" s="143" t="s">
+      <c r="BR49" s="64"/>
+      <c r="BT49" s="64"/>
+    </row>
+    <row r="50" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A50" s="56"/>
+      <c r="C50" s="73"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="G50" s="144"/>
-      <c r="H50" s="144"/>
-      <c r="I50" s="144"/>
-      <c r="J50" s="144"/>
-      <c r="K50" s="144"/>
-      <c r="L50" s="144"/>
-      <c r="M50" s="144"/>
-      <c r="N50" s="144"/>
-      <c r="O50" s="144"/>
-      <c r="P50" s="144"/>
-      <c r="Q50" s="144"/>
-      <c r="R50" s="144"/>
-      <c r="S50" s="144"/>
-      <c r="T50" s="144"/>
-      <c r="U50" s="144"/>
-      <c r="V50" s="144"/>
-      <c r="W50" s="144"/>
-      <c r="X50" s="144"/>
-      <c r="Y50" s="144"/>
-      <c r="Z50" s="144"/>
-      <c r="AA50" s="144"/>
-      <c r="AB50" s="144"/>
-      <c r="AC50" s="144"/>
-      <c r="AD50" s="144"/>
-      <c r="AE50" s="144"/>
-      <c r="AF50" s="144"/>
-      <c r="AG50" s="144"/>
-      <c r="AH50" s="144"/>
-      <c r="AI50" s="144"/>
-      <c r="AJ50" s="144"/>
-      <c r="AK50" s="144"/>
-      <c r="AL50" s="144"/>
-      <c r="AM50" s="144"/>
-      <c r="AN50" s="144"/>
-      <c r="AO50" s="144"/>
-      <c r="AP50" s="144"/>
-      <c r="AQ50" s="144"/>
-      <c r="AR50" s="144"/>
-      <c r="AS50" s="144"/>
-      <c r="AT50" s="144"/>
-      <c r="AU50" s="144"/>
-      <c r="AV50" s="144"/>
-      <c r="AW50" s="144"/>
-      <c r="AX50" s="144"/>
-      <c r="AY50" s="144"/>
-      <c r="AZ50" s="144"/>
-      <c r="BA50" s="144"/>
-      <c r="BB50" s="144"/>
-      <c r="BC50" s="144"/>
-      <c r="BD50" s="144"/>
-      <c r="BE50" s="144"/>
-      <c r="BF50" s="144"/>
-      <c r="BG50" s="144"/>
-      <c r="BH50" s="144"/>
-      <c r="BI50" s="144"/>
-      <c r="BJ50" s="144"/>
-      <c r="BK50" s="144"/>
-      <c r="BL50" s="145"/>
-      <c r="BR50" s="127"/>
-      <c r="BT50" s="127"/>
-    </row>
-    <row r="51" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A51" s="119"/>
-      <c r="B51" s="134"/>
-      <c r="C51" s="138"/>
-      <c r="E51" s="141"/>
-      <c r="F51" s="146" t="s">
+      <c r="G50" s="79"/>
+      <c r="H50" s="79"/>
+      <c r="I50" s="79"/>
+      <c r="J50" s="79"/>
+      <c r="K50" s="79"/>
+      <c r="L50" s="79"/>
+      <c r="M50" s="79"/>
+      <c r="N50" s="79"/>
+      <c r="O50" s="79"/>
+      <c r="P50" s="79"/>
+      <c r="Q50" s="79"/>
+      <c r="R50" s="79"/>
+      <c r="S50" s="79"/>
+      <c r="T50" s="79"/>
+      <c r="U50" s="79"/>
+      <c r="V50" s="79"/>
+      <c r="W50" s="79"/>
+      <c r="X50" s="79"/>
+      <c r="Y50" s="79"/>
+      <c r="Z50" s="79"/>
+      <c r="AA50" s="79"/>
+      <c r="AB50" s="79"/>
+      <c r="AC50" s="79"/>
+      <c r="AD50" s="79"/>
+      <c r="AE50" s="79"/>
+      <c r="AF50" s="79"/>
+      <c r="AG50" s="79"/>
+      <c r="AH50" s="79"/>
+      <c r="AI50" s="79"/>
+      <c r="AJ50" s="79"/>
+      <c r="AK50" s="79"/>
+      <c r="AL50" s="79"/>
+      <c r="AM50" s="79"/>
+      <c r="AN50" s="79"/>
+      <c r="AO50" s="79"/>
+      <c r="AP50" s="79"/>
+      <c r="AQ50" s="79"/>
+      <c r="AR50" s="79"/>
+      <c r="AS50" s="79"/>
+      <c r="AT50" s="79"/>
+      <c r="AU50" s="79"/>
+      <c r="AV50" s="79"/>
+      <c r="AW50" s="79"/>
+      <c r="AX50" s="79"/>
+      <c r="AY50" s="79"/>
+      <c r="AZ50" s="79"/>
+      <c r="BA50" s="79"/>
+      <c r="BB50" s="79"/>
+      <c r="BC50" s="79"/>
+      <c r="BD50" s="79"/>
+      <c r="BE50" s="79"/>
+      <c r="BF50" s="79"/>
+      <c r="BG50" s="79"/>
+      <c r="BH50" s="79"/>
+      <c r="BI50" s="79"/>
+      <c r="BJ50" s="79"/>
+      <c r="BK50" s="79"/>
+      <c r="BL50" s="80"/>
+      <c r="BR50" s="64"/>
+      <c r="BT50" s="64"/>
+    </row>
+    <row r="51" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A51" s="56"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="73"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="G51" s="147"/>
-      <c r="H51" s="147"/>
-      <c r="I51" s="147"/>
-      <c r="J51" s="147"/>
-      <c r="K51" s="148"/>
-      <c r="L51" s="132" t="s">
+      <c r="G51" s="82"/>
+      <c r="H51" s="82"/>
+      <c r="I51" s="82"/>
+      <c r="J51" s="82"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="M51" s="131"/>
-      <c r="N51" s="131"/>
-      <c r="O51" s="131"/>
-      <c r="P51" s="131"/>
-      <c r="Q51" s="131"/>
-      <c r="R51" s="131"/>
-      <c r="S51" s="131"/>
-      <c r="T51" s="131"/>
-      <c r="U51" s="131"/>
-      <c r="V51" s="131"/>
-      <c r="W51" s="131"/>
-      <c r="X51" s="131"/>
-      <c r="Y51" s="131"/>
-      <c r="Z51" s="131"/>
-      <c r="AA51" s="131"/>
-      <c r="AB51" s="131"/>
-      <c r="AC51" s="131"/>
-      <c r="AD51" s="131"/>
-      <c r="AE51" s="131"/>
-      <c r="AF51" s="131"/>
-      <c r="AG51" s="131"/>
-      <c r="AH51" s="131"/>
-      <c r="AI51" s="131"/>
-      <c r="AJ51" s="131"/>
-      <c r="AK51" s="131"/>
-      <c r="AL51" s="131"/>
-      <c r="AM51" s="131"/>
-      <c r="AN51" s="131"/>
-      <c r="AO51" s="131"/>
-      <c r="AP51" s="131"/>
-      <c r="AQ51" s="131"/>
-      <c r="AR51" s="131"/>
-      <c r="AS51" s="131"/>
-      <c r="AT51" s="131"/>
-      <c r="AU51" s="131"/>
-      <c r="AV51" s="131"/>
-      <c r="AW51" s="131"/>
-      <c r="AX51" s="131"/>
-      <c r="AY51" s="131"/>
-      <c r="AZ51" s="131"/>
-      <c r="BA51" s="131"/>
-      <c r="BB51" s="131"/>
-      <c r="BC51" s="131"/>
-      <c r="BD51" s="131"/>
-      <c r="BE51" s="131"/>
-      <c r="BF51" s="131"/>
-      <c r="BG51" s="131"/>
-      <c r="BH51" s="131"/>
-      <c r="BI51" s="131"/>
-      <c r="BJ51" s="131"/>
-      <c r="BK51" s="131"/>
-      <c r="BL51" s="133"/>
-      <c r="BR51" s="149"/>
-      <c r="BT51" s="127"/>
-    </row>
-    <row r="52" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A52" s="119"/>
-      <c r="B52" s="134"/>
-      <c r="C52" s="138"/>
-      <c r="E52" s="141"/>
-      <c r="F52" s="156" t="s">
+      <c r="M51" s="66"/>
+      <c r="N51" s="66"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="66"/>
+      <c r="Q51" s="66"/>
+      <c r="R51" s="66"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="66"/>
+      <c r="U51" s="66"/>
+      <c r="V51" s="66"/>
+      <c r="W51" s="66"/>
+      <c r="X51" s="66"/>
+      <c r="Y51" s="66"/>
+      <c r="Z51" s="66"/>
+      <c r="AA51" s="66"/>
+      <c r="AB51" s="66"/>
+      <c r="AC51" s="66"/>
+      <c r="AD51" s="66"/>
+      <c r="AE51" s="66"/>
+      <c r="AF51" s="66"/>
+      <c r="AG51" s="66"/>
+      <c r="AH51" s="66"/>
+      <c r="AI51" s="66"/>
+      <c r="AJ51" s="66"/>
+      <c r="AK51" s="66"/>
+      <c r="AL51" s="66"/>
+      <c r="AM51" s="66"/>
+      <c r="AN51" s="66"/>
+      <c r="AO51" s="66"/>
+      <c r="AP51" s="66"/>
+      <c r="AQ51" s="66"/>
+      <c r="AR51" s="66"/>
+      <c r="AS51" s="66"/>
+      <c r="AT51" s="66"/>
+      <c r="AU51" s="66"/>
+      <c r="AV51" s="66"/>
+      <c r="AW51" s="66"/>
+      <c r="AX51" s="66"/>
+      <c r="AY51" s="66"/>
+      <c r="AZ51" s="66"/>
+      <c r="BA51" s="66"/>
+      <c r="BB51" s="66"/>
+      <c r="BC51" s="66"/>
+      <c r="BD51" s="66"/>
+      <c r="BE51" s="66"/>
+      <c r="BF51" s="66"/>
+      <c r="BG51" s="66"/>
+      <c r="BH51" s="66"/>
+      <c r="BI51" s="66"/>
+      <c r="BJ51" s="66"/>
+      <c r="BK51" s="66"/>
+      <c r="BL51" s="68"/>
+      <c r="BR51" s="84"/>
+      <c r="BT51" s="64"/>
+    </row>
+    <row r="52" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A52" s="56"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="73"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="G52" s="157"/>
-      <c r="H52" s="157"/>
-      <c r="I52" s="157"/>
-      <c r="J52" s="157"/>
-      <c r="K52" s="158"/>
-      <c r="L52" s="132" t="s">
+      <c r="G52" s="86"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="86"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="M52" s="131"/>
-      <c r="N52" s="131"/>
-      <c r="O52" s="131"/>
-      <c r="P52" s="131"/>
-      <c r="Q52" s="131"/>
-      <c r="R52" s="131"/>
-      <c r="S52" s="131"/>
-      <c r="T52" s="131"/>
-      <c r="U52" s="131"/>
-      <c r="V52" s="131"/>
-      <c r="W52" s="131"/>
-      <c r="X52" s="131"/>
-      <c r="Y52" s="131"/>
-      <c r="Z52" s="131"/>
-      <c r="AA52" s="131"/>
-      <c r="AB52" s="131"/>
-      <c r="AC52" s="131"/>
-      <c r="AD52" s="131"/>
-      <c r="AE52" s="131"/>
-      <c r="AF52" s="131"/>
-      <c r="AG52" s="131"/>
-      <c r="AH52" s="131"/>
-      <c r="AI52" s="131"/>
-      <c r="AJ52" s="131"/>
-      <c r="AK52" s="132" t="s">
+      <c r="M52" s="66"/>
+      <c r="N52" s="66"/>
+      <c r="O52" s="66"/>
+      <c r="P52" s="66"/>
+      <c r="Q52" s="66"/>
+      <c r="R52" s="66"/>
+      <c r="S52" s="66"/>
+      <c r="T52" s="66"/>
+      <c r="U52" s="66"/>
+      <c r="V52" s="66"/>
+      <c r="W52" s="66"/>
+      <c r="X52" s="66"/>
+      <c r="Y52" s="66"/>
+      <c r="Z52" s="66"/>
+      <c r="AA52" s="66"/>
+      <c r="AB52" s="66"/>
+      <c r="AC52" s="66"/>
+      <c r="AD52" s="66"/>
+      <c r="AE52" s="66"/>
+      <c r="AF52" s="66"/>
+      <c r="AG52" s="66"/>
+      <c r="AH52" s="66"/>
+      <c r="AI52" s="66"/>
+      <c r="AJ52" s="66"/>
+      <c r="AK52" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="AL52" s="131"/>
-      <c r="AM52" s="131"/>
-      <c r="AN52" s="131"/>
-      <c r="AO52" s="131"/>
-      <c r="AP52" s="131"/>
-      <c r="AQ52" s="131"/>
-      <c r="AR52" s="131"/>
-      <c r="AS52" s="131"/>
-      <c r="AT52" s="131"/>
-      <c r="AU52" s="131"/>
-      <c r="AV52" s="131"/>
-      <c r="AW52" s="131"/>
-      <c r="AX52" s="131"/>
-      <c r="AY52" s="131"/>
-      <c r="AZ52" s="131"/>
-      <c r="BA52" s="131"/>
-      <c r="BB52" s="131"/>
-      <c r="BC52" s="131"/>
-      <c r="BD52" s="131"/>
-      <c r="BE52" s="131"/>
-      <c r="BF52" s="131"/>
-      <c r="BG52" s="131"/>
-      <c r="BH52" s="131"/>
-      <c r="BI52" s="131"/>
-      <c r="BJ52" s="131"/>
-      <c r="BK52" s="131"/>
-      <c r="BL52" s="133"/>
-      <c r="BR52" s="149"/>
-      <c r="BT52" s="127"/>
-    </row>
-    <row r="53" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A53" s="119"/>
-      <c r="B53" s="134"/>
-      <c r="C53" s="138"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="146" t="s">
+      <c r="AL52" s="66"/>
+      <c r="AM52" s="66"/>
+      <c r="AN52" s="66"/>
+      <c r="AO52" s="66"/>
+      <c r="AP52" s="66"/>
+      <c r="AQ52" s="66"/>
+      <c r="AR52" s="66"/>
+      <c r="AS52" s="66"/>
+      <c r="AT52" s="66"/>
+      <c r="AU52" s="66"/>
+      <c r="AV52" s="66"/>
+      <c r="AW52" s="66"/>
+      <c r="AX52" s="66"/>
+      <c r="AY52" s="66"/>
+      <c r="AZ52" s="66"/>
+      <c r="BA52" s="66"/>
+      <c r="BB52" s="66"/>
+      <c r="BC52" s="66"/>
+      <c r="BD52" s="66"/>
+      <c r="BE52" s="66"/>
+      <c r="BF52" s="66"/>
+      <c r="BG52" s="66"/>
+      <c r="BH52" s="66"/>
+      <c r="BI52" s="66"/>
+      <c r="BJ52" s="66"/>
+      <c r="BK52" s="66"/>
+      <c r="BL52" s="68"/>
+      <c r="BR52" s="84"/>
+      <c r="BT52" s="64"/>
+    </row>
+    <row r="53" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A53" s="56"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="73"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="G53" s="147"/>
-      <c r="H53" s="147"/>
-      <c r="I53" s="147"/>
-      <c r="J53" s="147"/>
-      <c r="K53" s="148"/>
-      <c r="L53" s="132" t="s">
+      <c r="G53" s="82"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="82"/>
+      <c r="J53" s="82"/>
+      <c r="K53" s="83"/>
+      <c r="L53" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="M53" s="131"/>
-      <c r="N53" s="131"/>
-      <c r="O53" s="131"/>
-      <c r="P53" s="131"/>
-      <c r="Q53" s="131"/>
-      <c r="R53" s="131"/>
-      <c r="S53" s="131"/>
-      <c r="T53" s="131"/>
-      <c r="U53" s="131"/>
-      <c r="V53" s="131"/>
-      <c r="W53" s="131"/>
-      <c r="X53" s="131"/>
-      <c r="Y53" s="131"/>
-      <c r="Z53" s="131"/>
-      <c r="AA53" s="131"/>
-      <c r="AB53" s="131"/>
-      <c r="AC53" s="131"/>
-      <c r="AD53" s="131"/>
-      <c r="AE53" s="131"/>
-      <c r="AF53" s="131"/>
-      <c r="AG53" s="131"/>
-      <c r="AH53" s="131"/>
-      <c r="AI53" s="131"/>
-      <c r="AJ53" s="131"/>
-      <c r="AK53" s="131"/>
-      <c r="AL53" s="131"/>
-      <c r="AM53" s="131"/>
-      <c r="AN53" s="131"/>
-      <c r="AO53" s="131"/>
-      <c r="AP53" s="131"/>
-      <c r="AQ53" s="131"/>
-      <c r="AR53" s="131"/>
-      <c r="AS53" s="131"/>
-      <c r="AT53" s="131"/>
-      <c r="AU53" s="131"/>
-      <c r="AV53" s="131"/>
-      <c r="AW53" s="131"/>
-      <c r="AX53" s="131"/>
-      <c r="AY53" s="131"/>
-      <c r="AZ53" s="131"/>
-      <c r="BA53" s="131"/>
-      <c r="BB53" s="131"/>
-      <c r="BC53" s="131"/>
-      <c r="BD53" s="131"/>
-      <c r="BE53" s="131"/>
-      <c r="BF53" s="131"/>
-      <c r="BG53" s="131"/>
-      <c r="BH53" s="131"/>
-      <c r="BI53" s="131"/>
-      <c r="BJ53" s="131"/>
-      <c r="BK53" s="131"/>
-      <c r="BL53" s="133"/>
-      <c r="BR53" s="149"/>
-      <c r="BT53" s="127"/>
-    </row>
-    <row r="54" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A54" s="119"/>
-      <c r="B54" s="134"/>
-      <c r="C54" s="138"/>
-      <c r="E54" s="141"/>
-      <c r="BR54" s="149"/>
-      <c r="BT54" s="127"/>
-    </row>
-    <row r="55" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A55" s="119"/>
-      <c r="B55" s="134"/>
-      <c r="C55" s="138"/>
-      <c r="E55" s="141"/>
-      <c r="G55" s="161"/>
-      <c r="BR55" s="149"/>
-      <c r="BT55" s="127"/>
-    </row>
-    <row r="56" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A56" s="119"/>
-      <c r="B56" s="134"/>
-      <c r="C56" s="138"/>
-      <c r="E56" s="141"/>
-      <c r="G56" s="161"/>
-      <c r="BR56" s="149"/>
-      <c r="BT56" s="127"/>
-    </row>
-    <row r="57" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A57" s="119"/>
-      <c r="B57" s="134"/>
-      <c r="C57" s="138"/>
-      <c r="D57" s="141">
+      <c r="M53" s="66"/>
+      <c r="N53" s="66"/>
+      <c r="O53" s="66"/>
+      <c r="P53" s="66"/>
+      <c r="Q53" s="66"/>
+      <c r="R53" s="66"/>
+      <c r="S53" s="66"/>
+      <c r="T53" s="66"/>
+      <c r="U53" s="66"/>
+      <c r="V53" s="66"/>
+      <c r="W53" s="66"/>
+      <c r="X53" s="66"/>
+      <c r="Y53" s="66"/>
+      <c r="Z53" s="66"/>
+      <c r="AA53" s="66"/>
+      <c r="AB53" s="66"/>
+      <c r="AC53" s="66"/>
+      <c r="AD53" s="66"/>
+      <c r="AE53" s="66"/>
+      <c r="AF53" s="66"/>
+      <c r="AG53" s="66"/>
+      <c r="AH53" s="66"/>
+      <c r="AI53" s="66"/>
+      <c r="AJ53" s="66"/>
+      <c r="AK53" s="66"/>
+      <c r="AL53" s="66"/>
+      <c r="AM53" s="66"/>
+      <c r="AN53" s="66"/>
+      <c r="AO53" s="66"/>
+      <c r="AP53" s="66"/>
+      <c r="AQ53" s="66"/>
+      <c r="AR53" s="66"/>
+      <c r="AS53" s="66"/>
+      <c r="AT53" s="66"/>
+      <c r="AU53" s="66"/>
+      <c r="AV53" s="66"/>
+      <c r="AW53" s="66"/>
+      <c r="AX53" s="66"/>
+      <c r="AY53" s="66"/>
+      <c r="AZ53" s="66"/>
+      <c r="BA53" s="66"/>
+      <c r="BB53" s="66"/>
+      <c r="BC53" s="66"/>
+      <c r="BD53" s="66"/>
+      <c r="BE53" s="66"/>
+      <c r="BF53" s="66"/>
+      <c r="BG53" s="66"/>
+      <c r="BH53" s="66"/>
+      <c r="BI53" s="66"/>
+      <c r="BJ53" s="66"/>
+      <c r="BK53" s="66"/>
+      <c r="BL53" s="68"/>
+      <c r="BR53" s="84"/>
+      <c r="BT53" s="64"/>
+    </row>
+    <row r="54" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A54" s="56"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="73"/>
+      <c r="E54" s="76"/>
+      <c r="BR54" s="84"/>
+      <c r="BT54" s="64"/>
+    </row>
+    <row r="55" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A55" s="56"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="73"/>
+      <c r="E55" s="76"/>
+      <c r="G55" s="89"/>
+      <c r="BR55" s="84"/>
+      <c r="BT55" s="64"/>
+    </row>
+    <row r="56" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A56" s="56"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="73"/>
+      <c r="E56" s="76"/>
+      <c r="G56" s="89"/>
+      <c r="BR56" s="84"/>
+      <c r="BT56" s="64"/>
+    </row>
+    <row r="57" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A57" s="56"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="76">
         <v>2</v>
       </c>
-      <c r="E57" s="120" t="s">
+      <c r="E57" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="BR57" s="149"/>
-      <c r="BT57" s="127"/>
-    </row>
-    <row r="58" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A58" s="119"/>
-      <c r="B58" s="134"/>
-      <c r="C58" s="138"/>
-      <c r="D58" s="141"/>
-      <c r="E58" s="146" t="s">
+      <c r="BR57" s="84"/>
+      <c r="BT57" s="64"/>
+    </row>
+    <row r="58" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A58" s="56"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="81" t="s">
         <v>74</v>
       </c>
-      <c r="F58" s="136"/>
-      <c r="G58" s="136"/>
-      <c r="H58" s="136"/>
-      <c r="I58" s="136"/>
-      <c r="J58" s="136"/>
-      <c r="K58" s="132" t="s">
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="71"/>
+      <c r="K58" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="L58" s="131"/>
-      <c r="M58" s="131"/>
-      <c r="N58" s="131"/>
-      <c r="O58" s="131"/>
-      <c r="P58" s="131"/>
-      <c r="Q58" s="131"/>
-      <c r="R58" s="131"/>
-      <c r="S58" s="131"/>
-      <c r="T58" s="131"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="131"/>
-      <c r="W58" s="131"/>
-      <c r="X58" s="131"/>
-      <c r="Y58" s="131"/>
-      <c r="Z58" s="131"/>
-      <c r="AA58" s="131"/>
-      <c r="AB58" s="131"/>
-      <c r="AC58" s="131"/>
-      <c r="AD58" s="131"/>
-      <c r="AE58" s="131"/>
-      <c r="AF58" s="131"/>
-      <c r="AG58" s="131"/>
-      <c r="AH58" s="131"/>
-      <c r="AI58" s="131"/>
-      <c r="AJ58" s="131"/>
-      <c r="AK58" s="131"/>
-      <c r="AL58" s="131"/>
-      <c r="AM58" s="131"/>
-      <c r="AN58" s="131"/>
-      <c r="AO58" s="131"/>
-      <c r="AP58" s="131"/>
-      <c r="AQ58" s="131"/>
-      <c r="AR58" s="131"/>
-      <c r="AS58" s="131"/>
-      <c r="AT58" s="131"/>
-      <c r="AU58" s="131"/>
-      <c r="AV58" s="131"/>
-      <c r="AW58" s="131"/>
-      <c r="AX58" s="131"/>
-      <c r="AY58" s="131"/>
-      <c r="AZ58" s="131"/>
-      <c r="BA58" s="131"/>
-      <c r="BB58" s="131"/>
-      <c r="BC58" s="131"/>
-      <c r="BD58" s="131"/>
-      <c r="BE58" s="131"/>
-      <c r="BF58" s="131"/>
-      <c r="BG58" s="131"/>
-      <c r="BH58" s="131"/>
-      <c r="BI58" s="131"/>
-      <c r="BJ58" s="131"/>
-      <c r="BK58" s="131"/>
-      <c r="BL58" s="133"/>
-      <c r="BR58" s="149"/>
-      <c r="BT58" s="127"/>
-    </row>
-    <row r="59" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A59" s="119"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="138"/>
-      <c r="D59" s="141"/>
-      <c r="E59" s="135" t="s">
+      <c r="L58" s="66"/>
+      <c r="M58" s="66"/>
+      <c r="N58" s="66"/>
+      <c r="O58" s="66"/>
+      <c r="P58" s="66"/>
+      <c r="Q58" s="66"/>
+      <c r="R58" s="66"/>
+      <c r="S58" s="66"/>
+      <c r="T58" s="66"/>
+      <c r="U58" s="66"/>
+      <c r="V58" s="66"/>
+      <c r="W58" s="66"/>
+      <c r="X58" s="66"/>
+      <c r="Y58" s="66"/>
+      <c r="Z58" s="66"/>
+      <c r="AA58" s="66"/>
+      <c r="AB58" s="66"/>
+      <c r="AC58" s="66"/>
+      <c r="AD58" s="66"/>
+      <c r="AE58" s="66"/>
+      <c r="AF58" s="66"/>
+      <c r="AG58" s="66"/>
+      <c r="AH58" s="66"/>
+      <c r="AI58" s="66"/>
+      <c r="AJ58" s="66"/>
+      <c r="AK58" s="66"/>
+      <c r="AL58" s="66"/>
+      <c r="AM58" s="66"/>
+      <c r="AN58" s="66"/>
+      <c r="AO58" s="66"/>
+      <c r="AP58" s="66"/>
+      <c r="AQ58" s="66"/>
+      <c r="AR58" s="66"/>
+      <c r="AS58" s="66"/>
+      <c r="AT58" s="66"/>
+      <c r="AU58" s="66"/>
+      <c r="AV58" s="66"/>
+      <c r="AW58" s="66"/>
+      <c r="AX58" s="66"/>
+      <c r="AY58" s="66"/>
+      <c r="AZ58" s="66"/>
+      <c r="BA58" s="66"/>
+      <c r="BB58" s="66"/>
+      <c r="BC58" s="66"/>
+      <c r="BD58" s="66"/>
+      <c r="BE58" s="66"/>
+      <c r="BF58" s="66"/>
+      <c r="BG58" s="66"/>
+      <c r="BH58" s="66"/>
+      <c r="BI58" s="66"/>
+      <c r="BJ58" s="66"/>
+      <c r="BK58" s="66"/>
+      <c r="BL58" s="68"/>
+      <c r="BR58" s="84"/>
+      <c r="BT58" s="64"/>
+    </row>
+    <row r="59" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A59" s="56"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F59" s="135" t="s">
+      <c r="F59" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="G59" s="136"/>
-      <c r="H59" s="136"/>
-      <c r="I59" s="136"/>
-      <c r="J59" s="136"/>
-      <c r="K59" s="136"/>
-      <c r="L59" s="136"/>
-      <c r="M59" s="136"/>
-      <c r="N59" s="136"/>
-      <c r="O59" s="136"/>
-      <c r="P59" s="136"/>
-      <c r="Q59" s="136"/>
-      <c r="R59" s="136"/>
-      <c r="S59" s="136"/>
-      <c r="T59" s="136"/>
-      <c r="U59" s="135" t="s">
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="71"/>
+      <c r="K59" s="71"/>
+      <c r="L59" s="71"/>
+      <c r="M59" s="71"/>
+      <c r="N59" s="71"/>
+      <c r="O59" s="71"/>
+      <c r="P59" s="71"/>
+      <c r="Q59" s="71"/>
+      <c r="R59" s="71"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="71"/>
+      <c r="U59" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="V59" s="136"/>
-      <c r="W59" s="136"/>
-      <c r="X59" s="136"/>
-      <c r="Y59" s="136"/>
-      <c r="Z59" s="136"/>
-      <c r="AA59" s="136"/>
-      <c r="AB59" s="136"/>
-      <c r="AC59" s="136"/>
-      <c r="AD59" s="136"/>
-      <c r="AE59" s="136"/>
-      <c r="AF59" s="137"/>
-      <c r="AG59" s="135" t="s">
+      <c r="V59" s="71"/>
+      <c r="W59" s="71"/>
+      <c r="X59" s="71"/>
+      <c r="Y59" s="71"/>
+      <c r="Z59" s="71"/>
+      <c r="AA59" s="71"/>
+      <c r="AB59" s="71"/>
+      <c r="AC59" s="71"/>
+      <c r="AD59" s="71"/>
+      <c r="AE59" s="71"/>
+      <c r="AF59" s="72"/>
+      <c r="AG59" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="AH59" s="136"/>
-      <c r="AI59" s="136"/>
-      <c r="AJ59" s="136"/>
-      <c r="AK59" s="136"/>
-      <c r="AL59" s="136"/>
-      <c r="AM59" s="136"/>
-      <c r="AN59" s="136"/>
-      <c r="AO59" s="136"/>
-      <c r="AP59" s="136"/>
-      <c r="AQ59" s="136"/>
-      <c r="AR59" s="137"/>
-      <c r="AS59" s="136" t="s">
+      <c r="AH59" s="71"/>
+      <c r="AI59" s="71"/>
+      <c r="AJ59" s="71"/>
+      <c r="AK59" s="71"/>
+      <c r="AL59" s="71"/>
+      <c r="AM59" s="71"/>
+      <c r="AN59" s="71"/>
+      <c r="AO59" s="71"/>
+      <c r="AP59" s="71"/>
+      <c r="AQ59" s="71"/>
+      <c r="AR59" s="72"/>
+      <c r="AS59" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="AT59" s="136"/>
-      <c r="AU59" s="136"/>
-      <c r="AV59" s="136"/>
-      <c r="AW59" s="136"/>
-      <c r="AX59" s="136"/>
-      <c r="AY59" s="136"/>
-      <c r="AZ59" s="136"/>
-      <c r="BA59" s="136"/>
-      <c r="BB59" s="136"/>
-      <c r="BC59" s="136"/>
-      <c r="BD59" s="136"/>
-      <c r="BE59" s="136"/>
-      <c r="BF59" s="136"/>
-      <c r="BG59" s="136"/>
-      <c r="BH59" s="136"/>
-      <c r="BI59" s="136"/>
-      <c r="BJ59" s="136"/>
-      <c r="BK59" s="136"/>
-      <c r="BL59" s="137"/>
-      <c r="BR59" s="149"/>
-      <c r="BT59" s="127"/>
-    </row>
-    <row r="60" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A60" s="119"/>
-      <c r="B60" s="134"/>
-      <c r="C60" s="138"/>
-      <c r="D60" s="141"/>
-      <c r="E60" s="159">
+      <c r="AT59" s="71"/>
+      <c r="AU59" s="71"/>
+      <c r="AV59" s="71"/>
+      <c r="AW59" s="71"/>
+      <c r="AX59" s="71"/>
+      <c r="AY59" s="71"/>
+      <c r="AZ59" s="71"/>
+      <c r="BA59" s="71"/>
+      <c r="BB59" s="71"/>
+      <c r="BC59" s="71"/>
+      <c r="BD59" s="71"/>
+      <c r="BE59" s="71"/>
+      <c r="BF59" s="71"/>
+      <c r="BG59" s="71"/>
+      <c r="BH59" s="71"/>
+      <c r="BI59" s="71"/>
+      <c r="BJ59" s="71"/>
+      <c r="BK59" s="71"/>
+      <c r="BL59" s="72"/>
+      <c r="BR59" s="84"/>
+      <c r="BT59" s="64"/>
+    </row>
+    <row r="60" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A60" s="56"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="88">
         <v>1</v>
       </c>
-      <c r="F60" s="162" t="s">
+      <c r="F60" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="G60" s="131"/>
-      <c r="H60" s="131"/>
-      <c r="I60" s="131"/>
-      <c r="J60" s="131"/>
-      <c r="K60" s="131"/>
-      <c r="L60" s="131"/>
-      <c r="M60" s="131"/>
-      <c r="N60" s="131"/>
-      <c r="O60" s="131"/>
-      <c r="P60" s="131"/>
-      <c r="Q60" s="131"/>
-      <c r="R60" s="131"/>
-      <c r="S60" s="131"/>
-      <c r="T60" s="133"/>
-      <c r="U60" s="160" t="s">
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="66"/>
+      <c r="K60" s="66"/>
+      <c r="L60" s="66"/>
+      <c r="M60" s="66"/>
+      <c r="N60" s="66"/>
+      <c r="O60" s="66"/>
+      <c r="P60" s="66"/>
+      <c r="Q60" s="66"/>
+      <c r="R60" s="66"/>
+      <c r="S60" s="66"/>
+      <c r="T60" s="68"/>
+      <c r="U60" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V60" s="163"/>
-      <c r="W60" s="163"/>
-      <c r="X60" s="163"/>
-      <c r="Y60" s="163"/>
-      <c r="Z60" s="163"/>
-      <c r="AA60" s="163"/>
-      <c r="AB60" s="163"/>
-      <c r="AC60" s="163"/>
-      <c r="AD60" s="163"/>
-      <c r="AE60" s="163"/>
-      <c r="AF60" s="164"/>
-      <c r="AG60" s="160" t="s">
+      <c r="V60" s="172"/>
+      <c r="W60" s="172"/>
+      <c r="X60" s="172"/>
+      <c r="Y60" s="172"/>
+      <c r="Z60" s="172"/>
+      <c r="AA60" s="172"/>
+      <c r="AB60" s="172"/>
+      <c r="AC60" s="172"/>
+      <c r="AD60" s="172"/>
+      <c r="AE60" s="172"/>
+      <c r="AF60" s="173"/>
+      <c r="AG60" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH60" s="163"/>
-      <c r="AI60" s="163"/>
-      <c r="AJ60" s="163"/>
-      <c r="AK60" s="163"/>
-      <c r="AL60" s="163"/>
-      <c r="AM60" s="163"/>
-      <c r="AN60" s="163"/>
-      <c r="AO60" s="163"/>
-      <c r="AP60" s="163"/>
-      <c r="AQ60" s="163"/>
-      <c r="AR60" s="164"/>
-      <c r="AS60" s="165" t="s">
+      <c r="AH60" s="172"/>
+      <c r="AI60" s="172"/>
+      <c r="AJ60" s="172"/>
+      <c r="AK60" s="172"/>
+      <c r="AL60" s="172"/>
+      <c r="AM60" s="172"/>
+      <c r="AN60" s="172"/>
+      <c r="AO60" s="172"/>
+      <c r="AP60" s="172"/>
+      <c r="AQ60" s="172"/>
+      <c r="AR60" s="173"/>
+      <c r="AS60" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT60" s="166"/>
-      <c r="AU60" s="166"/>
-      <c r="AV60" s="166"/>
-      <c r="AW60" s="166"/>
-      <c r="AX60" s="166"/>
-      <c r="AY60" s="166"/>
-      <c r="AZ60" s="166"/>
-      <c r="BA60" s="166"/>
-      <c r="BB60" s="166"/>
-      <c r="BC60" s="166"/>
-      <c r="BD60" s="166"/>
-      <c r="BE60" s="166"/>
-      <c r="BF60" s="166"/>
-      <c r="BG60" s="166"/>
-      <c r="BH60" s="166"/>
-      <c r="BI60" s="166"/>
-      <c r="BJ60" s="166"/>
-      <c r="BK60" s="166"/>
-      <c r="BL60" s="167"/>
-      <c r="BR60" s="149"/>
-      <c r="BT60" s="127"/>
-    </row>
-    <row r="61" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A61" s="119"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="138"/>
-      <c r="D61" s="141"/>
-      <c r="E61" s="159">
+      <c r="AT60" s="175"/>
+      <c r="AU60" s="175"/>
+      <c r="AV60" s="175"/>
+      <c r="AW60" s="175"/>
+      <c r="AX60" s="175"/>
+      <c r="AY60" s="175"/>
+      <c r="AZ60" s="175"/>
+      <c r="BA60" s="175"/>
+      <c r="BB60" s="175"/>
+      <c r="BC60" s="175"/>
+      <c r="BD60" s="175"/>
+      <c r="BE60" s="175"/>
+      <c r="BF60" s="175"/>
+      <c r="BG60" s="175"/>
+      <c r="BH60" s="175"/>
+      <c r="BI60" s="175"/>
+      <c r="BJ60" s="175"/>
+      <c r="BK60" s="175"/>
+      <c r="BL60" s="176"/>
+      <c r="BR60" s="84"/>
+      <c r="BT60" s="64"/>
+    </row>
+    <row r="61" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A61" s="56"/>
+      <c r="B61" s="69"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="88">
         <v>2</v>
       </c>
-      <c r="F61" s="162" t="s">
+      <c r="F61" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="G61" s="131"/>
-      <c r="H61" s="131"/>
-      <c r="I61" s="131"/>
-      <c r="J61" s="131"/>
-      <c r="K61" s="131"/>
-      <c r="L61" s="131"/>
-      <c r="M61" s="131"/>
-      <c r="N61" s="131"/>
-      <c r="O61" s="131"/>
-      <c r="P61" s="131"/>
-      <c r="Q61" s="131"/>
-      <c r="R61" s="131"/>
-      <c r="S61" s="131"/>
-      <c r="T61" s="133"/>
-      <c r="U61" s="160" t="s">
+      <c r="G61" s="66"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
+      <c r="M61" s="66"/>
+      <c r="N61" s="66"/>
+      <c r="O61" s="66"/>
+      <c r="P61" s="66"/>
+      <c r="Q61" s="66"/>
+      <c r="R61" s="66"/>
+      <c r="S61" s="66"/>
+      <c r="T61" s="68"/>
+      <c r="U61" s="171" t="s">
         <v>72</v>
       </c>
-      <c r="V61" s="163"/>
-      <c r="W61" s="163"/>
-      <c r="X61" s="163"/>
-      <c r="Y61" s="163"/>
-      <c r="Z61" s="163"/>
-      <c r="AA61" s="163"/>
-      <c r="AB61" s="163"/>
-      <c r="AC61" s="163"/>
-      <c r="AD61" s="163"/>
-      <c r="AE61" s="163"/>
-      <c r="AF61" s="164"/>
-      <c r="AG61" s="160" t="s">
+      <c r="V61" s="172"/>
+      <c r="W61" s="172"/>
+      <c r="X61" s="172"/>
+      <c r="Y61" s="172"/>
+      <c r="Z61" s="172"/>
+      <c r="AA61" s="172"/>
+      <c r="AB61" s="172"/>
+      <c r="AC61" s="172"/>
+      <c r="AD61" s="172"/>
+      <c r="AE61" s="172"/>
+      <c r="AF61" s="173"/>
+      <c r="AG61" s="171" t="s">
         <v>83</v>
       </c>
-      <c r="AH61" s="163"/>
-      <c r="AI61" s="163"/>
-      <c r="AJ61" s="163"/>
-      <c r="AK61" s="163"/>
-      <c r="AL61" s="163"/>
-      <c r="AM61" s="163"/>
-      <c r="AN61" s="163"/>
-      <c r="AO61" s="163"/>
-      <c r="AP61" s="163"/>
-      <c r="AQ61" s="163"/>
-      <c r="AR61" s="164"/>
-      <c r="AS61" s="165" t="s">
+      <c r="AH61" s="172"/>
+      <c r="AI61" s="172"/>
+      <c r="AJ61" s="172"/>
+      <c r="AK61" s="172"/>
+      <c r="AL61" s="172"/>
+      <c r="AM61" s="172"/>
+      <c r="AN61" s="172"/>
+      <c r="AO61" s="172"/>
+      <c r="AP61" s="172"/>
+      <c r="AQ61" s="172"/>
+      <c r="AR61" s="173"/>
+      <c r="AS61" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AT61" s="166"/>
-      <c r="AU61" s="166"/>
-      <c r="AV61" s="166"/>
-      <c r="AW61" s="166"/>
-      <c r="AX61" s="166"/>
-      <c r="AY61" s="166"/>
-      <c r="AZ61" s="166"/>
-      <c r="BA61" s="166"/>
-      <c r="BB61" s="166"/>
-      <c r="BC61" s="166"/>
-      <c r="BD61" s="166"/>
-      <c r="BE61" s="166"/>
-      <c r="BF61" s="166"/>
-      <c r="BG61" s="166"/>
-      <c r="BH61" s="166"/>
-      <c r="BI61" s="166"/>
-      <c r="BJ61" s="166"/>
-      <c r="BK61" s="166"/>
-      <c r="BL61" s="167"/>
-      <c r="BR61" s="149"/>
-      <c r="BT61" s="127"/>
-    </row>
-    <row r="62" spans="1:72" s="120" customFormat="1" ht="12" customHeight="1">
-      <c r="A62" s="119"/>
-      <c r="B62" s="134"/>
-      <c r="C62" s="168"/>
-      <c r="D62" s="169"/>
-      <c r="E62" s="170"/>
-      <c r="F62" s="170"/>
-      <c r="G62" s="170"/>
-      <c r="H62" s="170"/>
-      <c r="I62" s="170"/>
-      <c r="J62" s="170"/>
-      <c r="K62" s="170"/>
-      <c r="L62" s="170"/>
-      <c r="M62" s="170"/>
-      <c r="N62" s="170"/>
-      <c r="O62" s="170"/>
-      <c r="P62" s="170"/>
-      <c r="Q62" s="170"/>
-      <c r="R62" s="170"/>
-      <c r="S62" s="170"/>
-      <c r="T62" s="170"/>
-      <c r="U62" s="170"/>
-      <c r="V62" s="170"/>
-      <c r="W62" s="170"/>
-      <c r="X62" s="170"/>
-      <c r="Y62" s="170"/>
-      <c r="Z62" s="170"/>
-      <c r="AA62" s="170"/>
-      <c r="AB62" s="170"/>
-      <c r="AC62" s="170"/>
-      <c r="AD62" s="170"/>
-      <c r="AE62" s="170"/>
-      <c r="AF62" s="170"/>
-      <c r="AG62" s="171"/>
-      <c r="AH62" s="171"/>
-      <c r="AI62" s="171"/>
-      <c r="AJ62" s="171"/>
-      <c r="AK62" s="171"/>
-      <c r="AL62" s="171"/>
-      <c r="AM62" s="171"/>
-      <c r="AN62" s="171"/>
-      <c r="AO62" s="171"/>
-      <c r="AP62" s="171"/>
-      <c r="AQ62" s="171"/>
-      <c r="AR62" s="171"/>
-      <c r="AS62" s="171"/>
-      <c r="AT62" s="171"/>
-      <c r="AU62" s="170"/>
-      <c r="AV62" s="170"/>
-      <c r="AW62" s="170"/>
-      <c r="AX62" s="171"/>
-      <c r="AY62" s="171"/>
-      <c r="AZ62" s="171"/>
-      <c r="BA62" s="171"/>
-      <c r="BB62" s="171"/>
-      <c r="BC62" s="170"/>
-      <c r="BD62" s="170"/>
-      <c r="BE62" s="170"/>
-      <c r="BF62" s="171"/>
-      <c r="BG62" s="171"/>
-      <c r="BH62" s="171"/>
-      <c r="BI62" s="171"/>
-      <c r="BJ62" s="171"/>
-      <c r="BK62" s="170"/>
-      <c r="BL62" s="170"/>
-      <c r="BM62" s="170"/>
-      <c r="BN62" s="170"/>
-      <c r="BO62" s="170"/>
-      <c r="BP62" s="170"/>
-      <c r="BQ62" s="170"/>
-      <c r="BR62" s="172"/>
-      <c r="BT62" s="127"/>
+      <c r="AT61" s="175"/>
+      <c r="AU61" s="175"/>
+      <c r="AV61" s="175"/>
+      <c r="AW61" s="175"/>
+      <c r="AX61" s="175"/>
+      <c r="AY61" s="175"/>
+      <c r="AZ61" s="175"/>
+      <c r="BA61" s="175"/>
+      <c r="BB61" s="175"/>
+      <c r="BC61" s="175"/>
+      <c r="BD61" s="175"/>
+      <c r="BE61" s="175"/>
+      <c r="BF61" s="175"/>
+      <c r="BG61" s="175"/>
+      <c r="BH61" s="175"/>
+      <c r="BI61" s="175"/>
+      <c r="BJ61" s="175"/>
+      <c r="BK61" s="175"/>
+      <c r="BL61" s="176"/>
+      <c r="BR61" s="84"/>
+      <c r="BT61" s="64"/>
+    </row>
+    <row r="62" spans="1:72" s="57" customFormat="1" ht="12" customHeight="1">
+      <c r="A62" s="56"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="92"/>
+      <c r="E62" s="93"/>
+      <c r="F62" s="93"/>
+      <c r="G62" s="93"/>
+      <c r="H62" s="93"/>
+      <c r="I62" s="93"/>
+      <c r="J62" s="93"/>
+      <c r="K62" s="93"/>
+      <c r="L62" s="93"/>
+      <c r="M62" s="93"/>
+      <c r="N62" s="93"/>
+      <c r="O62" s="93"/>
+      <c r="P62" s="93"/>
+      <c r="Q62" s="93"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="93"/>
+      <c r="T62" s="93"/>
+      <c r="U62" s="93"/>
+      <c r="V62" s="93"/>
+      <c r="W62" s="93"/>
+      <c r="X62" s="93"/>
+      <c r="Y62" s="93"/>
+      <c r="Z62" s="93"/>
+      <c r="AA62" s="93"/>
+      <c r="AB62" s="93"/>
+      <c r="AC62" s="93"/>
+      <c r="AD62" s="93"/>
+      <c r="AE62" s="93"/>
+      <c r="AF62" s="93"/>
+      <c r="AG62" s="94"/>
+      <c r="AH62" s="94"/>
+      <c r="AI62" s="94"/>
+      <c r="AJ62" s="94"/>
+      <c r="AK62" s="94"/>
+      <c r="AL62" s="94"/>
+      <c r="AM62" s="94"/>
+      <c r="AN62" s="94"/>
+      <c r="AO62" s="94"/>
+      <c r="AP62" s="94"/>
+      <c r="AQ62" s="94"/>
+      <c r="AR62" s="94"/>
+      <c r="AS62" s="94"/>
+      <c r="AT62" s="94"/>
+      <c r="AU62" s="93"/>
+      <c r="AV62" s="93"/>
+      <c r="AW62" s="93"/>
+      <c r="AX62" s="94"/>
+      <c r="AY62" s="94"/>
+      <c r="AZ62" s="94"/>
+      <c r="BA62" s="94"/>
+      <c r="BB62" s="94"/>
+      <c r="BC62" s="93"/>
+      <c r="BD62" s="93"/>
+      <c r="BE62" s="93"/>
+      <c r="BF62" s="94"/>
+      <c r="BG62" s="94"/>
+      <c r="BH62" s="94"/>
+      <c r="BI62" s="94"/>
+      <c r="BJ62" s="94"/>
+      <c r="BK62" s="93"/>
+      <c r="BL62" s="93"/>
+      <c r="BM62" s="93"/>
+      <c r="BN62" s="93"/>
+      <c r="BO62" s="93"/>
+      <c r="BP62" s="93"/>
+      <c r="BQ62" s="93"/>
+      <c r="BR62" s="95"/>
+      <c r="BT62" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="38">
@@ -8782,6 +9353,14 @@
     <mergeCell ref="U31:AF31"/>
     <mergeCell ref="AG31:AR31"/>
     <mergeCell ref="AS31:BL31"/>
+    <mergeCell ref="AJ1:AM1"/>
+    <mergeCell ref="AN1:AR1"/>
+    <mergeCell ref="AS1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="AS2:AW2"/>
+    <mergeCell ref="AX2:BB2"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="F16:K17"/>
     <mergeCell ref="AE1:AI1"/>
@@ -8795,15 +9374,7 @@
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:AD2"/>
-    <mergeCell ref="AJ1:AM1"/>
-    <mergeCell ref="AN1:AR1"/>
-    <mergeCell ref="AS1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
     <mergeCell ref="AE2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="AS2:AW2"/>
-    <mergeCell ref="AX2:BB2"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -8813,7 +9384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:B12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
